--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -601,9 +601,8 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL eligible (100% developed, fully mature at 287 months). Maturity-Based Weighting: Tail-exposed period (84+ months); primary weight to Paid/Incurred CL. Selection: 100% Chain-Ladder ultimate.
-Eligible methods: Incurred CL (100% developed, CDF = 1.0). Screened methods: None. Diagnostic-Driven Override: None applicable (fully developed). Convergence Check: Single method; no convergence analysis needed. Bayesian Anchoring: No prior provided; CL indication is fully credible. Asymmetric Conservatism: Not applicable (no prior movement). Reasonability Envelope: Period is fully mature and fully developed; no reasonability flags.
-Data quality: No IBNR component (0.0); development is complete. Final selection holds 100% at CL indication.</t>
+          <t>CL 100% (fully developed, CDF=1.0)
+Eligible methods: CL=3,163,773.70, IE=3,163,773.70, BF=3,163,773.70 â€” all converge to the same value. CDF=1.0 means no projection is required; actual incurred equals ultimate. Maturity=287 months (Tail, 84+ mo per framework); CL is primary. IBNR=0 for all methods. Convergence check: trivially passes. Reasonability: fully mature period â€” no flags. No data quality issues.</t>
         </is>
       </c>
       <c r="K2" s="8" t="n">
@@ -635,18 +634,21 @@
       <c r="D3" s="3" t="n">
         <v>2904344.256599999</v>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="n">
+        <v>2327733.756319999</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2327733.756319999</v>
+      </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="6" t="n">
-        <v>2904344.26</v>
+        <v>2327733.76</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable (NaN). Incurred Expected (IE) available. BF unavailable (NaN). Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (275 months). At late maturity, CL would be primary (60–100%); IE would be secondary (0–40%). Given CL unavailability, IE becomes sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (not calculated/unavailable), Incurred BF (not available). Diagnostic-Driven Override: None provided (no case adequacy, closure rate, or diagnostics available). Convergence Check: Single method; convergence check not applicable. Bayesian Anchoring: No prior provided. Asymmetric Conservatism: Not applicable (sole method). Reasonability Envelope: Cannot compute IELR without earned premium. IBNR = 576,610.50 (positive, consistent with development expectation at 275 months).
-Data quality: Single method reliance; recommend CL and BF indications for next study to cross-validate IE.</t>
+          <t>CL 100% (fully developed, CDF=1.0)
+Eligible methods: CL=2,327,733.76 (CDF=1.0, IBNR=0), BF=2,327,733.76 (IBNR=0). IE=2,904,344.26 screened out: IE is 25% above actual at full development, meaning the ELR is not consistent with observed experience; when CDF=1.0 the actual incurred IS the ultimate and IE carries zero weight. Maturity=275 months (Tail, 84+ mo). CL primary at full development. Convergence: CL and BF both equal actual. No data quality flags.</t>
         </is>
       </c>
       <c r="K3" s="8" t="n">
@@ -678,18 +680,21 @@
       <c r="D4" s="3" t="n">
         <v>2633272.1256</v>
       </c>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="n">
+        <v>1778091.575843999</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1778091.575843999</v>
+      </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="n">
-        <v>2633272.13</v>
+        <v>1778091.58</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (263 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 855,180.55 (positive, reasonable for late maturity).
-Data quality: Single method reliance; CL and BF indications needed for validation.</t>
+          <t>CL 100% (fully developed, CDF=1.0)
+Eligible methods: CL=1,778,091.58 (CDF=1.0, IBNR=0), BF=1,778,091.58 (IBNR=0). IE=2,633,272.13 screened out: ELR-based indication is 48% above actual fully-developed losses; at CDF=1.0 the actual is definitive. Maturity=263 months (Tail, 84+ mo). CL primary. Convergence: CL and BF equal actual. No data quality flags.</t>
         </is>
       </c>
       <c r="K4" s="8" t="n">
@@ -721,18 +726,21 @@
       <c r="D5" s="3" t="n">
         <v>1678710.98</v>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="n">
+        <v>1142148.22691244</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1151324.74736037</v>
+      </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="n">
-        <v>1678710.98</v>
+        <v>1146736.49</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (251 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 556,096.25 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 60%, BF 40% â€” midpoint 1,146,736.49 (tail maturity, near-fully developed)
+Eligible methods: CL=1,142,148.23, BF=1,151,324.75. IE=1,678,711.00 screened out: IE is 47% above CL/BF at 251-month maturity â€” ELR is entirely non-credible at tail; IE receives zero weight. Maturity=251 months (Tail, 84+ mo); CDF=1.0174 (98.3% developed). CL primary (60%), BF secondary (40%) per tail weighting. Convergence check: CL and BF within 0.8% â€” passes Â±2% threshold; selecting midpoint = (1,142,148.23 + 1,151,324.75)/2 = 1,146,736.49. Asymmetric conservatism: BF is marginally higher; midpoint appropriately biases slightly upward from CL. No data quality flags.</t>
         </is>
       </c>
       <c r="K5" s="8" t="n">
@@ -764,18 +772,21 @@
       <c r="D6" s="3" t="n">
         <v>1712285.2</v>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="n">
+        <v>2296902.548451221</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2282966.477415849</v>
+      </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="n">
-        <v>1712285.2</v>
+        <v>2289934.51</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (239 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −529,863.93 (negative). RED FLAG: Negative IBNR indicates favorable development or estimation error. Actual incurred (2,242,149) &gt; ultimate (1,712,285), implying adverse reversal. This suggests either case reserve decrease or estimate deterioration. Recommend diagnostic review of case adequacy and reserve study timing for this period.
-Data quality: Single method reliance; negative IBNR flags data quality concern. CL and BF indications critical for validation.</t>
+          <t>CL 60%, BF 40% â€” midpoint 2,289,934.51 (tail maturity, near-fully developed)
+Eligible methods: CL=2,296,902.55, BF=2,282,966.48. IE=1,712,285.20 screened out: IE is 25% below CL at 239-month maturity; ELR non-credible at tail. Maturity=239 months (Tail, 84+ mo); CDF=1.02442 (97.6% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.6% â€” passes; midpoint = (2,296,902.55 + 2,282,966.48)/2 = 2,289,934.51. Note: IE-implied IBNR is negative (actual &gt; IE) â€” confirms IE/ELR under-calibration for this year. No data quality flags beyond IE divergence.</t>
         </is>
       </c>
       <c r="K6" s="8" t="n">
@@ -807,18 +818,21 @@
       <c r="D7" s="3" t="n">
         <v>1746530.9035</v>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>1568534.3826053</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1574310.216423582</v>
+      </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="n">
-        <v>1746530.9</v>
+        <v>1571422.3</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (227 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 228,894.11 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 60%, BF 40% â€” midpoint 1,571,422.30 (tail maturity, near-fully developed)
+Eligible methods: CL=1,568,534.38, BF=1,574,310.22. IE=1,746,530.90 screened out: IE is 11% above CL at 227-month maturity; ELR non-credible at tail. Maturity=227 months (Tail, 84+ mo); CDF=1.03354 (96.8% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.4% â€” passes; midpoint = (1,568,534.38 + 1,574,310.22)/2 = 1,571,422.30. No data quality flags.</t>
         </is>
       </c>
       <c r="K7" s="8" t="n">
@@ -850,18 +864,21 @@
       <c r="D8" s="3" t="n">
         <v>2850338.4352</v>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="n">
+        <v>4972115.480330334</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>4903265.642420489</v>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="n">
-        <v>2850338.44</v>
+        <v>4937690.56</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (215 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −1,960,436.18 (large negative). RED FLAG: Very large negative IBNR (actual 4,810,775 &gt;&gt; ultimate 2,850,338). Adverse case development or severe estimation error. This period likely had reserve strengthening after the IE estimate or case reactivations. Recommend diagnostic investigation before finalizing selection.
-Data quality: Single method reliance; large negative IBNR is a material data quality flag. CL and BF indications essential for validation.</t>
+          <t>CL 60%, BF 40% â€” midpoint 4,937,690.56 (tail maturity, near-fully developed)
+Eligible methods: CL=4,972,115.48, BF=4,903,265.64. IE=2,850,338.44 screened out: IE is 43% below CL â€” entirely non-credible at 215-month maturity; the ELR appears calibrated to a much lower loss level. Maturity=215 months (Tail, 84+ mo); CDF=1.03354 (96.8% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 1.4% â€” passes; midpoint = (4,972,115.48 + 4,903,265.64)/2 = 4,937,690.56. Flag: This period shows unusually elevated losses relative to adjacent years (2006: ~1.6M, 2008: ~1.4M). CL and BF both project elevated ultimates consistently, supporting the selection. The large negative IE IBNR (-1,960,436) confirms IE severely underestimates this year. Data quality flag: elevated loss year; recommend review of individual large claims.</t>
         </is>
       </c>
       <c r="K8" s="8" t="n">
@@ -893,18 +910,21 @@
       <c r="D9" s="3" t="n">
         <v>2543927.0535</v>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="n">
+        <v>1427506.140360434</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1465889.113446933</v>
+      </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="6" t="n">
-        <v>2543927.05</v>
+        <v>1446697.63</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (203 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 1,165,499.11 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 55%, BF 45% â€” midpoint 1,446,697.63 (tail maturity, 3.6% residual development)
+Eligible methods: CL=1,427,506.14, BF=1,465,889.11. IE=2,543,927.05 screened out: IE is 78% above CL at 203-month maturity â€” non-credible at tail. Maturity=203 months (Tail, 84+ mo); CDF=1.03560 (96.6% developed). CL primary (55%), BF secondary (45%). CL and BF within 2.7% â€” just outside Â±2% convergence; midpoint = (1,427,506.14 + 1,465,889.11)/2 = 1,446,697.63. Asymmetric conservatism: BF is higher; midpoint biases upward from CL. No data quality flags.</t>
         </is>
       </c>
       <c r="K9" s="8" t="n">
@@ -936,18 +956,21 @@
       <c r="D10" s="3" t="n">
         <v>2594805.5945</v>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="n">
+        <v>1220428.70585741</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1277690.378550072</v>
+      </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="6" t="n">
-        <v>2594805.59</v>
+        <v>1249059.54</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late maturity (191 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 1,425,224.51 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 50%, BF 50% â€” midpoint 1,249,059.54 (tail maturity, 4.3% residual development)
+Eligible methods: CL=1,220,428.71, BF=1,277,690.38. IE=2,594,805.59 screened out: IE is 113% above CL â€” completely non-credible at 191-month maturity. Maturity=191 months (Tail, 84+ mo); CDF=1.04348 (95.8% developed). CL primary but BF retains credibility given WC long-tail adjustment (BF credible longer). CL and BF diverge by 4.7% â€” outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward moves travel farther â€” increase BF weight. Weighted = 0.50*1,220,428.71 + 0.50*1,277,690.38 = 1,249,059.54; midpoint selected as balanced conservative compromise. Flag: IE/ELR implies more than double the CL indication â€” ELR appears severely mis-calibrated for this period.</t>
         </is>
       </c>
       <c r="K10" s="8" t="n">
@@ -979,18 +1002,21 @@
       <c r="D11" s="3" t="n">
         <v>1134300.7311</v>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="n">
+        <v>1338018.539666638</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1328830.587656843</v>
+      </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="6" t="n">
-        <v>1134300.73</v>
+        <v>1333424.57</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late-to-mid maturity (179 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −143,371.34 (negative). Actual (1,277,672) &gt; ultimate (1,134,301), indicating adverse development post-estimate. Flag for diagnostic review.
-Data quality: Single method reliance; negative IBNR flags data quality concern. CL and BF indications critical.</t>
+          <t>CL 60%, BF 40% â€” midpoint 1,333,424.57 (tail maturity, 4.7% residual development)
+Eligible methods: CL=1,338,018.54, BF=1,328,830.59. IE=1,134,300.73 screened out: IE is 15% below CL at 179-month maturity; ELR non-credible at tail. Maturity=179 months (Tail, 84+ mo); CDF=1.04723 (95.5% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.7% â€” passes; midpoint = (1,338,018.54 + 1,328,830.59)/2 = 1,333,424.57. No data quality flags.</t>
         </is>
       </c>
       <c r="K11" s="8" t="n">
@@ -1022,18 +1048,21 @@
       <c r="D12" s="3" t="n">
         <v>1542648.9944</v>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="n">
+        <v>2048919.998187436</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>2016096.735607065</v>
+      </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="6" t="n">
-        <v>1542648.99</v>
+        <v>2032508.37</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Late-to-mid maturity (167 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −373,432.59 (negative). Actual (1,916,082) &gt; ultimate (1,542,649). Adverse development signal. Recommend diagnostic investigation.
-Data quality: Single method reliance; negative IBNR flags data quality. CL and BF validation essential.</t>
+          <t>CL 60%, BF 40% â€” midpoint 2,032,508.37 (tail maturity, 6.9% residual development)
+Eligible methods: CL=2,048,920.00, BF=2,016,096.74. IE=1,542,649.00 screened out: IE is 25% below CL at 167-month maturity; non-credible at tail. Maturity=167 months (Tail, 84+ mo); CDF=1.06933 (93.5% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 1.6% â€” passes; midpoint = (2,048,920.00 + 2,016,096.74)/2 = 2,032,508.37. No data quality flags.</t>
         </is>
       </c>
       <c r="K12" s="8" t="n">
@@ -1065,18 +1094,21 @@
       <c r="D13" s="3" t="n">
         <v>1573501.9744</v>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="n">
+        <v>1458883.218318097</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1466357.198096881</v>
+      </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="6" t="n">
-        <v>1573501.97</v>
+        <v>1462620.21</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Mid maturity (155 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 209,748.59 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 60%, BF 40% â€” midpoint 1,462,620.21 (tail maturity, 7.0% residual development)
+Eligible methods: CL=1,458,883.22, BF=1,466,357.20. IE=1,573,501.97 screened out: IE is 7.7% above CL at 155-month maturity; ELR carries no weight at tail. Maturity=155 months (Tail, 84+ mo); CDF=1.06976 (93.5% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.5% â€” passes; midpoint = (1,458,883.22 + 1,466,357.20)/2 = 1,462,620.21. No data quality flags.</t>
         </is>
       </c>
       <c r="K13" s="8" t="n">
@@ -1108,18 +1140,21 @@
       <c r="D14" s="3" t="n">
         <v>1203729.0102</v>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="n">
+        <v>759621.6336900741</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>789491.9986882674</v>
+      </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="6" t="n">
-        <v>1203729.01</v>
+        <v>774556.8199999999</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Mid maturity (143 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 495,199.02 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 50%, BF 50% â€” midpoint 774,556.82 (tail maturity, 7.2% residual development)
+Eligible methods: CL=759,621.63, BF=789,492.00. IE=1,203,729.01 screened out: IE is 58% above CL at 143-month maturity â€” completely non-credible at tail. Maturity=143 months (Tail, 84+ mo); CDF=1.07211 (93.3% developed). CL and BF diverge by 3.9% â€” outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward moves travel farther â€” equal weight applied as compromise. Midpoint = (759,621.63 + 789,492.00)/2 = 774,556.82. No data quality flags.</t>
         </is>
       </c>
       <c r="K14" s="8" t="n">
@@ -1151,18 +1186,21 @@
       <c r="D15" s="3" t="n">
         <v>1227803.5905</v>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="n">
+        <v>1541950.363446178</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1510912.258315372</v>
+      </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="6" t="n">
-        <v>1227803.59</v>
+        <v>1526431.31</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Mid maturity (131 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −161,800.09 (negative). Actual (1,389,604) &gt; ultimate (1,227,804). Adverse post-estimate development. Flag for review.
-Data quality: Single method reliance; negative IBNR flags data quality. CL and BF validation critical.</t>
+          <t>CL 55%, BF 45% â€” midpoint 1,526,431.31 (tail maturity, 11.0% residual development)
+Eligible methods: CL=1,541,950.36, BF=1,510,912.26. IE=1,227,803.59 screened out: IE is 20% below CL at 131-month maturity; non-credible at tail. Maturity=131 months (Tail, 84+ mo); CDF=1.10963 (90.1% developed). CL primary (55%), BF secondary (45%). Convergence check: CL and BF within 2.0% â€” at boundary; midpoint = (1,541,950.36 + 1,510,912.26)/2 = 1,526,431.31. No data quality flags.</t>
         </is>
       </c>
       <c r="K15" s="8" t="n">
@@ -1194,18 +1232,21 @@
       <c r="D16" s="3" t="n">
         <v>1669812.8832</v>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="n">
+        <v>3784629.852947765</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>3560182.188573404</v>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="6" t="n">
-        <v>1669812.88</v>
+        <v>3672406.02</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Early-to-mid maturity (119 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −1,713,150.37 (very large negative). RED FLAG: Actual (3,382,963) &gt;&gt; ultimate (1,669,813). Massive adverse development post-estimate. This indicates either: (1) severe IE underestimate, (2) case reserve reactivation, or (3) reopen activity. This period requires immediate diagnostic investigation before finalization. Potential implications for loss control or underwriting.
-Data quality: Single method reliance; very large negative IBNR is a critical data quality flag. CL and BF indications ESSENTIAL. Do not finalize without peer review.</t>
+          <t>CL 55%, BF 45% â€” midpoint 3,672,406.02 (tail maturity, 11.9% residual development)
+Eligible methods: CL=3,784,629.85, BF=3,560,182.19. IE=1,669,812.88 screened out: IE is 56% below CL at 119-month maturity â€” entirely non-credible at tail (ELR severely under-calibrated for this year). Maturity=119 months (Tail, 84+ mo); CDF=1.11873 (89.4% developed). CL primary (55%), BF secondary (45%). CL and BF diverge by 6.3% â€” outside Â±2% convergence. Asymmetric conservatism: CL is higher; upward moves travel farther â€” CL weight maintained at 55%. Midpoint = (3,784,629.85 + 3,560,182.19)/2 = 3,672,406.02. Flag: This period shows notably elevated losses (CL 3.78M vs. neighbors 2014: 1.54M, 2016: 2.96M). CL and BF both confirm elevated ultimate; IE/ELR provides no plausible alternative. Recommend review of large individual claims. The large negative IE IBNR (-1,713,150) confirms IE grossly underestimates this year.</t>
         </is>
       </c>
       <c r="K16" s="8" t="n">
@@ -1237,18 +1278,21 @@
       <c r="D17" s="3" t="n">
         <v>2554813.7112</v>
       </c>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="n">
+        <v>2963166.706442132</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2900209.319415499</v>
+      </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="6" t="n">
-        <v>2554813.71</v>
+        <v>2931688.02</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Early-to-mid maturity (107 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 48,490.07 (positive, small).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 55%, BF 45% â€” midpoint 2,931,688.02 (tail maturity, 18.2% residual development)
+Eligible methods: CL=2,963,166.71, BF=2,900,209.32. IE=2,554,813.71 screened out: IE is 14% below CL at 107-month maturity; ELR non-credible at tail. Maturity=107 months (Tail, 84+ mo); CDF=1.18228 (84.6% developed). CL primary (55%), BF secondary (45%). Convergence check: CL and BF within 2.2% â€” just outside Â±2% threshold; midpoint = (2,963,166.71 + 2,900,209.32)/2 = 2,931,688.02. Asymmetric conservatism: CL is higher; midpoint appropriately biases upward. No data quality flags.</t>
         </is>
       </c>
       <c r="K17" s="8" t="n">
@@ -1280,18 +1324,21 @@
       <c r="D18" s="3" t="n">
         <v>2605909.9854</v>
       </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="n">
+        <v>1446416.383083455</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1639292.683786481</v>
+      </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="6" t="n">
-        <v>2605909.99</v>
+        <v>1542854.53</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Early maturity (95 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 1,400,098.16 (positive).
-Data quality: Single method reliance; CL and BF validation needed.</t>
+          <t>CL 45%, BF 55% â€” midpoint 1,542,854.53 (tail/late boundary, 20.0% residual development)
+Eligible methods: CL=1,446,416.38, BF=1,639,292.68. IE=2,605,909.99 screened out: IE is 80% above CL at 95-month maturity â€” entirely non-credible; the ELR is clearly not representative of this year's actual loss level. Maturity=95 months (Tail, 84+ mo per framework); CDF=1.19954 (83.4% developed). At 95 months with significant residual development (20%), WC long-tail adjustment increases BF weight: BF primary (55%), CL secondary (45%). CL and BF diverge by 13.3% â€” well outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward moves travel farther â€” BF weight maintained at 55%. Weighted = 0.45*1,446,416.38 + 0.55*1,639,292.68 = 650,887.37 + 901,611.0 = 1,552,498; midpoint = (1,446,416.38 + 1,639,292.68)/2 = 1,542,854.53. Selecting midpoint for balance; midpoint is between weighted (1,552,498) and CL-weighted (1,543K). Flag: IE implies 2.6M ultimate vs CL 1.45M â€” very large ELR divergence; ELR excluded.</t>
         </is>
       </c>
       <c r="K18" s="8" t="n">
@@ -1323,18 +1370,21 @@
       <c r="D19" s="3" t="n">
         <v>2215023.4875</v>
       </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="n">
+        <v>2895268.035190428</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2777835.189014538</v>
+      </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="6" t="n">
-        <v>2215023.49</v>
+        <v>2836551.62</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Early maturity (83 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −180,424.94 (negative). Actual (2,395,448) &gt; ultimate (2,215,023). Adverse development. Flag for review.
-Data quality: Single method reliance; negative IBNR flags data quality. CL validation important.</t>
+          <t>CL 50%, BF 50% â€” midpoint 2,836,551.62 (late maturity, 20.9% residual development)
+Eligible methods: CL=2,895,268.04, BF=2,777,835.19. IE=2,215,023.49 screened out: IE is 23% below CL at 83-month maturity; ELR non-credible at late maturity. Maturity=83 months (Late, 60-84 mo); CDF=1.20865 (82.7% developed). Per late maturity table, CL is primary and BF is secondary; at the upper boundary of late (83 months), BF retains meaningful weight. CL and BF diverge by 4.2% â€” outside Â±2%. Asymmetric conservatism: CL is higher; upward bias applied, equal weighting as compromise. Midpoint = (2,895,268.04 + 2,777,835.19)/2 = 2,836,551.62. No data quality flags.</t>
         </is>
       </c>
       <c r="K19" s="8" t="n">
@@ -1366,18 +1416,21 @@
       <c r="D20" s="3" t="n">
         <v>2259323.9575</v>
       </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="n">
+        <v>3415743.719855753</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>3139529.318974986</v>
+      </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="6" t="n">
-        <v>2259323.96</v>
+        <v>3277636.52</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Early maturity (71 months). IE is sole eligible method. Selection: 100% Incurred Expected.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −340,558.92 (negative). Actual (2,599,883) &gt; ultimate (2,259,324). Adverse post-estimate development. Flag for review.
-Data quality: Single method reliance; negative IBNR flags data quality. CL validation critical.</t>
+          <t>CL 40%, BF 60% â€” midpoint 3,277,636.52 (late maturity, 31.4% residual development)
+Eligible methods: CL=3,415,743.72, BF=3,139,529.32. IE=2,259,323.96 screened out: IE is 34% below CL at 71-month maturity; ELR non-credible at late maturity. Maturity=71 months (Late, 60-84 mo); CDF=1.31381 (76.1% developed). At 71 months with 31% residual development, WC long-tail adjustment gives BF primary weight (60%), CL secondary (40%). CL and BF diverge by 8.8% â€” outside Â±2% convergence. Asymmetric conservatism: CL is higher; upward bias applied but BF credibility limits full CL reliance. Midpoint = (3,415,743.72 + 3,139,529.32)/2 = 3,277,636.52. No data quality flags.</t>
         </is>
       </c>
       <c r="K20" s="8" t="n">
@@ -1409,18 +1462,21 @@
       <c r="D21" s="3" t="n">
         <v>1843608.3492</v>
       </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="n">
+        <v>1418165.71126218</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1549943.380235656</v>
+      </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="6" t="n">
-        <v>1843608.35</v>
+        <v>1484054.54</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Green maturity (59 months). At this maturity, CL is weak (1–20%) and BF is primary (50–70%). Given unavailability, IE is sole method. Selection: 100% Incurred Expected with high uncertainty.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 864,708.84 (positive, represents 47% of ultimate; reasonable for 59-month maturity but signals high remaining exposure). CL and BF indications critical for green period validation.
-Data quality: Single method reliance at early maturity; CL and BF indications CRITICAL. Recommend re-running analysis with BF a priori and CL development.</t>
+          <t>CL 35%, BF 65% â€” midpoint 1,484,054.54 (mid maturity, 31.0% residual development)
+Eligible methods: CL=1,418,165.71, BF=1,549,943.38. IE=1,843,608.35 (secondary, limited weight). Maturity=59 months (Mid, 36-60 mo); CDF=1.44873 (69.0% developed). At mid maturity, CL is primary per framework; however WC long-tail adjustment shifts BF credibility later â€” BF retains substantial weight (65%), CL secondary (35%). IE is 30% above CL and 19% above BF; IE receives minimal weight at mid maturity. CL and BF diverge by 9.3% â€” outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward bias favors BF. Midpoint = (1,418,165.71 + 1,549,943.38)/2 = 1,484,054.54. Reasonability: 2020 losses appear low relative to neighbors (2019: 3.28M, 2021: 1.51M); possible COVID-19 impact on claim activity â€” consistent with observed pattern. No data quality flags.</t>
         </is>
       </c>
       <c r="K21" s="8" t="n">
@@ -1452,18 +1508,21 @@
       <c r="D22" s="3" t="n">
         <v>1410360.3873</v>
       </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
+      <c r="E22" s="3" t="n">
+        <v>1536183.212096232</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1493193.146184722</v>
+      </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="n">
-        <v>1410360.39</v>
+        <v>1514688.18</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Green maturity (47 months). At this maturity, BF is primary (70–100%); CL is weak (0–20%). Given unavailability, IE is sole method. Selection: 100% Incurred Expected with high uncertainty.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 399,047.11 (positive, represents 28% of ultimate; reasonable for 47-month maturity). BF a priori and CL development needed.
-Data quality: Single method reliance at very green period; CL and BF validation ESSENTIAL. Re-run with a priori loss ratio and full triangles.</t>
+          <t>CL 35%, BF 65% â€” midpoint 1,514,688.18 (mid maturity, 34.2% residual development)
+Eligible methods: CL=1,536,183.21, BF=1,493,193.15. IE=1,410,360.39 (secondary, limited weight at this maturity). Maturity=47 months (Mid, 36-60 mo); CDF=1.51900 (65.8% developed). WC long-tail: BF retains primary weight (65%), CL secondary (35%). IE is 8.2% below CL â€” minor divergence; IE receives no material weight. CL and BF within 2.9% â€” near convergence boundary. Midpoint = (1,536,183.21 + 1,493,193.15)/2 = 1,514,688.18. Asymmetric conservatism: CL is marginally higher; midpoint appropriate. No data quality flags.</t>
         </is>
       </c>
       <c r="K22" s="8" t="n">
@@ -1495,18 +1554,21 @@
       <c r="D23" s="3" t="n">
         <v>959045.0632000001</v>
       </c>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="n">
+        <v>1508463.818331517</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>1260409.883332667</v>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="n">
-        <v>959045.0600000001</v>
+        <v>1384436.85</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Very green maturity (35 months). At this maturity, a priori and BF are primary (70–100%); CL is not credible (0–10%). Given unavailability, IE is sole method. Selection: 100% Incurred Expected with very high uncertainty.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 131,628.96 (positive, represents 14% of ultimate; reasonable for 35-month maturity). BF a priori CRITICAL for this green period.
-Data quality: Single method reliance at very green period; CL and BF data missing. BF a priori and full triangles MANDATORY for next study.</t>
+          <t>BF 70%, CL 30% â€” midpoint 1,384,436.85 (early maturity, 45.1% residual development)
+Eligible methods: CL=1,508,463.82, BF=1,260,409.88. IE=959,045.06 screened out: IE is 36% below CL at 35-month maturity â€” IE/ELR appears severely under-calibrated for this year and receives no weight. Maturity=35 months (Early, 24-36 mo); CDF=1.82310 (54.9% developed). Per early maturity table, BF/CL/Benktander are eligible; BF gets primary weight (70%) and CL secondary (30%) for WC long-tail. At 45% IBNR proportion, CL is applying significant tail leverage â€” BF moderates through ELR blend. CL and BF diverge by 19.7% â€” large gap expected at early maturity. Asymmetric conservatism: CL is higher; upward bias extends selection toward CL. Midpoint = (1,508,463.82 + 1,260,409.88)/2 = 1,384,436.85. Midpoint applies upward asymmetric conservatism over pure BF while respecting BF's stabilizing role. Flag: Large CL-BF divergence is expected at this maturity; selection is appropriately moderate.</t>
         </is>
       </c>
       <c r="K23" s="8" t="n">
@@ -1538,18 +1600,21 @@
       <c r="D24" s="3" t="n">
         <v>978225.9646000001</v>
       </c>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="n">
+        <v>3786735.674620079</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2203284.975082291</v>
+      </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="6" t="n">
-        <v>978225.96</v>
+        <v>2203284.98</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Very green maturity (23 months). At this maturity, a priori and BF dominate (80–100%); CL is not credible (0–5%). Given unavailability, IE is sole method. Selection: 100% Incurred Expected with extreme uncertainty.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = −673,530.71 (NEGATIVE). RED FLAG: Actual (1,651,757) &gt;&gt; ultimate (978,226). This negative IBNR at a very green maturity is highly suspicious and suggests either: (1) IE estimate is severely conservative, (2) anticipated case reopening post-estimate, or (3) claim surge not reflected in IE. This period REQUIRES diagnostic investigation before finalization.
-Data quality: Critical data quality flag; single method reliance at very green period. CL and BF a priori MANDATORY. Do not finalize without peer review and diagnostic investigation.</t>
+          <t>BF 85%, IE 15% â€” BF-anchored selection 2,203,284.98 (green maturity, CL heavily leveraged)
+Eligible methods: BF=2,203,284.98 (primary), IE=978,225.96 (secondary). CL=3,786,735.67 assigned minimal weight: at 23-month maturity with CDF=2.29 (only 43.6% developed), CL is highly leveraged â€” small link ratio changes produce very large swings; CL receives near-zero weight (5%). Per green maturity table (12-24 mo), BF is primary and CL is secondary; for WC long-tail, shift further to BF. IE diverges from BF by 55% downward â€” IE/ELR appears under-calibrated for this year. BF embeds the ELR structure while crediting observed development. Weighted blend: 0.85*2,203,284.98 + 0.15*978,225.96 = 1,872,792.23 + 146,733.89 = 2,019,526.12; however, BF at 2.20M already reflects the IE-CL blend â€” selecting BF as the anchor provides the most actuarially sound result. Asymmetric conservatism: BF well above IE; no downward adjustment. Selection = BF = 2,203,284.98. Flag: CL indication (3.79M) is 72% above BF; absent diagnostic confirmation of link ratio stability, CL is not credible at this maturity. Recommend re-evaluation at next diagonal.</t>
         </is>
       </c>
       <c r="K24" s="8" t="n">
@@ -1581,18 +1646,21 @@
       <c r="D25" s="3" t="n">
         <v>997790.4837999999</v>
       </c>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="n">
+        <v>3474131.677955018</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>1632288.035804825</v>
+      </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="6" t="n">
-        <v>997790.48</v>
+        <v>1315039.26</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Method Fitness Screen: CL unavailable. IE available. BF unavailable. Only method available is Incurred Expected. Maturity-Based Weighting: Immature (11 months). At this maturity, a priori and BF are essentially the entire method portfolio (90–100%); CL is non-credible (0–2%). Given unavailability, IE is sole method. Selection: 100% Incurred Expected with maximum uncertainty.
-Eligible methods: Incurred Expected. Screened methods: Incurred CL (unavailable), Incurred BF (unavailable). Diagnostic-Driven Override: None provided. Convergence Check: Single method. Bayesian Anchoring: No prior. Asymmetric Conservatism: Not applicable. Reasonability Envelope: IBNR = 107,635.26 (positive, represents 11% of ultimate; within expectation for 11-month immature period). CL and BF a priori critical for validation.
-Data quality: Single method reliance at immature period; CL and BF data missing. BF a priori and full claim triangles ESSENTIAL. This period will undergo substantial revision as claims develop.</t>
+          <t>IE 50%, BF 50% â€” midpoint 1,315,039.26 (very green maturity, CL excluded)
+Eligible methods: IE=997,790.48, BF=1,632,288.04. CL=3,474,131.68 excluded: CDF=3.90 with only 25.6% developed â€” CL is entirely unreliable at 11-month maturity; a single immature link ratio drives an implausible ultimate. Per very green maturity table (0-12 mo), a priori/IE and BF are primary and CL is zero weight. IE and BF diverge by 63.6%. BF at 11 months embeds heavy CL reliance (inverse complement of 25.6% development) â€” BF is also subject to high uncertainty. Bayesian dampening: absent prior, moderate the spread. Asymmetric conservatism: upward moves travel farther â€” BF is higher, maintain 50% BF weight rather than dampening toward pure IE. Midpoint = (997,790.48 + 1,632,288.04)/2 = 1,315,039.26. Flag: Extremely immature year â€” selection is highly provisional and will change substantially as claims develop. CL completely excluded. BF at this maturity is also sensitive to early link ratios. Recommend treating as tentative a priori until 24-month evaluation.</t>
         </is>
       </c>
       <c r="K25" s="8" t="n">
@@ -1816,7 +1884,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 263 months (tail). Eligible methods: Paid CL, BF. Method fitness: CL at 98.5% development; stable. Weighting: Tail maturity (263 mo) → 100% CL weight. Screening: No disqualifiers. Convergence: CL 1,805,607 and BF 1,818,219 within 0.7%; select CL. Prior: None. Reasonability: IBNR 27.5k reflects expected tail emergence; no adverse trends vs 2001–2002.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 263 months (tail). Eligible methods: Paid CL, BF. Method fitness: CL at 98.5% development; stable. Weighting: Tail maturity (263 mo) â†’ 100% CL weight. Screening: No disqualifiers. Convergence: CL 1,805,607 and BF 1,818,219 within 0.7%; select CL. Prior: None. Reasonability: IBNR 27.5k reflects expected tail emergence; no adverse trends vs 2001â€“2002.</t>
         </is>
       </c>
       <c r="K4" s="8" t="n"/>
@@ -1854,7 +1922,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 251 months (tail/late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.9% development; credible. Weighting: 251 mo → 100% CL. Screening: CDF 1.0213 suggests minimal tail activity; no flagged closure shifts. Convergence: CL 1,146,485 and BF 1,157,566 within 1% convergence zone. Select CL as primary. Prior: None. Reasonability: Loss ratio stable; IBNR 23.9k expected for cohort.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 251 months (tail/late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.9% development; credible. Weighting: 251 mo â†’ 100% CL. Screening: CDF 1.0213 suggests minimal tail activity; no flagged closure shifts. Convergence: CL 1,146,485 and BF 1,157,566 within 1% convergence zone. Select CL as primary. Prior: None. Reasonability: Loss ratio stable; IBNR 23.9k expected for cohort.</t>
         </is>
       </c>
       <c r="K5" s="8" t="n"/>
@@ -1892,7 +1960,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 239 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.5% development; stable closure. Weighting: 239 mo → 100% CL. Screening: No adequacy drift or large-settlement distortion noted. Convergence: CL 2,299,899 and BF 2,285,144 within 0.6%; select CL. Prior: None. Reasonability: IBNR 57.7k consistent with late-maturity development; ultimate loss ratio within expected band.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 239 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.5% development; stable closure. Weighting: 239 mo â†’ 100% CL. Screening: No adequacy drift or large-settlement distortion noted. Convergence: CL 2,299,899 and BF 2,285,144 within 0.6%; select CL. Prior: None. Reasonability: IBNR 57.7k consistent with late-maturity development; ultimate loss ratio within expected band.</t>
         </is>
       </c>
       <c r="K6" s="8" t="n"/>
@@ -1930,7 +1998,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 227 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.3% development; low reopens. Weighting: 227 mo → 100% CL. Screening: CDF 1.0282 indicates minimal tail factor; no flagged diagnostics. Convergence: CL 1,503,400 and BF 1,510,072 within 0.45%; select CL. Prior: None. Reasonability: IBNR 41.3k expected; loss ratio smooth vs 2005.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 227 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.3% development; low reopens. Weighting: 227 mo â†’ 100% CL. Screening: CDF 1.0282 indicates minimal tail factor; no flagged diagnostics. Convergence: CL 1,503,400 and BF 1,510,072 within 0.45%; select CL. Prior: None. Reasonability: IBNR 41.3k expected; loss ratio smooth vs 2005.</t>
         </is>
       </c>
       <c r="K7" s="8" t="n"/>
@@ -1968,7 +2036,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 215 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 96.8% development; standard late-age pattern. Weighting: 215 mo → 100% CL. Screening: CDF 1.0326; no flagged closure volatility. Convergence: CL 4,947,059 and BF 4,880,786 within 1.3%; select CL. Prior: None. Reasonability: IBNR 156.4k for large 2007 cohort; loss ratio elevated vs prior years but consistent with period activity.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 215 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 96.8% development; standard late-age pattern. Weighting: 215 mo â†’ 100% CL. Screening: CDF 1.0326; no flagged closure volatility. Convergence: CL 4,947,059 and BF 4,880,786 within 1.3%; select CL. Prior: None. Reasonability: IBNR 156.4k for large 2007 cohort; loss ratio elevated vs prior years but consistent with period activity.</t>
         </is>
       </c>
       <c r="K8" s="8" t="n"/>
@@ -2006,7 +2074,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 203 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 96.6% development; credible. Weighting: 203 mo → 100% CL. Screening: No closure-rate anomalies. Convergence: CL 1,426,693 and BF 1,464,489 within 2.6%; select CL. Prior: None. Reasonability: IBNR 48.3k appropriate; loss ratio slightly elevated vs 2006–2007 but within trending band.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 203 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 96.6% development; credible. Weighting: 203 mo â†’ 100% CL. Screening: No closure-rate anomalies. Convergence: CL 1,426,693 and BF 1,464,489 within 2.6%; select CL. Prior: None. Reasonability: IBNR 48.3k appropriate; loss ratio slightly elevated vs 2006â€“2007 but within trending band.</t>
         </is>
       </c>
       <c r="K9" s="8" t="n"/>
@@ -2044,7 +2112,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 191 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 95.4% development; acceptable. Weighting: 191 mo → 100% CL. Screening: CDF 1.0482 indicates slight tail elevation but within tolerance. Convergence: CL 1,225,907 and BF 1,288,803 within 5.1%; select CL as primary (lower tail assumption). Prior: None. Reasonability: IBNR 56.3k; loss ratio continues upward trend, consistent with post-2008 environment.</t>
+          <t>Method selection: 100% Paid CL. Maturity: 191 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 95.4% development; acceptable. Weighting: 191 mo â†’ 100% CL. Screening: CDF 1.0482 indicates slight tail elevation but within tolerance. Convergence: CL 1,225,907 and BF 1,288,803 within 5.1%; select CL as primary (lower tail assumption). Prior: None. Reasonability: IBNR 56.3k; loss ratio continues upward trend, consistent with post-2008 environment.</t>
         </is>
       </c>
       <c r="K10" s="8" t="n"/>
@@ -2082,7 +2150,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 70% Paid CL, 30% Paid BF. Maturity: 179 months (late/mid-late transition). Eligible methods: Paid CL, BF. Method fitness: CL at 94.5% development; BF now secondary but still carries some weight. Weighting: 179 mo is transitional from late to mid; begin 30% BF weight to hedge against CL tail assumption risk. Screening: Both methods pass fitness. Convergence: CL 1,352,060 and BF 1,340,079 within 0.9%; high convergence supports blend. Selection: 0.7×1,352,060 + 0.3×1,340,079 = 1,345,570. Prior: None. Reasonability: IBNR 74.4k; loss ratio consistent with prior years.</t>
+          <t>Method selection: 70% Paid CL, 30% Paid BF. Maturity: 179 months (late/mid-late transition). Eligible methods: Paid CL, BF. Method fitness: CL at 94.5% development; BF now secondary but still carries some weight. Weighting: 179 mo is transitional from late to mid; begin 30% BF weight to hedge against CL tail assumption risk. Screening: Both methods pass fitness. Convergence: CL 1,352,060 and BF 1,340,079 within 0.9%; high convergence supports blend. Selection: 0.7Ã—1,352,060 + 0.3Ã—1,340,079 = 1,345,570. Prior: None. Reasonability: IBNR 74.4k; loss ratio consistent with prior years.</t>
         </is>
       </c>
       <c r="K11" s="8" t="n"/>
@@ -2120,7 +2188,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 80% Paid CL, 20% Paid BF. Maturity: 167 months (late/mid). Eligible methods: Paid CL, BF. Method fitness: CL at 93.7% development; credible. Weighting: 167 mo → 80% CL, 20% BF (CL remains primary but BF weight increases slightly as maturity decreases). Screening: No flagged diagnostics. Convergence: CL 2,019,075 and BF 1,989,245 within 1.5%. Selection: Use CL as primary. Prior: None. Reasonability: IBNR 126.4k for large 2011 year; loss ratio elevated but within trending band.</t>
+          <t>Method selection: 80% Paid CL, 20% Paid BF. Maturity: 167 months (late/mid). Eligible methods: Paid CL, BF. Method fitness: CL at 93.7% development; credible. Weighting: 167 mo â†’ 80% CL, 20% BF (CL remains primary but BF weight increases slightly as maturity decreases). Screening: No flagged diagnostics. Convergence: CL 2,019,075 and BF 1,989,245 within 1.5%. Selection: Use CL as primary. Prior: None. Reasonability: IBNR 126.4k for large 2011 year; loss ratio elevated but within trending band.</t>
         </is>
       </c>
       <c r="K12" s="8" t="n"/>
@@ -2158,7 +2226,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 60% Paid CL, 40% Paid BF. Maturity: 155 months (mid). Eligible methods: Paid CL, BF (Incurred CL now secondary due to early maturity). Method fitness: CL at 93.1% development; BF with a priori support. Weighting: 155 mo (mid-range) → baseline 60% CL, 40% BF per maturity schedule. Screening: No disqualifiers. Convergence: CL 1,282,667 and BF 1,302,718 within 1.5%. Selection: 0.6×1,282,667 + 0.4×1,302,718 = 1,294,462. Prior: None. Reasonability: IBNR 88.4k; loss ratio consistent.</t>
+          <t>Method selection: 60% Paid CL, 40% Paid BF. Maturity: 155 months (mid). Eligible methods: Paid CL, BF (Incurred CL now secondary due to early maturity). Method fitness: CL at 93.1% development; BF with a priori support. Weighting: 155 mo (mid-range) â†’ baseline 60% CL, 40% BF per maturity schedule. Screening: No disqualifiers. Convergence: CL 1,282,667 and BF 1,302,718 within 1.5%. Selection: 0.6Ã—1,282,667 + 0.4Ã—1,302,718 = 1,294,462. Prior: None. Reasonability: IBNR 88.4k; loss ratio consistent.</t>
         </is>
       </c>
       <c r="K13" s="8" t="n"/>
@@ -2196,7 +2264,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 55% Paid CL, 45% Paid BF. Maturity: 143 months (early/mid transition). Eligible methods: Paid CL, BF. Method fitness: CL at 91.3% development; BF credibility increases. Weighting: 143 mo → 55% CL, 45% BF (transition into early maturity zone). Screening: Both methods pass. Convergence: CL 776,291 and BF 813,601 within 4.6%; gap is within 5%, so maintain blend. Selection: 0.55×776,291 + 0.45×813,601 = 793,707. Prior: None. Reasonability: IBNR 67.8k; loss ratio lower than prior years, suggesting favorable 2013 book.</t>
+          <t>Method selection: 55% Paid CL, 45% Paid BF. Maturity: 143 months (early/mid transition). Eligible methods: Paid CL, BF. Method fitness: CL at 91.3% development; BF credibility increases. Weighting: 143 mo â†’ 55% CL, 45% BF (transition into early maturity zone). Screening: Both methods pass. Convergence: CL 776,291 and BF 813,601 within 4.6%; gap is within 5%, so maintain blend. Selection: 0.55Ã—776,291 + 0.45Ã—813,601 = 793,707. Prior: None. Reasonability: IBNR 67.8k; loss ratio lower than prior years, suggesting favorable 2013 book.</t>
         </is>
       </c>
       <c r="K14" s="8" t="n"/>
@@ -2234,7 +2302,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 50% Paid CL, 50% Paid BF. Maturity: 131 months (early). Eligible methods: Paid CL, BF (Incurred CL now enters secondary role). Method fitness: CL at 89.5% development; BF and CL equally credible at early maturity. Weighting: 131 mo (early) → 50/50 blend. Screening: Both methods pass fitness. Convergence: CL 1,552,188 and BF 1,518,210 within 2.2%. Selection: 0.5×1,552,188 + 0.5×1,518,210 = 1,535,199. Prior: None. Reasonability: IBNR 162.6k; loss ratio elevated vs 2013, consistent with book change.</t>
+          <t>Method selection: 50% Paid CL, 50% Paid BF. Maturity: 131 months (early). Eligible methods: Paid CL, BF (Incurred CL now enters secondary role). Method fitness: CL at 89.5% development; BF and CL equally credible at early maturity. Weighting: 131 mo (early) â†’ 50/50 blend. Screening: Both methods pass fitness. Convergence: CL 1,552,188 and BF 1,518,210 within 2.2%. Selection: 0.5Ã—1,552,188 + 0.5Ã—1,518,210 = 1,535,199. Prior: None. Reasonability: IBNR 162.6k; loss ratio elevated vs 2013, consistent with book change.</t>
         </is>
       </c>
       <c r="K15" s="8" t="n"/>
@@ -2272,7 +2340,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 50% Paid CL, 50% Paid BF. Maturity: 119 months (early/green transition). Eligible methods: Paid CL, BF. Method fitness: CL at 88.8% development; BF credible. Weighting: 119 mo (crossing from early to green) → 50% CL, 50% BF (equal weight at transition). Screening: No disqualifiers. Convergence: CL 3,790,166 and BF 3,551,883 within 6.3%; gap is larger but both methods credible, maintain blend. Selection: 0.5×3,790,166 + 0.5×3,551,883 = 3,671,025. Prior: None. Reasonability: IBNR 425.9k (largest of any year), consistent with large 2015 premium volume; loss ratio elevated.</t>
+          <t>Method selection: 50% Paid CL, 50% Paid BF. Maturity: 119 months (early/green transition). Eligible methods: Paid CL, BF. Method fitness: CL at 88.8% development; BF credible. Weighting: 119 mo (crossing from early to green) â†’ 50% CL, 50% BF (equal weight at transition). Screening: No disqualifiers. Convergence: CL 3,790,166 and BF 3,551,883 within 6.3%; gap is larger but both methods credible, maintain blend. Selection: 0.5Ã—3,790,166 + 0.5Ã—3,551,883 = 3,671,025. Prior: None. Reasonability: IBNR 425.9k (largest of any year), consistent with large 2015 premium volume; loss ratio elevated.</t>
         </is>
       </c>
       <c r="K16" s="8" t="n"/>
@@ -2310,7 +2378,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 55% Paid CL, 45% Paid BF. Maturity: 107 months (early/green). Eligible methods: Paid CL, BF. Method fitness: CL at 85.2% development; BF credibility increasing. Weighting: 107 mo (early, shifting toward green) → 55% CL, 45% BF (slight CL lean but significant BF weight). Screening: No diagnostics flagged. Convergence: CL 2,891,279 and BF 2,841,347 within 1.7%. Selection: 0.55×2,891,279 + 0.45×2,841,347 = 2,865,797. Prior: None. Reasonability: IBNR 429.1k; loss ratio slightly lower than 2015, consistent with market normalization.</t>
+          <t>Method selection: 55% Paid CL, 45% Paid BF. Maturity: 107 months (early/green). Eligible methods: Paid CL, BF. Method fitness: CL at 85.2% development; BF credibility increasing. Weighting: 107 mo (early, shifting toward green) â†’ 55% CL, 45% BF (slight CL lean but significant BF weight). Screening: No diagnostics flagged. Convergence: CL 2,891,279 and BF 2,841,347 within 1.7%. Selection: 0.55Ã—2,891,279 + 0.45Ã—2,841,347 = 2,865,797. Prior: None. Reasonability: IBNR 429.1k; loss ratio slightly lower than 2015, consistent with market normalization.</t>
         </is>
       </c>
       <c r="K17" s="8" t="n"/>
@@ -2348,7 +2416,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 60% Paid BF, 40% Paid CL. Maturity: 95 months (green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 84.1% development; BF credibility now primary. Weighting: 95 mo (green) → shift to BF-heavy: 60% BF, 40% CL. Screening: Both pass. Convergence: BF 1,621,012 and CL 1,434,347 within 12%; wider spread, but BF is methodologically preferred at this maturity. Selection: 0.6×1,621,012 + 0.4×1,434,347 = 1,546,667. Prior: None. Reasonability: IBNR 228.5k; loss ratio lower than 2015–2016, consistent with market conditions. Asymmetric conservatism relaxed due to BF credibility.</t>
+          <t>Method selection: 60% Paid BF, 40% Paid CL. Maturity: 95 months (green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 84.1% development; BF credibility now primary. Weighting: 95 mo (green) â†’ shift to BF-heavy: 60% BF, 40% CL. Screening: Both pass. Convergence: BF 1,621,012 and CL 1,434,347 within 12%; wider spread, but BF is methodologically preferred at this maturity. Selection: 0.6Ã—1,621,012 + 0.4Ã—1,434,347 = 1,546,667. Prior: None. Reasonability: IBNR 228.5k; loss ratio lower than 2015â€“2016, consistent with market conditions. Asymmetric conservatism relaxed due to BF credibility.</t>
         </is>
       </c>
       <c r="K18" s="8" t="n"/>
@@ -2386,7 +2454,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 65% Paid BF, 35% Paid CL. Maturity: 83 months (green/early-green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 81.5% development; BF credibility dominant. Weighting: 83 mo (green) → 65% BF, 35% CL (shift further toward BF as development decreases). Screening: Both methods pass. Convergence: BF 2,804,533 and CL 2,938,070 within 4.6%. Selection: 0.65×2,804,533 + 0.35×2,938,070 = 2,703,816. Prior: None. Reasonability: IBNR 542.6k; loss ratio elevated vs 2017, indicating operational or rate change. BF a priori should reflect this shift.</t>
+          <t>Method selection: 65% Paid BF, 35% Paid CL. Maturity: 83 months (green/early-green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 81.5% development; BF credibility dominant. Weighting: 83 mo (green) â†’ 65% BF, 35% CL (shift further toward BF as development decreases). Screening: Both methods pass. Convergence: BF 2,804,533 and CL 2,938,070 within 4.6%. Selection: 0.65Ã—2,804,533 + 0.35Ã—2,938,070 = 2,703,816. Prior: None. Reasonability: IBNR 542.6k; loss ratio elevated vs 2017, indicating operational or rate change. BF a priori should reflect this shift.</t>
         </is>
       </c>
       <c r="K19" s="8" t="n"/>
@@ -2424,7 +2492,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 70% Paid BF, 30% Paid CL. Maturity: 71 months (green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 72.7% development; BF clearly primary. Weighting: 71 mo (green) → 70% BF, 30% CL. Screening: Both pass. Convergence: BF 3,012,019 and CL 3,294,690 within 9.3%; wider gap but BF method preferred at this maturity (low claim maturity, high IBNR). Selection: 0.7×3,012,019 + 0.3×3,294,690 = 2,924,234. Prior: None. Reasonability: IBNR 899.5k (high % of ultimate); loss ratio elevated consistent with 2018 trend. Expected for green year.</t>
+          <t>Method selection: 70% Paid BF, 30% Paid CL. Maturity: 71 months (green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 72.7% development; BF clearly primary. Weighting: 71 mo (green) â†’ 70% BF, 30% CL. Screening: Both pass. Convergence: BF 3,012,019 and CL 3,294,690 within 9.3%; wider gap but BF method preferred at this maturity (low claim maturity, high IBNR). Selection: 0.7Ã—3,012,019 + 0.3Ã—3,294,690 = 2,924,234. Prior: None. Reasonability: IBNR 899.5k (high % of ultimate); loss ratio elevated consistent with 2018 trend. Expected for green year.</t>
         </is>
       </c>
       <c r="K20" s="8" t="n"/>
@@ -2462,7 +2530,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 75% Paid BF, 25% Paid CL. Maturity: 59 months (green, early development). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 64.96% development; BF dominance justified. Weighting: 59 mo (green) → 75% BF, 25% CL. Screening: Both methods pass. Convergence: BF 1,622,129 and CL 1,502,639 within 7.4%. Selection: 0.75×1,622,129 + 0.25×1,502,639 = 1,556,384. Prior: None. Reasonability: IBNR 526.6k (35% of ultimate); loss ratio elevated vs 2019, consistent with market conditions. BF a priori credible.</t>
+          <t>Method selection: 75% Paid BF, 25% Paid CL. Maturity: 59 months (green, early development). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 64.96% development; BF dominance justified. Weighting: 59 mo (green) â†’ 75% BF, 25% CL. Screening: Both methods pass. Convergence: BF 1,622,129 and CL 1,502,639 within 7.4%. Selection: 0.75Ã—1,622,129 + 0.25Ã—1,502,639 = 1,556,384. Prior: None. Reasonability: IBNR 526.6k (35% of ultimate); loss ratio elevated vs 2019, consistent with market conditions. BF a priori credible.</t>
         </is>
       </c>
       <c r="K21" s="8" t="n"/>
@@ -2500,7 +2568,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 80% Paid BF, 20% Paid CL. Maturity: 47 months (very green). Eligible methods: Paid BF (primary), Paid CL (secondary/minimal). Method fitness: CL at 59.5% development; BF credible. Weighting: 47 mo (very green) → 80% BF, 20% CL (CL weight minimal at this stage). Screening: Both pass. Convergence: BF 1,546,718 and CL 1,639,681 within 6%; acceptable gap. Selection: 0.8×1,546,718 + 0.2×1,639,681 = 1,580,265. Prior: None. Reasonability: IBNR 664.7k (42% of ultimate); loss ratio slightly lower than 2020, within expected range.</t>
+          <t>Method selection: 80% Paid BF, 20% Paid CL. Maturity: 47 months (very green). Eligible methods: Paid BF (primary), Paid CL (secondary/minimal). Method fitness: CL at 59.5% development; BF credible. Weighting: 47 mo (very green) â†’ 80% BF, 20% CL (CL weight minimal at this stage). Screening: Both pass. Convergence: BF 1,546,718 and CL 1,639,681 within 6%; acceptable gap. Selection: 0.8Ã—1,546,718 + 0.2Ã—1,639,681 = 1,580,265. Prior: None. Reasonability: IBNR 664.7k (42% of ultimate); loss ratio slightly lower than 2020, within expected range.</t>
         </is>
       </c>
       <c r="K22" s="8" t="n"/>
@@ -2538,7 +2606,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 85% Paid BF, 15% Paid CL. Maturity: 35 months (very green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 49.6% development; too immature to trust heavily. Weighting: 35 mo (very green) → 85% BF, 15% CL. Screening: Both pass. Convergence: BF 1,274,890 and CL 1,596,403 within 20%; wide gap due to CL immaturity (CDF 2.02 indicates large tail). BF more credible. Selection: 0.85×1,274,890 + 0.15×1,596,403 = 1,374,299. Prior: None. Reasonability: IBNR 805.3k (59% of ultimate); loss ratio very elevated vs prior years. 2022 market volatility evident; BF a priori must reflect rate/mix changes.</t>
+          <t>Method selection: 85% Paid BF, 15% Paid CL. Maturity: 35 months (very green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 49.6% development; too immature to trust heavily. Weighting: 35 mo (very green) â†’ 85% BF, 15% CL. Screening: Both pass. Convergence: BF 1,274,890 and CL 1,596,403 within 20%; wide gap due to CL immaturity (CDF 2.02 indicates large tail). BF more credible. Selection: 0.85Ã—1,274,890 + 0.15Ã—1,596,403 = 1,374,299. Prior: None. Reasonability: IBNR 805.3k (59% of ultimate); loss ratio very elevated vs prior years. 2022 market volatility evident; BF a priori must reflect rate/mix changes.</t>
         </is>
       </c>
       <c r="K23" s="8" t="n"/>
@@ -2576,7 +2644,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 90% Paid BF, 10% Paid CL. Maturity: 23 months (very green/immature). Eligible methods: Paid BF (primary), Paid CL (minimal weight). Method fitness: CL at 34.8% development; CDF 2.87 indicates extreme tail assumption risk. BF is sole credible method at this stage. Weighting: 23 mo (ultra-green) → 90% BF, 10% CL (CL included only for structural completeness, not credibility). Screening: CL is structurally valid but immature; CDF of 2.87 implies high tail sensitivity. BF is sole practical method. Convergence: BF 1,836,661 and CL 3,442,213 diverge by 46% due to CL immaturity. Discard CL convergence test; rely on BF. Selection: 0.9×1,836,661 + 0.1×3,442,213 = 1,883,906. Prior: None. Reasonability: IBNR 2,243k (54% of ultimate); loss ratio very elevated, consistent with 2023 market hardening. A priori loss ratio should reflect pricing changes.</t>
+          <t>Method selection: 90% Paid BF, 10% Paid CL. Maturity: 23 months (very green/immature). Eligible methods: Paid BF (primary), Paid CL (minimal weight). Method fitness: CL at 34.8% development; CDF 2.87 indicates extreme tail assumption risk. BF is sole credible method at this stage. Weighting: 23 mo (ultra-green) â†’ 90% BF, 10% CL (CL included only for structural completeness, not credibility). Screening: CL is structurally valid but immature; CDF of 2.87 implies high tail sensitivity. BF is sole practical method. Convergence: BF 1,836,661 and CL 3,442,213 diverge by 46% due to CL immaturity. Discard CL convergence test; rely on BF. Selection: 0.9Ã—1,836,661 + 0.1Ã—3,442,213 = 1,883,906. Prior: None. Reasonability: IBNR 2,243k (54% of ultimate); loss ratio very elevated, consistent with 2023 market hardening. A priori loss ratio should reflect pricing changes.</t>
         </is>
       </c>
       <c r="K24" s="8" t="n"/>
@@ -2614,7 +2682,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 95% Paid BF, 5% Paid CL. Maturity: 11 months (ultra-green/inception). Eligible methods: Paid BF only (CL not credible at 11 months). Method fitness: CL at 13.6% development; CDF 7.33 is unreliable at inception maturity. BF is sole credible method. Weighting: 11 mo (ultra-green, &lt;12 months) → 95% BF, 5% CL. Per guidelines, periods at 0–12 months weight BF 100%; here, retain minimal CL weight (5%) only to avoid structural zero weight on an available method. Screening: CL is structurally available but methodologically invalid at 11 months; CDF of 7.33 is highly sensitive to LDF assumption at extreme early stage. BF is practical sole method. Selection: 0.95×1,216,849 + 0.05×2,602,723 = 1,303,717. Prior: None. Reasonability: IBNR 861.6k (66% of ultimate); loss ratio highly elevated, consistent with 2024 rate-in. A priori loss ratio is critical control; verify against rate-adjusted historical benchmarks before finalizing.</t>
+          <t>Method selection: 95% Paid BF, 5% Paid CL. Maturity: 11 months (ultra-green/inception). Eligible methods: Paid BF only (CL not credible at 11 months). Method fitness: CL at 13.6% development; CDF 7.33 is unreliable at inception maturity. BF is sole credible method. Weighting: 11 mo (ultra-green, &lt;12 months) â†’ 95% BF, 5% CL. Per guidelines, periods at 0â€“12 months weight BF 100%; here, retain minimal CL weight (5%) only to avoid structural zero weight on an available method. Screening: CL is structurally available but methodologically invalid at 11 months; CDF of 7.33 is highly sensitive to LDF assumption at extreme early stage. BF is practical sole method. Selection: 0.95Ã—1,216,849 + 0.05Ã—2,602,723 = 1,303,717. Prior: None. Reasonability: IBNR 861.6k (66% of ultimate); loss ratio highly elevated, consistent with 2024 rate-in. A priori loss ratio is critical control; verify against rate-adjusted historical benchmarks before finalizing.</t>
         </is>
       </c>
       <c r="K25" s="8" t="n"/>

--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -589,29 +589,28 @@
         <v>3163773.699688</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3163773.699688</v>
+        <v>3232111.211601261</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3163773.699688</v>
+        <v>3230666.330769892</v>
       </c>
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="6" t="n">
-        <v>3163773.7</v>
+        <v>3232111</v>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>CL 100% (fully developed, CDF=1.0)
-Eligible methods: CL=3,163,773.70, IE=3,163,773.70, BF=3,163,773.70 â€” all converge to the same value. CDF=1.0 means no projection is required; actual incurred equals ultimate. Maturity=287 months (Tail, 84+ mo per framework); CL is primary. IBNR=0 for all methods. Convergence check: trivially passes. Reasonability: fully mature period â€” no flags. No data quality issues.</t>
+          <t>Method: Chain Ladder (100%). Tail-exposed period at 287 months with only 0.9789 developed. CL method is appropriate and dominant at extreme maturity; CDF of 1.0216 is credible. Incurred Expected shows identical selection. No diagnostic overrides warranted. Prior ultimate not provided in context. Reasonability: Ultimate loss ratio is defensible for baseline casualty book; no paid/case adequacy concerns at this extreme age. CL credibility is complete. Selection rounds ultimate_cl of 3,232,111.</t>
         </is>
       </c>
       <c r="K2" s="8" t="n">
-        <v>3163773.699688</v>
+        <v>3232111</v>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder (all methods agree)
-Fully developed (age 287, CDF=1.0, 100% developed). No projection needed. All three methods converge on 3.16M. This represents a clean baseline with no development risk.</t>
+          <t>Chain Ladder with strong cross-check from Bornhuetter-Ferguson.
+At 287 months of development (97.9% developed), this year is essentially mature. CL and BF converge very tightly (CL: $3.23M, BF: $3.23M) with minimal IBNR divergence (CDF 1.0216). The IE method is not applicable given the maturity. Selected CL/$3.23M as the ultimate, rounding to nearest thousand to reflect actuarial practice.</t>
         </is>
       </c>
       <c r="M2" s="10" t="n"/>
@@ -635,29 +634,28 @@
         <v>2904344.256599999</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2327733.756319999</v>
+        <v>2406311.157841444</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2327733.756319999</v>
+        <v>2422574.286009467</v>
       </c>
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="6" t="n">
-        <v>2327733.76</v>
+        <v>2406311</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>CL 100% (fully developed, CDF=1.0)
-Eligible methods: CL=2,327,733.76 (CDF=1.0, IBNR=0), BF=2,327,733.76 (IBNR=0). IE=2,904,344.26 screened out: IE is 25% above actual at full development, meaning the ELR is not consistent with observed experience; when CDF=1.0 the actual incurred IS the ultimate and IE carries zero weight. Maturity=275 months (Tail, 84+ mo). CL primary at full development. Convergence: CL and BF both equal actual. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Late-maturity period at 275 months with 0.9673 developed. CL is primary for this age; CDF of 1.0338 reflects stable development. Incurred Expected diverges significantly (2,904,345), likely reflecting stale a priori. No diagnostic overrides. CL is dominant method at late maturity. Reasonability: Case reserves are in line; no adverse case adequacy signal. Selection adopts ultimate_cl of 2,406,311.</t>
         </is>
       </c>
       <c r="K3" s="8" t="n">
-        <v>2615977</v>
+        <v>2406311</v>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method with adjustment
-IE ultimate is 2.90M with IBNR of 577K (25% development remaining). At age 275 months, this is relatively mature, but the positive IBNR warrants some credence. I applied a modest blend toward actual (2.33M) due to: (1) only one method available; (2) CL and BF unavailable create method concentration risk; (3) high year-to-year volatility in the book suggests IE model may not fully capture all risk. Selected 90% IE + 10% actual = 2.62M, balancing the method indication with empirical restraint.</t>
+          <t>Chain Ladder heavily weighted.
+At 275 months and 96.7% developed, this is highly mature. CL ($2.41M) and BF ($2.42M) are very close. IE ($2.90M) produces a large positive IBNR ($577K) that appears inconsistent with the CL/BF picture, suggesting over-reservation in the IE assumption. CL is selected given its stability and convergence with BF at this maturity.</t>
         </is>
       </c>
       <c r="M3" s="10" t="n"/>
@@ -681,29 +679,28 @@
         <v>2633272.1256</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1778091.575843999</v>
+        <v>1838114.684293428</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1778091.575843999</v>
+        <v>1864080.322749911</v>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="n">
-        <v>1778091.58</v>
+        <v>1838115</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>CL 100% (fully developed, CDF=1.0)
-Eligible methods: CL=1,778,091.58 (CDF=1.0, IBNR=0), BF=1,778,091.58 (IBNR=0). IE=2,633,272.13 screened out: ELR-based indication is 48% above actual fully-developed losses; at CDF=1.0 the actual is definitive. Maturity=263 months (Tail, 84+ mo). CL primary. Convergence: CL and BF equal actual. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Late maturity at 263 months, 0.9673 developed. CL credible and primary. Incurred Expected (2,633,272) is materially higher, suggesting prior override; however, at this maturity CL dominates. Negative IBNR of -855,181 in IE view indicates prior was too high. No diagnostic overrides applied; CL method fitness is sound. Reasonability: Selection passes checks. Case-to-ultimate appears consistent. Selection: ultimate_cl of 1,838,115.</t>
         </is>
       </c>
       <c r="K4" s="8" t="n">
-        <v>2605000</v>
+        <v>1838115</v>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method with adjustment
-IE shows 2.63M ultimate with IBNR of 855K (48% development remaining). At age 263 months, development is still meaningful. However, the large IBNR projection relative to actual (1.78M) and the absence of CL/BF cross-checks raise credibility concerns. I applied 85% IE + 15% actual to moderate the projection, yielding 2.61M. This reflects appropriate skepticism of a single-method indication without collateral support.</t>
+          <t>Chain Ladder with BF confirmation.
+At 263 months and 96.7% developed, excellent maturity. CL ($1.84M) and BF ($1.86M) are nearly identical. IE ($2.63M) shows large positive IBNR, inconsistent with CL/BF, reflecting a poor a priori loss ratio assumption. CL selected for reliability at this age.</t>
         </is>
       </c>
       <c r="M4" s="10" t="n"/>
@@ -727,29 +724,28 @@
         <v>1678710.98</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1142148.22691244</v>
+        <v>1180703.770294253</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1151324.74736037</v>
+        <v>1205205.056137874</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="n">
-        <v>1146736.49</v>
+        <v>1180704</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 1,146,736.49 (tail maturity, near-fully developed)
-Eligible methods: CL=1,142,148.23, BF=1,151,324.75. IE=1,678,711.00 screened out: IE is 47% above CL/BF at 251-month maturity â€” ELR is entirely non-credible at tail; IE receives zero weight. Maturity=251 months (Tail, 84+ mo); CDF=1.0174 (98.3% developed). CL primary (60%), BF secondary (40%) per tail weighting. Convergence check: CL and BF within 0.8% â€” passes Â±2% threshold; selecting midpoint = (1,142,148.23 + 1,151,324.75)/2 = 1,146,736.49. Asymmetric conservatism: BF is marginally higher; midpoint appropriately biases slightly upward from CL. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Late maturity at 251 months, 0.9508 developed. CL is primary method. Incurred Expected (1,678,711) diverges upward, indicating prior conservatism. CL CDF of 1.0517 is reasonable for this maturity and type. Negative IBNR in IE (-556,096) flags prior issue; CL avoids that. No diagnostic triggers. Reasonability: Selection is defensible. Paid-to-ultimate will follow natural pattern. Selection: ultimate_cl of 1,180,704.</t>
         </is>
       </c>
       <c r="K5" s="8" t="n">
-        <v>1654000</v>
+        <v>1180704</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method with downward adjustment
-IE indicates 1.68M ultimate (IBNR of 556K, 50% remaining development). Actual is 1.12M. The IBNR direction and magnitude seem reasonable, but given: (1) absence of CL/BF, (2) high volatility in surrounding years, and (3) a modest actual loss, I tempered the IE projection. Selected 75% IE + 25% actual = 1.65M, acknowledging legitimate development but capping confidence given lack of corroborating methods.</t>
+          <t>Chain Ladder as primary with Bornhuetter-Ferguson verification.
+At 251 months and 95.1% developed, maturity is high. CL ($1.18M) and BF ($1.21M) are tightly aligned. IE ($1.68M) again shows material positive IBNR inconsistent with the CL/BF consensus. The IE divergence suggests the earned exposure or base loss ratio used was overstated. CL is selected.</t>
         </is>
       </c>
       <c r="M5" s="10" t="n"/>
@@ -773,29 +769,28 @@
         <v>1712285.2</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2296902.548451221</v>
+        <v>2374439.17965539</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2282966.477415849</v>
+        <v>2337547.781384359</v>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="n">
-        <v>2289934.51</v>
+        <v>2374439</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 2,289,934.51 (tail maturity, near-fully developed)
-Eligible methods: CL=2,296,902.55, BF=2,282,966.48. IE=1,712,285.20 screened out: IE is 25% below CL at 239-month maturity; ELR non-credible at tail. Maturity=239 months (Tail, 84+ mo); CDF=1.02442 (97.6% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.6% â€” passes; midpoint = (2,296,902.55 + 2,282,966.48)/2 = 2,289,934.51. Note: IE-implied IBNR is negative (actual &gt; IE) â€” confirms IE/ELR under-calibration for this year. No data quality flags beyond IE divergence.</t>
+          <t>Method: Chain Ladder (100%). Mid-late maturity at 239 months, 0.9443 developed. CL is primary. Incurred Expected shows large negative IBNR (-529,864), indicating prior was severely overstated; CL is more credible. CDF 1.0590 is reasonable. BF (2,337,548) is close but CL is preferred at this maturity due to stability. No case adequacy concerns flagged. Reasonability: Loss ratio trend smooth. Selection: ultimate_cl of 2,374,439.</t>
         </is>
       </c>
       <c r="K6" s="8" t="n">
-        <v>2242149</v>
+        <v>2337548</v>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged)
-IE shows negative IBNR (-530K), indicating the method projects ultimate below current incurred loss of 2.24M. This is a red flag: either (a) the IE model is flawed, (b) reserves were over-held and are now developing favorably, or (c) the year has hit ceiling on reserves. Given only IE available and its negative IBNR signal, I revert to actual incurred as the best prudent choice. No development assumption beats a method flagged as likely overstated.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder confirmed as reasonable.
+At 239 months and 94.4% developed. CL ($2.37M) and BF ($2.34M) are well-aligned. IE ($1.71M) produces a large NEGATIVE IBNR (−$530K), which is a strong red flag: the earned base loss ratio assumption was too low. This suggests earned premium or loss ratio data issues. Given IE's clear failure to reserve, use BF ($2.34M) or CL ($2.37M)—selected BF to recognize the a priori calibration issue while staying near CL.</t>
         </is>
       </c>
       <c r="M6" s="10" t="n"/>
@@ -819,29 +814,28 @@
         <v>1746530.9035</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1568534.3826053</v>
+        <v>1621483.460500283</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1574310.216423582</v>
+        <v>1629492.028329561</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="n">
-        <v>1571422.3</v>
+        <v>1621483</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 1,571,422.30 (tail maturity, near-fully developed)
-Eligible methods: CL=1,568,534.38, BF=1,574,310.22. IE=1,746,530.90 screened out: IE is 11% above CL at 227-month maturity; ELR non-credible at tail. Maturity=227 months (Tail, 84+ mo); CDF=1.03354 (96.8% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.4% â€” passes; midpoint = (1,568,534.38 + 1,574,310.22)/2 = 1,571,422.30. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Mid-late maturity at 227 months, 0.9360 developed. CL dominates. Incurred Expected (1,746,531) slightly higher, reflecting prior conservatism (positive IBNR of 228,894); CL is more credible. CDF 1.0684 appropriate. No diagnostic overrides. Reasonability: Selection passes checks; loss ratio trend continues smoothly. Selection: ultimate_cl of 1,621,483.</t>
         </is>
       </c>
       <c r="K7" s="8" t="n">
-        <v>1746531</v>
+        <v>1629492</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 1.75M with modest positive IBNR of 229K (13% remaining). Actual is 1.52M. The small IBNR and relatively mature age (227 months) suggest the method is stable. The positive IBNR is credible and consistent with expected development. Selected IE ultimate = 1.75M.</t>
+          <t>Bornhuetter-Ferguson selected over Chain Ladder.
+At 227 months and 93.6% developed. CL ($1.62M) and BF ($1.63M) are very close. IE ($1.75M) shows positive IBNR, smaller than prior years but still inconsistent. The CL/BF convergence is strong, but at this maturity, BF's reliance on exposure and explicit assumptions is valued. Selected BF ($1.63M) as a slight hedge against CDF estimation volatility.</t>
         </is>
       </c>
       <c r="M7" s="10" t="n"/>
@@ -865,29 +859,28 @@
         <v>2850338.4352</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>4972115.480330334</v>
+        <v>5139959.381484465</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4903265.642420489</v>
+        <v>4993322.359472784</v>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="n">
-        <v>4937690.56</v>
+        <v>5139959</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 4,937,690.56 (tail maturity, near-fully developed)
-Eligible methods: CL=4,972,115.48, BF=4,903,265.64. IE=2,850,338.44 screened out: IE is 43% below CL â€” entirely non-credible at 215-month maturity; the ELR appears calibrated to a much lower loss level. Maturity=215 months (Tail, 84+ mo); CDF=1.03354 (96.8% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 1.4% â€” passes; midpoint = (4,972,115.48 + 4,903,265.64)/2 = 4,937,690.56. Flag: This period shows unusually elevated losses relative to adjacent years (2006: ~1.6M, 2008: ~1.4M). CL and BF both project elevated ultimates consistently, supporting the selection. The large negative IE IBNR (-1,960,436) confirms IE severely underestimates this year. Data quality flag: elevated loss year; recommend review of individual large claims.</t>
+          <t>Method: Chain Ladder (100%). Mid-late maturity at 215 months, 0.9360 developed. CL is primary. Incurred Expected (2,850,338) materially lower, with large negative IBNR (-1,960,436), indicating severe prior understatement. CL CDF of 1.0684 is stable. BF (4,993,322) is close to CL. CL is most credible; IE prior was flawed. No diagnostic overrides. Reasonability: Selection represents true exposure. Selection: ultimate_cl of 5,139,959.</t>
         </is>
       </c>
       <c r="K8" s="8" t="n">
-        <v>4810775</v>
+        <v>5139959</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with large negative IBNR)
-IE projects 2.85M ultimate (negative IBNR of -1.96M), meaning it suggests ultimate is 1.96M below actual (4.81M). This is a dramatic negative IBNR signal, likely indicating severe IE model misspecification or that the year experienced extraordinary late development reversals. With no CL/BF to cross-check and a method showing such extreme negative IBNR, I select actual incurred (4.81M) as the most defensible choice pending further investigation of this anomaly.</t>
+          <t>Chain Ladder with Bornhuetter-Ferguson confirmation.
+At 215 months and 93.6% developed. CL ($5.14M) and BF ($4.99M) are reasonably aligned (difference ~2.8%). IE ($2.85M) produces LARGE NEGATIVE IBNR (−$1.96M), which is untenable and indicates serious calibration failure in the IE model. This is likely a year of elevated loss activity; CL and BF both indicate higher development. Selected CL ($5.14M) as it is development-driven and BF confirms the magnitude.</t>
         </is>
       </c>
       <c r="M8" s="10" t="n"/>
@@ -911,29 +904,28 @@
         <v>2543927.0535</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1427506.140360434</v>
+        <v>1475694.522240827</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1465889.113446933</v>
+        <v>1546104.303039575</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="6" t="n">
-        <v>1446697.63</v>
+        <v>1475695</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>CL 55%, BF 45% â€” midpoint 1,446,697.63 (tail maturity, 3.6% residual development)
-Eligible methods: CL=1,427,506.14, BF=1,465,889.11. IE=2,543,927.05 screened out: IE is 78% above CL at 203-month maturity â€” non-credible at tail. Maturity=203 months (Tail, 84+ mo); CDF=1.03560 (96.6% developed). CL primary (55%), BF secondary (45%). CL and BF within 2.7% â€” just outside Â±2% convergence; midpoint = (1,427,506.14 + 1,465,889.11)/2 = 1,446,697.63. Asymmetric conservatism: BF is higher; midpoint biases upward from CL. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Mid-late maturity at 203 months, 0.9341 developed. CL is primary. Incurred Expected (2,543,927) shows large positive IBNR (1,165,499), indicating prior was too conservative. CL CDF 1.0706 is stable. BF (1,546,104) is close to CL. CL is most credible. No diagnostic overrides. Reasonability: Selection is sound. Selection: ultimate_cl of 1,475,695.</t>
         </is>
       </c>
       <c r="K9" s="8" t="n">
-        <v>2543927</v>
+        <v>1546104</v>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 2.54M with positive IBNR of 1.17M (46% development). Actual is 1.38M. The large IBNR suggests significant remaining development, which is plausible given age 203 months and the normal tail of loss development. The IE method is the only available indicator, and its positive IBNR aligns with expected development curves. Selected IE ultimate = 2.54M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder as secondary.
+At 203 months and 93.4% developed. CL ($1.48M) and BF ($1.55M) show a ~4.8% difference. IE ($2.54M) produces large positive IBNR ($1.17M) well above CL/BF, indicating an overstated earned base. At this maturity, both methods are credible; BF ($1.55M) is selected to reflect a measured view between explicit development (CL) and a priori exposure calibration (BF).</t>
         </is>
       </c>
       <c r="M9" s="10" t="n"/>
@@ -957,29 +949,28 @@
         <v>2594805.5945</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1220428.70585741</v>
+        <v>1261626.766498187</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1277690.378550072</v>
+        <v>1358892.734030707</v>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="6" t="n">
-        <v>1249059.54</v>
+        <v>1261627</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>CL 50%, BF 50% â€” midpoint 1,249,059.54 (tail maturity, 4.3% residual development)
-Eligible methods: CL=1,220,428.71, BF=1,277,690.38. IE=2,594,805.59 screened out: IE is 113% above CL â€” completely non-credible at 191-month maturity. Maturity=191 months (Tail, 84+ mo); CDF=1.04348 (95.8% developed). CL primary but BF retains credibility given WC long-tail adjustment (BF credible longer). CL and BF diverge by 4.7% â€” outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward moves travel farther â€” increase BF weight. Weighted = 0.50*1,220,428.71 + 0.50*1,277,690.38 = 1,249,059.54; midpoint selected as balanced conservative compromise. Flag: IE/ELR implies more than double the CL indication â€” ELR appears severely mis-calibrated for this period.</t>
+          <t>Method: Chain Ladder (100%). Mid maturity at 191 months, 0.9270 developed. CL is primary. Incurred Expected (2,594,806) shows very large positive IBNR (1,425,225), indicating severely overstated prior. CL CDF 1.0787 reasonable. BF (1,358,893) close to CL. CL method is most credible; prior needs re-examination. No diagnostic overrides. Reasonability: Selection passes checks. Selection: ultimate_cl of 1,261,627.</t>
         </is>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2594806</v>
+        <v>1358893</v>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 2.59M with positive IBNR of 1.43M (55% development). Actual is 1.17M. At age 191 months, substantial development is normal and expected. The IE method shows strong development signal. Without conflicting methods and with reasonable IBNR magnitude, I rely on IE indication. Selected IE ultimate = 2.59M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder as alternative.
+At 191 months and 92.7% developed. CL ($1.26M) and BF ($1.36M) diverge ~7.3%, with BF higher. IE ($2.59M) shows excessive positive IBNR. The higher BF indicates potential under-development in the CL tail. At this maturity, both are credible; selected BF ($1.36M) as it incorporates a priori premium/exposure and tempers reliance on potentially unstable tail development.</t>
         </is>
       </c>
       <c r="M10" s="10" t="n"/>
@@ -1003,29 +994,28 @@
         <v>1134300.7311</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1338018.539666638</v>
+        <v>1383186.085030906</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1328830.587656843</v>
+        <v>1364200.286416272</v>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="6" t="n">
-        <v>1333424.57</v>
+        <v>1383186</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 1,333,424.57 (tail maturity, 4.7% residual development)
-Eligible methods: CL=1,338,018.54, BF=1,328,830.59. IE=1,134,300.73 screened out: IE is 15% below CL at 179-month maturity; ELR non-credible at tail. Maturity=179 months (Tail, 84+ mo); CDF=1.04723 (95.5% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.7% â€” passes; midpoint = (1,338,018.54 + 1,328,830.59)/2 = 1,333,424.57. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Mid maturity at 179 months, 0.9237 developed. CL is primary. Incurred Expected (1,134,301) shows negative IBNR (-143,371), indicating prior was too high. CL CDF 1.0826 stable. BF (1,364,200) very close to CL. CL is most credible at this maturity. No diagnostic overrides. Reasonability: Selection passes checks. Selection: ultimate_cl of 1,383,186.</t>
         </is>
       </c>
       <c r="K11" s="8" t="n">
-        <v>1277672</v>
+        <v>1383186</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with negative IBNR)
-IE shows negative IBNR (-143K), projecting ultimate (1.13M) below actual (1.28M). This negative signal is smaller in magnitude than 2007 but still a red flag. At age 179 months, some development is expected. However, the IE model signaling contraction below actual suggests either model breakdown or exceptional reserve adequacy. I conservatively select actual incurred = 1.28M.</t>
+          <t>Chain Ladder selected; Bornhuetter-Ferguson cross-check.
+At 179 months and 92.4% developed. CL ($1.38M) and BF ($1.36M) are very close. IE ($1.13M) produces NEGATIVE IBNR (−$143K), replicating the pattern seen in 2005, 2007, and 2011. The IE method's persistent negative IBNR across diverse years confirms systematic bias in its assumptions. CL selected for simplicity and development-driven reliability at this maturity.</t>
         </is>
       </c>
       <c r="M11" s="10" t="n"/>
@@ -1049,29 +1039,28 @@
         <v>1542648.9944</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2048919.998187436</v>
+        <v>2118085.472523049</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2016096.735607065</v>
+        <v>2063205.530353971</v>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="6" t="n">
-        <v>2032508.37</v>
+        <v>2118085</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 2,032,508.37 (tail maturity, 6.9% residual development)
-Eligible methods: CL=2,048,920.00, BF=2,016,096.74. IE=1,542,649.00 screened out: IE is 25% below CL at 167-month maturity; non-credible at tail. Maturity=167 months (Tail, 84+ mo); CDF=1.06933 (93.5% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 1.6% â€” passes; midpoint = (2,048,920.00 + 2,016,096.74)/2 = 2,032,508.37. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Mid maturity at 167 months, 0.9046 developed. CL is primary. Incurred Expected (1,542,649) shows negative IBNR (-373,433), indicating prior was too high. CL CDF 1.1054 slightly elevated but reasonable. BF (2,063,206) close to CL. CL is most credible. No diagnostic overrides. Reasonability: Selection passes. Selection: ultimate_cl of 2,118,085.</t>
         </is>
       </c>
       <c r="K12" s="8" t="n">
-        <v>1916082</v>
+        <v>2063206</v>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with negative IBNR)
-IE projects 1.54M ultimate with negative IBNR (-373K), indicating ultimate is projected below the actual 1.92M. The negative signal, despite reasonable maturity (age 167), is a warning that the IE method is not credible for this year. I select actual incurred (1.92M) = 1.92M, pending investigation of the IE model's validity for this cohort.</t>
+          <t>Bornhuetter-Ferguson selected as primary; Chain Ladder as reference.
+At 167 months and 90.5% developed, still high maturity. CL ($2.12M) and BF ($2.06M) are ~2.6% apart. IE ($1.54M) produces NEGATIVE IBNR (−$373K), yet another red flag in the IE pattern. The CL/BF consensus is strong; BF ($2.06M) is selected to balance between development indication and a priori exposure, with CL confirming the direction.</t>
         </is>
       </c>
       <c r="M12" s="10" t="n"/>
@@ -1095,29 +1084,28 @@
         <v>1573501.9744</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1458883.218318097</v>
+        <v>1508130.79747419</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1466357.198096881</v>
+        <v>1514388.956038969</v>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="6" t="n">
-        <v>1462620.21</v>
+        <v>1508131</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>CL 60%, BF 40% â€” midpoint 1,462,620.21 (tail maturity, 7.0% residual development)
-Eligible methods: CL=1,458,883.22, BF=1,466,357.20. IE=1,573,501.97 screened out: IE is 7.7% above CL at 155-month maturity; ELR carries no weight at tail. Maturity=155 months (Tail, 84+ mo); CDF=1.06976 (93.5% developed). CL primary (60%), BF secondary (40%). Convergence check: CL and BF within 0.5% â€” passes; midpoint = (1,458,883.22 + 1,466,357.20)/2 = 1,462,620.21. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Mid maturity at 155 months, 0.9043 developed. CL is primary. Incurred Expected (1,573,502) shows positive IBNR (209,749), indicating prior was slightly conservative. CL CDF 1.1059 reasonable. BF (1,514,389) very close to CL. CL is most credible at this maturity. No diagnostic overrides. Reasonability: Selection passes. Selection: ultimate_cl of 1,508,131.</t>
         </is>
       </c>
       <c r="K13" s="8" t="n">
-        <v>1573502</v>
+        <v>1514389</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 1.57M with modest positive IBNR of 210K (13% development). Actual is 1.36M. The small IBNR is credible, and the IE method shows stability. At age 155 months, the year is reasonably mature. Selected IE ultimate = 1.57M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder confirmed.
+At 155 months and 90.4% developed. CL ($1.51M) and BF ($1.51M) converge exactly to $1.51M. IE ($1.57M) shows positive IBNR ($210K), which is reasonable at this maturity. However, the tight CL/BF alignment is compelling. Selected BF ($1.51M) as all methods agree; either CL or BF is defensible.</t>
         </is>
       </c>
       <c r="M13" s="10" t="n"/>
@@ -1141,29 +1129,28 @@
         <v>1203729.0102</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>759621.6336900741</v>
+        <v>785264.2115634154</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>789491.9986882674</v>
+        <v>826155.6335107618</v>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="6" t="n">
-        <v>774556.8199999999</v>
+        <v>785264</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>CL 50%, BF 50% â€” midpoint 774,556.82 (tail maturity, 7.2% residual development)
-Eligible methods: CL=759,621.63, BF=789,492.00. IE=1,203,729.01 screened out: IE is 58% above CL at 143-month maturity â€” completely non-credible at tail. Maturity=143 months (Tail, 84+ mo); CDF=1.07211 (93.3% developed). CL and BF diverge by 3.9% â€” outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward moves travel farther â€” equal weight applied as compromise. Midpoint = (759,621.63 + 789,492.00)/2 = 774,556.82. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Early-mid maturity at 143 months, 0.9023 developed. CL is primary at this point. Incurred Expected (1,203,729) shows large positive IBNR (495,199), indicating prior was overstated. CL CDF 1.1083 reasonable. BF (826,156) close to CL. CL is most credible; prior needs adjustment. No diagnostic overrides. Reasonability: Selection passes checks. Selection: ultimate_cl of 785,264.</t>
         </is>
       </c>
       <c r="K14" s="8" t="n">
-        <v>1203729</v>
+        <v>826156</v>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 1.20M with positive IBNR of 495K (41% development). Actual is 0.71M. At age 143 months, substantial development remains expected. The IBNR magnitude is consistent with typical patterns at this maturity. IE is the sole indicator. Selected IE ultimate = 1.20M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder as alternative.
+At 143 months and 90.2% developed. CL ($0.79M) and BF ($0.83M) diverge ~5.2%, with BF higher. IE ($1.20M) shows substantial positive IBNR ($495K), inconsistent with CL/BF. The CL/BF split is small relative to maturity; selected BF ($0.83M) as it moderates CL's lower indication with exposure-based judgment.</t>
         </is>
       </c>
       <c r="M14" s="10" t="n"/>
@@ -1187,29 +1174,28 @@
         <v>1227803.5905</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1541950.363446178</v>
+        <v>1594002.043543045</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1510912.258315372</v>
+        <v>1547044.536114278</v>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="6" t="n">
-        <v>1526431.31</v>
+        <v>1594002</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>CL 55%, BF 45% â€” midpoint 1,526,431.31 (tail maturity, 11.0% residual development)
-Eligible methods: CL=1,541,950.36, BF=1,510,912.26. IE=1,227,803.59 screened out: IE is 20% below CL at 131-month maturity; non-credible at tail. Maturity=131 months (Tail, 84+ mo); CDF=1.10963 (90.1% developed). CL primary (55%), BF secondary (45%). Convergence check: CL and BF within 2.0% â€” at boundary; midpoint = (1,541,950.36 + 1,510,912.26)/2 = 1,526,431.31. No data quality flags.</t>
+          <t>Method: Chain Ladder (100%). Early maturity at 131 months, 0.8718 developed. Transitioning to CL-primary from BF; CL CDF 1.1471 is elevated but credible given only 87% developed. Incurred Expected (1,227,804) shows negative IBNR (-161,800), indicating prior was too high. BF (1,547,045) close to CL. CL is primary but elevated CDF warrants watch. Reasonability: Selection is sound. Selection: ultimate_cl of 1,594,002.</t>
         </is>
       </c>
       <c r="K15" s="8" t="n">
-        <v>1389604</v>
+        <v>1594002</v>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with negative IBNR)
-IE projects 1.23M ultimate with negative IBNR (-162K), below actual 1.39M. The negative signal, though modest in magnitude, indicates IE model misalignment. At age 131 months with expected development ahead, the reversal to actual is prudent. Selected actual incurred = 1.39M.</t>
+          <t>Chain Ladder selected; Bornhuetter-Ferguson cross-check.
+At 131 months and 87.2% developed. CL ($1.59M) and BF ($1.55M) are close (~2.5%). IE ($1.23M) produces NEGATIVE IBNR (−$162K), again inconsistent with CL/BF's higher development indication. The CL/BF consensus at 87% maturity is credible; selected CL ($1.59M) for development-driven clarity.</t>
         </is>
       </c>
       <c r="M15" s="10" t="n"/>
@@ -1233,29 +1219,28 @@
         <v>1669812.8832</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3784629.852947765</v>
+        <v>3912387.754278917</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3560182.188573404</v>
+        <v>3608922.416514333</v>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="6" t="n">
-        <v>3672406.02</v>
+        <v>3912388</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>CL 55%, BF 45% â€” midpoint 3,672,406.02 (tail maturity, 11.9% residual development)
-Eligible methods: CL=3,784,629.85, BF=3,560,182.19. IE=1,669,812.88 screened out: IE is 56% below CL at 119-month maturity â€” entirely non-credible at tail (ELR severely under-calibrated for this year). Maturity=119 months (Tail, 84+ mo); CDF=1.11873 (89.4% developed). CL primary (55%), BF secondary (45%). CL and BF diverge by 6.3% â€” outside Â±2% convergence. Asymmetric conservatism: CL is higher; upward moves travel farther â€” CL weight maintained at 55%. Midpoint = (3,784,629.85 + 3,560,182.19)/2 = 3,672,406.02. Flag: This period shows notably elevated losses (CL 3.78M vs. neighbors 2014: 1.54M, 2016: 2.96M). CL and BF both confirm elevated ultimate; IE/ELR provides no plausible alternative. Recommend review of large individual claims. The large negative IE IBNR (-1,713,150) confirms IE grossly underestimates this year.</t>
+          <t>Method: Chain Ladder (100%). Early maturity at 119 months, 0.8647 developed. CL CDF 1.1565 elevated (only 86.5% developed). Incurred Expected (1,669,813) shows large negative IBNR (-1,713,150), indicating severely overstated prior. This signals case adequacy concerns. CL is more credible than IE despite elevated CDF. BF (3,608,922) closer to CL. However, CL at this immaturity (86.5% developed) with high CDF warrants Bayesian anchoring: move 50% of gap between IE and CL. Midpoint: ~2,790,600. But CL multi-period credibility and IE breakdown argue for CL. Selection: ultimate_cl of 3,912,388. Flag: High CDF and negative IE IBNR warrant next-study scrutiny of case adequacy.</t>
         </is>
       </c>
       <c r="K16" s="8" t="n">
-        <v>3382963</v>
+        <v>3608922</v>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method critically flagged with large negative IBNR)
-IE projects 1.67M ultimate with massive negative IBNR (-1.71M), implying IE estimates are 1.71M below the actual 3.38M. This is an extreme model failure signal (50% negative IBNR). Given this critical red flag and lack of CL/BF support, I revert to actual incurred (3.38M) as the only defensible selection. The IE model is clearly unreliable for this year.</t>
+          <t>Bornhuetter-Ferguson selected over Chain Ladder.
+At 119 months and 86.5% developed. CL ($3.91M) and BF ($3.61M) diverge ~8.1%, with CL higher. IE ($1.67M) produces LARGE NEGATIVE IBNR (−$1.71M), rendering IE non-credible. This is a higher-loss year; CL's CDF (1.156) implies strong tail development. Maturity is moderate; selected BF ($3.61M) to temper CL's optimistic tail and avoid over-reserving on high-volatility years, while staying well above IE.</t>
         </is>
       </c>
       <c r="M16" s="10" t="n"/>
@@ -1279,29 +1264,28 @@
         <v>2554813.7112</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2963166.706442132</v>
+        <v>3039136.425044341</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2900209.319415499</v>
+        <v>2954226.339973489</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="6" t="n">
-        <v>2931688.02</v>
+        <v>3039136</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>CL 55%, BF 45% â€” midpoint 2,931,688.02 (tail maturity, 18.2% residual development)
-Eligible methods: CL=2,963,166.71, BF=2,900,209.32. IE=2,554,813.71 screened out: IE is 14% below CL at 107-month maturity; ELR non-credible at tail. Maturity=107 months (Tail, 84+ mo); CDF=1.18228 (84.6% developed). CL primary (55%), BF secondary (45%). Convergence check: CL and BF within 2.2% â€” just outside Â±2% threshold; midpoint = (2,963,166.71 + 2,900,209.32)/2 = 2,931,688.02. Asymmetric conservatism: CL is higher; midpoint appropriately biases upward. No data quality flags.</t>
+          <t>Method: Chain Ladder (85%) + Bornhuetter-Ferguson (15%). Early maturity at 107 months, 0.8247 developed. CL CDF 1.2126 is materially elevated due to low maturity. Incurred Expected (2,554,814) shows positive IBNR (48,490), indicating prior was reasonable. BF (2,954,226) is significantly lower than CL (3,039,136). Large dispersion (3.0%) between CL and BF at this maturity argues for CL primacy per method fitness, but BF weight of 15% reflects immaturity caution. CL methodology dominates incurred triangles; CDF credibility intact. Reasonability: Selection reflects high CDF credibility. Selection: ultimate_cl of 3,039,136.</t>
         </is>
       </c>
       <c r="K17" s="8" t="n">
-        <v>2554814</v>
+        <v>2954226</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 2.55M with small positive IBNR of 48K (2% development). Actual is 2.51M. IE and actual are nearly aligned, suggesting method stability and limited remaining development. At age 107 months, maturity is high. Selected IE ultimate = 2.55M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder as secondary.
+At 107 months and 82.5% developed, maturity drops below 85%. CL ($3.04M) and BF ($2.95M) are close (~2.9%). IE ($2.55M) shows modest positive IBNR ($48K), the smallest positive amount yet. At lower maturity, BF's explicit assumptions become more valuable; selected BF ($2.95M) to balance CL's development indication with a priori calibration.</t>
         </is>
       </c>
       <c r="M17" s="10" t="n"/>
@@ -1325,29 +1309,28 @@
         <v>2605909.9854</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1446416.383083455</v>
+        <v>1483499.631003856</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1639292.683786481</v>
+        <v>1693597.198835409</v>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="6" t="n">
-        <v>1542854.53</v>
+        <v>1483500</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>CL 45%, BF 55% â€” midpoint 1,542,854.53 (tail/late boundary, 20.0% residual development)
-Eligible methods: CL=1,446,416.38, BF=1,639,292.68. IE=2,605,909.99 screened out: IE is 80% above CL at 95-month maturity â€” entirely non-credible; the ELR is clearly not representative of this year's actual loss level. Maturity=95 months (Tail, 84+ mo per framework); CDF=1.19954 (83.4% developed). At 95 months with significant residual development (20%), WC long-tail adjustment increases BF weight: BF primary (55%), CL secondary (45%). CL and BF diverge by 13.3% â€” well outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward moves travel farther â€” BF weight maintained at 55%. Weighted = 0.45*1,446,416.38 + 0.55*1,639,292.68 = 650,887.37 + 901,611.0 = 1,552,498; midpoint = (1,446,416.38 + 1,639,292.68)/2 = 1,542,854.53. Selecting midpoint for balance; midpoint is between weighted (1,552,498) and CL-weighted (1,543K). Flag: IE implies 2.6M ultimate vs CL 1.45M â€” very large ELR divergence; ELR excluded.</t>
+          <t>Method: Chain Ladder (70%) + Bornhuetter-Ferguson (30%). Green maturity at 95 months, 0.8128 developed (only ~81% reported). CL CDF 1.2303 is high, warranting BF weight increase to 30%. Incurred Expected (2,605,910) shows large positive IBNR (1,400,098), indicating prior well overstated. CL (1,483,500) and BF (1,693,597) show 12.4% dispersion; not converged. CL is favored per incurred method fitness; prior issue in IE supports downward movement. Baseline maturity weights: CL 70%, BF 30%. Blend: 0.70 * 1,483,500 + 0.30 * 1,693,597 = 1,548,218. Bayesian anchoring to no prior: selection is 1,483,500 (CL-biased due to credible CDF and IE prior breakdown). Reasonability: Selection passes. Selection: 1,483,500.</t>
         </is>
       </c>
       <c r="K18" s="8" t="n">
-        <v>2605910</v>
+        <v>1693597</v>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method
-IE ultimate 2.61M with positive IBNR of 1.40M (54% development). Actual is 1.21M. At age 95 months, substantial development is expected. The IBNR represents a meaningful projection (116% above actual), but at this immaturity it is plausible. Without conflicting methods, I rely on IE. Selected IE ultimate = 2.61M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder alternative considered.
+At 95 months and 81.3% developed, maturity is moderate-low. CL ($1.48M) and BF ($1.69M) diverge ~12.4%, a notable split. IE ($2.61M) shows large positive IBNR ($1.40M), suggesting an underreserved a priori base. CL's high CDF (1.230) may be inflated by limited development. Selected BF ($1.69M) as the lower maturity and divergence between CL/BF favor explicit exposure assumptions over tail extrapolation.</t>
         </is>
       </c>
       <c r="M18" s="10" t="n"/>
@@ -1371,29 +1354,28 @@
         <v>2215023.4875</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2895268.035190428</v>
+        <v>2966255.157584634</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2777835.189014538</v>
+        <v>2821693.050311851</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="6" t="n">
-        <v>2836551.62</v>
+        <v>2966255</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>CL 50%, BF 50% â€” midpoint 2,836,551.62 (late maturity, 20.9% residual development)
-Eligible methods: CL=2,895,268.04, BF=2,777,835.19. IE=2,215,023.49 screened out: IE is 23% below CL at 83-month maturity; ELR non-credible at late maturity. Maturity=83 months (Late, 60-84 mo); CDF=1.20865 (82.7% developed). Per late maturity table, CL is primary and BF is secondary; at the upper boundary of late (83 months), BF retains meaningful weight. CL and BF diverge by 4.2% â€” outside Â±2%. Asymmetric conservatism: CL is higher; upward bias applied, equal weighting as compromise. Midpoint = (2,895,268.04 + 2,777,835.19)/2 = 2,836,551.62. No data quality flags.</t>
+          <t>Method: Chain Ladder (65%) + Bornhuetter-Ferguson (35%). Green maturity at 83 months, 0.8076 developed. CL CDF 1.2383 is high; BF weight increased to 35%. Incurred Expected (2,215,023) shows negative IBNR (-180,425), indicating prior was too high. CL (2,966,255) and BF (2,821,693) show 5.1% dispersion; not converged. CL is favored per incurred method fitness. Blend: 0.65 * 2,966,255 + 0.35 * 2,821,693 = 2,911,821. However, CL credibility is strong; selection toward CL: 2,966,255. Prior IE was overstated; downward movement justified by IE breakdown. Reasonability: Selection passes. Selection: 2,966,255.</t>
         </is>
       </c>
       <c r="K19" s="8" t="n">
-        <v>2395448</v>
+        <v>2821693</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with modest negative IBNR)
-IE projects 2.22M ultimate with negative IBNR (-180K), below actual 2.40M. At age 83 months, development is still expected, but the IE method's contraction signal relative to actual is concerning. The negative IBNR, while smaller in percentage than 2015/2007, signals model unreliability. I conservatively select actual incurred = 2.40M.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder as verification.
+At 83 months and 80.8% developed, maturity continues to decline. CL ($2.97M) and BF ($2.82M) differ ~5.0%, with CL higher. IE ($2.22M) produces NEGATIVE IBNR (−$180K), returning to IE's problematic pattern. BF ($2.82M) is selected for its balance between development and a priori calibration at this lower maturity; CL confirms the general magnitude.</t>
         </is>
       </c>
       <c r="M19" s="10" t="n"/>
@@ -1417,29 +1399,28 @@
         <v>2259323.9575</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3415743.719855753</v>
+        <v>3499492.034195393</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3139529.318974986</v>
+        <v>3180683.889838104</v>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="6" t="n">
-        <v>3277636.52</v>
+        <v>3180684</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>CL 40%, BF 60% â€” midpoint 3,277,636.52 (late maturity, 31.4% residual development)
-Eligible methods: CL=3,415,743.72, BF=3,139,529.32. IE=2,259,323.96 screened out: IE is 34% below CL at 71-month maturity; ELR non-credible at late maturity. Maturity=71 months (Late, 60-84 mo); CDF=1.31381 (76.1% developed). At 71 months with 31% residual development, WC long-tail adjustment gives BF primary weight (60%), CL secondary (40%). CL and BF diverge by 8.8% â€” outside Â±2% convergence. Asymmetric conservatism: CL is higher; upward bias applied but BF credibility limits full CL reliance. Midpoint = (3,415,743.72 + 3,139,529.32)/2 = 3,277,636.52. No data quality flags.</t>
+          <t>Method: Bornhuetter-Ferguson (60%) + Chain Ladder (40%). Green maturity at 71 months, 0.7429 developed. CL CDF 1.3460 is very high (only 74% developed). Baseline maturity argues for BF weight increase to 60% due to low development. Incurred Expected (2,259,324) shows negative IBNR (-340,559), indicating prior too high. CL (3,499,492) and BF (3,180,684) show 10.0% dispersion; partial convergence threshold. CL is elevated by high CDF; BF is more credible at this immaturity. Blend: 0.40 * 3,499,492 + 0.60 * 3,180,684 = 3,306,766. Selection moderates upward from BF alone due to CL credibility at this maturity. Reasonability: Selection passes. Selection: 3,306,766. Conservative at immaturity. Adjusted to 3,180,684 (BF-biased, 60% weight) to reflect immaturity caution and IE prior breakdown.</t>
         </is>
       </c>
       <c r="K20" s="8" t="n">
-        <v>2599883</v>
+        <v>3180684</v>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with negative IBNR)
-IE projects 2.26M ultimate with negative IBNR (-341K), below actual 2.60M. At age 71 months, this is a mid-immature year where development is important, but IE projecting below actual is a credibility signal failure. I select actual incurred (2.60M) as the safer choice given the IE method's negative flag.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder cautioned.
+At 71 months and 74.3% developed, maturity is moderate-low. CL ($3.50M) and BF ($3.18M) diverge ~9.8%, with CL's CDF (1.346) suggesting strong tail. IE ($2.26M) shows NEGATIVE IBNR (−$341K). CL's high CDF is less credible at 74% development given the sparse tail data. Selected BF ($3.18M) to balance development indication with earned exposure—a more conservative but defensible pick than CL's optimistic tail extrapolation.</t>
         </is>
       </c>
       <c r="M20" s="10" t="n"/>
@@ -1463,29 +1444,28 @@
         <v>1843608.3492</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1418165.71126218</v>
+        <v>1452936.758950002</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1549943.380235656</v>
+        <v>1580397.837315658</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="6" t="n">
-        <v>1484054.54</v>
+        <v>1580398</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>CL 35%, BF 65% â€” midpoint 1,484,054.54 (mid maturity, 31.0% residual development)
-Eligible methods: CL=1,418,165.71, BF=1,549,943.38. IE=1,843,608.35 (secondary, limited weight). Maturity=59 months (Mid, 36-60 mo); CDF=1.44873 (69.0% developed). At mid maturity, CL is primary per framework; however WC long-tail adjustment shifts BF credibility later â€” BF retains substantial weight (65%), CL secondary (35%). IE is 30% above CL and 19% above BF; IE receives minimal weight at mid maturity. CL and BF diverge by 9.3% â€” outside Â±2% convergence. Asymmetric conservatism: BF is higher; upward bias favors BF. Midpoint = (1,418,165.71 + 1,549,943.38)/2 = 1,484,054.54. Reasonability: 2020 losses appear low relative to neighbors (2019: 3.28M, 2021: 1.51M); possible COVID-19 impact on claim activity â€” consistent with observed pattern. No data quality flags.</t>
+          <t>Method: Bornhuetter-Ferguson (70%) + Incurred Expected (30%). Very green maturity at 59 months, 0.6737 developed. CL CDF 1.4843 is very high; CL credibility is low at only 67% reported. BF is primary (70%). Incurred Expected (1,843,608) shows large positive IBNR (864,709), indicating prior overstated. CL (1,452,937) is materially lower. Dispersion: 21.3% between CL and BF; large spread warrants caution. BF (1,580,398) is preferred given immaturity and IE prior issue. Blend: 0.70 * 1,580,398 + 0.30 * 1,843,608 = 1,670,301. Selection stays with BF due to greater credibility at immaturity. Reasonability: Selection passes. Selection: 1,580,398.</t>
         </is>
       </c>
       <c r="K21" s="8" t="n">
-        <v>1843608</v>
+        <v>1580398</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method with modest confidence
-IE ultimate 1.84M with positive IBNR of 865K (47% development). Actual is 0.98M. At age 59 months, the year is moderately immature and development is clearly expected. IE projects 88% growth above actual. At this immaturity, single-method reliance is heightened risk, but the positive IBNR direction is at least credible. Selected IE ultimate = 1.84M, with a note that this is a high-uncertainty selection due to immaturity and method concentration.</t>
+          <t>Bornhuetter-Ferguson selected over Chain Ladder.
+At 59 months and 67.4% developed, maturity is low. CL ($1.45M) and BF ($1.58M) are close (~8.2%), but CL's CDF (1.484) is elevated and potentially unstable at only 67% development. IE ($1.84M) shows large positive IBNR ($865K), over-reserving relative to CL/BF. Selected BF ($1.58M) to weight the earned exposure base more heavily when tail factors are uncertain; CL's higher CDF is less trustworthy here.</t>
         </is>
       </c>
       <c r="M21" s="10" t="n"/>
@@ -1509,29 +1489,28 @@
         <v>1410360.3873</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1536183.212096232</v>
+        <v>1586156.437175669</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1493193.146184722</v>
+        <v>1522445.724910811</v>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="n">
-        <v>1514688.18</v>
+        <v>1522446</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>CL 35%, BF 65% â€” midpoint 1,514,688.18 (mid maturity, 34.2% residual development)
-Eligible methods: CL=1,536,183.21, BF=1,493,193.15. IE=1,410,360.39 (secondary, limited weight at this maturity). Maturity=47 months (Mid, 36-60 mo); CDF=1.51900 (65.8% developed). WC long-tail: BF retains primary weight (65%), CL secondary (35%). IE is 8.2% below CL â€” minor divergence; IE receives no material weight. CL and BF within 2.9% â€” near convergence boundary. Midpoint = (1,536,183.21 + 1,493,193.15)/2 = 1,514,688.18. Asymmetric conservatism: CL is marginally higher; midpoint appropriate. No data quality flags.</t>
+          <t>Method: Bornhuetter-Ferguson (70%) + Incurred Expected (30%). Very green maturity at 47 months, 0.6376 developed. CL CDF 1.5684 is very high; CL credibility low. BF is primary (70%). Incurred Expected (1,410,360) shows large positive IBNR (399,047), indicating prior overstated but less severely than 2020. CL (1,586,156) is moderately higher. Dispersion: 12.4%; BF and IE more aligned than with CL. BF (1,522,446) is preferred. Blend: 0.70 * 1,522,446 + 0.30 * 1,410,360 = 1,489,351. Selection stays with BF. Reasonability: Selection passes. Selection: 1,522,446.</t>
         </is>
       </c>
       <c r="K22" s="8" t="n">
-        <v>1410360</v>
+        <v>1522446</v>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method with caution
-IE ultimate 1.41M with positive IBNR of 399K (39% development). Actual is 1.01M. At age 47 months, immaturity is substantial. IE projects 39% growth. Without CL/BF for validation and given high immaturity, confidence is limited, but the positive IBNR direction is the only signal available. Selected IE ultimate = 1.41M, flagged as high-uncertainty for next study.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder not favored.
+At 47 months and 63.8% developed, maturity is notably low. CL ($1.59M) and BF ($1.52M) differ ~4.6%. IE ($1.41M) shows reasonable positive IBNR ($399K). CL's CDF (1.568) extrapolates from very little tail development. At &lt;64% development, explicit exposure assumptions (BF) are more credible than high CDFs from sparse data. Selected BF ($1.52M).</t>
         </is>
       </c>
       <c r="M22" s="10" t="n"/>
@@ -1555,29 +1534,28 @@
         <v>959045.0632000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1508463.818331517</v>
+        <v>1531321.168115382</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1260409.883332667</v>
+        <v>1268262.016843523</v>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="n">
-        <v>1384436.85</v>
+        <v>1268262</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>BF 70%, CL 30% â€” midpoint 1,384,436.85 (early maturity, 45.1% residual development)
-Eligible methods: CL=1,508,463.82, BF=1,260,409.88. IE=959,045.06 screened out: IE is 36% below CL at 35-month maturity â€” IE/ELR appears severely under-calibrated for this year and receives no weight. Maturity=35 months (Early, 24-36 mo); CDF=1.82310 (54.9% developed). Per early maturity table, BF/CL/Benktander are eligible; BF gets primary weight (70%) and CL secondary (30%) for WC long-tail. At 45% IBNR proportion, CL is applying significant tail leverage â€” BF moderates through ELR blend. CL and BF diverge by 19.7% â€” large gap expected at early maturity. Asymmetric conservatism: CL is higher; upward bias extends selection toward CL. Midpoint = (1,508,463.82 + 1,260,409.88)/2 = 1,384,436.85. Midpoint applies upward asymmetric conservatism over pure BF while respecting BF's stabilizing role. Flag: Large CL-BF divergence is expected at this maturity; selection is appropriately moderate.</t>
+          <t>Method: Bornhuetter-Ferguson (80%) + A Priori / Incurred Expected (20%). Very green maturity at 35 months, 0.5403 developed. CL CDF 1.8507 is extremely high; CL is unreliable (only 54% developed). BF is primary (80%). Incurred Expected (959,045) shows positive IBNR (131,629), indicating prior reasonable. CL (1,531,321) is notably higher. Dispersion: 21.4%. BF (1,268,262) is most credible. Blend: 0.80 * 1,268,262 + 0.20 * 959,045 = 1,192,690. Selection stays with BF to reflect immaturity and IE credibility. However, given very green status and elevated CL CDF, conservative bias toward lower BF value: 1,268,262. Reasonability: Selection passes. Selection: 1,268,262.</t>
         </is>
       </c>
       <c r="K23" s="8" t="n">
-        <v>959045</v>
+        <v>1268262</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Incurred Expense (IE) method with caution
-IE ultimate 0.96M with positive IBNR of 132K (14% development). Actual is 0.83M. At age 35 months, the year is very immature. IE projects modest 16% growth. The small IBNR relative to actual suggests the projection is conservative, which is appropriate at this early age. Selected IE ultimate = 0.96M, understanding that significant tail development may emerge.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder significantly elevated.
+At 35 months and 54.0% developed, maturity is low. CL ($1.53M) and BF ($1.27M) diverge ~20.5%, a large gap. IE ($0.96M) shows modest positive IBNR ($132K). CL's extremely high CDF (1.851) is unreliable at 54% development—this reflects tail inflation from sparse data and potential volatility. Selected BF ($1.27M) as the more measured indication using earned premium/exposure basis, well above IE but below CL's inflated CDF.</t>
         </is>
       </c>
       <c r="M23" s="10" t="n"/>
@@ -1601,29 +1579,28 @@
         <v>978225.9646000001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>3786735.674620079</v>
+        <v>3729479.431733147</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>2203284.975082291</v>
+        <v>2196734.166711039</v>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="6" t="n">
-        <v>2203284.98</v>
+        <v>2196734</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>BF 85%, IE 15% â€” BF-anchored selection 2,203,284.98 (green maturity, CL heavily leveraged)
-Eligible methods: BF=2,203,284.98 (primary), IE=978,225.96 (secondary). CL=3,786,735.67 assigned minimal weight: at 23-month maturity with CDF=2.29 (only 43.6% developed), CL is highly leveraged â€” small link ratio changes produce very large swings; CL receives near-zero weight (5%). Per green maturity table (12-24 mo), BF is primary and CL is secondary; for WC long-tail, shift further to BF. IE diverges from BF by 55% downward â€” IE/ELR appears under-calibrated for this year. BF embeds the ELR structure while crediting observed development. Weighted blend: 0.85*2,203,284.98 + 0.15*978,225.96 = 1,872,792.23 + 146,733.89 = 2,019,526.12; however, BF at 2.20M already reflects the IE-CL blend â€” selecting BF as the anchor provides the most actuarially sound result. Asymmetric conservatism: BF well above IE; no downward adjustment. Selection = BF = 2,203,284.98. Flag: CL indication (3.79M) is 72% above BF; absent diagnostic confirmation of link ratio stability, CL is not credible at this maturity. Recommend re-evaluation at next diagonal.</t>
+          <t>Method: Bornhuetter-Ferguson (85%) + A Priori / Incurred Expected (15%). Sparse period at 23 months, 0.4429 developed. CL CDF 2.2579 is extremely elevated; CL is noise at only 44% developed. BF is dominant (85%). Incurred Expected (978,226) shows large negative IBNR (-673,531), indicating prior was severely overstated; IE prior requires re-examination. CL (3,729,479) is implausibly high due to CDF distortion. BF (2,196,734) is most credible. Blend: 0.85 * 2,196,734 + 0.15 * 978,226 = 2,012,768. Selection: BF-dominant (2,196,734). IE prior is unreliable at this sparse age; BF with external a priori is preferred. Reasonability: Selection passes immaturity checks. Flag: IE prior estimation needs review for 2023 cohort. Selection: 2,196,734.</t>
         </is>
       </c>
       <c r="K24" s="8" t="n">
-        <v>1651757</v>
+        <v>2196734</v>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE method flagged with negative IBNR at extreme immaturity)
-IE projects 0.98M ultimate with negative IBNR (-674K), below actual 1.65M. This is problematic: at age 23 months (extremely immature), the method projects contraction below actual, which violates normal development expectations. This negative IBNR is a critical red flag at extreme immaturity. I conservatively revert to actual incurred (1.65M) pending further data.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder not credible at this immaturity.
+At 23 months and 44.3% developed, maturity is very low. CL ($3.73M) and BF ($2.20M) diverge ~69.7%, a massive gap. IE ($0.98M) shows NEGATIVE IBNR (−$674K). CL's CDF (2.258) is extreme and not credible at only 44% development—this is tail extrapolation noise. Selected BF ($2.20M) as the only defensible method using earned exposure; CL is rejected for being based on insufficient development.</t>
         </is>
       </c>
       <c r="M24" s="10" t="n"/>
@@ -1647,29 +1624,28 @@
         <v>997790.4837999999</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3474131.677955018</v>
+        <v>3316284.904411623</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1632288.035804825</v>
+        <v>1620119.377358282</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="6" t="n">
-        <v>1315039.26</v>
+        <v>1620119</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>IE 50%, BF 50% â€” midpoint 1,315,039.26 (very green maturity, CL excluded)
-Eligible methods: IE=997,790.48, BF=1,632,288.04. CL=3,474,131.68 excluded: CDF=3.90 with only 25.6% developed â€” CL is entirely unreliable at 11-month maturity; a single immature link ratio drives an implausible ultimate. Per very green maturity table (0-12 mo), a priori/IE and BF are primary and CL is zero weight. IE and BF diverge by 63.6%. BF at 11 months embeds heavy CL reliance (inverse complement of 25.6% development) â€” BF is also subject to high uncertainty. Bayesian dampening: absent prior, moderate the spread. Asymmetric conservatism: upward moves travel farther â€” BF is higher, maintain 50% BF weight rather than dampening toward pure IE. Midpoint = (997,790.48 + 1,632,288.04)/2 = 1,315,039.26. Flag: Extremely immature year â€” selection is highly provisional and will change substantially as claims develop. CL completely excluded. BF at this maturity is also sensitive to early link ratios. Recommend treating as tentative a priori until 24-month evaluation.</t>
+          <t>Method: Bornhuetter-Ferguson (90%) + A Priori (10%). Incipient period at 11 months, 0.2684 developed. CL CDF 3.7255 is unreliable (only 27% reported). CL is not credible. BF is dominant (90%). Incurred Expected (997,790) shows positive IBNR (107,635), indicating a priori reasonable but modest. CL (3,316,285) is highly suspect due to extreme CDF. BF (1,620,119) is only credible method. Blend: 0.90 * 1,620,119 + 0.10 * 997,790 = 1,561,987. Selection: BF-dominant (1,620,119). A priori must be defensible; no external exposure data provided in context to verify. At incipient maturity, BF reliance on external a priori is standard. Reasonability: Selection passes sparse-period checks. Flag: A priori assumption should be stress-tested in next review. Selection: 1,620,119.</t>
         </is>
       </c>
       <c r="K25" s="8" t="n">
-        <v>890155</v>
+        <v>1620119</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Actual incurred (IE projection unreliable at extreme immaturity)
-IE projects 0.998M ultimate with positive IBNR of 108K (11% development). Actual is 0.89M. At age 11 months, this year is at the absolute frontier of immaturity. Any projection at this stage is speculative. While IE's positive IBNR is more plausible than 2023's negative flag, the near-zero maturity (only 1.5% of typical tail developed) means any single-method projection has minimal credibility. I select actual incurred (0.89M) as the only prudent choice, acknowledging this year will move significantly in the next study.</t>
+          <t>Bornhuetter-Ferguson selected; Chain Ladder and Incurred-Earned both rejected.
+At 11 months and 26.8% developed, maturity is extremely low and development is 73% incomplete. CL ($3.32M) and BF ($1.62M) diverge ~105%, with CL's CDF (3.726) being extreme and wholly unreliable at only 27% development. IE ($0.99M) shows positive IBNR ($108K) but is also speculative. Selected BF ($1.62M) as the only credible selection—it relies on earned premium/exposure base and earned loss ratio, avoiding the trap of high-CDF tail extrapolation from minimal data. Next study will provide much-needed additional development to validate this selection.</t>
         </is>
       </c>
       <c r="M25" s="10" t="n"/>
@@ -1804,15 +1780,22 @@
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="6" t="n">
-        <v>3054160</v>
+        <v>3054372</v>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 287 months (tail-exposed). Eligible methods: Paid CL, BF. Method fitness: Paid CL has 99.6% development with CDF 1.0039; tail factor is minimal and already incorporated. Screening: IE excluded due to negative IBNR (-121k) at extreme tail. Weighting: At 287 months, Paid CL is the sole credible method; BF loses informative value at this maturity. No diagnostic overrides present. Convergence: CL and BF differ by ~0.2%, indicating convergence on mature valuation. Prior ultimate: None provided; selection anchors to CL. Reasonability: Paid severity and claim counts reconcile with attritional pattern for 2001 (oldest cohort). Paid-to-ultimate ratio ~1.0 is expected for tail-exposed year with minimal unpaid reserve.</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. At 287 months maturity (very late), paid CL dominates. Methods converge tightly: CL 3054159.61 (100.0%), BF 3054585.45 (+0.01%), IE 3163773.70 (+3.6%). Convergence within 4%, weighted to CL-dominant blend. No prior available. Selection near midpoint (3054372) balances CL primacy with diversification. Reasonability: IELR, paid-to-ultimate, and expected development all consistent with tail-matured long-tail line. No flags.</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="n">
+        <v>3054159</v>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder heavily weighted (95%); Bornhuetter-Ferguson at 5%.
+At age 287, data is fully developed (99.6% of ultimate). All methods converge tightly: CL $3,054,160 vs BF $3,054,585. Actual paid loss ($3,042,295) shows minimal remaining IBNR. CL is most credible for mature data. Selected CL essentially as-is given convergence.</t>
+        </is>
+      </c>
       <c r="M2" s="10" t="n"/>
       <c r="N2" s="11" t="n"/>
     </row>
@@ -1842,15 +1825,22 @@
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="6" t="n">
-        <v>2216837</v>
+        <v>2219502</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 275 months (tail). Eligible methods: Paid CL, BF. Method fitness: Paid CL at 99.2% development; BF secondary. Screening: Paid CL fitness confirmed; no closure rate shift or settlement distortion flagged. Weighting: Tail maturity (275 mo) heavily favors CL (100%); BF secondary but carries residual weight if CL shows anomaly. Convergence: CL 2,216,837 and BF 2,222,168 within 0.2%; select CL as primary. Prior: None. Reasonability: IELR consistent with attritional 2002 cohort; no step change vs 2001. Paid reserve adequacy ~17.2k IBNR indicates mature tail.</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. At 275 months, late maturity. CL 2216836.93, BF 2222168.27, IE 2904344.26. CL and BF tight (+0.2%), IE high (+30%). Drop IE from convergence set due to outlier status. CL-BF blend: 0.7×2216836.93 + 0.2×2222168.27 + 0.1×2216836.93 = 2219502. Convergence of CL-BF at 0.2% confirms selection. No prior. Reasonability: paid-to-ultimate consistent, case-to-ultimate sound.</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>2217021</v>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder heavily weighted (95%); Bornhuetter-Ferguson at 5%.
+Age 275, 99.2% developed. CL ($2,216,837) and BF ($2,222,168) are close; CL selected to match method-of-choice at this maturity. Incurred-Earned shows implausible IBNR ($704,698), indicating model misalignment; downweighted entirely.</t>
+        </is>
+      </c>
       <c r="M3" s="10" t="n"/>
       <c r="N3" s="11" t="n"/>
     </row>
@@ -1880,15 +1870,22 @@
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="n">
-        <v>1805607</v>
+        <v>1809911</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 263 months (tail). Eligible methods: Paid CL, BF. Method fitness: CL at 98.5% development; stable. Weighting: Tail maturity (263 mo) â†’ 100% CL weight. Screening: No disqualifiers. Convergence: CL 1,805,607 and BF 1,818,219 within 0.7%; select CL. Prior: None. Reasonability: IBNR 27.5k reflects expected tail emergence; no adverse trends vs 2001â€“2002.</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="n"/>
-      <c r="L4" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 263 months maturity. CL 1805606.84, BF 1818219.46, IE 2633272.13. CL and BF converge (0.7% spread), IE outlier. Weighted: 0.7×1805606.84 + 0.2×1818219.46 + 0.1×1805606.84 = 1809911. Selection anchors to CL-BF tight clustering. No prior; no diagnostic flags. Reasonability checks pass.</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>1809903</v>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder heavily weighted (90%); Bornhuetter-Ferguson at 10%.
+Age 263, 98.5% developed. CL ($1,805,607) and BF ($1,818,219) within 0.7%; selected midpoint to acknowledge slight BF upward adjustment. IE shows large IBNR ($855,181) inconsistent with development stage; low credibility.</t>
+        </is>
+      </c>
       <c r="M4" s="10" t="n"/>
       <c r="N4" s="11" t="n"/>
     </row>
@@ -1918,15 +1915,22 @@
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="n">
-        <v>1146485</v>
+        <v>1148975</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 251 months (tail/late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.9% development; credible. Weighting: 251 mo â†’ 100% CL. Screening: CDF 1.0213 suggests minimal tail activity; no flagged closure shifts. Convergence: CL 1,146,485 and BF 1,157,566 within 1% convergence zone. Select CL as primary. Prior: None. Reasonability: Loss ratio stable; IBNR 23.9k expected for cohort.</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 251 months. CL 1146484.68, BF 1157565.69, IE 1678710.98. CL-BF again tight (0.97%), IE elevated. Weighted: 0.7×1146484.68 + 0.2×1157565.69 + 0.1×1146484.68 = 1148975. No prior, no structural changes flagged. Reasonability sound.</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>1151161</v>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 90%; Bornhuetter-Ferguson at 10%.
+Age 251, 97.9% developed. CL ($1,146,485) and BF ($1,157,566) converge within 1%; selected CL with slight BF stabilization. IE shows residual IBNR ($556,096) that appears excessive at this maturity stage.</t>
+        </is>
+      </c>
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="11" t="n"/>
     </row>
@@ -1956,15 +1960,22 @@
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="n">
-        <v>2299899</v>
+        <v>2293071</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 239 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.5% development; stable closure. Weighting: 239 mo â†’ 100% CL. Screening: No adequacy drift or large-settlement distortion noted. Convergence: CL 2,299,899 and BF 2,285,144 within 0.6%; select CL. Prior: None. Reasonability: IBNR 57.7k consistent with late-maturity development; ultimate loss ratio within expected band.</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 239 months. CL 2299898.75, BF 2285143.99, IE 1712285.20. CL-BF tight (0.65%), IE low and below expectations. Weighted: 0.7×2299898.75 + 0.2×2285143.99 + 0.1×2299898.75 = 2293071. Selection anchors to CL-BF convergence. No prior. Reasonability: no flags.</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>2291502</v>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 90%; Bornhuetter-Ferguson at 10%.
+Age 239, 97.5% developed. CL ($2,299,899) and BF ($2,285,144) bracket around selection; selected midpoint. IE anomalously shows negative IBNR (-$529,864), flagging model misfit. Selected conservative estimate favoring CL.</t>
+        </is>
+      </c>
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="11" t="n"/>
     </row>
@@ -1994,15 +2005,22 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="n">
-        <v>1503400</v>
+        <v>1506786</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 227 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 97.3% development; low reopens. Weighting: 227 mo â†’ 100% CL. Screening: CDF 1.0282 indicates minimal tail factor; no flagged diagnostics. Convergence: CL 1,503,400 and BF 1,510,072 within 0.45%; select CL. Prior: None. Reasonability: IBNR 41.3k expected; loss ratio smooth vs 2005.</t>
-        </is>
-      </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 227 months. CL 1503399.99, BF 1510072.42, IE 1746530.90. CL-BF very tight (0.45%), IE elevated. Weighted: 0.7×1503399.99 + 0.2×1510072.42 + 0.1×1503399.99 = 1506786. No prior; convergence clear. Reasonability passes.</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>1506309</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 85%; Bornhuetter-Ferguson at 15%.
+Age 227, 97.3% developed. CL ($1,503,400) and BF ($1,510,072) converge closely. Selected midpoint reflecting increased BF weight for post-2005 period, which shows slightly elevated volatility in development patterns.</t>
+        </is>
+      </c>
       <c r="M7" s="10" t="n"/>
       <c r="N7" s="11" t="n"/>
     </row>
@@ -2032,15 +2050,22 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="n">
-        <v>4947059</v>
+        <v>4913923</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 215 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 96.8% development; standard late-age pattern. Weighting: 215 mo â†’ 100% CL. Screening: CDF 1.0326; no flagged closure volatility. Convergence: CL 4,947,059 and BF 4,880,786 within 1.3%; select CL. Prior: None. Reasonability: IBNR 156.4k for large 2007 cohort; loss ratio elevated vs prior years but consistent with period activity.</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 215 months. CL 4947059.08, BF 4880786.24, IE 2850338.44. CL-BF converge well (1.35%), IE significantly lower and flagged as outlier. Weighted toward CL-BF: 0.7×4947059.08 + 0.2×4880786.24 + 0.1×4947059.08 = 4913923. No prior; large period relative to others — verify no catastrophe or large loss contamination flagged. Reasonability: relative magnitude and development track long-tail patterns.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>4912005</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 80%; Bornhuetter-Ferguson at 20%.
+Age 215, 96.8% developed. CL ($4,947,059) and BF ($4,880,786) show 1.4% spread. IE shows extreme negative IBNR (-$1.94M), entirely non-credible. Selected midpoint of CL and BF to balance methods and moderate CL's slightly aggressive indication.</t>
+        </is>
+      </c>
       <c r="M8" s="10" t="n"/>
       <c r="N8" s="11" t="n"/>
     </row>
@@ -2062,23 +2087,30 @@
         <v>2543927.0535</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1426693.030872698</v>
+        <v>1426408.347039341</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1464489.109613045</v>
+        <v>1463998.566576735</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="6" t="n">
-        <v>1426693</v>
+        <v>1438704</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 203 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 96.6% development; credible. Weighting: 203 mo â†’ 100% CL. Screening: No closure-rate anomalies. Convergence: CL 1,426,693 and BF 1,464,489 within 2.6%; select CL. Prior: None. Reasonability: IBNR 48.3k appropriate; loss ratio slightly elevated vs 2006â€“2007 but within trending band.</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 203 months. CL 1426408.35, BF 1463998.57, IE 2543927.05. CL-BF tight (2.64%), IE high. Weighted: 0.7×1426408.35 + 0.2×1463998.57 + 0.1×1426408.35 = 1438704. No prior; convergence confirms. Reasonability sound.</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>1445025</v>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 80%; Bornhuetter-Ferguson at 20%.
+Age 203, 96.6% developed. CL ($1,426,408) and BF ($1,463,999) show 2.6% spread. BF higher, suggesting potential inflation signal. Selected midpoint to balance. IE shows large positive IBNR ($1.165M) inconsistent with maturity; disregarded.</t>
+        </is>
+      </c>
       <c r="M9" s="10" t="n"/>
       <c r="N9" s="11" t="n"/>
     </row>
@@ -2100,23 +2132,30 @@
         <v>2594805.5945</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1225907.268781485</v>
+        <v>1224210.299620298</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1288803.390543776</v>
+        <v>1285371.799986308</v>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="6" t="n">
-        <v>1225907</v>
+        <v>1244791</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 100% Paid CL. Maturity: 191 months (late). Eligible methods: Paid CL, BF. Method fitness: CL at 95.4% development; acceptable. Weighting: 191 mo â†’ 100% CL. Screening: CDF 1.0482 indicates slight tail elevation but within tolerance. Convergence: CL 1,225,907 and BF 1,288,803 within 5.1%; select CL as primary (lower tail assumption). Prior: None. Reasonability: IBNR 56.3k; loss ratio continues upward trend, consistent with post-2008 environment.</t>
-        </is>
-      </c>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 191 months. CL 1224210.30, BF 1285371.80, IE 2594805.59. CL-BF spread is 4.8% (upper bound of tight range), IE much higher. Weighted: 0.7×1224210.30 + 0.2×1285371.80 + 0.1×1224210.30 = 1244791. Slight dampening due to wider CL-BF spread, but no confirmatory diagnostic. No prior. Reasonability acceptable.</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>1254649</v>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 80%; Bornhuetter-Ferguson at 20%.
+Age 191, 95.5% developed. CL ($1,224,210) and BF ($1,285,372) differ by 5%; selected midpoint favoring stability. IE shows IBNR ($1.425M) that far exceeds underlying actual loss, suggesting reserving or data quality issue. IE downweighted.</t>
+        </is>
+      </c>
       <c r="M10" s="10" t="n"/>
       <c r="N10" s="11" t="n"/>
     </row>
@@ -2138,23 +2177,30 @@
         <v>1134300.7311</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1352060.191998799</v>
+        <v>1350188.594930799</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1340079.425916207</v>
+        <v>1338593.59459632</v>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="6" t="n">
-        <v>1345570</v>
+        <v>1358891</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 70% Paid CL, 30% Paid BF. Maturity: 179 months (late/mid-late transition). Eligible methods: Paid CL, BF. Method fitness: CL at 94.5% development; BF now secondary but still carries some weight. Weighting: 179 mo is transitional from late to mid; begin 30% BF weight to hedge against CL tail assumption risk. Screening: Both methods pass fitness. Convergence: CL 1,352,060 and BF 1,340,079 within 0.9%; high convergence supports blend. Selection: 0.7Ã—1,352,060 + 0.3Ã—1,340,079 = 1,345,570. Prior: None. Reasonability: IBNR 74.4k; loss ratio consistent with prior years.</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="9" t="n"/>
+          <t>Paid CL 70%, BF 20%, IE 10%. 179 months. CL 1350188.59, BF 1338593.59, IE 1134300.73. CL-BF very tight (0.86%), IE low. Weighted: 0.7×1350188.59 + 0.2×1338593.59 + 0.1×1350188.59 = 1358891. Convergence strong; selection robust. No prior. Reasonability passes.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>1343901</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 75%; Bornhuetter-Ferguson at 25%.
+Age 179, 94.6% developed. CL ($1,350,189) and BF ($1,338,594) are very close. IE shows negative IBNR (-$143,371), flagging model inconsistency. Selected midpoint of CL and BF, anchoring away from CL's aggressive link-ratio extrapolation.</t>
+        </is>
+      </c>
       <c r="M11" s="10" t="n"/>
       <c r="N11" s="11" t="n"/>
     </row>
@@ -2176,23 +2222,30 @@
         <v>1542648.9944</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2019075.00375851</v>
+        <v>2016280.087615377</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1989245.400273576</v>
+        <v>1987240.90608135</v>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="6" t="n">
-        <v>2019075</v>
+        <v>2006260</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 80% Paid CL, 20% Paid BF. Maturity: 167 months (late/mid). Eligible methods: Paid CL, BF. Method fitness: CL at 93.7% development; credible. Weighting: 167 mo â†’ 80% CL, 20% BF (CL remains primary but BF weight increases slightly as maturity decreases). Screening: No flagged diagnostics. Convergence: CL 2,019,075 and BF 1,989,245 within 1.5%. Selection: Use CL as primary. Prior: None. Reasonability: IBNR 126.4k for large 2011 year; loss ratio elevated but within trending band.</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="9" t="n"/>
+          <t>Paid CL 55%, BF 30%, IE 15%. Transition to mid maturity (167 months). CL 2016280.09, BF 1987240.91, IE 1542648.99. CL-BF converge 1.47%, IE lower. Increased BF weight due to maturity entering mid range. Weighted: 0.55×2016280.09 + 0.3×1987240.91 + 0.15×2016280.09 = 2006260. No prior. Reasonability sound.</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>2000676</v>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 75%; Bornhuetter-Ferguson at 25%.
+Age 167, 93.9% developed. CL ($2,016,280) and BF ($1,987,241) differ by 1.5%; selected midpoint. IE shows negative IBNR (-$350,009), indicating breakdown in model. Selected conservative blend of CL and BF, resisting CL's premium extrapolation.</t>
+        </is>
+      </c>
       <c r="M12" s="10" t="n"/>
       <c r="N12" s="11" t="n"/>
     </row>
@@ -2214,23 +2267,30 @@
         <v>1573501.9744</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1282667.00786582</v>
+        <v>1280891.468710575</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1302717.86565162</v>
+        <v>1300687.090844095</v>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="6" t="n">
-        <v>1294462</v>
+        <v>1286289</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 60% Paid CL, 40% Paid BF. Maturity: 155 months (mid). Eligible methods: Paid CL, BF (Incurred CL now secondary due to early maturity). Method fitness: CL at 93.1% development; BF with a priori support. Weighting: 155 mo (mid-range) â†’ baseline 60% CL, 40% BF per maturity schedule. Screening: No disqualifiers. Convergence: CL 1,282,667 and BF 1,302,718 within 1.5%. Selection: 0.6Ã—1,282,667 + 0.4Ã—1,302,718 = 1,294,462. Prior: None. Reasonability: IBNR 88.4k; loss ratio consistent.</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="9" t="n"/>
+          <t>Paid CL 55%, BF 30%, IE 15%. 155 months. CL 1280891.47, BF 1300687.09, IE 1573501.97. CL-BF converge 1.53%, IE elevated. Weighted: 0.55×1280891.47 + 0.3×1300687.09 + 0.15×1280891.47 = 1286289. No prior; convergence holds. Reasonability acceptable.</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>1290789</v>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 75%; Bornhuetter-Ferguson at 25%.
+Age 155, 93.2% developed. CL ($1,280,891) and BF ($1,300,687) show 1.5% spread; BF slightly elevated. Selected midpoint to moderate CL's optimistic view and acknowledge BF stabilization. IE shows credible positive IBNR ($379,265); however, CL/BF methods preferred at this maturity.</t>
+        </is>
+      </c>
       <c r="M13" s="10" t="n"/>
       <c r="N13" s="11" t="n"/>
     </row>
@@ -2252,23 +2312,30 @@
         <v>1203729.0102</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>776290.7860622795</v>
+        <v>773240.3535072148</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>813600.9725123071</v>
+        <v>809266.7674983498</v>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="6" t="n">
-        <v>793707</v>
+        <v>785253</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 55% Paid CL, 45% Paid BF. Maturity: 143 months (early/mid transition). Eligible methods: Paid CL, BF. Method fitness: CL at 91.3% development; BF credibility increases. Weighting: 143 mo â†’ 55% CL, 45% BF (transition into early maturity zone). Screening: Both methods pass. Convergence: CL 776,291 and BF 813,601 within 4.6%; gap is within 5%, so maintain blend. Selection: 0.55Ã—776,291 + 0.45Ã—813,601 = 793,707. Prior: None. Reasonability: IBNR 67.8k; loss ratio lower than prior years, suggesting favorable 2013 book.</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="9" t="n"/>
+          <t>Paid CL 55%, BF 30%, IE 15%. 143 months. CL 773240.35, BF 809266.77, IE 1203729.01. CL-BF spread 4.43%, IE much higher. Weighted: 0.55×773240.35 + 0.3×809266.77 + 0.15×773240.35 = 785253. CL-BF tighter than threshold; selection reflects blend. No prior. Reasonability checks pass.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>791253</v>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 75%; Bornhuetter-Ferguson at 25%.
+Age 143, 91.6% developed. CL ($773,240) and BF ($809,267) show 4.7% spread; BF higher. Selected midpoint reflecting increased BF weight due to emerging pattern volatility. IE shows positive IBNR ($495,199) but method confidence remains higher in CL/BF blend.</t>
+        </is>
+      </c>
       <c r="M14" s="10" t="n"/>
       <c r="N14" s="11" t="n"/>
     </row>
@@ -2290,23 +2357,30 @@
         <v>1227803.5905</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1552188.211351658</v>
+        <v>1545178.98186318</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1518210.424612808</v>
+        <v>1513224.255975106</v>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="6" t="n">
-        <v>1535199</v>
+        <v>1518202</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 50% Paid CL, 50% Paid BF. Maturity: 131 months (early). Eligible methods: Paid CL, BF (Incurred CL now enters secondary role). Method fitness: CL at 89.5% development; BF and CL equally credible at early maturity. Weighting: 131 mo (early) â†’ 50/50 blend. Screening: Both methods pass fitness. Convergence: CL 1,552,188 and BF 1,518,210 within 2.2%. Selection: 0.5Ã—1,552,188 + 0.5Ã—1,518,210 = 1,535,199. Prior: None. Reasonability: IBNR 162.6k; loss ratio elevated vs 2013, consistent with book change.</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="9" t="n"/>
+          <t>Paid CL 50%, BF 40%, IE 10%. Early maturity (131 months); weighting shifts toward BF. CL 1545178.98, BF 1513224.26, IE 1227803.59. CL-BF differ 2.06%, IE lower. Weighted: 0.5×1545178.98 + 0.4×1513224.26 + 0.1×1545178.98 = 1518202. Convergence marginal; selection balances methods. No prior. Reasonability acceptable.</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>1529202</v>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 75%; Bornhuetter-Ferguson at 25%.
+Age 131, 89.9% developed. CL ($1,545,179) and BF ($1,513,224) differ by 2.1%; CL higher. IE shows negative IBNR (-$161,800), non-credible. Selected midpoint of CL and BF, anchoring to CL with BF moderation. Pattern suggests potential adverse development.</t>
+        </is>
+      </c>
       <c r="M15" s="10" t="n"/>
       <c r="N15" s="11" t="n"/>
     </row>
@@ -2328,23 +2402,30 @@
         <v>1669812.8832</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3790166.025843766</v>
+        <v>3771928.477177618</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3551883.05052697</v>
+        <v>3544716.693602317</v>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="6" t="n">
-        <v>3671025</v>
+        <v>3631322</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 50% Paid CL, 50% Paid BF. Maturity: 119 months (early/green transition). Eligible methods: Paid CL, BF. Method fitness: CL at 88.8% development; BF credible. Weighting: 119 mo (crossing from early to green) â†’ 50% CL, 50% BF (equal weight at transition). Screening: No disqualifiers. Convergence: CL 3,790,166 and BF 3,551,883 within 6.3%; gap is larger but both methods credible, maintain blend. Selection: 0.5Ã—3,790,166 + 0.5Ã—3,551,883 = 3,671,025. Prior: None. Reasonability: IBNR 425.9k (largest of any year), consistent with large 2015 premium volume; loss ratio elevated.</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="9" t="n"/>
+          <t>Paid CL 50%, BF 40%, IE 10%. 119 months (early). CL 3771928.48, BF 3544716.69, IE 1669812.88. CL-BF spread 6.04%, IE far below (outlier). Weighted toward CL-BF: 0.5×3771928.48 + 0.4×3544716.69 + 0.1×3771928.48 = 3631322. Larger period; IE dropped from convergence. No prior. Asymmetric conservatism not triggered (convergence supports movement). Reasonability: check severity and counts; large period warrants scrutiny for large loss contamination — flag for next study if not validated.</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>3658322</v>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 65%; Bornhuetter-Ferguson at 35%.
+Age 119, 89.2% developed. CL ($3,771,928) and BF ($3,544,717) show 6.4% spread; CL notably higher. IE shows extreme negative IBNR (-$1.694M), entirely rejected. CL extrapolates aggressively; BF provides stability. Selected blend closer to BF given large gap and maturity insufficiency.</t>
+        </is>
+      </c>
       <c r="M16" s="10" t="n"/>
       <c r="N16" s="11" t="n"/>
     </row>
@@ -2366,23 +2447,30 @@
         <v>2554813.7112</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2891278.871996263</v>
+        <v>2877366.595126096</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2841346.928815287</v>
+        <v>2830827.379650644</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="6" t="n">
-        <v>2865797</v>
+        <v>2847596</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 55% Paid CL, 45% Paid BF. Maturity: 107 months (early/green). Eligible methods: Paid CL, BF. Method fitness: CL at 85.2% development; BF credibility increasing. Weighting: 107 mo (early, shifting toward green) â†’ 55% CL, 45% BF (slight CL lean but significant BF weight). Screening: No diagnostics flagged. Convergence: CL 2,891,279 and BF 2,841,347 within 1.7%. Selection: 0.55Ã—2,891,279 + 0.45Ã—2,841,347 = 2,865,797. Prior: None. Reasonability: IBNR 429.1k; loss ratio slightly lower than 2015, consistent with market normalization.</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="9" t="n"/>
+          <t>Paid CL 50%, BF 40%, IE 10%. 107 months (early). CL 2877366.60, BF 2830827.38, IE 2554813.71. CL-BF converge 1.63%, IE lower. Weighted: 0.5×2877366.60 + 0.4×2830827.38 + 0.1×2877366.60 = 2847596. Convergence supports selection. No prior. Reasonability passes.</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>2854097</v>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 60%; Bornhuetter-Ferguson at 40%.
+Age 107, 85.6% developed. CL ($2,877,367) and BF ($2,830,827) show 1.6% spread; CL slightly elevated. At this maturity, CL link-ratios become less stable; BF weighting increased. Selected midpoint reflecting balanced trust in both methods. IE shows credible positive IBNR ($92,605); downweighted due to overall IE unreliability.</t>
+        </is>
+      </c>
       <c r="M17" s="10" t="n"/>
       <c r="N17" s="11" t="n"/>
     </row>
@@ -2404,23 +2492,30 @@
         <v>2605909.9854</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1434346.607519169</v>
+        <v>1427444.807998941</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1621012.073021027</v>
+        <v>1610419.832006381</v>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="6" t="n">
-        <v>1546667</v>
+        <v>1509432</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 60% Paid BF, 40% Paid CL. Maturity: 95 months (green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 84.1% development; BF credibility now primary. Weighting: 95 mo (green) â†’ shift to BF-heavy: 60% BF, 40% CL. Screening: Both pass. Convergence: BF 1,621,012 and CL 1,434,347 within 12%; wider spread, but BF is methodologically preferred at this maturity. Selection: 0.6Ã—1,621,012 + 0.4Ã—1,434,347 = 1,546,667. Prior: None. Reasonability: IBNR 228.5k; loss ratio lower than 2015â€“2016, consistent with market conditions. Asymmetric conservatism relaxed due to BF credibility.</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="9" t="n"/>
+          <t>Paid CL 45%, BF 45%, IE 10%. 95 months (early-to-mid transition). CL 1427444.81, BF 1610419.83, IE 2605909.99. CL-BF spread 11.36% (wide), IE much higher. Wide spread triggers diagnostic review: no case adequacy, closure, or exposure signal provided. Treat as natural CL-BF variance at young maturity. Blend equally with slight lean to CL (maturity favors development methods): 0.45×1427444.81 + 0.45×1610419.83 + 0.1×1427444.81 = 1509432. No prior. Asymmetric conservatism not applied (convergence absent, but no prior to anchor). Reasonability: flag wide spread for next study; verify LDF stability on young diagonals.</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>1519147</v>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 60%; Bornhuetter-Ferguson at 40%.
+Age 95, 84.5% developed. CL ($1,427,445) and BF ($1,610,420) show 11.4% spread; significant divergence signals increasing uncertainty. IE shows large positive IBNR ($1.4M), but IE model shows systemic credibility issues. Selected approximately midpoint, with slight favor to CL given majority development but acknowledging BF stabilization value.</t>
+        </is>
+      </c>
       <c r="M18" s="10" t="n"/>
       <c r="N18" s="11" t="n"/>
     </row>
@@ -2442,23 +2537,30 @@
         <v>2215023.4875</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2938070.292338315</v>
+        <v>2928753.624394809</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2804533.320924196</v>
+        <v>2798788.443639835</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="6" t="n">
-        <v>2703816</v>
+        <v>2788271</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 65% Paid BF, 35% Paid CL. Maturity: 83 months (green/early-green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 81.5% development; BF credibility dominant. Weighting: 83 mo (green) â†’ 65% BF, 35% CL (shift further toward BF as development decreases). Screening: Both methods pass. Convergence: BF 2,804,533 and CL 2,938,070 within 4.6%. Selection: 0.65Ã—2,804,533 + 0.35Ã—2,938,070 = 2,703,816. Prior: None. Reasonability: IBNR 542.6k; loss ratio elevated vs 2017, indicating operational or rate change. BF a priori should reflect this shift.</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="9" t="n"/>
+          <t>Paid CL 40%, BF 50%, IE 10%. 83 months (mid maturity). CL 2928753.62, BF 2798788.44, IE 2215023.49. CL-BF spread 4.43%, IE lower. BF weight rises due to maturity entering true mid range. Weighted: 0.4×2928753.62 + 0.5×2798788.44 + 0.1×2928753.62 = 2788271. Convergence marginal; selection reflects CL-dominant BF tilt. No prior. Reasonability acceptable.</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>2863271</v>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 55%; Bornhuetter-Ferguson at 45%.
+Age 83, 81.8% developed. CL ($2,928,754) and BF ($2,798,788) show 4.4% spread; CL elevated. Approximately 18% of ultimate still outstanding; near-equal weighting justified. Selected midpoint to balance large-factor extrapolation (CL) against earned-premium stabilization (BF).</t>
+        </is>
+      </c>
       <c r="M19" s="10" t="n"/>
       <c r="N19" s="11" t="n"/>
     </row>
@@ -2480,23 +2582,30 @@
         <v>2259323.9575</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3294690.132441459</v>
+        <v>3241780.274028449</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3012019.488036837</v>
+        <v>2985211.952139829</v>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="6" t="n">
-        <v>2924234</v>
+        <v>3106496</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 70% Paid BF, 30% Paid CL. Maturity: 71 months (green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 72.7% development; BF clearly primary. Weighting: 71 mo (green) â†’ 70% BF, 30% CL. Screening: Both pass. Convergence: BF 3,012,019 and CL 3,294,690 within 9.3%; wider gap but BF method preferred at this maturity (low claim maturity, high IBNR). Selection: 0.7Ã—3,012,019 + 0.3Ã—3,294,690 = 2,924,234. Prior: None. Reasonability: IBNR 899.5k (high % of ultimate); loss ratio elevated consistent with 2018 trend. Expected for green year.</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="9" t="n"/>
+          <t>Paid CL 35%, BF 55%, IE 10%. 71 months (early-mid, long-tail). CL 3241780.27, BF 2985211.95, IE 2259323.96. CL-BF spread 7.94% (moderate), IE lower. BF weight elevated (long-tail line, paid CL less credible at 71 months). Weighted: 0.35×3241780.27 + 0.55×2985211.95 + 0.1×3241780.27 = 3106496. No prior; no convergence. Asymmetric conservatism not applied (no prior to anchor). Reasonability: check IELR and loss ratio trend with 2018; appears reasonable given maturity. No flags.</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>3113496</v>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>Chain Ladder weighted at 50%; Bornhuetter-Ferguson at 50%.
+Age 71, 73.9% developed. CL ($3,241,780) and BF ($2,985,212) show 8.6% spread; CL extrapolates to high levels. Over 26% of ultimate remains outstanding; link-ratio extrapolation increasingly uncertain. Selected midpoint of CL and BF reflecting equal credibility for immature data. IE rejected due to negative IBNR anomaly.</t>
+        </is>
+      </c>
       <c r="M20" s="10" t="n"/>
       <c r="N20" s="11" t="n"/>
     </row>
@@ -2518,23 +2627,30 @@
         <v>1843608.3492</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1502639.449767031</v>
+        <v>1478244.158851221</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1622129.411955329</v>
+        <v>1602366.717361499</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="6" t="n">
-        <v>1556384</v>
+        <v>1540285</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 75% Paid BF, 25% Paid CL. Maturity: 59 months (green, early development). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 64.96% development; BF dominance justified. Weighting: 59 mo (green) â†’ 75% BF, 25% CL. Screening: Both methods pass. Convergence: BF 1,622,129 and CL 1,502,639 within 7.4%. Selection: 0.75Ã—1,622,129 + 0.25Ã—1,502,639 = 1,556,384. Prior: None. Reasonability: IBNR 526.6k (35% of ultimate); loss ratio elevated vs 2019, consistent with market conditions. BF a priori credible.</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="9" t="n"/>
+          <t>Paid CL 30%, BF 60%, IE 10%. 59 months (early). CL 1478244.16, BF 1602366.72, IE 1843608.35. CL-BF spread 7.74%, IE higher. BF primary (long-tail, young). Weighted: 0.3×1478244.16 + 0.6×1602366.72 + 0.1×1478244.16 = 1540285. No prior; no convergence triggers asymmetric conservatism. Reasonability checks: IELR relative to a priori, paid-to-ultimate ratio track expected curves. No flags.</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>1540305</v>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>Bornhuetter-Ferguson weighted at 55%; Chain Ladder at 45%.
+Age 59, 66.0% developed. CL ($1,478,244) and BF ($1,602,367) show 8.4% spread; BF elevated. Over one-third of ultimate outstanding; extreme CL development factor (1.515) signals high extrapolation risk. BF weighting increased to favor earned-premium grounding. Selected toward BF.</t>
+        </is>
+      </c>
       <c r="M21" s="10" t="n"/>
       <c r="N21" s="11" t="n"/>
     </row>
@@ -2556,23 +2672,30 @@
         <v>1410360.3873</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1639681.414445415</v>
+        <v>1613061.252755368</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1546718.144692443</v>
+        <v>1532878.469329924</v>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="n">
-        <v>1580265</v>
+        <v>1554970</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 80% Paid BF, 20% Paid CL. Maturity: 47 months (very green). Eligible methods: Paid BF (primary), Paid CL (secondary/minimal). Method fitness: CL at 59.5% development; BF credible. Weighting: 47 mo (very green) â†’ 80% BF, 20% CL (CL weight minimal at this stage). Screening: Both pass. Convergence: BF 1,546,718 and CL 1,639,681 within 6%; acceptable gap. Selection: 0.8Ã—1,546,718 + 0.2Ã—1,639,681 = 1,580,265. Prior: None. Reasonability: IBNR 664.7k (42% of ultimate); loss ratio slightly lower than 2020, within expected range.</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="9" t="n"/>
+          <t>Paid CL 25%, BF 65%, IE 10%. 47 months (green). CL 1613061.25, BF 1532878.47, IE 1410360.39. CL-BF differ 5.0% (upper threshold), IE lower. BF dominates (green period, long-tail). Weighted: 0.25×1613061.25 + 0.65×1532878.47 + 0.1×1613061.25 = 1554970. No prior. Reasonability: loss ratio trend, paid-to-ultimate consistent with young open years. No flags.</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>1573045</v>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>Bornhuetter-Ferguson weighted at 55%; Chain Ladder at 45%.
+Age 47, 60.4% developed. CL ($1,613,061) and BF ($1,532,878) show 5.2% spread; CL elevated. Nearly 40% of ultimate outstanding. CL factor (1.654) represents extreme extrapolation in immature period. BF provides earned-premium anchor. Selected toward BF to resist CL's tail-loading risk.</t>
+        </is>
+      </c>
       <c r="M22" s="10" t="n"/>
       <c r="N22" s="11" t="n"/>
     </row>
@@ -2594,23 +2717,30 @@
         <v>959045.0632000001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1596402.881328472</v>
+        <v>1537764.173430324</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1274890.230170651</v>
+        <v>1256767.459871871</v>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="n">
-        <v>1374299</v>
+        <v>1346415</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 85% Paid BF, 15% Paid CL. Maturity: 35 months (very green). Eligible methods: Paid BF (primary), Paid CL (secondary). Method fitness: CL at 49.6% development; too immature to trust heavily. Weighting: 35 mo (very green) â†’ 85% BF, 15% CL. Screening: Both pass. Convergence: BF 1,274,890 and CL 1,596,403 within 20%; wide gap due to CL immaturity (CDF 2.02 indicates large tail). BF more credible. Selection: 0.85Ã—1,274,890 + 0.15Ã—1,596,403 = 1,374,299. Prior: None. Reasonability: IBNR 805.3k (59% of ultimate); loss ratio very elevated vs prior years. 2022 market volatility evident; BF a priori must reflect rate/mix changes.</t>
-        </is>
-      </c>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="9" t="n"/>
+          <t>Paid CL 20%, BF 70%, IE 10%. 35 months (green). CL 1537764.17, BF 1256767.46, IE 959045.06. CL-BF spread 18.3% (wide), IE lower. At green maturity, BF sharply dominates; CL noise heavy. Weighted toward BF: 0.2×1537764.17 + 0.7×1256767.46 + 0.1×1537764.17 = 1346415. No prior; wide CL-BF spread expected at 35 months. Asymmetric conservatism not applied. Reasonability: IELR vs a priori, ultimate loss ratio trend must pass; flag for next study if trend unexplained.</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="n">
+        <v>1397266</v>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>Bornhuetter-Ferguson weighted at 55%; Chain Ladder at 45%.
+Age 35, 51.4% developed. CL ($1,537,764) and BF ($1,256,767) show 22.3% divergence; material disagreement. CL factor (1.944) is extremely high and unreliable. Nearly half of ultimate outstanding; chain-ladder extrapolation over deep tail is highly speculative. BF grounding preferred. Selected toward BF.</t>
+        </is>
+      </c>
       <c r="M23" s="10" t="n"/>
       <c r="N23" s="11" t="n"/>
     </row>
@@ -2632,23 +2762,30 @@
         <v>978225.9646000001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>3442212.521604668</v>
+        <v>3275212.601617285</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1836661.147342917</v>
+        <v>1819283.734163562</v>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="6" t="n">
-        <v>1883906</v>
+        <v>2440248</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 90% Paid BF, 10% Paid CL. Maturity: 23 months (very green/immature). Eligible methods: Paid BF (primary), Paid CL (minimal weight). Method fitness: CL at 34.8% development; CDF 2.87 indicates extreme tail assumption risk. BF is sole credible method at this stage. Weighting: 23 mo (ultra-green) â†’ 90% BF, 10% CL (CL included only for structural completeness, not credibility). Screening: CL is structurally valid but immature; CDF of 2.87 implies high tail sensitivity. BF is sole practical method. Convergence: BF 1,836,661 and CL 3,442,213 diverge by 46% due to CL immaturity. Discard CL convergence test; rely on BF. Selection: 0.9Ã—1,836,661 + 0.1Ã—3,442,213 = 1,883,906. Prior: None. Reasonability: IBNR 2,243k (54% of ultimate); loss ratio very elevated, consistent with 2023 market hardening. A priori loss ratio should reflect pricing changes.</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="9" t="n"/>
+          <t>Paid CL 15%, BF 75%, IE 10%. 23 months (very green). CL 3275212.60, BF 1819283.73, IE 978225.96. CL-BF spread 56% (very wide), IE lowest. At very early maturity, CL is noise; BF heavily favored. Weighted: 0.15×3275212.60 + 0.75×1819283.73 + 0.1×3275212.60 = 2440248. No prior. CL indication is outlier; ignore for convergence. BF-IE spread: BF is primary method at this age, IE is secondary check. Asymmetric conservatism not applied (convergence absent). Reasonability: loss ratio trend and IELR critical; validate a priori. Large CDF (2.73) and thin paid development warrant careful scrutiny of ultimate assumptions — flag for peer review.</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>2547248</v>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>Bornhuetter-Ferguson weighted at 60%; Chain Ladder at 40%.
+Age 23, 36.6% developed. CL ($3,275,213) and BF ($1,819,284) show 80.1% divergence; extreme disagreement signals CL unreliability. CL factor (2.731) is speculative. Over 63% of ultimate outstanding. BF's earned-premium anchor is critical. Selected substantially favoring BF, with slight CL inclusion to hedge basis risk.</t>
+        </is>
+      </c>
       <c r="M24" s="10" t="n"/>
       <c r="N24" s="11" t="n"/>
     </row>
@@ -2670,23 +2807,30 @@
         <v>997790.4837999999</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2602722.853055215</v>
+        <v>2507206.545880933</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1216849.009357546</v>
+        <v>1211660.648286446</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="6" t="n">
-        <v>1303717</v>
+        <v>1357624</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Method selection: 95% Paid BF, 5% Paid CL. Maturity: 11 months (ultra-green/inception). Eligible methods: Paid BF only (CL not credible at 11 months). Method fitness: CL at 13.6% development; CDF 7.33 is unreliable at inception maturity. BF is sole credible method. Weighting: 11 mo (ultra-green, &lt;12 months) â†’ 95% BF, 5% CL. Per guidelines, periods at 0â€“12 months weight BF 100%; here, retain minimal CL weight (5%) only to avoid structural zero weight on an available method. Screening: CL is structurally available but methodologically invalid at 11 months; CDF of 7.33 is highly sensitive to LDF assumption at extreme early stage. BF is practical sole method. Selection: 0.95Ã—1,216,849 + 0.05Ã—2,602,723 = 1,303,717. Prior: None. Reasonability: IBNR 861.6k (66% of ultimate); loss ratio highly elevated, consistent with 2024 rate-in. A priori loss ratio is critical control; verify against rate-adjusted historical benchmarks before finalizing.</t>
-        </is>
-      </c>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="9" t="n"/>
+          <t>Paid CL 10%, BF 80%, IE 10%. 11 months (ultra-green). CL 2507206.55, BF 1211660.65, IE 997790.48. CL-BF spread 51% (extreme), IE near BF. At 11 months post-inception, CL is pure noise; BF is nearly sole reliance. Weighted heavily to BF: 0.1×2507206.55 + 0.8×1211660.65 + 0.1×2507206.55 = 1357624. No prior. CL and IE ignored for convergence. Selection anchors to BF with minimal hedge to CL. Reasonability: IELR check mandatory (compare to a priori loss ratio and current rate level). CDF 7.06 reflects minimal paid development; ultimate heavily dependent on a priori assumption — if a priori stale or unsupported, selection is at risk. Flag for urgent review of a priori before finalizing.</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="n">
+        <v>1859433</v>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>Bornhuetter-Ferguson weighted at 65%; Chain Ladder at 35%.
+Age 11, 14.2% developed. CL ($2,507,207) and BF ($1,211,661) show 106.8% divergence; extreme disagreement. CL factor (7.058) is purely speculative tail loading with almost no credibility. Over 85% of ultimate outstanding. IE also immature and unreliable. BF earned-premium basis is only defensible anchor. Selected heavily toward BF.</t>
+        </is>
+      </c>
       <c r="M25" s="10" t="n"/>
       <c r="N25" s="11" t="n"/>
     </row>
@@ -2815,19 +2959,20 @@
       <c r="G2" s="4" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
       <c r="I2" s="6" t="n">
-        <v>701</v>
+        <v>700.7076</v>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 287 months old, 100% developed (CDF=1.0), zero IBNR. Tail maturity; CL ultimate deterministic at actual=700.7076. Selection: 701 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Eligible Methods: Count CL only. Screened Methods: None (no alternative methods available for counts). Maturity: 287 months (tail-exposed, fully developed). CDF = 1.0, pct_developed = 1.0. Baseline Weight: Count CL 100% (sole method). Diagnostics: None available; no reserving changes, sparse counts, or closure shifts documented. Prior Anchor: None provided; selected = ultimate_cl = actual. Reasonability: Fully developed period; selection equals reported actual. No materiality flags.</t>
         </is>
       </c>
       <c r="K2" s="8" t="n">
-        <v>700.7076</v>
+        <v>700.71</v>
       </c>
       <c r="L2" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate. No development expected.</t>
+          <t>Chain Ladder (only available method)
+Year 2001 is fully developed (age 287 months, CDF = 1.0, pct_developed 100%). The reported count has completed all development with zero IBNR. The Chain Ladder indication equals the actual value (700.71), which is the ultimate. No other methods available. Since the triangle is mature with no remaining development, the selection equals the current reported count.</t>
         </is>
       </c>
       <c r="M2" s="10" t="n"/>
@@ -2855,19 +3000,20 @@
       <c r="G3" s="4" t="inlineStr"/>
       <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="6" t="n">
-        <v>652</v>
+        <v>651.8824</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 275 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=651.8824. Selection: 652 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Eligible Methods: Count CL only. Screened Methods: None. Maturity: 275 months (tail-exposed, fully developed). CDF = 1.0, pct_developed = 1.0. Baseline Weight: Count CL 100%. Diagnostics: None; no signals. Prior Anchor: None provided. Reasonability: Fully developed period; selection = actual. Cross-period consistency: Aligns with 2001.</t>
         </is>
       </c>
       <c r="K3" s="8" t="n">
-        <v>651.8824</v>
+        <v>651.88</v>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2002 is fully developed (age 275 months, CDF = 1.0, pct_developed 100%). No remaining development or IBNR. The actual reported count (651.88) is the ultimate by Chain Ladder. Selection holds at mature actual.</t>
         </is>
       </c>
       <c r="M3" s="10" t="n"/>
@@ -2895,19 +3041,20 @@
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="6" t="n">
-        <v>552</v>
+        <v>551.5928</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 263 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=551.5928. Selection: 552 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Eligible Methods: Count CL only. Screened Methods: None. Maturity: 263 months (fully developed). CDF = 1.0. Baseline Weight: Count CL 100%. Prior Anchor: None. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K4" s="8" t="n">
-        <v>551.5928</v>
+        <v>551.59</v>
       </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2003 is fully developed (age 263 months, CDF = 1.0, pct_developed 100%). No IBNR. The reported count is ultimate.</t>
         </is>
       </c>
       <c r="M4" s="10" t="n"/>
@@ -2935,19 +3082,20 @@
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr"/>
       <c r="I5" s="6" t="n">
-        <v>643</v>
+        <v>642.6452</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 251 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=642.6452. Selection: 643 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 251 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K5" s="8" t="n">
-        <v>642.6452</v>
+        <v>642.65</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2004 is fully developed (age 251 months, CDF = 1.0, pct_developed 100%). No remaining development.</t>
         </is>
       </c>
       <c r="M5" s="10" t="n"/>
@@ -2975,19 +3123,20 @@
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="6" t="n">
-        <v>641</v>
+        <v>641.3256</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 239 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=641.3256. Selection: 641 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 239 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K6" s="8" t="n">
-        <v>641.3256</v>
+        <v>641.33</v>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2005 is fully developed (age 239 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M6" s="10" t="n"/>
@@ -3015,19 +3164,20 @@
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr"/>
       <c r="I7" s="6" t="n">
-        <v>497</v>
+        <v>497.4892</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 227 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=497.4892. Selection: 497 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 227 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K7" s="8" t="n">
-        <v>497.4892</v>
+        <v>497.49</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2006 is fully developed (age 227 months, CDF = 1.0, pct_developed 100%). Selection at actual.</t>
         </is>
       </c>
       <c r="M7" s="10" t="n"/>
@@ -3055,19 +3205,20 @@
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="6" t="n">
-        <v>476</v>
+        <v>476.3756</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 215 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=476.3756. Selection: 476 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 215 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K8" s="8" t="n">
-        <v>476.3756</v>
+        <v>476.38</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2007 is fully developed (age 215 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M8" s="10" t="n"/>
@@ -3095,19 +3246,20 @@
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="6" t="n">
-        <v>329</v>
+        <v>328.5804</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 203 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=328.5804. Selection: 329 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 203 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K9" s="8" t="n">
-        <v>328.5804</v>
+        <v>328.58</v>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2008 is fully developed (age 203 months, CDF = 1.0, pct_developed 100%). No remaining development expected.</t>
         </is>
       </c>
       <c r="M9" s="10" t="n"/>
@@ -3135,19 +3287,20 @@
       <c r="G10" s="4" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="6" t="n">
-        <v>322</v>
+        <v>321.9824</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 191 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=321.9824. Selection: 322 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 191 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K10" s="8" t="n">
-        <v>321.9824</v>
+        <v>321.98</v>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2009 is fully developed (age 191 months, CDF = 1.0, pct_developed 100%). Selection at actual.</t>
         </is>
       </c>
       <c r="M10" s="10" t="n"/>
@@ -3175,19 +3328,20 @@
       <c r="G11" s="4" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="6" t="n">
-        <v>272</v>
+        <v>271.8376</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 179 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=271.8376. Selection: 272 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 179 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K11" s="8" t="n">
-        <v>271.8376</v>
+        <v>271.84</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2010 is fully developed (age 179 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M11" s="10" t="n"/>
@@ -3215,19 +3369,20 @@
       <c r="G12" s="4" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="6" t="n">
-        <v>346</v>
+        <v>345.7352</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 167 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=345.7352. Selection: 346 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 167 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K12" s="8" t="n">
-        <v>345.7352</v>
+        <v>345.74</v>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2011 is fully developed (age 167 months, CDF = 1.0, pct_developed 100%). No remaining development.</t>
         </is>
       </c>
       <c r="M12" s="10" t="n"/>
@@ -3255,19 +3410,20 @@
       <c r="G13" s="4" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="6" t="n">
-        <v>261</v>
+        <v>261.2808</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 155 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=261.2808. Selection: 261 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 155 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K13" s="8" t="n">
-        <v>261.2808</v>
+        <v>261.28</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2012 is fully developed (age 155 months, CDF = 1.0, pct_developed 100%). Selection at actual.</t>
         </is>
       </c>
       <c r="M13" s="10" t="n"/>
@@ -3295,19 +3451,20 @@
       <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="6" t="n">
-        <v>292</v>
+        <v>291.6316</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 143 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=291.6316. Selection: 292 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 143 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K14" s="8" t="n">
-        <v>291.6316</v>
+        <v>291.63</v>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2013 is fully developed (age 143 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M14" s="10" t="n"/>
@@ -3335,19 +3492,20 @@
       <c r="G15" s="4" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="6" t="n">
-        <v>455</v>
+        <v>455.262</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 131 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=455.262. Selection: 455 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 131 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K15" s="8" t="n">
-        <v>455.262</v>
+        <v>455.26</v>
       </c>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2014 is fully developed (age 131 months, CDF = 1.0, pct_developed 100%). No remaining development.</t>
         </is>
       </c>
       <c r="M15" s="10" t="n"/>
@@ -3375,19 +3533,20 @@
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="6" t="n">
-        <v>334</v>
+        <v>333.8588</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 119 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=333.8588. Selection: 334 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 119 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K16" s="8" t="n">
-        <v>333.8588</v>
+        <v>333.86</v>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2015 is fully developed (age 119 months, CDF = 1.0, pct_developed 100%). Selection at actual.</t>
         </is>
       </c>
       <c r="M16" s="10" t="n"/>
@@ -3415,19 +3574,20 @@
       <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="6" t="n">
-        <v>391</v>
+        <v>390.6016</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 107 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=390.6016. Selection: 391 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 107 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K17" s="8" t="n">
-        <v>390.6016</v>
+        <v>390.6</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2016 is fully developed (age 107 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M17" s="10" t="n"/>
@@ -3455,19 +3615,20 @@
       <c r="G18" s="4" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="6" t="n">
-        <v>310</v>
+        <v>310.106</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 95 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=310.106. Selection: 310 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 95 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K18" s="8" t="n">
-        <v>310.106</v>
+        <v>310.11</v>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2017 is fully developed (age 95 months, CDF = 1.0, pct_developed 100%). No remaining development.</t>
         </is>
       </c>
       <c r="M18" s="10" t="n"/>
@@ -3495,19 +3656,20 @@
       <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
       <c r="I19" s="6" t="n">
-        <v>326</v>
+        <v>325.9412</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 83 months old, 100% developed, zero IBNR. Tail maturity; CL ultimate deterministic at actual=325.9412. Selection: 326 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 83 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K19" s="8" t="n">
-        <v>325.9412</v>
+        <v>325.94</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2018 is fully developed (age 83 months, CDF = 1.0, pct_developed 100%). Selection at actual.</t>
         </is>
       </c>
       <c r="M19" s="10" t="n"/>
@@ -3535,19 +3697,20 @@
       <c r="G20" s="4" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="6" t="n">
-        <v>358</v>
+        <v>357.6116</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 71 months old, 100% developed, zero IBNR. Late maturity; CL ultimate deterministic at actual=357.6116. Selection: 358 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 71 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K20" s="8" t="n">
-        <v>357.6116</v>
+        <v>357.61</v>
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2019 is fully developed (age 71 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M20" s="10" t="n"/>
@@ -3575,19 +3738,20 @@
       <c r="G21" s="4" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
       <c r="I21" s="6" t="n">
-        <v>371</v>
+        <v>370.8076</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 59 months old, 100% developed, zero IBNR. Mid maturity; CL ultimate deterministic at actual=370.8076. Selection: 371 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 59 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K21" s="8" t="n">
-        <v>370.8076</v>
+        <v>370.81</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2020 is fully developed (age 59 months, CDF = 1.0, pct_developed 100%). No remaining development.</t>
         </is>
       </c>
       <c r="M21" s="10" t="n"/>
@@ -3615,11 +3779,11 @@
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="6" t="n">
-        <v>330</v>
+        <v>329.9</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 47 months old, 100% developed, zero IBNR. Early-to-mid maturity; CL ultimate deterministic at actual=329.9. Selection: 330 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 47 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K22" s="8" t="n">
@@ -3627,7 +3791,8 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2021 is fully developed (age 47 months, CDF = 1.0, pct_developed 100%). Selection at actual.</t>
         </is>
       </c>
       <c r="M22" s="10" t="n"/>
@@ -3655,19 +3820,20 @@
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
       <c r="I23" s="6" t="n">
-        <v>298</v>
+        <v>298.2296</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 35 months old, 100% developed, zero IBNR. Early maturity; CL ultimate deterministic at actual=298.2296. Selection: 298 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 35 months (fully developed, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K23" s="8" t="n">
-        <v>298.2296</v>
+        <v>298.23</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2022 is fully developed (age 35 months, CDF = 1.0, pct_developed 100%). No IBNR.</t>
         </is>
       </c>
       <c r="M23" s="10" t="n"/>
@@ -3695,19 +3861,20 @@
       <c r="G24" s="4" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
       <c r="I24" s="6" t="n">
-        <v>305</v>
+        <v>304.8276</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 23 months old, 100% developed, zero IBNR. Green maturity; CL ultimate deterministic at actual=304.8276. Selection: 305 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Maturity: 23 months (early; fully developed by count standards, CDF = 1.0). Baseline Weight: Count CL 100%. Reasonability: Fully developed; selection = actual.</t>
         </is>
       </c>
       <c r="K24" s="8" t="n">
-        <v>304.8276</v>
+        <v>304.83</v>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available, CDF = 1.0, pct_developed = 1.0. Fully mature year with zero IBNR; actual count equals ultimate.</t>
+          <t>Chain Ladder (only available method)
+Year 2023 is fully developed (age 23 months, CDF = 1.0, pct_developed 100%). No remaining development expected.</t>
         </is>
       </c>
       <c r="M24" s="10" t="n"/>
@@ -3729,25 +3896,26 @@
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="n">
-        <v>286.2106832000001</v>
+        <v>286.82508896</v>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
       <c r="I25" s="6" t="n">
-        <v>286</v>
+        <v>286.8251</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Chain Ladder method, sole indicator. Period 11 months old (very green), 89.45% developed (CDF=1.118). CL ultimate=286.2107 with IBNR=30.2083. No alternate methods (a priori, Benktander) provided. CL extrapolation via CDF is standard for counts at green maturity when development is measurable. Selection: 286 (rounded).</t>
+          <t>Method Selection: Count Chain Ladder (100% weight). Eligible Methods: Count CL only. Screened Methods: None. Maturity: 11 months (green period, sparse development). CDF = 1.1204 (expected tail factor), pct_developed = 89.25%. Baseline Weight: Count CL 100% (sole method available for counts; appropriate for green periods). Diagnostic Overrides: None documented (no closure, adequacy, or severity signals in context). Prior Anchor: None provided; selected = ultimate_cl from CL projection. Asymmetric Conservatism: Not applied (convergence rule overrides; single method). Reasonability: Actual = 256.0024; projected ultimate = 286.8251 reflects expected count tail development (11% increase) typical for immature cohorts. IBNR = 30.82 counts is reasonable for 11-month period. No materiality flags. Cross-period: Consistent with 2023 maturity pattern.</t>
         </is>
       </c>
       <c r="K25" s="8" t="n">
-        <v>286.2107</v>
+        <v>286.83</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>Chain Ladder only method available; immature year at 11 months (age 0.92 years). CDF = 1.118 indicates 12% additional development expected. pct_developed = 0.894 confirms incompleteness. IBNR = 30.21. Other methods (IE, BF) unavailable. Chain Ladder ultimate of 286.21 is sole credible indication for early-year frequency. No prior available for comparison. Data volatility across historical years argues for reliance on development factors rather than trend adjustment.</t>
+          <t>Chain Ladder (only available method)
+Year 2024 is immature (age 11 months, pct_developed 89.25%, CDF 1.1204). Only Chain Ladder available; Incurred Estimate and Bornhuetter-Ferguson not computed. Chain Ladder projects ultimate of 286.83 from current actual of 256.00. Expected IBNR of 30.82 claims over remaining development. Selection at CL projection; no alternative methods to cross-check, but CL is appropriate for developing count data.</t>
         </is>
       </c>
       <c r="M25" s="10" t="n"/>

--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -591,7 +591,7 @@
         <v>3042294.662276</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3279961.952959755</v>
+        <v>3231957.295999402</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>3054159.611458877</v>
@@ -603,7 +603,7 @@
         <v>3163773.699688</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>3275846.139913155</v>
+        <v>3230518.847907371</v>
       </c>
       <c r="J2" s="3" t="n">
         <v>3054585.445649627</v>
@@ -613,15 +613,15 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 287 months (fully developed). Paid CL ultimate 3,054,160; Incurred CL 3,279,962. Paid CL is preferred at full maturity when payment data is highly credible and case adequacy effects are minimal. Convergence near 1.004 CDF indicates minimal tail. No material diagnostic concerns. Prior ultimate anchoring not specified, but selection reflects most mature measure choice.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 3,054,159.61. Year is at extreme tail maturity (287 months, 100% developed). Incurred IE disqualified (negative IBNR -121,479). Paid CL is primary method for fully-developed tail periods; closure rate stable (CDF 1.0039). Convergence not applicable—Paid CL is sole viable method at this age.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
-        <v>3054159.6</v>
+        <v>3054159.61</v>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. At 287 days of age and 99.6% developed, Paid loss CDFs are minimal (1.0039) and objective. Selected CL (3,054,160) over IE or BF as most credible for near-complete maturity.</t>
+          <t>Paid Loss, Chain Ladder. Fully mature (287 months); Paid and Incurred ultimates nearly converge. Paid preferred for stability; CL ultimate of 3,054,160 is credible with minimal IBNR (11,865).</t>
         </is>
       </c>
       <c r="O2" s="8" t="n"/>
@@ -645,7 +645,7 @@
         <v>2199646.228088</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2441936.099343652</v>
+        <v>2406196.567468195</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>2216836.925286216</v>
@@ -657,7 +657,7 @@
         <v>2904344.256599999</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2463561.601749763</v>
+        <v>2422440.488926942</v>
       </c>
       <c r="J3" s="3" t="n">
         <v>2222168.273848376</v>
@@ -667,15 +667,15 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 275 months (fully developed). Paid CL ultimate 2,216,837; Incurred CL 2,441,936. Paid CL 1.008 CDF indicates closure of final claims. Incurred CL higher (1.049 CDF) suggesting reserve bias. At this maturity, paid data is most credible. No IBNR concerns.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 2,216,836.93. Age 275 months, 99.2% developed. Incurred IE disqualified (negative IBNR -704,698). Paid CL is standard for tail years. Paid development very stable (CDF 1.0078). Incurred CL secondary (2,406,196.57) but Paid CL preferred at this extreme maturity.</t>
         </is>
       </c>
       <c r="M3" s="6" t="n">
-        <v>2216836.9</v>
+        <v>2216836.93</v>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 275 days, 99.2% developed. Paid CL (2,216,837) is stable and tightly developed. Incurred CL shows higher (2,441,936) with greater uncertainty.</t>
+          <t>Paid Loss, Chain Ladder. Mature (275 months, 99% developed); Incurred shows high estimate (2,904,344) with negative IBNR bias. Paid CL of 2,216,837 aligns with economic patterns; low IBNR of 17,191.</t>
         </is>
       </c>
       <c r="O3" s="8" t="n"/>
@@ -699,10 +699,10 @@
         <v>1778091.575843999</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1865327.593932697</v>
+        <v>1838027.15186976</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1805606.841693755</v>
+        <v>1805248.444146774</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2633272.1256</v>
@@ -711,25 +711,25 @@
         <v>2633272.1256</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>1901242.15568236</v>
+        <v>1863959.013395105</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>1818219.46023032</v>
+        <v>1817704.641044055</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1805606.84</v>
+        <v>1805248.44</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 263 months (fully developed). Paid CL 1,805,607 (CDF 1.015); Incurred CL 1,865,328 (CDF 1.049). Paid CL is lower and reflects actual payment finality. Incurred CL IBNR of 87k suggests residual case reserves. Paid measure is more objective at full maturity.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,805,248.44. Age 263 months (&gt;20 years). Incurred IE disqualified (negative IBNR -855,180). Paid CL (1,805,248.44) vs. Incurred CL (1,838,027.15): difference 1.8%. Paid CL preferred for tail maturity with stable closure rate (CDF 1.0153).</t>
         </is>
       </c>
       <c r="M4" s="6" t="n">
-        <v>1805606.8</v>
+        <v>1805248.44</v>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 263 days, 98.5% developed. Paid CL (1,805,607) is objective and closely developed. Incurred shows wide method spread (1.87Mâ€“2.63M).</t>
+          <t>Paid Loss, Chain Ladder. Mature (263 months, 98% developed); Incurred at 1,838,027 vs Paid at 1,805,248. Paid CL of 1,805,248 preferred for stability; Incurred shows IBNR of 59,936 suggesting conservative estimate in tail.</t>
         </is>
       </c>
       <c r="O4" s="8" t="n"/>
@@ -753,10 +753,10 @@
         <v>1122614.7306</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1197241.693034361</v>
+        <v>1180647.544279885</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1146484.675271811</v>
+        <v>1146826.988085745</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>1678710.98</v>
@@ -765,25 +765,25 @@
         <v>1678710.98</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1227252.83497899</v>
+        <v>1205129.044034783</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1157565.689018229</v>
+        <v>1158056.329824789</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>1146484.68</v>
+        <v>1146826.99</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 251 months (fully developed). Paid CL 1,146,485; Incurred CL 1,197,242. CDF 1.021 for Paid, 1.066 for Incurred. Incurred shows larger tail estimation (74.6k IBNR). Paid CL is cleaner at this age. No red flags on paid development.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,146,826.99. Age 251 months. Incurred IE disqualified (negative IBNR -556,096). Paid CL (1,146,826.99) vs. Incurred CL (1,180,647.54): 2.9% difference. Paid CL is primary for late tail; stable closure dynamics (CDF 1.0216).</t>
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1146484.7</v>
+        <v>1146826.99</v>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 251 days, 97.9% developed. Paid CL (1,146,485) shows tight development (CDF 1.0213). Incurred CL (1,197,242) is higher with more residual uncertainty.</t>
+          <t>Paid Loss, Chain Ladder. Mature (251 months, 98% developed); Paid CL of 1,146,827 slightly below Incurred CL of 1,180,648. Paid preferred for lower tail volatility; IBNR of 24,212 is modest.</t>
         </is>
       </c>
       <c r="O5" s="8" t="n"/>
@@ -807,10 +807,10 @@
         <v>2242149.132116</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2401480.441600801</v>
+        <v>2374326.10705006</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>2299898.748514981</v>
+        <v>2302875.950306176</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>1712285.2</v>
@@ -819,25 +819,25 @@
         <v>1712285.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2355754.322648214</v>
+        <v>2337470.78034635</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>2285143.987228427</v>
+        <v>2287302.07750861</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2299898.75</v>
+        <v>2302875.95</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 239 months (fully developed). Paid CL 2,299,899; Incurred CL 2,401,480. Paid shows normal development (CDF 1.026). Incurred CL IBNR of 159k and IE showing negative adjustment (-529.9k) indicates incurred measure instability. Paid is more reliable. Selected paid with confidence in tail closure.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 2,302,875.95. Age 239 months. Incurred IE disqualified (negative IBNR of -529,863 is implausible; case adequacy assumption broken). Paid CL (2,302,875.95) vs. Incurred CL (2,374,326.11): 3.0% difference. Paid CL preferred for stability; Incurred methods unreliable.</t>
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>2299898.7</v>
+        <v>2302875.95</v>
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 239 days, 97.5% developed. Paid CL (2,299,899) is conservative and well-developed. Incurred IE produces negative IBNR (âˆ’529,864), signaling misfit.</t>
+          <t>Paid Loss, Chain Ladder. Mature (239 months, 94% developed); Incurred shows negative IBNR (-529,864), indicating overstatement in prior periods. Paid CL of 2,302,876 is credible with positive IBNR of 60,727.</t>
         </is>
       </c>
       <c r="O6" s="8" t="n"/>
@@ -861,10 +861,10 @@
         <v>1462141.027856</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1639299.505334746</v>
+        <v>1621406.244220771</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1503399.990216312</v>
+        <v>1505496.30449533</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1746530.9035</v>
@@ -873,25 +873,25 @@
         <v>1746530.9035</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1647257.820909316</v>
+        <v>1629414.18011988</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1510072.418888043</v>
+        <v>1512437.61792685</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1503399.99</v>
+        <v>1505496.3</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 227 months (fully developed). Paid CL 1,503,400; Incurred CL 1,639,300. Paid CDF 1.028; Incurred 1.080. Incurred shows 121.7k IBNR and IE volatility. Paid measure reflects actual cash finality. No material concerns on paid development trajectory.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,505,496.30. Age 227 months (late tail). Incurred IE disqualified (negative IBNR -284,389). Paid CL (1,505,496.30) vs. Incurred CL (1,621,406.24): 7.1% difference. Paid CL preferred; Incurred CL link ratios show instability (case adequacy shifting). Paid development stable (CDF 1.0297).</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1503399.9</v>
+        <v>1505496.3</v>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 227 days, 97.3% developed. Paid CL (1,503,400) is stable. Incurred shows wide divergence (1.64Mâ€“1.75M). Paid's tighter CDF (1.0282) preferred at this maturity.</t>
+          <t>Paid Loss, Chain Ladder. Mature (227 months, 97% developed); Incurred at 1,621,406 and Paid at 1,505,496 diverge moderately. Paid CL of 1,505,496 preferred given cleaner paid emergence; positive IBNR of 43,355.</t>
         </is>
       </c>
       <c r="O7" s="8" t="n"/>
@@ -915,10 +915,10 @@
         <v>4790693.153152</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>5196434.670328665</v>
+        <v>5139714.612697149</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>4947059.081403897</v>
+        <v>4955930.27138136</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>2850338.4352</v>
@@ -927,25 +927,25 @@
         <v>2850338.4352</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>5022316.132969944</v>
+        <v>4993195.311194554</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>4880786.238340226</v>
+        <v>4885727.119172582</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4947059.08</v>
+        <v>4955930.27</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 215 months. Paid CL 4,947,059; Incurred CL 5,196,435. Paid CDF 1.033, Incurred 1.081. Large Incurred IBNR (385.7k) and negative IE (-1,960.4k) indicate case adequacy instability. Paid CL more objective. Note: High loss period, paid development normal for this size.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 4,955,930.27. Age 215 months. Incurred IE disqualified (negative IBNR of -1,960,436; case adequacy severely degraded). Paid CL (4,955,930.27) vs. Incurred CL (5,139,714.61): 3.6% difference. Paid CL preferred; Incurred methods unreliable due to case reserve instability. Paid CDF 1.0345 is reasonable.</t>
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>4947059.1</v>
+        <v>4955930.27</v>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 215 days, 96.8% developed. Paid CL (4,947,059) is credible with reasonable IBNR (156,366). Incurred CL much higher (5,196,435) with large IBNR variance across methods.</t>
+          <t>Paid Loss, Chain Ladder. Mature (215 months, 97% developed); Incurred shows negative IBNR (-1,960,436) reflecting volatility in incurred reporting. Paid CL of 4,955,930 is stable; IBNR of 165,237 reasonable for 97% developed.</t>
         </is>
       </c>
       <c r="O8" s="8" t="n"/>
@@ -969,10 +969,10 @@
         <v>1378427.939547998</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1491908.711537647</v>
+        <v>1475624.248541786</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1426693.030872698</v>
+        <v>1428966.218134835</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>2543927.0535</v>
@@ -981,25 +981,25 @@
         <v>2543927.0535</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1571929.595302119</v>
+        <v>1545991.138779771</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1464489.109613045</v>
+        <v>1468399.061680042</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1426693.03</v>
+        <v>1428966.22</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 203 months. Paid CL 1,426,693; Incurred CL 1,491,909. Paid CDF 1.035, Incurred 1.082. Incurred IE shows 1,165.5k IBNR (unrealistic), suggesting case adequacy bias. Paid measure is cleaner. IBNR on Paid (48.3k) is reasonable tail.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,428,966.22. Age 203 months. Incurred IE disqualified (negative IBNR -1,165,499). Paid CL (1,428,966.22) vs. Incurred CL (1,475,624.25): 3.2% difference. Paid CL is stable; Incurred CL shows case adequacy issues (CDF 1.0705). Paid development is more credible (CDF 1.0367).</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>1426693</v>
+        <v>1428966.22</v>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 203 days, 96.6% developed. Paid CL (1,426,693) shows tight development. Incurred CL (1,491,909) and BF (1,571,930) both higher with elevated uncertainty.</t>
+          <t>Paid Loss, Chain Ladder. Mature (203 months, 96% developed); Incurred inflated estimate (2,543,927) with IBNR of 1,165,499 appears inconsistent with development pattern. Paid CL of 1,428,966 with IBNR of 50,538 more credible.</t>
         </is>
       </c>
       <c r="O9" s="8" t="n"/>
@@ -1023,10 +1023,10 @@
         <v>1169581.089256</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1276754.755235623</v>
+        <v>1261566.686868999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1225907.268781485</v>
+        <v>1226405.584124</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2594805.5945</v>
@@ -1035,25 +1035,25 @@
         <v>2594805.5945</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1387394.90739657</v>
+        <v>1358778.177118244</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1288803.390543776</v>
+        <v>1289809.274039944</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1225907.27</v>
+        <v>1226405.58</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 191 months. Paid CL 1,225,907; Incurred CL 1,276,755. Paid CDF 1.048, Incurred 1.092. Incurred IE (1,425.2k IBNR) is illogical relative to actual reported. Paid measure reflects real payment momentum. Convergence check: Paid and Incurred within reasonable distance; Paid selected as more objective.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,226,405.58. Age 191 months. Incurred IE disqualified (negative IBNR -1,425,224). Paid CL (1,226,405.58) vs. Incurred CL (1,261,566.69): 2.8% difference. Paid CL preferred; Incurred CL link ratios unstable (CDF 1.0786 vs. Paid CDF 1.0486). Paid method more credible.</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>1225907.3</v>
+        <v>1226405.58</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 191 days, 95.4% developed. Paid CL (1,225,907) preferred. Incurred shows large outlier with IE (2,594,806) producing negative IBNR relative to actual (1,169,581).</t>
+          <t>Paid Loss, Chain Ladder. Mature (191 months, 95% developed); Incurred at 2,594,806 with huge IBNR (1,425,225) seems excessive given maturity. Paid CL of 1,226,406 with moderate IBNR of 56,824 more reasonable.</t>
         </is>
       </c>
       <c r="O10" s="8" t="n"/>
@@ -1077,10 +1077,10 @@
         <v>1277672.072084001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1401305.900053323</v>
+        <v>1383120.216654225</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1352060.191998799</v>
+        <v>1360648.27608661</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>1134300.7311</v>
@@ -1089,25 +1089,25 @@
         <v>1134300.7311</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1377748.680231413</v>
+        <v>1364150.388313432</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1340079.425916207</v>
+        <v>1346844.958654484</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1352060.19</v>
+        <v>1360648.28</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 179 months. Paid CL 1,352,060; Incurred CL 1,401,306. Paid CDF 1.058, Incurred 1.097. Incurred IE shows negative IBNR (-143.4k), indicating overstated reported reserves. Paid development is steady. IBNR 74.4k on paid is credible tail.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,360,648.28. Age 179 months. Incurred IE disqualified (negative IBNR of -143,371; case adequacy assumption violated). Paid CL (1,360,648.28) vs. Incurred CL (1,383,120.22): 1.6% difference within convergence band. Paid CL selected; closure rate stable (CDF 1.0649) and Paid method more robust.</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>1352060.2</v>
+        <v>1360648.28</v>
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 179 days, 94.5% developed. Paid CL (1,352,060) is stable. Incurred IE shows negative IBNR (âˆ’143,371), indicating poor model fit.</t>
+          <t>Paid Loss, Chain Ladder. Mature (179 months, 94% developed); Incurred shows negative IBNR (-143,371) suggesting overestimation in prior reporting. Paid CL of 1,360,648 is stable with reasonable IBNR of 82,976.</t>
         </is>
       </c>
       <c r="O11" s="8" t="n"/>
@@ -1131,10 +1131,10 @@
         <v>1892658.297732</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2122505.959947404</v>
+        <v>2117984.607676839</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2019075.00375851</v>
+        <v>2044396.423211293</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1542648.9944</v>
@@ -1143,25 +1143,25 @@
         <v>1542648.9944</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2066111.95371665</v>
+        <v>2063139.071221794</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1989245.400273576</v>
+        <v>2007155.987135647</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2019075</v>
+        <v>2044396.42</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 167 months. Paid CL 2,019,075; Incurred CL 2,122,506. Paid CDF 1.067, Incurred 1.108. Incurred IE shows -350k negative reserve (stale case reserves), Paid normal. Paid CDF 1.067 reasonable for this age. Selected Paid CL as more stable measure.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 2,044,396.42. Age 167 months. Incurred IE disqualified (negative IBNR of -373,432). Paid CL (2,044,396.42) vs. Incurred CL (2,117,984.61): 3.5% difference. Paid CL preferred; Incurred CL shows elevated CDF (1.1054) indicating link ratio volatility and case reserve degradation. Paid development more stable (CDF 1.0802).</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>2019075</v>
+        <v>2044396.42</v>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 167 days, 93.7% developed. Paid CL (2,019,075) is conservative and credible. Incurred CL (2,122,506) is higher; IE shows negative IBNR.</t>
+          <t>Paid Loss, Chain Ladder. Semi-mature (167 months, 93% developed); Incurred at 2,117,985 vs Paid at 2,044,396. Paid CL of 2,044,396 preferred; IBNR of 151,738 reasonable given development level.</t>
         </is>
       </c>
       <c r="O12" s="8" t="n"/>
@@ -1185,10 +1185,10 @@
         <v>1194236.878339999</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1511278.297096373</v>
+        <v>1508058.979134975</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1282667.00786582</v>
+        <v>1307266.93761061</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>1573501.9744</v>
@@ -1197,25 +1197,25 @@
         <v>1573501.9744</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1517352.322522519</v>
+        <v>1514321.194828627</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1302717.86565162</v>
+        <v>1330286.384612934</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1282667.01</v>
+        <v>1307266.94</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 155 months. Paid CL 1,282,667; Incurred CL 1,511,278. Paid CDF 1.074, Incurred 1.108. Incurred IE (379.3k IBNR) diverges significantly, suggesting case bias. Paid measure is developing smoothly. Paid IBNR 88.4k is reasonable for expected tail.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,307,266.94. Age 155 months (late maturity, 60–84 months band lower range). Incurred IE disqualified (negative IBNR -209,748). Paid CL (1,307,266.94) vs. Incurred CL (1,508,058.98): 13.3% divergence signals Incurred CL instability. Paid CL is primary; closure rate stable (CDF 1.0946).</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>1282667</v>
+        <v>1307266.94</v>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 155 days, 93.1% developed. Paid CL (1,282,667) with IBNR (88,430). Incurred CL (1,511,278) shows larger IBNR; IE slightly above but within tolerance.</t>
+          <t>Paid Loss, Chain Ladder. Semi-mature (155 months, 91% developed); Incurred shows positive IBNR but higher estimate (1,508,059). Paid CL of 1,307,267 is stable baseline; IBNR of 113,030 proportional to development.</t>
         </is>
       </c>
       <c r="O13" s="8" t="n"/>
@@ -1239,10 +1239,10 @@
         <v>708529.9908599999</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>787766.7671870498</v>
+        <v>785226.8166825377</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>776290.7860622795</v>
+        <v>789162.5275511343</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>1203729.0102</v>
@@ -1251,25 +1251,25 @@
         <v>1203729.0102</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>829605.9365744647</v>
+        <v>826103.9099766345</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>813600.9725123071</v>
+        <v>831520.7819741224</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>776290.79</v>
+        <v>789162.53</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 143 months. Paid CL 776,291; Incurred CL 787,767. Paid CDF 1.096, Incurred 1.112. Close convergence (1.5% apart). Paid selected as primary at this maturity with Incurred CL as secondary confirmation. Paid IBNR 67.8k is reasonable.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 789,162.53. Age 143 months. Incurred IE disqualified (negative IBNR -495,199). Paid CL (789,162.53) vs. Incurred CL (785,226.82): 0.5% convergence within acceptable band. Paid CL selected; both methods close but Paid shows superior fitness (stable CDF 1.1138 vs. Incurred CDF 1.0823 suggests CDF escalation anomaly in Incurred). Paid preferred.</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>776290.8</v>
+        <v>789162.53</v>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 143 days, 91.3% developed. Paid CL (776,291) is tightest and most credible. Incurred shows wide method spread (787,767â€“1,203,729).</t>
+          <t>Paid Loss, Chain Ladder. Semi-mature (143 months, 90% developed); Incurred at 785,227 vs Paid at 789,163 converge closely. Paid CL of 789,163 slightly higher but within method variance; IBNR of 80,633.</t>
         </is>
       </c>
       <c r="O14" s="8" t="n"/>
@@ -1293,10 +1293,10 @@
         <v>1389603.684732</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1603562.482294016</v>
+        <v>1593926.135949576</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1552188.211351658</v>
+        <v>1576996.525485472</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>1227803.5905</v>
@@ -1305,25 +1305,25 @@
         <v>1227803.5905</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1553426.038251954</v>
+        <v>1546993.562196584</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1518210.424612808</v>
+        <v>1535502.295789674</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1552188.21</v>
+        <v>1576996.53</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 131 months. Paid CL 1,552,188; Incurred CL 1,603,562. Paid CDF 1.117, Incurred 1.154. Incurred IE negative IBNR (-161.8k) signals case reserve over-statement. Paid is more credible. Paid IBNR 162.6k is reasonable for maturity.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,576,996.53. Age 131 months (late-to-mid transition, 84 months threshold). Incurred IE disqualified (negative IBNR of -161,800). Paid CL (1,576,996.53) vs. Incurred CL (1,593,926.14): 1.1% convergence. Paid CL selected; late maturity band and Paid method's stability preferred. CDF 1.1349 shows development still present.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>1552188.2</v>
+        <v>1576996.53</v>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 131 days, 89.5% developed. Paid CL (1,552,188) is stable with reasonable IBNR (162,585). Incurred CL higher (1,603,562) with elevated uncertainty.</t>
+          <t>Paid Loss, Chain Ladder. Semi-mature (131 months, 88% developed); Incurred at 1,593,926 slightly higher. Paid CL of 1,576,997 represents stable development with reasonable IBNR of 187,393 given maturity.</t>
         </is>
       </c>
       <c r="O15" s="8" t="n"/>
@@ -1347,10 +1347,10 @@
         <v>3364231.298548001</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3926874.473669822</v>
+        <v>3912201.443389074</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3790166.025843766</v>
+        <v>3849598.119511252</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>1669812.8832</v>
@@ -1359,25 +1359,25 @@
         <v>1669812.8832</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3614248.969194431</v>
+        <v>3608853.655823925</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3551883.05052697</v>
+        <v>3574765.423295849</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3790166.03</v>
+        <v>3849598.12</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 119 months. Paid CL 3,790,166; Incurred CL 3,926,874. Paid CDF 1.127, Incurred 1.161. Incurred IE shows catastrophic -1,713k negative IBNR, completely unreliable. Paid measure is the only credible option. Paid IBNR 425.9k reasonable for this maturity and size.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 3,849,598.12. Age 119 months (mid-maturity band). Incurred IE disqualified (negative IBNR of -1,713,150; implausible). Paid CL (3,849,598.12) vs. Incurred CL (3,912,201.44): 1.6% convergence. Paid CL selected; Incurred IE severely disqualified, and Paid CL stability preferred at this maturity. CDF 1.1443 indicates meaningful development remains.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>3790166</v>
+        <v>3849598.12</v>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 119 days, 88.8% developed. Paid CL (3,790,166) is balanced. Incurred shows extreme divergence: CL (3,926,874) vs IE (1,669,813, with âˆ’1.71M IBNR). Paid credibility preferred.</t>
+          <t>Paid Loss, Chain Ladder. Semi-mature (119 months, 87% developed); Incurred shows negative IBNR (-1,713,150) reflecting reporting volatility. Paid CL of 3,849,598 with IBNR of 485,367 more credible given 87% development.</t>
         </is>
       </c>
       <c r="O16" s="8" t="n"/>
@@ -1401,10 +1401,10 @@
         <v>2462208.676391999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3012277.997028591</v>
+        <v>3038991.699049049</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>2891278.871996263</v>
+        <v>2999163.000705052</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>2554813.7112</v>
@@ -1413,25 +1413,25 @@
         <v>2554813.7112</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2935440.451726489</v>
+        <v>2954126.002485343</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>2841346.928815287</v>
+        <v>2919609.047669128</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2891278.87</v>
+        <v>2999163</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 107 months. Paid CL 2,891,279; Incurred CL 3,012,278. Paid CDF 1.174, Incurred 1.202. Incurred IE positive (92.6k IBNR) but Incurred CL IBNR 506k signals divergence. Paid measure at 1.174 is reasonable for this maturity. Paid development stable.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 2,999,163.00. Age 107 months (mid-maturity, 60–84 month band). Incurred IE disqualified (negative IBNR -48,490 marginal). Paid CL (2,999,163.00) vs. Incurred CL (3,038,991.70): 1.3% convergence. Paid CL selected; entering mid-maturity phase where Paid CL remains primary. CDF 1.2181 shows substantial development ahead.</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>2891278.9</v>
+        <v>2999163</v>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 107 days, 85.2% developed. Paid CL (2,891,279) with solid IBNR (429,070). Incurred CL (3,012,278) is higher; IE at 2,554,814 shows method divergence.</t>
+          <t>Paid Loss, Chain Ladder. Semi-mature (107 months, 82% developed); Incurred at 3,038,992 vs Paid at 2,999,163. Paid CL of 2,999,163 preferred; methods generally converge; IBNR of 536,954 appropriate for 82% maturity.</t>
         </is>
       </c>
       <c r="O17" s="8" t="n"/>
@@ -1455,10 +1455,10 @@
         <v>1205811.828916</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1479229.479295419</v>
+        <v>1483428.985619581</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1434346.607519169</v>
+        <v>1488161.050025837</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>2605909.9854</v>
@@ -1467,25 +1467,25 @@
         <v>2605909.9854</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1687482.722635417</v>
+        <v>1693496.327321603</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1621012.073021027</v>
+        <v>1700231.874815779</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1434346.61</v>
+        <v>1488161.05</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 95 months. Paid CL 1,434,347; Incurred CL 1,479,229. Paid CDF 1.190, Incurred 1.227. Incurred IE (1,400k IBNR) shows case growth bias. Paid measure more stable. At 95 months, paid development reasonable. Paid IBNR 228.5k credible for maturity.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,488,161.05. Age 95 months (mid-maturity lower range). Incurred IE disqualified (negative IBNR -1,400,098; implausible). Paid CL (1,488,161.05) vs. Incurred CL (1,483,428.99): 0.3% convergence. Both very close; Paid CL selected for superior fitness. CDF 1.2342 indicates ~19% development remaining.</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>1434346.6</v>
+        <v>1488161.05</v>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 95 days, 84.1% developed. Paid CL (1,434,347) is credible. Incurred CL (1,479,229) is close but higher with greater residual IBNR spread.</t>
+          <t>Paid Loss, Chain Ladder. Developing (95 months, 81% developed); Incurred shows large IBNR (277,617) with high tail factor (CDF 1.230). Paid CL of 1,488,161 more stable; IBNR of 282,349 reasonable for development stage.</t>
         </is>
       </c>
       <c r="O18" s="8" t="n"/>
@@ -1509,10 +1509,10 @@
         <v>2395448.423304001</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2960949.473612469</v>
+        <v>2966113.902250904</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2938070.292338315</v>
+        <v>3053327.907687196</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>2215023.4875</v>
@@ -1521,25 +1521,25 @@
         <v>2215023.4875</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>2818487.762476162</v>
+        <v>2821607.863241079</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>2804533.320924196</v>
+        <v>2872704.241843637</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2938070.29</v>
+        <v>3053327.91</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 83 months. Paid CL 2,938,070; Incurred CL 2,960,949. Paid CDF 1.227, Incurred 1.236. Very close convergence (0.8% apart). Both measures reasonable. Paid selected with Incurred as secondary check. Paid IBNR 542.6k reasonable for maturity.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 3,053,327.91. Age 83 months (mid-maturity band, 36–60+ mo). Incurred IE disqualified (negative IBNR of -180,424). Paid CL (3,053,327.91) vs. Incurred CL (2,966,113.90): 2.9% difference. Paid CL selected; Incurred IE failure disqualifies blending. CDF 1.2746 shows significant development. Paid method more robust at this maturity.</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>2938070.3</v>
+        <v>3053327.91</v>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 83 days, 81.5% developed. Paid CL (2,938,070) with reasonable IBNR (542,622). Incurred CL higher (2,960,949) with larger IBNR (565,501).</t>
+          <t>Paid Loss, Chain Ladder. Developing (83 months, 78% developed); Incurred shows negative IBNR (-180,425) despite high CDF. Paid CL of 3,053,328 with IBNR of 657,879 reflects consistent development; tail factor CDF 1.275.</t>
         </is>
       </c>
       <c r="O19" s="8" t="n"/>
@@ -1563,10 +1563,10 @@
         <v>2395189.834488001</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3482306.165211298</v>
+        <v>3499325.385714762</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3294690.132441459</v>
+        <v>3379669.118916158</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>2259323.9575</v>
@@ -1575,25 +1575,25 @@
         <v>2259323.9575</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>3172400.04746508</v>
+        <v>3180603.953488337</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3012019.488036837</v>
+        <v>3053318.649679323</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3294690.13</v>
+        <v>3379669.12</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 71 months. Paid CL 3,294,690; Incurred CL 3,482,306. Paid CDF 1.376, Incurred 1.339. Paid higher here (unusual), but Incurred IE negative (-135.9k) signals case adequacy decline. Paid CDF 1.376 indicates significant tail development expected. Paid measure is cleaner. Paid IBNR 899.5k reflects substantial remaining development.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 3,379,669.12. Age 71 months (early maturity, 36–60 boundary). Incurred IE disqualified (negative IBNR of -340,558). Paid CL (3,379,669.12) vs. Incurred CL (3,499,325.39): 3.4% difference. Paid CL selected; ~29% development remains (CDF 1.4110). At early maturity, Paid CL credibility exceeds Incurred CL; Incurred IE disqualified.</t>
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>3294690.1</v>
+        <v>3379669.12</v>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 71 days, 72.7% developed. Paid CL (3,294,690) is conservative. Incurred CL (3,482,306) is higher; IE shows negative IBNR (âˆ’340,559), indicating poor fit at this maturity.</t>
+          <t>Paid Loss, Chain Ladder. Developing (71 months, 71% developed); Paid CL of 3,379,669 with IBNR of 984,479 is stable anchor. Incurred shows negative IBNR (-340,559) inconsistent with development pattern. Paid CDF of 1.411 appropriate for maturity.</t>
         </is>
       </c>
       <c r="O20" s="8" t="n"/>
@@ -1617,10 +1617,10 @@
         <v>976050.8625559999</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1451570.488544801</v>
+        <v>1452867.568993012</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1502370.929493663</v>
+        <v>1541396.593032421</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>1843608.3492</v>
@@ -1629,25 +1629,25 @@
         <v>1843608.3492</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>1579228.718643454</v>
+        <v>1580338.684271852</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>1621915.376244909</v>
+        <v>1652240.308933594</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1502370.93</v>
+        <v>1541396.59</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 59 months. Paid CL 1,502,371; Incurred CL 1,451,570. Paid CDF 1.539, Incurred 1.483. Paid higher, reflecting newer claims and heavy development ahead. Paid CDF 1.539 is substantial. Incurred IE (864.7k IBNR) is 59.6% of reportedâ€”unrealistic. Paid measure is primary. IBNR 526.3k significant but reasonable for age 59.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,541,396.59. Age 59 months (early maturity, high immaturity). Incurred IE disqualified (negative IBNR -864,708). Paid CL (1,541,396.59) vs. Incurred CL (1,452,867.57): 5.8% divergence signals Incurred instability. Paid CL is primary; ~37% development remains (CDF 1.5792). Paid BF secondary (1,652,240.31) is 7.2% higher but Paid CL credible at 59 months.</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>1502370.9</v>
+        <v>1541396.59</v>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 59 days, 65.0% developed. Paid CL (1,502,371) with IBNR (526,320) is credible. Incurred CL (1,451,570) is lower with lower IBNR; at this immature stage, Paid's development profile is more reliable.</t>
+          <t>Paid Loss, Chain Ladder. Early developing (59 months, 63% developed); Paid CL of 1,541,397 with IBNR of 565,346 reflects early development stage. CDF of 1.579 substantial but credible given only 63% maturity. Incurred at 1,452,867 lower, but Paid CL more stable.</t>
         </is>
       </c>
       <c r="O21" s="8" t="n"/>
@@ -1671,10 +1671,10 @@
         <v>974979.4133360002</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1585114.784191883</v>
+        <v>1586080.903195961</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1639388.404900304</v>
+        <v>1690287.645861596</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>1410360.3873</v>
@@ -1683,25 +1683,25 @@
         <v>1410360.3873</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1521854.800216676</v>
+        <v>1522402.900950825</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1546568.256997011</v>
+        <v>1571825.990505082</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1639388.4</v>
+        <v>1690287.65</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 47 months. Paid CL 1,639,388; Incurred CL 1,585,115. Paid CDF 1.681, Incurred 1.567. Paid development is heavy (67.1% IBNR ratio). Incurred IE (399k IBNR, 39.4% of reported) also substantial. Paid shows stronger development signal; selected as primary. Paid IBNR 664.4k reflects significant immaturity.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,690,287.65. Age 47 months (green maturity, 24–36 boundary). Incurred IE disqualified (negative IBNR -435,380). Paid CL (1,690,287.65) vs. Incurred CL (1,586,080.90): 6.2% divergence. At green maturity, baseline is BF-heavy, but Paid CL (1,690,287.65) and Paid BF (1,571,825.99) differ 7.0%. Paid CL selected as more data-driven; 42% development remains (CDF 1.7337).</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>1639388.4</v>
+        <v>1690287.65</v>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 47 days, 59.5% developed. Paid CL (1,639,388) with IBNR (664,409). Incurred CL (1,585,115) is lower; IE shows negative IBNR (399,047). Maintain Paid for consistency.</t>
+          <t>Paid Loss, Chain Ladder. Early developing (47 months, 58% developed); Paid CL of 1,690,288 with IBNR of 715,308 reflects 58% development. CDF of 1.734 reflects high tail uncertainty. Incurred at 1,586,081 lower but Paid CL provides more conservative tail estimate.</t>
         </is>
       </c>
       <c r="O22" s="8" t="n"/>
@@ -1725,10 +1725,10 @@
         <v>791103.7101360001</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1539912.420262669</v>
+        <v>1557461.13912603</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1562862.384231543</v>
+        <v>1645673.387741628</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>959045.0632000001</v>
@@ -1737,25 +1737,25 @@
         <v>959045.0632000001</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1271153.077093026</v>
+        <v>1276959.319457941</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1264690.734714008</v>
+        <v>1289119.195209133</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1562862.38</v>
+        <v>1645673.39</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 35 months. Paid CL 1,562,862; Incurred CL 1,539,912. Paid CDF 1.976, Incurred 1.861. Paid shows accelerated development (49.5% IBNR ratio). Very close convergence (1.5% apart). Paid selected for its objective payment-based development. Paid IBNR 771.8k reflects green maturity.</t>
+          <t>Paid Loss selected. Paid CL ultimate of 1,645,673.39. Age 35 months (green, transitioning toward very green). Paid CL (1,645,673.39) vs. Paid BF (1,289,119.20): 21.6% divergence signals extreme immaturity. Paid BF is typically primary for &lt;24 mo. However, ~52% development has occurred (CDF 2.0802). Paid CL selected with reduced confidence due to potential link ratio volatility; Incurred IE disqualified (negative IBNR -167,941).</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>1562862.4</v>
+        <v>1645673.39</v>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss CL. 35 days, 50.6% developed. Paid CL (1,562,862) with IBNR (771,759). Incurred CL (1,539,912) is close but lower; large immature year volatility favors Paid's more stable development curve.</t>
+          <t>Paid Loss, Chain Ladder. Early developing (35 months, 48% developed); Paid CL of 1,645,673 with IBNR of 854,570 reflects 48% development stage and high uncertainty (CDF 2.080). Incurred at 1,557,461 lower but tail factor higher at 1.882; Paid CL more stable.</t>
         </is>
       </c>
       <c r="O23" s="8" t="n"/>
@@ -1779,10 +1779,10 @@
         <v>1199242.068356001</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>3783910.827529524</v>
+        <v>3909734.914216431</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3369891.480069201</v>
+        <v>3548451.088388032</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>978225.9646000001</v>
@@ -1791,25 +1791,25 @@
         <v>978225.9646000001</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2202966.427497723</v>
+        <v>2216708.772179807</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1829347.110948638</v>
+        <v>1846864.707762819</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3369891.48</v>
+        <v>1846864.71</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 23 months. Paid CL 3,369,891; Incurred CL 3,783,911. Paid CDF 2.810, Incurred 2.291. Paid shows stronger development factor, reflecting real payment acceleration. Paid CDF 2.810 indicates 64% of ultimate still to develop. Incurred IE negative (-221k) unreliable. Paid IBNR 2,170.6k (64.4% of ultimate) reasonable for age 23.</t>
+          <t>Paid Loss selected. Paid BF ultimate of 1,846,864.71. Age 23 months (very green, 12–24 month boundary). Paid CL (3,548,451.09) shows extreme elevation (CDF 2.9589, 66% development) indicating volatile link ratios at extreme immaturity. Paid BF (1,846,864.71) is more stable method for very early years; prior loss ratio credible. Incurred IE disqualified (negative IBNR of -221,016). Paid BF is primary at this age.</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>1829347.1</v>
+        <v>3548451.09</v>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss BF. 23 days, 35.6% developed. Paid BF (1,829,347) with IBNR (630,105). Paid CL (3,369,891) shows extreme CDF (2.810) with elevated IBNR; BF dampens extrapolation risk. Incurred equally volatile.</t>
+          <t>Paid Loss, Chain Ladder. Immature (23 months, 34% developed); Paid CL of 3,548,451 with high IBNR of 2,349,209 reflects substantial development ahead (CDF 2.959). Incurred at 3,909,735 higher with lower IBNR, but Paid CL more consistent with tail development pattern.</t>
         </is>
       </c>
       <c r="O24" s="8" t="n"/>
@@ -1833,10 +1833,10 @@
         <v>355247.7609319999</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3471540.028680828</v>
+        <v>3586977.039069097</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>2579684.132128034</v>
+        <v>2757367.938729235</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>997790.4837999999</v>
@@ -1845,25 +1845,25 @@
         <v>997790.4837999999</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1632097.176702247</v>
+        <v>1640330.959347003</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1215632.726422747</v>
+        <v>1224487.089019148</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2579684.13</v>
+        <v>1224487.09</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>Paid CL selected. Age 11 months. Paid CL 2,579,684; Incurred CL 3,471,540. Paid CDF 7.262, Incurred 3.900. Paid shows extreme development factor, reflecting only 13.8% developed to date. Paid CDF credible given incipient claim emergence. Incurred IE (642.5k IBNR, 64.4% of reported) diverges sharply. At 11 months, Paid CL tail is justified. IBNR 2,224.4k (86.2% of ultimate) reflects heavy development ahead.</t>
+          <t>Paid Loss selected. Paid BF ultimate of 1,224,487.09. Age 11 months (&lt;12 months, extreme immaturity). Paid CL (2,757,367.94) inflated by extreme CDF (7.7618) indicating unreliable link ratios (&lt;13% developed). Paid BF (1,224,487.09) is primary method for a priori estimation at extreme youth; prior loss ratio informative. Incurred IE disqualified (negative IBNR -642,542). Paid BF selected per maturity-based hierarchy for very green years.</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>1215632.7</v>
+        <v>2757367.94</v>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Paid Loss BF. 11 days, 13.8% developed. Paid BF (1,215,633) with IBNR (860,385). Paid CL (2,579,684) shows extreme CDF (7.262) driven by minimal historical development; BF's Bayesian approach provides stability. Incurred CL equally extreme.</t>
+          <t>Paid Loss, Chain Ladder. Highly immature (11 months, 13% developed); Paid CL of 2,757,368 with extreme IBNR of 2,402,120 reflects very early stage (CDF 7.762). High uncertainty but CL is most credible single-method selection given maturity constraints and paid emergence patterns.</t>
         </is>
       </c>
       <c r="O25" s="8" t="n"/>
@@ -1984,19 +1984,19 @@
         <v>700.7076000000001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>700.7076</v>
+        <v>700.71</v>
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 287 months (fully developed, CDF 1.000). Ultimate 700.7 counts. No IBNR needed (0.0). All three methods (CL, IE, BF) converge on ~700-701, indicating full closure and claim count maturity. Reported Count is appropriate measure at this age. Zero additional development expected.</t>
+          <t>Reported Count selected. Reported CL ultimate of 700.71 (CDF 1.0, 100% developed). All methods (CL, IE, BF) converge at 700.7–700.8 for fully-developed tail period. Reported IE (700.78) is 0.01% higher but adds minimal IBNR (0.07 counts). Reported CL selected as standard method for fully-developed years. Count data shows no case adequacy issues.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n">
-        <v>700.7076</v>
+        <v>700.71</v>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 287 days, 100% developed. CDF = 1.0; actual = ultimate. CL, IE, and BF all converge to approximately 700.71.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 287 months); all methods converge at 700.71. No IBNR needed; count development complete.</t>
         </is>
       </c>
       <c r="K2" s="8" t="n"/>
@@ -2026,19 +2026,19 @@
         <v>651.8824000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>651.8824</v>
+        <v>651.88</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 275 months (fully developed, CDF 1.000). Ultimate 651.9 counts. Zero IBNR. Reported IE shows 31.3 additional counts (overstated relative to CL/BF convergence). Reported CL and BF both indicate ~651.9, suggesting stable closure. CL selected as primary.</t>
+          <t>Reported Count selected. Reported CL ultimate of 651.88 (CDF 1.0, 100% developed). Reported IE (683.17) shows elevated IBNR (+31.28 counts), implying late reporting, but at full maturity this is implausible. Reported CL is primary. Reported BF (651.88) identical. Selection based on data-driven CL at extreme tail maturity.</t>
         </is>
       </c>
       <c r="I3" s="6" t="n">
-        <v>651.8824</v>
+        <v>651.88</v>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 275 days, 100% developed. CDF = 1.0; actual = ultimate. No residual development expected.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 275 months); CL ultimate of 651.88 with zero IBNR. IE method (683.17) and BF method (651.88) converge on same estimate.</t>
         </is>
       </c>
       <c r="K3" s="8" t="n"/>
@@ -2068,19 +2068,19 @@
         <v>551.5928</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>551.5928</v>
+        <v>551.59</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 263 months (fully developed, CDF 1.000). Ultimate 551.6 counts. Zero IBNR on CL. IE shows +97 counts (11.7% inflation, unreliable). CL and BF converge at 551.6, confirming full development. Reported Count CL is most credible.</t>
+          <t>Reported Count selected. Reported CL ultimate of 551.59 (CDF 1.0, 100% developed). Reported IE projects 648.44 (+96.85 IBNR) but this contradicts full development; case adequacy assumption fails. Reported CL is sole credible method at full maturity. IE disqualified due to implausible late reporting assumption at 100% development.</t>
         </is>
       </c>
       <c r="I4" s="6" t="n">
-        <v>551.5928</v>
+        <v>551.59</v>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 263 days, 100% developed. CDF = 1.0; actual = ultimate. No residual development.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 263 months); CL ultimate of 551.59. IE suggests higher estimate (648.44) with positive IBNR of 96.85; CL preferred for fully developed year.</t>
         </is>
       </c>
       <c r="K4" s="8" t="n"/>
@@ -2110,19 +2110,19 @@
         <v>642.6452</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>642.6452</v>
+        <v>642.65</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 251 months (fully developed, CDF 1.000). Ultimate 642.6 counts. CL shows zero IBNR. IE shows -14.8 counts (negative, illogical). CL at 642.6 is credible. BF at 642.6 confirms. Reported Count CL selected.</t>
+          <t>Reported Count selected. Reported CL ultimate of 642.65 (CDF 1.0, 100% developed). Reported IE (627.84) shows negative IBNR (-14.81), disqualifying it. Reported BF (642.65) identical. Reported CL is primary. Count is fully developed; no late-reporting signal.</t>
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>642.6452</v>
+        <v>642.65</v>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 251 days, 100% developed. CDF = 1.0; actual = ultimate. CL and BF identical at 642.65.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 251 months); CL ultimate of 642.65 with zero IBNR. IE method shows negative IBNR (-14.81) suggesting reported count is stable and complete.</t>
         </is>
       </c>
       <c r="K5" s="8" t="n"/>
@@ -2152,19 +2152,19 @@
         <v>641.3256</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>641.3256</v>
+        <v>641.33</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 239 months (fully developed, CDF 1.000). Ultimate 641.3 counts. CL zero IBNR. IE shows -17.7 counts (unreliable negative). CL and BF both ~641.3. Reported Count CL is only credible method at this maturity.</t>
+          <t>Reported Count selected. Reported CL ultimate of 641.33 (CDF 1.0, 100% developed). Reported IE (623.61) shows negative IBNR (-17.71), disqualifying case adequacy assumption. Reported BF (641.33) identical. CL is standard at full maturity; IE fitness fails.</t>
         </is>
       </c>
       <c r="I6" s="6" t="n">
-        <v>641.3256</v>
+        <v>641.33</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 239 days, 100% developed. CDF = 1.0; actual = ultimate. Minimal expected development.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 239 months); CL ultimate of 641.33. IE and BF converge at similar levels; reported count development is complete.</t>
         </is>
       </c>
       <c r="K6" s="8" t="n"/>
@@ -2194,19 +2194,19 @@
         <v>497.4892</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>497.4892</v>
+        <v>497.49</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 227 months (fully developed, CDF 1.000). Ultimate 497.5 counts. CL shows zero IBNR. IE shows +109.3 counts (22% inflation). CL at 497.5 and BF converge. Reported Count CL is objective measure. IE unreliable.</t>
+          <t>Reported Count selected. Reported CL ultimate of 497.49 (CDF 1.0, 100% developed). Reported IE (606.74) projects +109.26 IBNR despite full development; assumption violated. Reported BF (497.49) identical. Reported CL is sole credible method at maturity level.</t>
         </is>
       </c>
       <c r="I7" s="6" t="n">
-        <v>497.4892</v>
+        <v>497.49</v>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 227 days, 100% developed. CDF = 1.0; actual = ultimate. IE shows positive IBNR (+109.26) inconsistent with mature data.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 227 months); CL ultimate of 497.49. IE method estimates 606.74 with large IBNR (109.26), but CL is credible for fully developed year.</t>
         </is>
       </c>
       <c r="K7" s="8" t="n"/>
@@ -2236,19 +2236,19 @@
         <v>476.3756</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>476.3756</v>
+        <v>476.38</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 215 months (fully developed, CDF 1.000). Ultimate 476.4 counts. CL zero IBNR. IE shows +74.1 counts (15.6% overstate). CL 476.4 and BF converge. Reported Count CL is credible at full maturity. No additional development.</t>
+          <t>Reported Count selected. Reported CL ultimate of 476.38 (CDF 1.0, 100% developed). Reported IE (550.47) shows +74.10 IBNR; implausible at full development. Reported CL is primary. IE disqualified. BF matches CL.</t>
         </is>
       </c>
       <c r="I8" s="6" t="n">
-        <v>476.3756</v>
+        <v>476.38</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 215 days, 100% developed. CDF = 1.0; actual = ultimate. IE (+74.10) not credible at maturity; CL preferred.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 215 months); CL ultimate of 476.38. IE method shows inflation (550.47) with IBNR of 74.10; CL preferred for fully matured cohort.</t>
         </is>
       </c>
       <c r="K8" s="8" t="n"/>
@@ -2278,19 +2278,19 @@
         <v>328.5804000000001</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>328.5804</v>
+        <v>328.58</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 203 months (fully developed, CDF 1.000). Ultimate 328.6 counts. CL zero IBNR. IE shows +115.5 counts (35.2% inflation). CL 328.6 and BF converge. Reported Count CL only credible method. IE severely overestimates.</t>
+          <t>Reported Count selected. Reported CL ultimate of 328.58 (CDF 1.0, 100% developed). Reported IE (444.10) projects +115.52 IBNR despite full maturity; case adequacy assumption fails at 100% development. Reported CL is standard. IE disqualified for implausible development assumption.</t>
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>328.5804</v>
+        <v>328.58</v>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 203 days, 100% developed. CDF = 1.0; actual = ultimate. IE shows large positive IBNR (+115.52) inconsistent with full development.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 203 months); CL ultimate of 328.58. IE inflates estimate to 444.10 with IBNR of 115.52; CL more conservative and credible.</t>
         </is>
       </c>
       <c r="K9" s="8" t="n"/>
@@ -2320,19 +2320,19 @@
         <v>321.9824</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>321.9824</v>
+        <v>321.98</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 191 months (fully developed, CDF 1.000). Ultimate 322.0 counts. CL zero IBNR. IE shows +62.4 counts (19.4% overstate). CL and BF both 322.0. Reported Count CL is only objective measure at full development.</t>
+          <t>Reported Count selected. Reported CL ultimate of 321.98 (CDF 1.0, 100% developed). Reported IE (384.40) shows +62.42 IBNR; implausible at full development. Reported BF (321.98) matches CL. Reported CL is primary; IE fitness fails.</t>
         </is>
       </c>
       <c r="I10" s="6" t="n">
-        <v>321.9824</v>
+        <v>321.98</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 191 days, 100% developed. CDF = 1.0; actual = ultimate. CL and BF converge to 321.98; IE inflated at +62.42.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 191 months); CL ultimate of 321.98. IE method (384.40) shows inflation with IBNR of 62.42; CL preferred for fully reported cohort.</t>
         </is>
       </c>
       <c r="K10" s="8" t="n"/>
@@ -2362,19 +2362,19 @@
         <v>271.8376</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>271.8376</v>
+        <v>271.84</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 179 months (fully developed, CDF 1.000). Ultimate 271.8 counts. CL zero IBNR. IE shows +42.4 counts (15.6% inflation). CL 271.8 and BF converge. Reported Count CL is credible primary. IE unreliable.</t>
+          <t>Reported Count selected. Reported CL ultimate of 271.84 (CDF 1.0, 100% developed). Reported IE (314.20) projects +42.36 IBNR despite full development; case adequacy assumption violated. Reported CL selected as standard at maturity. IE disqualified.</t>
         </is>
       </c>
       <c r="I11" s="6" t="n">
-        <v>271.8376</v>
+        <v>271.84</v>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 179 days, 100% developed. CDF = 1.0; actual = ultimate. IE (+42.36) not credible; CL stable.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 179 months); CL ultimate of 271.84. IE and BF estimates higher; CL reflects actual reported count maturity.</t>
         </is>
       </c>
       <c r="K11" s="8" t="n"/>
@@ -2404,19 +2404,19 @@
         <v>345.7352</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>345.7352</v>
+        <v>345.74</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 167 months (fully developed, CDF 1.000). Ultimate 345.7 counts. CL zero IBNR. IE shows -26.4 counts (negative, illogical). CL 345.7 and BF converge. Reported Count CL is only sound method. IE unreliable at all ages.</t>
+          <t>Reported Count selected. Reported CL ultimate of 345.74 (CDF 1.0, 100% developed). Reported IE (319.33) shows negative IBNR (-26.41), disqualifying case adequacy model. Reported BF (345.74) matches CL. CL is primary at full maturity; IE fitness fails.</t>
         </is>
       </c>
       <c r="I12" s="6" t="n">
-        <v>345.7352</v>
+        <v>345.74</v>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 167 days, 100% developed. CDF = 1.0; actual = ultimate. IE shows negative IBNR (âˆ’26.41); CL most credible.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 167 months); CL ultimate of 345.74. IE method shows negative IBNR (-26.41) suggesting reported counts are complete and stable.</t>
         </is>
       </c>
       <c r="K12" s="8" t="n"/>
@@ -2446,19 +2446,19 @@
         <v>261.2808</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>261.2808</v>
+        <v>261.28</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 155 months (fully developed, CDF 1.000). Ultimate 261.3 counts. CL zero IBNR. IE shows +37.7 counts (14.4% inflation). CL 261.3 and BF converge. Reported Count CL is objective measure. IE consistently biased.</t>
+          <t>Reported Count selected. Reported CL ultimate of 261.28 (CDF 1.0, 100% developed). Reported IE (298.97) shows +37.68 IBNR despite full development; assumption violated. Reported BF (261.28) identical. Reported CL is primary. IE disqualified.</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
-        <v>261.2808</v>
+        <v>261.28</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 155 days, 100% developed. CDF = 1.0; actual = ultimate. IE (+37.68) not consistent with mature year; CL preferred.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 155 months); CL ultimate of 261.28. IE method shows IBNR of 37.68; CL is most credible for fully reported year.</t>
         </is>
       </c>
       <c r="K13" s="8" t="n"/>
@@ -2488,19 +2488,19 @@
         <v>291.6316</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>291.6316</v>
+        <v>291.63</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 143 months (fully developed, CDF 1.000). Ultimate 291.6 counts. CL zero IBNR. IE shows +14.1 counts (4.8% overstate). CL 291.6 and BF converge. Reported Count CL is credible. IE method not reliable across all periods.</t>
+          <t>Reported Count selected. Reported CL ultimate of 291.63 (CDF 1.0, 100% developed). Reported IE (305.75) shows +14.12 IBNR despite full maturity; implausible. Reported BF (291.63) matches CL. Reported CL is standard at full development; IE fitness marginal but fails on plausibility.</t>
         </is>
       </c>
       <c r="I14" s="6" t="n">
-        <v>291.6316</v>
+        <v>291.63</v>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 143 days, 100% developed. CDF = 1.0; actual = ultimate. Small IE adjustment (+14.12) immaterial.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 143 months); CL ultimate of 291.63. Methods show modest IBNR ranges; CL is credible and centered estimate.</t>
         </is>
       </c>
       <c r="K14" s="8" t="n"/>
@@ -2530,19 +2530,19 @@
         <v>455.2620000000001</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>455.262</v>
+        <v>455.26</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 131 months (fully developed, CDF 1.000). Ultimate 455.3 counts. CL zero IBNR. IE shows -113.9 counts (severely negative, illogical). CL 455.3 and BF converge. Reported Count CL is only credible method. IE completely unreliable.</t>
+          <t>Reported Count selected. Reported CL ultimate of 455.26 (CDF 1.0, 100% developed). Reported IE (341.33) shows negative IBNR (-113.93), disqualifying case adequacy assumption. Reported BF (455.26) matches CL. Reported CL is primary; IE fitness fails.</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>455.262</v>
+        <v>455.26</v>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 131 days, 100% developed. CDF = 1.0; actual = ultimate. IE shows large negative IBNR (âˆ’113.93); CL most credible.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 131 months); CL ultimate of 455.26. IE method shows negative IBNR (-113.93) suggesting reported counts are complete; CL is credible.</t>
         </is>
       </c>
       <c r="K15" s="8" t="n"/>
@@ -2572,19 +2572,19 @@
         <v>333.8588</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>333.8588</v>
+        <v>333.86</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 119 months (fully developed, CDF 1.000). Ultimate 333.9 counts. CL zero IBNR. IE shows +33.5 counts (10% inflation). CL 333.9 and BF converge. Reported Count CL is credible primary at full maturity.</t>
+          <t>Reported Count selected. Reported CL ultimate of 333.86 (CDF 1.0, 100% developed). Reported IE (367.36) shows +33.50 IBNR at full development; assumption violated. Reported BF (333.86) identical. Reported CL is standard at maturity. IE disqualified on fitness grounds.</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
-        <v>333.8588</v>
+        <v>333.86</v>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 119 days, 100% developed. CDF = 1.0; actual = ultimate. IE (+33.50) immaterial; CL stable.</t>
+          <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 119 months); CL ultimate of 333.86. IE method shows modest IBNR of 33.50; CL represents reported count maturity.</t>
         </is>
       </c>
       <c r="K16" s="8" t="n"/>
@@ -2614,19 +2614,19 @@
         <v>389.6759484250073</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>389.703</v>
+        <v>389.7</v>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 107 months (CDF 0.9977, slight reopening). Ultimate 389.7 counts. CL shows -0.9 IBNR (slight closure adjustment). IE shows +10.9 counts (2.8% inflation). CL 389.7 and BF (389.676) converge within 0.1%. Reported Count CL is credible primary.</t>
+          <t>Reported Count selected. Reported CL ultimate of 389.70 (CDF 0.9977, 100.2% developed). Slight CDF &lt;1.0 indicates potential reopens or count adjustments (marginal). Reported IE (401.53) shows +10.93 IBNR (2.7% adjustment). Reported CL selected as primary; IE is secondary backup. BF shows minimal negative IBNR (-0.93). CL is most credible.</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>389.7032</v>
+        <v>389.7</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 107 days, 100.2% developed (slight negative IBNR possible due to data reconciliation). CL (389.70) preferred; CDF 0.9977 with minimal IBNR (âˆ’0.90).</t>
+          <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9977, 107 months); CL ultimate of 389.70 with slight negative IBNR (-0.90). BF method shows similar result; development is essentially complete.</t>
         </is>
       </c>
       <c r="K17" s="8" t="n"/>
@@ -2656,19 +2656,19 @@
         <v>309.2949996487254</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>309.393</v>
+        <v>309.39</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 95 months (CDF 0.9977, slight reopening). Ultimate 309.4 counts. CL shows -0.7 IBNR (closure adjustment). IE shows +41.7 counts (13.4% inflation, unreliable). CL 309.4 and BF converge. Reported Count CL is primary measure.</t>
+          <t>Reported Count selected. Reported CL ultimate of 309.39 (CDF 0.9977, 100.2% developed). Similar to 2016, slight CDF &lt;1.0 (reopens marginal). Reported IE (351.80) shows +41.69 IBNR (13.5% inflation) despite near-full development; fitness questionable. Reported CL is primary. BF shows minor negative (-0.81). CL most credible.</t>
         </is>
       </c>
       <c r="I18" s="6" t="n">
-        <v>309.3928</v>
+        <v>309.39</v>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 95 days, 100.2% developed. CL (309.39) with minimal IBNR (âˆ’0.71). BF (309.29) very close; CL selected for consistency.</t>
+          <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9977, 95 months); CL ultimate of 309.39 with minimal IBNR (-0.71). IE method estimates 351.80 with IBNR of 41.69; CL reflects lower development tail.</t>
         </is>
       </c>
       <c r="K18" s="8" t="n"/>
@@ -2689,28 +2689,28 @@
         <v>325.9412</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>324.9313820118081</v>
+        <v>324.963901165332</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>349.5307063275</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>324.8549325164175</v>
+        <v>324.890018774179</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>324.931</v>
+        <v>324.96</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 83 months (CDF 0.9969, slight reopening). Ultimate 324.9 counts. CL shows -1.0 IBNR (closure). IE shows +23.6 counts (7.3% inflation). CL 324.9 and BF (324.855) converge. Reported Count CL is most credible. Reopening effect minor.</t>
+          <t>Reported Count selected. Reported CL ultimate of 324.96 (CDF 0.997, 100.3% developed). CDF &lt;1.0 indicates marginal reopens. Reported IE (349.53) shows +23.59 IBNR (7.3% adjustment); fitness marginal. Reported CL is primary for near-full development. BF shows minor negative (-1.05). CL selected.</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>324.9314</v>
+        <v>324.96</v>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 83 days, 100.3% developed. CL (324.93) with minimal negative IBNR (âˆ’1.01), indicating near-complete reporting. CDF 0.9969 stable.</t>
+          <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9970, 83 months); CL ultimate of 324.96 with slight negative IBNR (-0.98). IE and BF show slightly higher estimates; CL credible for near-mature cohort.</t>
         </is>
       </c>
       <c r="K19" s="8" t="n"/>
@@ -2731,28 +2731,28 @@
         <v>357.6116</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>356.503662045344</v>
+        <v>356.539340954676</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>337.5429992505</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>356.5625877737231</v>
+        <v>356.5964706929142</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>356.504</v>
+        <v>356.54</v>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 71 months (CDF 0.9969, slight reopening). Ultimate 356.5 counts. CL shows -1.1 IBNR (closure effect). IE shows -20.1 counts (negative, unreliable). CL 356.5 and BF (356.563) converge tightly. Reported Count CL is credible primary.</t>
+          <t>Reported Count selected. Reported CL ultimate of 356.54 (CDF 0.997, 100.3% developed). CDF &lt;1.0 signals marginal reopens. Reported IE (337.54) shows negative IBNR (-20.07); disqualifies case adequacy assumption. Reported CL is primary. BF shows minor negative (-1.02). Reported CL selected as most credible method.</t>
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>356.5037</v>
+        <v>356.54</v>
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 71 days, 100.3% developed. CL (356.50) with minimal negative IBNR (âˆ’1.11). IE shows negative IBNR (âˆ’20.07); CL most credible.</t>
+          <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9970, 71 months); CL ultimate of 356.54 with slight negative IBNR (-1.07). IE method negative IBNR (-20.07) suggests reported count overstatement; CL is credible anchor.</t>
         </is>
       </c>
       <c r="K20" s="8" t="n"/>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 59 months (CDF 0.9962, reopening effect). Ultimate 369.4 counts. CL shows -1.4 IBNR (closure). IE shows -12.7 counts (negative). CL 369.4 and BF (369.443) converge. Reported Count CL is primary. Slight reopening embedded in CDF.</t>
+          <t>Reported Count selected. Reported CL ultimate of 369.40 (CDF 0.9962, 100.4% developed). CDF &lt;1.0 indicates reopens. Reported IE (358.12) shows negative IBNR (-12.69); case adequacy fails. Reported CL is primary. BF shows minor negative (-1.36). At near-full maturity, Reported CL is most reliable.</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 59 days, 100.4% developed. CL (369.40) with minimal negative IBNR (âˆ’1.41). CDF 0.9962 shows slight reversal typical of mid-maturity. Maintain CL.</t>
+          <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9962, 59 months); CL ultimate of 369.40 with small negative IBNR (-1.41). Methods show modest development remaining; CL reflects current maturity.</t>
         </is>
       </c>
       <c r="K21" s="8" t="n"/>
@@ -2824,19 +2824,19 @@
         <v>328.527809088843</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>328.648</v>
+        <v>328.65</v>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 47 months (CDF 0.9962, reopening effect). Ultimate 328.6 counts. CL shows -1.3 IBNR (closure). IE shows +30.2 counts (9.2% inflation). CL 328.6 and BF (328.528) converge. Reported Count CL is credible primary. Reopening minor.</t>
+          <t>Reported Count selected. Reported CL ultimate of 328.65 (CDF 0.9962, 100.4% developed). CDF &lt;1.0 indicates reopens. Reported IE (360.11) shows +30.21 IBNR (9.2% adjustment); plausibility questionable at near-full development. Reported CL is primary. BF shows minor negative (-1.37). CL selected.</t>
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>328.6477</v>
+        <v>328.65</v>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 47 days, 100.4% developed. CL (328.65) with minimal negative IBNR (âˆ’1.25). IE slightly positive (+30.21); CL preferred for consistency.</t>
+          <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9962, 47 months); CL ultimate of 328.65 with negative IBNR (-1.25). IE method shows IBNR of 30.21; CL reflects lower developmental pattern and is credible.</t>
         </is>
       </c>
       <c r="K22" s="8" t="n"/>
@@ -2866,19 +2866,19 @@
         <v>297.2069189605764</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>297.335</v>
+        <v>297.34</v>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 35 months (CDF 0.9970, reopening). Ultimate 297.3 counts. CL shows -0.9 IBNR (closure). IE shows +41.8 counts (14.0% inflation). CL 297.3 and BF (297.207) converge. Reported Count CL is primary. Reopening very minor.</t>
+          <t>Reported Count selected. Reported CL ultimate of 297.34 (CDF 0.9970, 100.3% developed). CDF &lt;1.0 marginal. Reported IE (339.98) shows +41.75 IBNR (14.0% adjustment); fitness weak at near-full development. Reported CL is primary. BF shows minor negative (-1.02). CL most credible at 48% developed.</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>297.3352</v>
+        <v>297.34</v>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 35 days, 100.3% developed. CL (297.34) with minimal negative IBNR (âˆ’0.89). CDF 0.9970 suggests near-complete reporting despite immature calendar age.</t>
+          <t>Reported Count, Chain Ladder. Developing (CDF 0.9970, 35 months); CL ultimate of 297.34 with slight negative IBNR (-0.89). IE method shows IBNR of 41.75; CL reflects reported count stability in early development.</t>
         </is>
       </c>
       <c r="K23" s="8" t="n"/>
@@ -2908,19 +2908,19 @@
         <v>303.8727418976421</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>303.913</v>
+        <v>303.91</v>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 23 months (CDF 0.9970, reopening). Ultimate 303.9 counts. CL shows -0.9 IBNR (closure effect). IE shows +12.6 counts (4.2% inflation). CL 303.9 and BF (303.873) converge tightly. Reported Count CL is primary. Young age, reopening embedded in CDF.</t>
+          <t>Reported Count selected. Reported CL ultimate of 303.91 (CDF 0.9970, 100.3% developed). CDF &lt;1.0 marginal. Reported IE (317.43) shows +12.61 IBNR (4.1% adjustment); marginal given 53% development. Reported CL is primary. BF shows minor negative (-0.95). CL selected as most data-driven method.</t>
         </is>
       </c>
       <c r="I24" s="6" t="n">
-        <v>303.9134</v>
+        <v>303.91</v>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 23 days, 100.3% developed. CL (303.91) with minimal negative IBNR (âˆ’0.91). CDF 0.9970 consistent with prior years; minimal expected development.</t>
+          <t>Reported Count, Chain Ladder. Developing (CDF 0.9970, 23 months); CL ultimate of 303.91 with slight negative IBNR (-0.91). Methods cluster around 303-317 range; CL is credible for developing cohort.</t>
         </is>
       </c>
       <c r="K24" s="8" t="n"/>
@@ -2950,19 +2950,19 @@
         <v>286.0723437533045</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>285.352</v>
+        <v>286.07</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Reported Count CL selected. Age 11 months (CDF 1.1146, significant development ahead). Ultimate 285.4 counts. CL shows +29.3 IBNR (10.3% of reported). IE shows +36.4 counts (12.6% of reported, consistent with CL). CL 285.4 and IE 292.4 show 2.4% convergence. CL selected as primary; at 11 months, CDF 1.1146 indicates ~10% additional claim count development expected.</t>
+          <t>Reported Count selected. Reported CL ultimate of 285.35 (CDF 1.1146, 89.7% developed). High CDF indicates significant development ahead (10.3%). Reported IE (292.35) shows +36.35 IBNR (12.4% adjustment); fitness weak at very early stage. Reported BF (286.07) very close to CL (0.26% difference). At extreme immaturity, Reported BF is typically primary, but CL and BF nearly converge. Selected midpoint/BF (286.07) for very green period; CDF volatility at 11 months. BF slightly preferred for a priori credibility.</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>285.3523</v>
+        <v>285.35</v>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Reported Count CL. 11 days, 89.7% developed. CL (285.35) with IBNR (+29.35). CDF 1.1146 elevated (high extrapolation risk); BF (286.07) very close. CL maintains consistency with prior selections.</t>
+          <t>Reported Count, Chain Ladder. Early developing (CDF 1.1146, 11 months); CL ultimate of 285.35 with IBNR of 29.35. CDF greater than 1.0 suggests early development may reverse; CL provides credible estimate at this immature stage despite tail uncertainty.</t>
         </is>
       </c>
       <c r="K25" s="8" t="n"/>

--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losses" sheetId="1" state="visible" r:id="rId1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,9 +26,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -41,26 +51,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE7F6"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE6CC"/>
+        <fgColor rgb="FFF4B084"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -68,46 +82,33 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -473,22 +474,12 @@
   <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="18.7109375" customWidth="1" min="1" max="11"/>
+    <col width="30.7109375" customWidth="1" min="12" max="12"/>
+    <col width="18.7109375" customWidth="1" min="13" max="13"/>
+    <col width="30.7109375" customWidth="1" min="14" max="14"/>
+    <col width="18.7109375" customWidth="1" min="15" max="15"/>
+    <col width="40.7109375" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -611,21 +602,21 @@
       <c r="K2" s="4" t="n">
         <v>3054159.61</v>
       </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid CL ultimate of 3,054,159.61. Year is at extreme tail maturity (287 months, 100% developed). Incurred IE disqualified (negative IBNR -121,479). Paid CL is primary method for fully-developed tail periods; closure rate stable (CDF 1.0039). Convergence not applicable—Paid CL is sole viable method at this age.</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid CL ultimate of 3,054,159.61. Year is at extreme tail maturity (287 months, 100% developed). Incurred IE disqualified (negative IBNR -121,479). Paid CL is primary method for fully-developed tail periods; closure rate stable (CDF 1.0039). Convergence not applicableâ€”Paid CL is sole viable method at this age.</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="n">
         <v>3054159.61</v>
       </c>
-      <c r="N2" s="7" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Fully mature (287 months); Paid and Incurred ultimates nearly converge. Paid preferred for stability; CL ultimate of 3,054,160 is credible with minimal IBNR (11,865).</t>
         </is>
       </c>
-      <c r="O2" s="8" t="n"/>
-      <c r="P2" s="9" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -665,21 +656,21 @@
       <c r="K3" s="4" t="n">
         <v>2216836.93</v>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 2,216,836.93. Age 275 months, 99.2% developed. Incurred IE disqualified (negative IBNR -704,698). Paid CL is standard for tail years. Paid development very stable (CDF 1.0078). Incurred CL secondary (2,406,196.57) but Paid CL preferred at this extreme maturity.</t>
         </is>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="M3" s="5" t="n">
         <v>2216836.93</v>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (275 months, 99% developed); Incurred shows high estimate (2,904,344) with negative IBNR bias. Paid CL of 2,216,837 aligns with economic patterns; low IBNR of 17,191.</t>
         </is>
       </c>
-      <c r="O3" s="8" t="n"/>
-      <c r="P3" s="9" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -719,21 +710,21 @@
       <c r="K4" s="4" t="n">
         <v>1805248.44</v>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,805,248.44. Age 263 months (&gt;20 years). Incurred IE disqualified (negative IBNR -855,180). Paid CL (1,805,248.44) vs. Incurred CL (1,838,027.15): difference 1.8%. Paid CL preferred for tail maturity with stable closure rate (CDF 1.0153).</t>
         </is>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="M4" s="5" t="n">
         <v>1805248.44</v>
       </c>
-      <c r="N4" s="7" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (263 months, 98% developed); Incurred at 1,838,027 vs Paid at 1,805,248. Paid CL of 1,805,248 preferred for stability; Incurred shows IBNR of 59,936 suggesting conservative estimate in tail.</t>
         </is>
       </c>
-      <c r="O4" s="8" t="n"/>
-      <c r="P4" s="9" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -773,21 +764,21 @@
       <c r="K5" s="4" t="n">
         <v>1146826.99</v>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,146,826.99. Age 251 months. Incurred IE disqualified (negative IBNR -556,096). Paid CL (1,146,826.99) vs. Incurred CL (1,180,647.54): 2.9% difference. Paid CL is primary for late tail; stable closure dynamics (CDF 1.0216).</t>
         </is>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="M5" s="5" t="n">
         <v>1146826.99</v>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (251 months, 98% developed); Paid CL of 1,146,827 slightly below Incurred CL of 1,180,648. Paid preferred for lower tail volatility; IBNR of 24,212 is modest.</t>
         </is>
       </c>
-      <c r="O5" s="8" t="n"/>
-      <c r="P5" s="9" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -827,21 +818,21 @@
       <c r="K6" s="4" t="n">
         <v>2302875.95</v>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 2,302,875.95. Age 239 months. Incurred IE disqualified (negative IBNR of -529,863 is implausible; case adequacy assumption broken). Paid CL (2,302,875.95) vs. Incurred CL (2,374,326.11): 3.0% difference. Paid CL preferred for stability; Incurred methods unreliable.</t>
         </is>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="M6" s="5" t="n">
         <v>2302875.95</v>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (239 months, 94% developed); Incurred shows negative IBNR (-529,864), indicating overstatement in prior periods. Paid CL of 2,302,876 is credible with positive IBNR of 60,727.</t>
         </is>
       </c>
-      <c r="O6" s="8" t="n"/>
-      <c r="P6" s="9" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -881,21 +872,21 @@
       <c r="K7" s="4" t="n">
         <v>1505496.3</v>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,505,496.30. Age 227 months (late tail). Incurred IE disqualified (negative IBNR -284,389). Paid CL (1,505,496.30) vs. Incurred CL (1,621,406.24): 7.1% difference. Paid CL preferred; Incurred CL link ratios show instability (case adequacy shifting). Paid development stable (CDF 1.0297).</t>
         </is>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="M7" s="5" t="n">
         <v>1505496.3</v>
       </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (227 months, 97% developed); Incurred at 1,621,406 and Paid at 1,505,496 diverge moderately. Paid CL of 1,505,496 preferred given cleaner paid emergence; positive IBNR of 43,355.</t>
         </is>
       </c>
-      <c r="O7" s="8" t="n"/>
-      <c r="P7" s="9" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -935,21 +926,21 @@
       <c r="K8" s="4" t="n">
         <v>4955930.27</v>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 4,955,930.27. Age 215 months. Incurred IE disqualified (negative IBNR of -1,960,436; case adequacy severely degraded). Paid CL (4,955,930.27) vs. Incurred CL (5,139,714.61): 3.6% difference. Paid CL preferred; Incurred methods unreliable due to case reserve instability. Paid CDF 1.0345 is reasonable.</t>
         </is>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="M8" s="5" t="n">
         <v>4955930.27</v>
       </c>
-      <c r="N8" s="7" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (215 months, 97% developed); Incurred shows negative IBNR (-1,960,436) reflecting volatility in incurred reporting. Paid CL of 4,955,930 is stable; IBNR of 165,237 reasonable for 97% developed.</t>
         </is>
       </c>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="9" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -989,21 +980,21 @@
       <c r="K9" s="4" t="n">
         <v>1428966.22</v>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,428,966.22. Age 203 months. Incurred IE disqualified (negative IBNR -1,165,499). Paid CL (1,428,966.22) vs. Incurred CL (1,475,624.25): 3.2% difference. Paid CL is stable; Incurred CL shows case adequacy issues (CDF 1.0705). Paid development is more credible (CDF 1.0367).</t>
         </is>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="M9" s="5" t="n">
         <v>1428966.22</v>
       </c>
-      <c r="N9" s="7" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (203 months, 96% developed); Incurred inflated estimate (2,543,927) with IBNR of 1,165,499 appears inconsistent with development pattern. Paid CL of 1,428,966 with IBNR of 50,538 more credible.</t>
         </is>
       </c>
-      <c r="O9" s="8" t="n"/>
-      <c r="P9" s="9" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1043,21 +1034,21 @@
       <c r="K10" s="4" t="n">
         <v>1226405.58</v>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,226,405.58. Age 191 months. Incurred IE disqualified (negative IBNR -1,425,224). Paid CL (1,226,405.58) vs. Incurred CL (1,261,566.69): 2.8% difference. Paid CL preferred; Incurred CL link ratios unstable (CDF 1.0786 vs. Paid CDF 1.0486). Paid method more credible.</t>
         </is>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="M10" s="5" t="n">
         <v>1226405.58</v>
       </c>
-      <c r="N10" s="7" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (191 months, 95% developed); Incurred at 2,594,806 with huge IBNR (1,425,225) seems excessive given maturity. Paid CL of 1,226,406 with moderate IBNR of 56,824 more reasonable.</t>
         </is>
       </c>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="9" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1097,21 +1088,21 @@
       <c r="K11" s="4" t="n">
         <v>1360648.28</v>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,360,648.28. Age 179 months. Incurred IE disqualified (negative IBNR of -143,371; case adequacy assumption violated). Paid CL (1,360,648.28) vs. Incurred CL (1,383,120.22): 1.6% difference within convergence band. Paid CL selected; closure rate stable (CDF 1.0649) and Paid method more robust.</t>
         </is>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="M11" s="5" t="n">
         <v>1360648.28</v>
       </c>
-      <c r="N11" s="7" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Mature (179 months, 94% developed); Incurred shows negative IBNR (-143,371) suggesting overestimation in prior reporting. Paid CL of 1,360,648 is stable with reasonable IBNR of 82,976.</t>
         </is>
       </c>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="9" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1151,21 +1142,21 @@
       <c r="K12" s="4" t="n">
         <v>2044396.42</v>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 2,044,396.42. Age 167 months. Incurred IE disqualified (negative IBNR of -373,432). Paid CL (2,044,396.42) vs. Incurred CL (2,117,984.61): 3.5% difference. Paid CL preferred; Incurred CL shows elevated CDF (1.1054) indicating link ratio volatility and case reserve degradation. Paid development more stable (CDF 1.0802).</t>
         </is>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="M12" s="5" t="n">
         <v>2044396.42</v>
       </c>
-      <c r="N12" s="7" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Semi-mature (167 months, 93% developed); Incurred at 2,117,985 vs Paid at 2,044,396. Paid CL of 2,044,396 preferred; IBNR of 151,738 reasonable given development level.</t>
         </is>
       </c>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="9" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1205,21 +1196,21 @@
       <c r="K13" s="4" t="n">
         <v>1307266.94</v>
       </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid CL ultimate of 1,307,266.94. Age 155 months (late maturity, 60–84 months band lower range). Incurred IE disqualified (negative IBNR -209,748). Paid CL (1,307,266.94) vs. Incurred CL (1,508,058.98): 13.3% divergence signals Incurred CL instability. Paid CL is primary; closure rate stable (CDF 1.0946).</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="n">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid CL ultimate of 1,307,266.94. Age 155 months (late maturity, 60â€“84 months band lower range). Incurred IE disqualified (negative IBNR -209,748). Paid CL (1,307,266.94) vs. Incurred CL (1,508,058.98): 13.3% divergence signals Incurred CL instability. Paid CL is primary; closure rate stable (CDF 1.0946).</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
         <v>1307266.94</v>
       </c>
-      <c r="N13" s="7" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Semi-mature (155 months, 91% developed); Incurred shows positive IBNR but higher estimate (1,508,059). Paid CL of 1,307,267 is stable baseline; IBNR of 113,030 proportional to development.</t>
         </is>
       </c>
-      <c r="O13" s="8" t="n"/>
-      <c r="P13" s="9" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1259,21 +1250,21 @@
       <c r="K14" s="4" t="n">
         <v>789162.53</v>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 789,162.53. Age 143 months. Incurred IE disqualified (negative IBNR -495,199). Paid CL (789,162.53) vs. Incurred CL (785,226.82): 0.5% convergence within acceptable band. Paid CL selected; both methods close but Paid shows superior fitness (stable CDF 1.1138 vs. Incurred CDF 1.0823 suggests CDF escalation anomaly in Incurred). Paid preferred.</t>
         </is>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M14" s="5" t="n">
         <v>789162.53</v>
       </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Semi-mature (143 months, 90% developed); Incurred at 785,227 vs Paid at 789,163 converge closely. Paid CL of 789,163 slightly higher but within method variance; IBNR of 80,633.</t>
         </is>
       </c>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="9" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1313,21 +1304,21 @@
       <c r="K15" s="4" t="n">
         <v>1576996.53</v>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,576,996.53. Age 131 months (late-to-mid transition, 84 months threshold). Incurred IE disqualified (negative IBNR of -161,800). Paid CL (1,576,996.53) vs. Incurred CL (1,593,926.14): 1.1% convergence. Paid CL selected; late maturity band and Paid method's stability preferred. CDF 1.1349 shows development still present.</t>
         </is>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M15" s="5" t="n">
         <v>1576996.53</v>
       </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Semi-mature (131 months, 88% developed); Incurred at 1,593,926 slightly higher. Paid CL of 1,576,997 represents stable development with reasonable IBNR of 187,393 given maturity.</t>
         </is>
       </c>
-      <c r="O15" s="8" t="n"/>
-      <c r="P15" s="9" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1367,21 +1358,21 @@
       <c r="K16" s="4" t="n">
         <v>3849598.12</v>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 3,849,598.12. Age 119 months (mid-maturity band). Incurred IE disqualified (negative IBNR of -1,713,150; implausible). Paid CL (3,849,598.12) vs. Incurred CL (3,912,201.44): 1.6% convergence. Paid CL selected; Incurred IE severely disqualified, and Paid CL stability preferred at this maturity. CDF 1.1443 indicates meaningful development remains.</t>
         </is>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M16" s="5" t="n">
         <v>3849598.12</v>
       </c>
-      <c r="N16" s="7" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Semi-mature (119 months, 87% developed); Incurred shows negative IBNR (-1,713,150) reflecting reporting volatility. Paid CL of 3,849,598 with IBNR of 485,367 more credible given 87% development.</t>
         </is>
       </c>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="9" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1421,21 +1412,21 @@
       <c r="K17" s="4" t="n">
         <v>2999163</v>
       </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid CL ultimate of 2,999,163.00. Age 107 months (mid-maturity, 60–84 month band). Incurred IE disqualified (negative IBNR -48,490 marginal). Paid CL (2,999,163.00) vs. Incurred CL (3,038,991.70): 1.3% convergence. Paid CL selected; entering mid-maturity phase where Paid CL remains primary. CDF 1.2181 shows substantial development ahead.</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="n">
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid CL ultimate of 2,999,163.00. Age 107 months (mid-maturity, 60â€“84 month band). Incurred IE disqualified (negative IBNR -48,490 marginal). Paid CL (2,999,163.00) vs. Incurred CL (3,038,991.70): 1.3% convergence. Paid CL selected; entering mid-maturity phase where Paid CL remains primary. CDF 1.2181 shows substantial development ahead.</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
         <v>2999163</v>
       </c>
-      <c r="N17" s="7" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Semi-mature (107 months, 82% developed); Incurred at 3,038,992 vs Paid at 2,999,163. Paid CL of 2,999,163 preferred; methods generally converge; IBNR of 536,954 appropriate for 82% maturity.</t>
         </is>
       </c>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="9" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1475,21 +1466,21 @@
       <c r="K18" s="4" t="n">
         <v>1488161.05</v>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,488,161.05. Age 95 months (mid-maturity lower range). Incurred IE disqualified (negative IBNR -1,400,098; implausible). Paid CL (1,488,161.05) vs. Incurred CL (1,483,428.99): 0.3% convergence. Both very close; Paid CL selected for superior fitness. CDF 1.2342 indicates ~19% development remaining.</t>
         </is>
       </c>
-      <c r="M18" s="6" t="n">
+      <c r="M18" s="5" t="n">
         <v>1488161.05</v>
       </c>
-      <c r="N18" s="7" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Developing (95 months, 81% developed); Incurred shows large IBNR (277,617) with high tail factor (CDF 1.230). Paid CL of 1,488,161 more stable; IBNR of 282,349 reasonable for development stage.</t>
         </is>
       </c>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="9" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1529,21 +1520,21 @@
       <c r="K19" s="4" t="n">
         <v>3053327.91</v>
       </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid CL ultimate of 3,053,327.91. Age 83 months (mid-maturity band, 36–60+ mo). Incurred IE disqualified (negative IBNR of -180,424). Paid CL (3,053,327.91) vs. Incurred CL (2,966,113.90): 2.9% difference. Paid CL selected; Incurred IE failure disqualifies blending. CDF 1.2746 shows significant development. Paid method more robust at this maturity.</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="n">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid CL ultimate of 3,053,327.91. Age 83 months (mid-maturity band, 36â€“60+ mo). Incurred IE disqualified (negative IBNR of -180,424). Paid CL (3,053,327.91) vs. Incurred CL (2,966,113.90): 2.9% difference. Paid CL selected; Incurred IE failure disqualifies blending. CDF 1.2746 shows significant development. Paid method more robust at this maturity.</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="n">
         <v>3053327.91</v>
       </c>
-      <c r="N19" s="7" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Developing (83 months, 78% developed); Incurred shows negative IBNR (-180,425) despite high CDF. Paid CL of 3,053,328 with IBNR of 657,879 reflects consistent development; tail factor CDF 1.275.</t>
         </is>
       </c>
-      <c r="O19" s="8" t="n"/>
-      <c r="P19" s="9" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1583,21 +1574,21 @@
       <c r="K20" s="4" t="n">
         <v>3379669.12</v>
       </c>
-      <c r="L20" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid CL ultimate of 3,379,669.12. Age 71 months (early maturity, 36–60 boundary). Incurred IE disqualified (negative IBNR of -340,558). Paid CL (3,379,669.12) vs. Incurred CL (3,499,325.39): 3.4% difference. Paid CL selected; ~29% development remains (CDF 1.4110). At early maturity, Paid CL credibility exceeds Incurred CL; Incurred IE disqualified.</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="n">
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid CL ultimate of 3,379,669.12. Age 71 months (early maturity, 36â€“60 boundary). Incurred IE disqualified (negative IBNR of -340,558). Paid CL (3,379,669.12) vs. Incurred CL (3,499,325.39): 3.4% difference. Paid CL selected; ~29% development remains (CDF 1.4110). At early maturity, Paid CL credibility exceeds Incurred CL; Incurred IE disqualified.</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="n">
         <v>3379669.12</v>
       </c>
-      <c r="N20" s="7" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Developing (71 months, 71% developed); Paid CL of 3,379,669 with IBNR of 984,479 is stable anchor. Incurred shows negative IBNR (-340,559) inconsistent with development pattern. Paid CDF of 1.411 appropriate for maturity.</t>
         </is>
       </c>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="9" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1637,21 +1628,21 @@
       <c r="K21" s="4" t="n">
         <v>1541396.59</v>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,541,396.59. Age 59 months (early maturity, high immaturity). Incurred IE disqualified (negative IBNR -864,708). Paid CL (1,541,396.59) vs. Incurred CL (1,452,867.57): 5.8% divergence signals Incurred instability. Paid CL is primary; ~37% development remains (CDF 1.5792). Paid BF secondary (1,652,240.31) is 7.2% higher but Paid CL credible at 59 months.</t>
         </is>
       </c>
-      <c r="M21" s="6" t="n">
+      <c r="M21" s="5" t="n">
         <v>1541396.59</v>
       </c>
-      <c r="N21" s="7" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Early developing (59 months, 63% developed); Paid CL of 1,541,397 with IBNR of 565,346 reflects early development stage. CDF of 1.579 substantial but credible given only 63% maturity. Incurred at 1,452,867 lower, but Paid CL more stable.</t>
         </is>
       </c>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1691,21 +1682,21 @@
       <c r="K22" s="4" t="n">
         <v>1690287.65</v>
       </c>
-      <c r="L22" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid CL ultimate of 1,690,287.65. Age 47 months (green maturity, 24–36 boundary). Incurred IE disqualified (negative IBNR -435,380). Paid CL (1,690,287.65) vs. Incurred CL (1,586,080.90): 6.2% divergence. At green maturity, baseline is BF-heavy, but Paid CL (1,690,287.65) and Paid BF (1,571,825.99) differ 7.0%. Paid CL selected as more data-driven; 42% development remains (CDF 1.7337).</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="n">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid CL ultimate of 1,690,287.65. Age 47 months (green maturity, 24â€“36 boundary). Incurred IE disqualified (negative IBNR -435,380). Paid CL (1,690,287.65) vs. Incurred CL (1,586,080.90): 6.2% divergence. At green maturity, baseline is BF-heavy, but Paid CL (1,690,287.65) and Paid BF (1,571,825.99) differ 7.0%. Paid CL selected as more data-driven; 42% development remains (CDF 1.7337).</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="n">
         <v>1690287.65</v>
       </c>
-      <c r="N22" s="7" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Early developing (47 months, 58% developed); Paid CL of 1,690,288 with IBNR of 715,308 reflects 58% development. CDF of 1.734 reflects high tail uncertainty. Incurred at 1,586,081 lower but Paid CL provides more conservative tail estimate.</t>
         </is>
       </c>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1745,21 +1736,21 @@
       <c r="K23" s="4" t="n">
         <v>1645673.39</v>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid CL ultimate of 1,645,673.39. Age 35 months (green, transitioning toward very green). Paid CL (1,645,673.39) vs. Paid BF (1,289,119.20): 21.6% divergence signals extreme immaturity. Paid BF is typically primary for &lt;24 mo. However, ~52% development has occurred (CDF 2.0802). Paid CL selected with reduced confidence due to potential link ratio volatility; Incurred IE disqualified (negative IBNR -167,941).</t>
         </is>
       </c>
-      <c r="M23" s="6" t="n">
+      <c r="M23" s="5" t="n">
         <v>1645673.39</v>
       </c>
-      <c r="N23" s="7" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Early developing (35 months, 48% developed); Paid CL of 1,645,673 with IBNR of 854,570 reflects 48% development stage and high uncertainty (CDF 2.080). Incurred at 1,557,461 lower but tail factor higher at 1.882; Paid CL more stable.</t>
         </is>
       </c>
-      <c r="O23" s="8" t="n"/>
-      <c r="P23" s="9" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1799,21 +1790,21 @@
       <c r="K24" s="4" t="n">
         <v>1846864.71</v>
       </c>
-      <c r="L24" s="5" t="inlineStr">
-        <is>
-          <t>Paid Loss selected. Paid BF ultimate of 1,846,864.71. Age 23 months (very green, 12–24 month boundary). Paid CL (3,548,451.09) shows extreme elevation (CDF 2.9589, 66% development) indicating volatile link ratios at extreme immaturity. Paid BF (1,846,864.71) is more stable method for very early years; prior loss ratio credible. Incurred IE disqualified (negative IBNR of -221,016). Paid BF is primary at this age.</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="n">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Paid Loss selected. Paid BF ultimate of 1,846,864.71. Age 23 months (very green, 12â€“24 month boundary). Paid CL (3,548,451.09) shows extreme elevation (CDF 2.9589, 66% development) indicating volatile link ratios at extreme immaturity. Paid BF (1,846,864.71) is more stable method for very early years; prior loss ratio credible. Incurred IE disqualified (negative IBNR of -221,016). Paid BF is primary at this age.</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="n">
         <v>3548451.09</v>
       </c>
-      <c r="N24" s="7" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Immature (23 months, 34% developed); Paid CL of 3,548,451 with high IBNR of 2,349,209 reflects substantial development ahead (CDF 2.959). Incurred at 3,909,735 higher with lower IBNR, but Paid CL more consistent with tail development pattern.</t>
         </is>
       </c>
-      <c r="O24" s="8" t="n"/>
-      <c r="P24" s="9" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1853,25 +1844,25 @@
       <c r="K25" s="4" t="n">
         <v>1224487.09</v>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Paid Loss selected. Paid BF ultimate of 1,224,487.09. Age 11 months (&lt;12 months, extreme immaturity). Paid CL (2,757,367.94) inflated by extreme CDF (7.7618) indicating unreliable link ratios (&lt;13% developed). Paid BF (1,224,487.09) is primary method for a priori estimation at extreme youth; prior loss ratio informative. Incurred IE disqualified (negative IBNR -642,542). Paid BF selected per maturity-based hierarchy for very green years.</t>
         </is>
       </c>
-      <c r="M25" s="6" t="n">
+      <c r="M25" s="5" t="n">
         <v>2757367.94</v>
       </c>
-      <c r="N25" s="7" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Paid Loss, Chain Ladder. Highly immature (11 months, 13% developed); Paid CL of 2,757,368 with extreme IBNR of 2,402,120 reflects very early stage (CDF 7.762). High uncertainty but CL is most credible single-method selection given maturity constraints and paid emergence patterns.</t>
         </is>
       </c>
-      <c r="O25" s="8" t="n"/>
-      <c r="P25" s="9" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
     </row>
     <row r="26"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1884,18 +1875,12 @@
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="18.7109375" customWidth="1" min="1" max="7"/>
+    <col width="30.7109375" customWidth="1" min="8" max="8"/>
+    <col width="18.7109375" customWidth="1" min="9" max="9"/>
+    <col width="30.7109375" customWidth="1" min="10" max="10"/>
+    <col width="18.7109375" customWidth="1" min="11" max="11"/>
+    <col width="40.7109375" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1986,21 +1971,21 @@
       <c r="G2" s="4" t="n">
         <v>700.71</v>
       </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>Reported Count selected. Reported CL ultimate of 700.71 (CDF 1.0, 100% developed). All methods (CL, IE, BF) converge at 700.7–700.8 for fully-developed tail period. Reported IE (700.78) is 0.01% higher but adds minimal IBNR (0.07 counts). Reported CL selected as standard method for fully-developed years. Count data shows no case adequacy issues.</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="n">
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Reported Count selected. Reported CL ultimate of 700.71 (CDF 1.0, 100% developed). All methods (CL, IE, BF) converge at 700.7â€“700.8 for fully-developed tail period. Reported IE (700.78) is 0.01% higher but adds minimal IBNR (0.07 counts). Reported CL selected as standard method for fully-developed years. Count data shows no case adequacy issues.</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="n">
         <v>700.71</v>
       </c>
-      <c r="J2" s="7" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 287 months); all methods converge at 700.71. No IBNR needed; count development complete.</t>
         </is>
       </c>
-      <c r="K2" s="8" t="n"/>
-      <c r="L2" s="9" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2028,21 +2013,21 @@
       <c r="G3" s="4" t="n">
         <v>651.88</v>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 651.88 (CDF 1.0, 100% developed). Reported IE (683.17) shows elevated IBNR (+31.28 counts), implying late reporting, but at full maturity this is implausible. Reported CL is primary. Reported BF (651.88) identical. Selection based on data-driven CL at extreme tail maturity.</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="5" t="n">
         <v>651.88</v>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 275 months); CL ultimate of 651.88 with zero IBNR. IE method (683.17) and BF method (651.88) converge on same estimate.</t>
         </is>
       </c>
-      <c r="K3" s="8" t="n"/>
-      <c r="L3" s="9" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2070,21 +2055,21 @@
       <c r="G4" s="4" t="n">
         <v>551.59</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 551.59 (CDF 1.0, 100% developed). Reported IE projects 648.44 (+96.85 IBNR) but this contradicts full development; case adequacy assumption fails. Reported CL is sole credible method at full maturity. IE disqualified due to implausible late reporting assumption at 100% development.</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="5" t="n">
         <v>551.59</v>
       </c>
-      <c r="J4" s="7" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 263 months); CL ultimate of 551.59. IE suggests higher estimate (648.44) with positive IBNR of 96.85; CL preferred for fully developed year.</t>
         </is>
       </c>
-      <c r="K4" s="8" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2112,21 +2097,21 @@
       <c r="G5" s="4" t="n">
         <v>642.65</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 642.65 (CDF 1.0, 100% developed). Reported IE (627.84) shows negative IBNR (-14.81), disqualifying it. Reported BF (642.65) identical. Reported CL is primary. Count is fully developed; no late-reporting signal.</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="5" t="n">
         <v>642.65</v>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 251 months); CL ultimate of 642.65 with zero IBNR. IE method shows negative IBNR (-14.81) suggesting reported count is stable and complete.</t>
         </is>
       </c>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="9" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2154,21 +2139,21 @@
       <c r="G6" s="4" t="n">
         <v>641.33</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 641.33 (CDF 1.0, 100% developed). Reported IE (623.61) shows negative IBNR (-17.71), disqualifying case adequacy assumption. Reported BF (641.33) identical. CL is standard at full maturity; IE fitness fails.</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="5" t="n">
         <v>641.33</v>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 239 months); CL ultimate of 641.33. IE and BF converge at similar levels; reported count development is complete.</t>
         </is>
       </c>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="9" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2196,21 +2181,21 @@
       <c r="G7" s="4" t="n">
         <v>497.49</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 497.49 (CDF 1.0, 100% developed). Reported IE (606.74) projects +109.26 IBNR despite full development; assumption violated. Reported BF (497.49) identical. Reported CL is sole credible method at maturity level.</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="5" t="n">
         <v>497.49</v>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 227 months); CL ultimate of 497.49. IE method estimates 606.74 with large IBNR (109.26), but CL is credible for fully developed year.</t>
         </is>
       </c>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="9" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2238,21 +2223,21 @@
       <c r="G8" s="4" t="n">
         <v>476.38</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 476.38 (CDF 1.0, 100% developed). Reported IE (550.47) shows +74.10 IBNR; implausible at full development. Reported CL is primary. IE disqualified. BF matches CL.</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>476.38</v>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 215 months); CL ultimate of 476.38. IE method shows inflation (550.47) with IBNR of 74.10; CL preferred for fully matured cohort.</t>
         </is>
       </c>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="9" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2280,21 +2265,21 @@
       <c r="G9" s="4" t="n">
         <v>328.58</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 328.58 (CDF 1.0, 100% developed). Reported IE (444.10) projects +115.52 IBNR despite full maturity; case adequacy assumption fails at 100% development. Reported CL is standard. IE disqualified for implausible development assumption.</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="5" t="n">
         <v>328.58</v>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 203 months); CL ultimate of 328.58. IE inflates estimate to 444.10 with IBNR of 115.52; CL more conservative and credible.</t>
         </is>
       </c>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2322,21 +2307,21 @@
       <c r="G10" s="4" t="n">
         <v>321.98</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 321.98 (CDF 1.0, 100% developed). Reported IE (384.40) shows +62.42 IBNR; implausible at full development. Reported BF (321.98) matches CL. Reported CL is primary; IE fitness fails.</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="5" t="n">
         <v>321.98</v>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 191 months); CL ultimate of 321.98. IE method (384.40) shows inflation with IBNR of 62.42; CL preferred for fully reported cohort.</t>
         </is>
       </c>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="9" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2364,21 +2349,21 @@
       <c r="G11" s="4" t="n">
         <v>271.84</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 271.84 (CDF 1.0, 100% developed). Reported IE (314.20) projects +42.36 IBNR despite full development; case adequacy assumption violated. Reported CL selected as standard at maturity. IE disqualified.</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="I11" s="5" t="n">
         <v>271.84</v>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 179 months); CL ultimate of 271.84. IE and BF estimates higher; CL reflects actual reported count maturity.</t>
         </is>
       </c>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="9" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2406,21 +2391,21 @@
       <c r="G12" s="4" t="n">
         <v>345.74</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 345.74 (CDF 1.0, 100% developed). Reported IE (319.33) shows negative IBNR (-26.41), disqualifying case adequacy model. Reported BF (345.74) matches CL. CL is primary at full maturity; IE fitness fails.</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="5" t="n">
         <v>345.74</v>
       </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 167 months); CL ultimate of 345.74. IE method shows negative IBNR (-26.41) suggesting reported counts are complete and stable.</t>
         </is>
       </c>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="9" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2448,21 +2433,21 @@
       <c r="G13" s="4" t="n">
         <v>261.28</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 261.28 (CDF 1.0, 100% developed). Reported IE (298.97) shows +37.68 IBNR despite full development; assumption violated. Reported BF (261.28) identical. Reported CL is primary. IE disqualified.</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="I13" s="5" t="n">
         <v>261.28</v>
       </c>
-      <c r="J13" s="7" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 155 months); CL ultimate of 261.28. IE method shows IBNR of 37.68; CL is most credible for fully reported year.</t>
         </is>
       </c>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="9" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2490,21 +2475,21 @@
       <c r="G14" s="4" t="n">
         <v>291.63</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 291.63 (CDF 1.0, 100% developed). Reported IE (305.75) shows +14.12 IBNR despite full maturity; implausible. Reported BF (291.63) matches CL. Reported CL is standard at full development; IE fitness marginal but fails on plausibility.</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="5" t="n">
         <v>291.63</v>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 143 months); CL ultimate of 291.63. Methods show modest IBNR ranges; CL is credible and centered estimate.</t>
         </is>
       </c>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="9" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2532,21 +2517,21 @@
       <c r="G15" s="4" t="n">
         <v>455.26</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 455.26 (CDF 1.0, 100% developed). Reported IE (341.33) shows negative IBNR (-113.93), disqualifying case adequacy assumption. Reported BF (455.26) matches CL. Reported CL is primary; IE fitness fails.</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="I15" s="5" t="n">
         <v>455.26</v>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 131 months); CL ultimate of 455.26. IE method shows negative IBNR (-113.93) suggesting reported counts are complete; CL is credible.</t>
         </is>
       </c>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="9" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2574,21 +2559,21 @@
       <c r="G16" s="4" t="n">
         <v>333.86</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 333.86 (CDF 1.0, 100% developed). Reported IE (367.36) shows +33.50 IBNR at full development; assumption violated. Reported BF (333.86) identical. Reported CL is standard at maturity. IE disqualified on fitness grounds.</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="5" t="n">
         <v>333.86</v>
       </c>
-      <c r="J16" s="7" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Fully developed (CDF 1.0, 119 months); CL ultimate of 333.86. IE method shows modest IBNR of 33.50; CL represents reported count maturity.</t>
         </is>
       </c>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="9" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2616,21 +2601,21 @@
       <c r="G17" s="4" t="n">
         <v>389.7</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 389.70 (CDF 0.9977, 100.2% developed). Slight CDF &lt;1.0 indicates potential reopens or count adjustments (marginal). Reported IE (401.53) shows +10.93 IBNR (2.7% adjustment). Reported CL selected as primary; IE is secondary backup. BF shows minimal negative IBNR (-0.93). CL is most credible.</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="5" t="n">
         <v>389.7</v>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9977, 107 months); CL ultimate of 389.70 with slight negative IBNR (-0.90). BF method shows similar result; development is essentially complete.</t>
         </is>
       </c>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="9" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2658,21 +2643,21 @@
       <c r="G18" s="4" t="n">
         <v>309.39</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 309.39 (CDF 0.9977, 100.2% developed). Similar to 2016, slight CDF &lt;1.0 (reopens marginal). Reported IE (351.80) shows +41.69 IBNR (13.5% inflation) despite near-full development; fitness questionable. Reported CL is primary. BF shows minor negative (-0.81). CL most credible.</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="5" t="n">
         <v>309.39</v>
       </c>
-      <c r="J18" s="7" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9977, 95 months); CL ultimate of 309.39 with minimal IBNR (-0.71). IE method estimates 351.80 with IBNR of 41.69; CL reflects lower development tail.</t>
         </is>
       </c>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="9" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2700,21 +2685,21 @@
       <c r="G19" s="4" t="n">
         <v>324.96</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 324.96 (CDF 0.997, 100.3% developed). CDF &lt;1.0 indicates marginal reopens. Reported IE (349.53) shows +23.59 IBNR (7.3% adjustment); fitness marginal. Reported CL is primary for near-full development. BF shows minor negative (-1.05). CL selected.</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="I19" s="5" t="n">
         <v>324.96</v>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9970, 83 months); CL ultimate of 324.96 with slight negative IBNR (-0.98). IE and BF show slightly higher estimates; CL credible for near-mature cohort.</t>
         </is>
       </c>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="9" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2742,21 +2727,21 @@
       <c r="G20" s="4" t="n">
         <v>356.54</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 356.54 (CDF 0.997, 100.3% developed). CDF &lt;1.0 signals marginal reopens. Reported IE (337.54) shows negative IBNR (-20.07); disqualifies case adequacy assumption. Reported CL is primary. BF shows minor negative (-1.02). Reported CL selected as most credible method.</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="5" t="n">
         <v>356.54</v>
       </c>
-      <c r="J20" s="7" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9970, 71 months); CL ultimate of 356.54 with slight negative IBNR (-1.07). IE method negative IBNR (-20.07) suggests reported count overstatement; CL is credible anchor.</t>
         </is>
       </c>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="9" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2784,21 +2769,21 @@
       <c r="G21" s="4" t="n">
         <v>369.4</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 369.40 (CDF 0.9962, 100.4% developed). CDF &lt;1.0 indicates reopens. Reported IE (358.12) shows negative IBNR (-12.69); case adequacy fails. Reported CL is primary. BF shows minor negative (-1.36). At near-full maturity, Reported CL is most reliable.</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="5" t="n">
         <v>369.4</v>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9962, 59 months); CL ultimate of 369.40 with small negative IBNR (-1.41). Methods show modest development remaining; CL reflects current maturity.</t>
         </is>
       </c>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="9" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2826,21 +2811,21 @@
       <c r="G22" s="4" t="n">
         <v>328.65</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 328.65 (CDF 0.9962, 100.4% developed). CDF &lt;1.0 indicates reopens. Reported IE (360.11) shows +30.21 IBNR (9.2% adjustment); plausibility questionable at near-full development. Reported CL is primary. BF shows minor negative (-1.37). CL selected.</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="5" t="n">
         <v>328.65</v>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Nearly mature (CDF 0.9962, 47 months); CL ultimate of 328.65 with negative IBNR (-1.25). IE method shows IBNR of 30.21; CL reflects lower developmental pattern and is credible.</t>
         </is>
       </c>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="9" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2868,21 +2853,21 @@
       <c r="G23" s="4" t="n">
         <v>297.34</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 297.34 (CDF 0.9970, 100.3% developed). CDF &lt;1.0 marginal. Reported IE (339.98) shows +41.75 IBNR (14.0% adjustment); fitness weak at near-full development. Reported CL is primary. BF shows minor negative (-1.02). CL most credible at 48% developed.</t>
         </is>
       </c>
-      <c r="I23" s="6" t="n">
+      <c r="I23" s="5" t="n">
         <v>297.34</v>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Developing (CDF 0.9970, 35 months); CL ultimate of 297.34 with slight negative IBNR (-0.89). IE method shows IBNR of 41.75; CL reflects reported count stability in early development.</t>
         </is>
       </c>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="9" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2910,21 +2895,21 @@
       <c r="G24" s="4" t="n">
         <v>303.91</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 303.91 (CDF 0.9970, 100.3% developed). CDF &lt;1.0 marginal. Reported IE (317.43) shows +12.61 IBNR (4.1% adjustment); marginal given 53% development. Reported CL is primary. BF shows minor negative (-0.95). CL selected as most data-driven method.</t>
         </is>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="5" t="n">
         <v>303.91</v>
       </c>
-      <c r="J24" s="7" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Developing (CDF 0.9970, 23 months); CL ultimate of 303.91 with slight negative IBNR (-0.91). Methods cluster around 303-317 range; CL is credible for developing cohort.</t>
         </is>
       </c>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="9" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2952,24 +2937,24 @@
       <c r="G25" s="4" t="n">
         <v>286.07</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Reported Count selected. Reported CL ultimate of 285.35 (CDF 1.1146, 89.7% developed). High CDF indicates significant development ahead (10.3%). Reported IE (292.35) shows +36.35 IBNR (12.4% adjustment); fitness weak at very early stage. Reported BF (286.07) very close to CL (0.26% difference). At extreme immaturity, Reported BF is typically primary, but CL and BF nearly converge. Selected midpoint/BF (286.07) for very green period; CDF volatility at 11 months. BF slightly preferred for a priori credibility.</t>
         </is>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="5" t="n">
         <v>285.35</v>
       </c>
-      <c r="J25" s="7" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Reported Count, Chain Ladder. Early developing (CDF 1.1146, 11 months); CL ultimate of 285.35 with IBNR of 29.35. CDF greater than 1.0 suggests early development may reverse; CL provides credible estimate at this immature stage despite tail uncertainty.</t>
         </is>
       </c>
-      <c r="K25" s="8" t="n"/>
-      <c r="L25" s="9" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
     </row>
     <row r="26"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -17,19 +17,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -51,7 +43,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
+        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -86,25 +78,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -471,15 +478,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.7109375" customWidth="1" min="1" max="11"/>
-    <col width="30.7109375" customWidth="1" min="12" max="12"/>
-    <col width="18.7109375" customWidth="1" min="13" max="13"/>
-    <col width="30.7109375" customWidth="1" min="14" max="14"/>
-    <col width="18.7109375" customWidth="1" min="15" max="15"/>
-    <col width="40.7109375" customWidth="1" min="16" max="16"/>
+    <col width="18.7109375" customWidth="1" min="1" max="9"/>
+    <col width="22.7109375" customWidth="1" min="10" max="10"/>
+    <col width="30.7109375" customWidth="1" min="11" max="11"/>
+    <col width="22.7109375" customWidth="1" min="12" max="12"/>
+    <col width="30.7109375" customWidth="1" min="13" max="13"/>
+    <col width="22.7109375" customWidth="1" min="14" max="14"/>
+    <col width="40.7109375" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,1377 +496,1204 @@
           <t>Accident Period</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Current Age</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Incurred CL</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Paid CL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Incurred IE</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Paid IE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Initial Expected</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Incurred BF</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Paid BF</t>
         </is>
       </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Rules-Based AI Selection</t>
+        </is>
+      </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Rules-Based AI Selection</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>Rules-Based AI Reasoning</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Open-Ended AI Selection</t>
+        </is>
+      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Open-Ended AI Selection</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
           <t>Open-Ended AI Reasoning</t>
         </is>
       </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>User Selection</t>
+        </is>
+      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>User Selection</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
           <t>User Reasoning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>3163773.699688</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="8" t="n">
         <v>3042294.662276</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="8" t="n">
         <v>3196360.568794786</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="8" t="n">
         <v>3054159.611458877</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="8" t="n">
         <v>3163773.699688</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>3163773.699688</v>
-      </c>
-      <c r="I2" s="3" t="n">
+      <c r="H2" s="8" t="n">
         <v>3196028.345938407</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="I2" s="8" t="n">
         <v>3054585.445649627</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="J2" s="9" t="n">
         <v>3196360.57</v>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 287 months maturity (tail-exposed), CDF 1.0103 and 98.98% developed indicate full maturity. Incurred CL ultimate of 3.196M reflects final case reserves and estimated IBNR. Paid CL 3.054M is only marginally different (1.4% variance), both reasonable. Incurred preferred at this maturity per framework §2. Very high development and low remaining uncertainty support this selection. Loss ratio (3.20M / premium) consistent with historical portfolio.</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="n">
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 287 months maturity (tail-exposed), CDF 1.0103 and 98.98% developed indicate full maturity. Incurred CL ultimate of 3.196M reflects final case reserves and estimated IBNR. Paid CL 3.054M is only marginally different (1.4% variance), both reasonable. Incurred preferred at this maturity per framework Â§2. Very high development and low remaining uncertainty support this selection. Loss ratio (3.20M / premium) consistent with historical portfolio.</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="n">
         <v>3196360.57</v>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Tail-mature at 287 months (98.98% developed, CDF 1.0103). Incurred CL 3.196M reflects final case reserves and fully estimated IBNR. Paid CL 3.054M is only 1.4% lower but Incurred CL is preferred at extreme maturity per standard practice. Both measures highly credible; Incurred preferred as more direct reflection of case-based reserve adequacy.</t>
         </is>
       </c>
-      <c r="O2" s="6" t="n"/>
-      <c r="P2" s="6" t="n"/>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="A3" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C3" s="8" t="n">
         <v>2327733.756319999</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="8" t="n">
         <v>2199646.228088</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="8" t="n">
         <v>2379694.756036815</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="8" t="n">
         <v>2216836.925286216</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="8" t="n">
         <v>2904344.256599999</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>2904344.256599999</v>
-      </c>
-      <c r="I3" s="3" t="n">
+      <c r="H3" s="8" t="n">
         <v>2391150.55829088</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="I3" s="8" t="n">
         <v>2222168.273848376</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="J3" s="9" t="n">
         <v>2379694.76</v>
       </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 275 months, 97.8% developed with CDF 1.0223. Incurred CL 2.38M vs. Paid CL 2.22M (6.7% variance) reflects ongoing case development. Incurred BF 2.39M aligns closely (0.3% variance). Framework §4 Convergence: Incurred CL and Paid BF cluster within 2%, midpoint selected. Incurred CL represents expected development trajectory at late maturity.</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="n">
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 275 months, 97.8% developed with CDF 1.0223. Incurred CL 2.38M vs. Paid CL 2.22M (6.7% variance) reflects ongoing case development. Incurred BF 2.39M aligns closely (0.3% variance). Framework Â§4 Convergence: Incurred CL and Paid BF cluster within 2%, midpoint selected. Incurred CL represents expected development trajectory at late maturity.</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n">
         <v>2379694.76</v>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 275 months (97.8% developed, CDF 1.0223). Incurred CL 2.379M vs. Paid CL 2.217M (6.7% variance). Incurred BF 2.391M converges very closely (0.3% variance). Strong CL/BF convergence combined with late maturity supports Incurred CL selection. Reflects case reserve development credibility.</t>
         </is>
       </c>
-      <c r="O3" s="6" t="n"/>
-      <c r="P3" s="6" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>1778091.575843999</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="8" t="n">
         <v>1778091.575843999</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="8" t="n">
         <v>1839414.768991383</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="8" t="n">
         <v>1805606.841693755</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="8" t="n">
         <v>2633272.1256</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>2633272.1256</v>
-      </c>
-      <c r="I4" s="3" t="n">
+      <c r="H4" s="8" t="n">
         <v>1865880.72372408</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="I4" s="8" t="n">
         <v>1818219.46023032</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="9" t="n">
         <v>1839414.77</v>
       </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 263 months, 96.7% developed. Incurred CL 1.84M vs. Paid CL 1.81M (1.6% variance). Incurred BF 1.87M also close. Framework §4 Convergence applies: methods cluster within ±2%. Selected Incurred CL as primary method at this late maturity, reflecting case adequacy and reserve estimation practices.</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="n">
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 263 months, 96.7% developed. Incurred CL 1.84M vs. Paid CL 1.81M (1.6% variance). Incurred BF 1.87M also close. Framework Â§4 Convergence applies: methods cluster within Â±2%. Selected Incurred CL as primary method at this late maturity, reflecting case adequacy and reserve estimation practices.</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n">
         <v>1839414.77</v>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 263 months (96.7% developed, CDF 1.0345). Incurred CL 1.839M, Paid CL 1.806M (1.6% variance), Incurred BF 1.866M. Methods cluster tightly within 2%. Incurred CL selected as baseline at this maturity; represents expected development trajectory with 61K IBNR (3.3% of ultimate).</t>
         </is>
       </c>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="A5" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>1122614.7306</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="8" t="n">
         <v>1122614.7306</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>1161331.701587282</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="8" t="n">
         <v>1148422.652748158</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="8" t="n">
         <v>1678710.98</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>1678710.98</v>
-      </c>
-      <c r="I5" s="3" t="n">
+      <c r="H5" s="8" t="n">
         <v>1178580.312371218</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="I5" s="8" t="n">
         <v>1160339.554450718</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="J5" s="9" t="n">
         <v>1161331.7</v>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 251 months, 96.7% developed. Incurred CL 1.16M, Paid CL 1.15M (1.1% variance), Incurred BF 1.18M. Tight convergence (§4) suggests high credibility across methods. Incurred CL selected per maturity-based hierarchy (§2: late stage). IBNR 39K represents 3.3% of ultimate, reasonable for this maturity.</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n">
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 251 months, 96.7% developed. Incurred CL 1.16M, Paid CL 1.15M (1.1% variance), Incurred BF 1.18M. Tight convergence (Â§4) suggests high credibility across methods. Incurred CL selected per maturity-based hierarchy (Â§2: late stage). IBNR 39K represents 3.3% of ultimate, reasonable for this maturity.</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="n">
         <v>1161331.7</v>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 251 months (96.7% developed, CDF 1.0345). Incurred CL 1.161M, Paid CL 1.148M (1.1% variance), Incurred BF 1.179M. Very tight convergence (within 2%) across all methods. Incurred CL selected per maturity-based hierarchy. IBNR 39K represents 3.3% of ultimate, reasonable for this development stage.</t>
         </is>
       </c>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="6" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="A6" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>2242149.132116</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="8" t="n">
         <v>2242149.132116</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="8" t="n">
         <v>2351717.567121524</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="8" t="n">
         <v>2302180.830765267</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="8" t="n">
         <v>1712285.2</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>1712285.2</v>
-      </c>
-      <c r="I6" s="3" t="n">
+      <c r="H6" s="8" t="n">
         <v>2321925.892841888</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="I6" s="8" t="n">
         <v>2286798.70427573</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="J6" s="9" t="n">
         <v>2351717.57</v>
       </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 239 months, 95.3% developed. Incurred CL 2.35M, Paid CL 2.30M (2.2% variance), Incurred BF 2.32M. Framework §4 Convergence: methods within 2% range. Note: Incurred IE (alternative method) shows 1.71M with negative IBNR (-0.53M), reflecting data anomaly or shift; rejected due to unreasonableness. Incurred CL represents credible development trajectory.</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="n">
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 239 months, 95.3% developed. Incurred CL 2.35M, Paid CL 2.30M (2.2% variance), Incurred BF 2.32M. Framework Â§4 Convergence: methods within 2% range. Note: Incurred IE (alternative method) shows 1.71M with negative IBNR (-0.53M), reflecting data anomaly or shift; rejected due to unreasonableness. Incurred CL represents credible development trajectory.</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="n">
         <v>2351717.57</v>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 239 months (95.3% developed, CDF 1.0489). Incurred CL 2.352M, Paid CL 2.302M (2.2% variance), Incurred BF 2.322M. Methods cluster within 2% range. Incurred IE shows 1.712M with negative IBNR (-0.530M), data quality issue; rejected. Incurred CL represents credible development trajectory.</t>
         </is>
       </c>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="A7" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>1517636.792660001</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="8" t="n">
         <v>1462141.027856</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="8" t="n">
         <v>1591800.052318661</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="8" t="n">
         <v>1501288.651138375</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="8" t="n">
         <v>1746530.9035</v>
       </c>
-      <c r="H7" s="3" t="n">
-        <v>1746530.9035</v>
-      </c>
-      <c r="I7" s="3" t="n">
+      <c r="H7" s="8" t="n">
         <v>1599009.088577111</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="I7" s="8" t="n">
         <v>1507683.591445887</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="J7" s="9" t="n">
         <v>1591800.05</v>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 227 months, 95.3% developed. Incurred CL 1.59M vs. Paid CL 1.50M (5.4% variance). Incurred BF 1.60M (0.6% offset). Framework §2 (late maturity) and §4 (Incurred CL/BF convergence) support Incurred CL. Paid CL shows lower IBNR (39K) but Incurred reflects case adequacy changes better at this stage.</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="n">
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 227 months, 95.3% developed. Incurred CL 1.59M vs. Paid CL 1.50M (5.4% variance). Incurred BF 1.60M (0.6% offset). Framework Â§2 (late maturity) and Â§4 (Incurred CL/BF convergence) support Incurred CL. Paid CL shows lower IBNR (39K) but Incurred reflects case adequacy changes better at this stage.</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>1591800.05</v>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 227 months (95.3% developed, CDF 1.0489). Incurred CL 1.592M vs. Paid CL 1.501M (5.4% variance), Incurred BF 1.599M (0.6% variance). Incurred CL and BF convergence strong. Incurred CL preferred at late maturity reflecting case adequacy. Paid CL shows lower credibility with greater variance.</t>
         </is>
       </c>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="A8" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>4810774.614816</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="8" t="n">
         <v>4790693.153152</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>5045865.598800745</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="8" t="n">
         <v>4927814.149603676</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="8" t="n">
         <v>2850338.4352</v>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>2850338.4352</v>
-      </c>
-      <c r="I8" s="3" t="n">
+      <c r="H8" s="8" t="n">
         <v>4943574.201784778</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="I8" s="8" t="n">
         <v>4870006.462175752</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="J8" s="9" t="n">
         <v>5045865.6</v>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 215 months, 95.3% developed. Incurred CL 5.05B is primary method selection at late maturity. Paid CL 4.93B (2.4% lower) and Incurred BF 4.94B (2.1% lower). Framework §4 Convergence check: Incurred CL and paid estimates within 2.5%, but Incurred CL selected per framework §2 (late maturity baseline). IBNR of 235M (4.7% of ultimate) consistent with development trajectory.</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="n">
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 215 months, 95.3% developed. Incurred CL 5.05B is primary method selection at late maturity. Paid CL 4.93B (2.4% lower) and Incurred BF 4.94B (2.1% lower). Framework Â§4 Convergence check: Incurred CL and paid estimates within 2.5%, but Incurred CL selected per framework Â§2 (late maturity baseline). IBNR of 235M (4.7% of ultimate) consistent with development trajectory.</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="n">
         <v>5045865.6</v>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 215 months (95.3% developed, CDF 1.0489). Incurred CL 5.046M is primary method selection. Paid CL 4.928M (2.4% lower), Incurred BF 4.944M (2.1% lower). Methods within 2.5% convergence range. Incurred CL selected per late-maturity framework. IBNR 235M (4.7% of ultimate) consistent with development trajectory.</t>
         </is>
       </c>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
+      <c r="N8" s="11" t="n"/>
+      <c r="O8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="A9" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>1378427.939547998</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="8" t="n">
         <v>1378427.939547998</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="8" t="n">
         <v>1448969.131870866</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="8" t="n">
         <v>1419583.273515399</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="8" t="n">
         <v>2543927.0535</v>
       </c>
-      <c r="H9" s="3" t="n">
-        <v>2543927.0535</v>
-      </c>
-      <c r="I9" s="3" t="n">
+      <c r="H9" s="8" t="n">
         <v>1502275.745266665</v>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="I9" s="8" t="n">
         <v>1452179.278711238</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="J9" s="9" t="n">
         <v>1448969.13</v>
       </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 203 months, 95.1% developed. Incurred CL 1.45M, Paid CL 1.42M (1.9% variance), Incurred BF 1.50M. Framework §2 (mid-stage, 36-60 months equivalent maturity): Incurred CL and Paid CL are both primary. Incurred CL selected per standard hierarchy, supported by tight method convergence. IBNR 71K is 4.9% of ultimate.</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="n">
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 203 months, 95.1% developed. Incurred CL 1.45M, Paid CL 1.42M (1.9% variance), Incurred BF 1.50M. Framework Â§2 (mid-stage, 36-60 months equivalent maturity): Incurred CL and Paid CL are both primary. Incurred CL selected per standard hierarchy, supported by tight method convergence. IBNR 71K is 4.9% of ultimate.</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="n">
         <v>1448969.13</v>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Late maturity at 203 months (95.1% developed, CDF 1.0512). Incurred CL 1.449M, Paid CL 1.420M (1.9% variance), Incurred BF 1.502M. Incurred CL and Paid CL converge closely. Incurred CL selected per standard hierarchy at mid-to-late stage. IBNR 71K is 4.9% of ultimate, appropriate for development level.</t>
         </is>
       </c>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="A10" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>1169581.089256</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="8" t="n">
         <v>1169581.089256</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="8" t="n">
         <v>1243450.075977988</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="8" t="n">
         <v>1223411.606541121</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="8" t="n">
         <v>2594805.5945</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>2594805.5945</v>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="H10" s="8" t="n">
         <v>1323729.344750299</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="I10" s="8" t="n">
         <v>1283753.39779014</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="J10" s="9" t="n">
         <v>1243450.08</v>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 191 months, 94.1% developed. Incurred CL 1.24M, Paid CL 1.22M (1.7% variance), Incurred BF 1.32M (6.4% higher). Framework §2 &amp; §4: Incurred CL and Paid CL convergence within 2% supports Incurred CL selection. Paid BF shows modest premium reflecting timing expectations. Incurred CL is most direct and credible at this maturity.</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="n">
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 191 months, 94.1% developed. Incurred CL 1.24M, Paid CL 1.22M (1.7% variance), Incurred BF 1.32M (6.4% higher). Framework Â§2 &amp; Â§4: Incurred CL and Paid CL convergence within 2% supports Incurred CL selection. Paid BF shows modest premium reflecting timing expectations. Incurred CL is most direct and credible at this maturity.</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>1243450.08</v>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Mid-maturity at 191 months (94.1% developed, CDF 1.0632). Incurred CL 1.243M, Paid CL 1.223M (1.7% variance), Incurred BF 1.324M (6.4% higher). Incurred CL and Paid CL convergence within 2% supports selection. Incurred CL most direct estimate at this maturity. IBNR 74K represents 5.9% of ultimate.</t>
         </is>
       </c>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="O10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="A11" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>1277672.072084001</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="8" t="n">
         <v>1277672.072084001</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="8" t="n">
         <v>1366518.130636961</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="8" t="n">
         <v>1344897.335890034</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="8" t="n">
         <v>1134300.7311</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>1134300.7311</v>
-      </c>
-      <c r="I11" s="3" t="n">
+      <c r="H11" s="8" t="n">
         <v>1351420.196541743</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="I11" s="8" t="n">
         <v>1334370.575269829</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="J11" s="9" t="n">
         <v>1366518.13</v>
       </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 179 months, 93.5% developed. Incurred CL 1.37M, Paid CL 1.34M (1.6% variance), Incurred BF 1.35M. Framework §4 Convergence: all three methods cluster tightly. Incurred CL selected as primary method per §2 maturity hierarchy (mid-stage). IBNR 89K represents reasonable 6.5% of ultimate at this development level.</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="n">
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 179 months, 93.5% developed. Incurred CL 1.37M, Paid CL 1.34M (1.6% variance), Incurred BF 1.35M. Framework Â§4 Convergence: all three methods cluster tightly. Incurred CL selected as primary method per Â§2 maturity hierarchy (mid-stage). IBNR 89K represents reasonable 6.5% of ultimate at this development level.</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n">
         <v>1366518.13</v>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Mid-maturity at 179 months (93.5% developed, CDF 1.0695). Incurred CL 1.367M, Paid CL 1.345M (1.6% variance), Incurred BF 1.351M. Tight convergence across all three methods. Incurred CL selected as primary method per mid-stage hierarchy. IBNR 89K represents 6.5% of ultimate, reasonable for development level.</t>
         </is>
       </c>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="A12" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>1916081.580416</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="8" t="n">
         <v>1892658.297732</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="8" t="n">
         <v>2064690.91616036</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="8" t="n">
         <v>2001206.411407335</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="8" t="n">
         <v>1542648.9944</v>
       </c>
-      <c r="H12" s="3" t="n">
-        <v>1542648.9944</v>
-      </c>
-      <c r="I12" s="3" t="n">
+      <c r="H12" s="8" t="n">
         <v>2027116.137961699</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="I12" s="8" t="n">
         <v>1976333.643488819</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="J12" s="9" t="n">
         <v>2064690.92</v>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 167 months, 92.8% developed. Incurred CL 2.06M, Paid CL 2.00M (2.9% variance). Incurred BF 2.03M (1.5% variance). Framework §4 &amp; §2: late-mid maturity with method convergence within 3%. Incurred CL selected as primary at this stage, reflecting developed case reserves and estimated IBNR. IBNR 149K is 7.2% of ultimate.</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="n">
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 167 months, 92.8% developed. Incurred CL 2.06M, Paid CL 2.00M (2.9% variance). Incurred BF 2.03M (1.5% variance). Framework Â§4 &amp; Â§2: late-mid maturity with method convergence within 3%. Incurred CL selected as primary at this stage, reflecting developed case reserves and estimated IBNR. IBNR 149K is 7.2% of ultimate.</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="n">
         <v>2064690.92</v>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Mid-maturity at 167 months (92.8% developed, CDF 1.0776). Incurred CL 2.065M, Paid CL 2.001M (2.9% variance), Incurred BF 2.027M (1.5% variance). Methods converge within 3%. Incurred CL selected at late-mid maturity stage, reflecting developed case reserves. IBNR 149K is 7.2% of ultimate.</t>
         </is>
       </c>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
+      <c r="N12" s="11" t="n"/>
+      <c r="O12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="A13" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>1363753.380531999</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="8" t="n">
         <v>1194236.878339999</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="8" t="n">
         <v>1475255.850013807</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="8" t="n">
         <v>1264875.627675566</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="8" t="n">
         <v>1573501.9744</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>1573501.9744</v>
-      </c>
-      <c r="I13" s="3" t="n">
+      <c r="H13" s="8" t="n">
         <v>1482681.467398056</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="I13" s="8" t="n">
         <v>1282111.297861324</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="J13" s="9" t="n">
         <v>1475255.85</v>
       </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 155 months, 92.4% developed. Incurred CL 1.48M, Paid CL 1.26M (14.8% variance). Incurred BF 1.48M (0.04% variance). Framework §4 Convergence: Incurred CL and BF cluster within 1%. Paid CL shows lower credibility (larger deviation). Incurred CL selected per §2 (early-mid stage baseline). IBNR 112K is reasonable 7.6% of ultimate.</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="n">
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 155 months, 92.4% developed. Incurred CL 1.48M, Paid CL 1.26M (14.8% variance). Incurred BF 1.48M (0.04% variance). Framework Â§4 Convergence: Incurred CL and BF cluster within 1%. Paid CL shows lower credibility (larger deviation). Incurred CL selected per Â§2 (early-mid stage baseline). IBNR 112K is reasonable 7.6% of ultimate.</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>1475255.85</v>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Mid-maturity at 155 months (92.4% developed, CDF 1.0818). Incurred CL 1.475M, Paid CL 1.265M (14.8% variance), Incurred BF 1.483M (0.04% variance). Incurred CL and BF cluster tightly within 1%. Paid CL shows lower credibility. Incurred CL selected per mid-stage baseline. IBNR 112K is 7.6% of ultimate.</t>
         </is>
       </c>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="A14" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>708529.9908599999</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="8" t="n">
         <v>708529.9908599999</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="8" t="n">
         <v>769526.2801642057</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="8" t="n">
         <v>762971.6617653245</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="8" t="n">
         <v>1203729.0102</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>1203729.0102</v>
-      </c>
-      <c r="I14" s="3" t="n">
+      <c r="H14" s="8" t="n">
         <v>803943.2403390912</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="I14" s="8" t="n">
         <v>794421.8029895274</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="J14" s="9" t="n">
         <v>769526.28</v>
       </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 143 months, 92.1% developed. Incurred CL 769.5K, Paid CL 763.0K (0.9% variance), Incurred BF 803.9K (4.5% variance). Framework §2 (early maturity, 24-36 mo equivalent): Incurred CL is primary. §4 Convergence: Incurred CL and Paid CL within 1%. Selected Incurred CL. IBNR 61K is 7.9% of ultimate, consistent with remaining development.</t>
-        </is>
-      </c>
-      <c r="M14" s="5" t="n">
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 143 months, 92.1% developed. Incurred CL 769.5K, Paid CL 763.0K (0.9% variance), Incurred BF 803.9K (4.5% variance). Framework Â§2 (early maturity, 24-36 mo equivalent): Incurred CL is primary. Â§4 Convergence: Incurred CL and Paid CL within 1%. Selected Incurred CL. IBNR 61K is 7.9% of ultimate, consistent with remaining development.</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="n">
         <v>769526.28</v>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Mid-maturity at 143 months (92.1% developed, CDF 1.0861). Incurred CL 769.5K, Paid CL 763.0K (0.9% variance), Incurred BF 803.9K (4.5% variance). Incurred CL and Paid CL converge tightly within 1%. Selected Incurred CL as primary at early-mid stage. IBNR 61K is 7.9% of ultimate.</t>
         </is>
       </c>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
+      <c r="N14" s="11" t="n"/>
+      <c r="O14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
+      <c r="A15" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>1389603.684732</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="8" t="n">
         <v>1389603.684732</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="8" t="n">
         <v>1545756.020435727</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="8" t="n">
         <v>1522264.681624703</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="8" t="n">
         <v>1227803.5905</v>
       </c>
-      <c r="H15" s="3" t="n">
-        <v>1227803.5905</v>
-      </c>
-      <c r="I15" s="3" t="n">
+      <c r="H15" s="8" t="n">
         <v>1513636.453103785</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="I15" s="8" t="n">
         <v>1496603.242870816</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="J15" s="9" t="n">
         <v>1545756.02</v>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 131 months, 89.9% developed. Incurred CL 1.55M, Paid CL 1.52M (1.8% variance), Incurred BF 1.51M (2.2% variance). Framework §2 (early maturity): Incurred CL is primary. §4 Convergence: all three methods within 2.5%. Selected Incurred CL as most direct estimate. IBNR 156K is 10.1% of ultimate, reflecting increasing development needs.</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="n">
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 131 months, 89.9% developed. Incurred CL 1.55M, Paid CL 1.52M (1.8% variance), Incurred BF 1.51M (2.2% variance). Framework Â§2 (early maturity): Incurred CL is primary. Â§4 Convergence: all three methods within 2.5%. Selected Incurred CL as most direct estimate. IBNR 156K is 10.1% of ultimate, reflecting increasing development needs.</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="n">
         <v>1545756.02</v>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Early-mid maturity at 131 months (89.9% developed, CDF 1.1124). Incurred CL 1.546M, Paid CL 1.522M (1.8% variance), Incurred BF 1.514M (2.2% variance). All methods converge within 2.5%. Incurred CL selected per early-maturity hierarchy. IBNR 156K represents 10.1% of ultimate, reflecting ongoing development needs.</t>
         </is>
       </c>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="A16" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <v>3382963.258076001</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="8" t="n">
         <v>3364231.298548001</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="8" t="n">
         <v>3806012.584434826</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="8" t="n">
         <v>3701619.422324063</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="8" t="n">
         <v>1669812.8832</v>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>1669812.8832</v>
-      </c>
-      <c r="I16" s="3" t="n">
+      <c r="H16" s="8" t="n">
         <v>3568567.798184989</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="8" t="n">
         <v>3516428.207912127</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="J16" s="9" t="n">
         <v>3806012.58</v>
       </c>
-      <c r="L16" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 119 months, 88.9% developed. Incurred CL 3.81B, Paid CL 3.70B (2.8% variance), Incurred BF 3.57B (6.2% lower). Framework §2 (early stage, 24-36 mo): Incurred CL is primary method. Note: Incurred IE (alternative method) shows 1.67B with negative IBNR (-1.71B), indicating data anomaly or reserve adjustment; rejected. §4 Convergence: CL methods within 3%. Selected Incurred CL. IBNR 423K is 11.1% of ultimate.</t>
-        </is>
-      </c>
-      <c r="M16" s="5" t="n">
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 119 months, 88.9% developed. Incurred CL 3.81B, Paid CL 3.70B (2.8% variance), Incurred BF 3.57B (6.2% lower). Framework Â§2 (early stage, 24-36 mo): Incurred CL is primary method. Note: Incurred IE (alternative method) shows 1.67B with negative IBNR (-1.71B), indicating data anomaly or reserve adjustment; rejected. Â§4 Convergence: CL methods within 3%. Selected Incurred CL. IBNR 423K is 11.1% of ultimate.</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n">
         <v>3806012.58</v>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Early maturity at 119 months (88.9% developed, CDF 1.1251). Incurred CL 3.806M, Paid CL 3.702M (2.8% variance), Incurred BF 3.569M (6.2% lower). Incurred CL and Paid CL converge within 3%. Incurred IE shows 1.669M with negative IBNR (-1.713M), data anomaly; rejected. Incurred CL preferred. IBNR 423K is 11.1% of ultimate.</t>
         </is>
       </c>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
+      <c r="N16" s="11" t="n"/>
+      <c r="O16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="A17" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>2506323.643367999</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="8" t="n">
         <v>2462208.676391999</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="8" t="n">
         <v>2884036.877638761</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="8" t="n">
         <v>2775780.543107491</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="8" t="n">
         <v>2554813.7112</v>
       </c>
-      <c r="H17" s="3" t="n">
-        <v>2554813.7112</v>
-      </c>
-      <c r="I17" s="3" t="n">
+      <c r="H17" s="8" t="n">
         <v>2840919.555541876</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="I17" s="8" t="n">
         <v>2750818.561824248</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="J17" s="9" t="n">
         <v>2884036.88</v>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 107 months, 86.9% developed. Incurred CL 2.88M, Paid CL 2.78M (3.6% variance), Incurred BF 2.84M (1.4% variance). Framework §2 (early stage): Incurred CL and BF baseline. §4 Convergence: Incurred CL and BF within 2%. Selected Incurred CL per standard hierarchy. IBNR 378K is 13.1% of ultimate, appropriate for 107-month maturity.</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="n">
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 107 months, 86.9% developed. Incurred CL 2.88M, Paid CL 2.78M (3.6% variance), Incurred BF 2.84M (1.4% variance). Framework Â§2 (early stage): Incurred CL and BF baseline. Â§4 Convergence: Incurred CL and BF within 2%. Selected Incurred CL per standard hierarchy. IBNR 378K is 13.1% of ultimate, appropriate for 107-month maturity.</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="n">
         <v>2884036.88</v>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Early maturity at 107 months (86.9% developed, CDF 1.1507). Incurred CL 2.884M, Paid CL 2.776M (3.6% variance), Incurred BF 2.841M (1.4% variance). Incurred CL and BF convergence strong. Incurred CL selected per early-stage hierarchy. IBNR 378K is 13.1% of ultimate, appropriate for 107-month maturity.</t>
         </is>
       </c>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
+      <c r="A18" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>1205811.828916</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="8" t="n">
         <v>1205811.828916</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="8" t="n">
         <v>1408623.103930131</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="8" t="n">
         <v>1379767.312627784</v>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="8" t="n">
         <v>2605909.9854</v>
       </c>
-      <c r="H18" s="3" t="n">
-        <v>2605909.9854</v>
-      </c>
-      <c r="I18" s="3" t="n">
+      <c r="H18" s="8" t="n">
         <v>1581006.531627083</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="I18" s="8" t="n">
         <v>1534354.422925048</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="J18" s="9" t="n">
         <v>1408623.1</v>
       </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 95 months, 85.6% developed. Incurred CL 1.41M, Paid CL 1.38M (2.2% variance), Incurred BF 1.58M (12.2% higher). Framework §2 (early stage): Incurred CL primary. Paid CL and BF show higher IBNR (375K and 202K respectively). §4 Convergence: CL methods within 2.5%, selected Incurred CL. IBNR 203K is 14.4% of ultimate.</t>
-        </is>
-      </c>
-      <c r="M18" s="5" t="n">
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 95 months, 85.6% developed. Incurred CL 1.41M, Paid CL 1.38M (2.2% variance), Incurred BF 1.58M (12.2% higher). Framework Â§2 (early stage): Incurred CL primary. Paid CL and BF show higher IBNR (375K and 202K respectively). Â§4 Convergence: CL methods within 2.5%, selected Incurred CL. IBNR 203K is 14.4% of ultimate.</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n">
         <v>1408623.1</v>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="M18" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Early maturity at 95 months (85.6% developed, CDF 1.1682). Incurred CL 1.409M, Paid CL 1.380M (2.2% variance), Incurred BF 1.581M (12.2% higher). Incurred CL and Paid CL converge within 2.5%. Incurred CL selected as primary at early stage. IBNR 203K is 14.4% of ultimate.</t>
         </is>
       </c>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
+      <c r="N18" s="11" t="n"/>
+      <c r="O18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="A19" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <v>2395448.423304001</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="8" t="n">
         <v>2395448.423304001</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="8" t="n">
         <v>2841165.143915472</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="8" t="n">
         <v>2796668.708826229</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="8" t="n">
         <v>2215023.4875</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>2215023.4875</v>
-      </c>
-      <c r="I19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>2742937.201645587</v>
       </c>
-      <c r="J19" s="3" t="n">
+      <c r="I19" s="8" t="n">
         <v>2713223.76554902</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="J19" s="9" t="n">
         <v>2841165.14</v>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 83 months, 84.3% developed. Incurred CL 2.84M, Paid CL 2.80M (1.6% variance), Incurred BF 2.74M (3.7% lower). Framework §2 (early stage, 24-36 mo range): Incurred CL primary. §4 Convergence: Incurred CL and Paid CL within 2%. Selected Incurred CL. IBNR 446K is 15.7% of ultimate, reasonable for 83-month development.</t>
-        </is>
-      </c>
-      <c r="M19" s="5" t="n">
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 83 months, 84.3% developed. Incurred CL 2.84M, Paid CL 2.80M (1.6% variance), Incurred BF 2.74M (3.7% lower). Framework Â§2 (early stage, 24-36 mo range): Incurred CL primary. Â§4 Convergence: Incurred CL and Paid CL within 2%. Selected Incurred CL. IBNR 446K is 15.7% of ultimate, reasonable for 83-month development.</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>2841165.14</v>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Early maturity at 83 months (84.3% developed, CDF 1.1861). Incurred CL 2.841M, Paid CL 2.797M (1.6% variance), Incurred BF 2.743M (3.7% lower). Incurred CL and Paid CL converge within 2%. Incurred CL selected per early-stage baseline. IBNR 446K is 15.7% of ultimate, reasonable for 83-month development.</t>
         </is>
       </c>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="A20" s="3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="C20" s="8" t="n">
         <v>2599882.874291999</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="8" t="n">
         <v>2395189.834488001</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="8" t="n">
         <v>3198349.686727937</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="8" t="n">
         <v>2972537.917173816</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="8" t="n">
         <v>2259323.9575</v>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>2259323.9575</v>
-      </c>
-      <c r="I20" s="3" t="n">
+      <c r="H20" s="8" t="n">
         <v>3022641.652894619</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="I20" s="8" t="n">
         <v>2834012.278936059</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="J20" s="9" t="n">
         <v>3198349.69</v>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 71 months, 81.3% developed. Incurred CL 3.20M, Paid CL 2.97M (7.3% variance), Incurred BF 3.02M (5.6% variance). Framework §2 (green stage, 12-24 mo): Incurred CL and BF are co-primary. §4 Convergence: Incurred BF and Paid CL cluster near 3.0M (within 2%); Incurred CL slightly higher. Selected Incurred CL as best estimate of developed case reserves, with IBNR 598K (18.7% of ultimate) reflecting substantial remaining development.</t>
-        </is>
-      </c>
-      <c r="M20" s="5" t="n">
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 71 months, 81.3% developed. Incurred CL 3.20M, Paid CL 2.97M (7.3% variance), Incurred BF 3.02M (5.6% variance). Framework Â§2 (green stage, 12-24 mo): Incurred CL and BF are co-primary. Â§4 Convergence: Incurred BF and Paid CL cluster near 3.0M (within 2%); Incurred CL slightly higher. Selected Incurred CL as best estimate of developed case reserves, with IBNR 598K (18.7% of ultimate) reflecting substantial remaining development.</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n">
         <v>3198349.69</v>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="M20" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Green stage at 71 months (81.3% developed, CDF 1.2302). Incurred CL 3.198M, Paid CL 2.973M (7.3% variance), Incurred BF 3.023M (5.6% variance). Paid CL and Incurred BF cluster near 3.0M (within 2%); Incurred CL slightly higher. Incurred CL reflects early case reserve establishment best. IBNR 598K (18.7% of ultimate) reflects substantial remaining development.</t>
         </is>
       </c>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
+      <c r="N20" s="11" t="n"/>
+      <c r="O20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
+      <c r="A21" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <v>978899.5094679999</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="8" t="n">
         <v>976050.8625559999</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="8" t="n">
         <v>1272753.120311486</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="8" t="n">
         <v>1341782.33085796</v>
       </c>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="8" t="n">
         <v>1843608.3492</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>1843608.3492</v>
-      </c>
-      <c r="I21" s="3" t="n">
+      <c r="H21" s="8" t="n">
         <v>1404552.341700722</v>
       </c>
-      <c r="J21" s="3" t="n">
+      <c r="I21" s="8" t="n">
         <v>1478565.743710778</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="J21" s="9" t="n">
         <v>1272753.12</v>
       </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 59 months, 76.9% developed. Incurred CL 1.27M, Paid CL 1.34M (5.4% variance), Incurred BF 1.40M (10% variance). Framework §2 (green stage, 12-24 mo): Incurred BF and Paid BF primary, but Incurred CL is developing with limited data. §4 Convergence: Incurred CL is lowest, Paid/Incurred BF clustered. Framework §7 Reasonability: Incurred CL shows strong reserve adequacy with IBNR 294K (23.1% of ultimate). Selected Incurred CL as more conservative estimate given maturity.</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="n">
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 59 months, 76.9% developed. Incurred CL 1.27M, Paid CL 1.34M (5.4% variance), Incurred BF 1.40M (10% variance). Framework Â§2 (green stage, 12-24 mo): Incurred BF and Paid BF primary, but Incurred CL is developing with limited data. Â§4 Convergence: Incurred CL is lowest, Paid/Incurred BF clustered. Framework Â§7 Reasonability: Incurred CL shows strong reserve adequacy with IBNR 294K (23.1% of ultimate). Selected Incurred CL as more conservative estimate given maturity.</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="n">
         <v>1272753.12</v>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Green stage at 59 months (76.9% developed, CDF 1.3002). Incurred CL 1.273M is lowest estimate, Paid CL 1.342M (5.4% higher), Incurred BF 1.405M (10.4% higher). Incurred CL more conservative at this immature stage with high tail exposure. IBNR 294K (23.1% of ultimate) reflects reasonable development expectation.</t>
         </is>
       </c>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="A22" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C22" s="8" t="n">
         <v>1011313.279736</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="8" t="n">
         <v>974979.4133360002</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="8" t="n">
         <v>1382219.838183875</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="8" t="n">
         <v>1438688.114141852</v>
       </c>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="8" t="n">
         <v>1410360.3873</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>1410360.3873</v>
-      </c>
-      <c r="I22" s="3" t="n">
+      <c r="H22" s="8" t="n">
         <v>1389771.107480668</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="I22" s="8" t="n">
         <v>1429557.703400638</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="J22" s="9" t="n">
         <v>1382219.84</v>
       </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 47 months, 73.2% developed. Incurred CL 1.38M, Paid CL 1.44M (4.3% variance), Incurred BF 1.39M (0.8% variance). Framework §2 (green stage): Incurred BF primary with framework §4 Convergence: Incurred CL and BF within 1%, extremely tight. Selected Incurred CL reflecting case reserve development credibility. IBNR 371K is 26.8% of ultimate, appropriate for 47-month development stage.</t>
-        </is>
-      </c>
-      <c r="M22" s="5" t="n">
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 47 months, 73.2% developed. Incurred CL 1.38M, Paid CL 1.44M (4.3% variance), Incurred BF 1.39M (0.8% variance). Framework Â§2 (green stage): Incurred BF primary with framework Â§4 Convergence: Incurred CL and BF within 1%, extremely tight. Selected Incurred CL reflecting case reserve development credibility. IBNR 371K is 26.8% of ultimate, appropriate for 47-month development stage.</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="n">
         <v>1382219.84</v>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="M22" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Green stage at 47 months (73.2% developed, CDF 1.3668). Incurred CL 1.382M, Paid CL 1.439M (4.3% variance), Incurred BF 1.390M (0.8% variance). Incurred CL and BF converge extremely tightly within 1%. Selected Incurred CL reflecting case reserve credibility. IBNR 371K is 26.8% of ultimate.</t>
         </is>
       </c>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="A23" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C23" s="8" t="n">
         <v>827416.1066440007</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="8" t="n">
         <v>791103.7101360001</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="8" t="n">
         <v>1301300.197111128</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="8" t="n">
         <v>1384955.340447214</v>
       </c>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="8" t="n">
         <v>959045.0632000001</v>
       </c>
-      <c r="H23" s="3" t="n">
-        <v>959045.0632000001</v>
-      </c>
-      <c r="I23" s="3" t="n">
+      <c r="H23" s="8" t="n">
         <v>1176663.880908888</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="I23" s="8" t="n">
         <v>1202330.309066862</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="J23" s="9" t="n">
         <v>1301300.2</v>
       </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 35 months, 63.6% developed. Incurred CL 1.30M, Paid CL 1.38M (6.0% variance), Incurred BF 1.18M (9.5% lower). Framework §2 (very green, 0-12 mo equivalent): BF and Paid BF are typically primary, but CL methods have limited credibility. §4 Convergence: Paid CL and Incurred CL within 6%. Framework §3 Diagnostic override: CL methods increasingly uncertain; however, Incurred CL (1.30M) vs. Paid CL (1.38M) represent case-based development. Selected Incurred CL as more conservative, IBNR 474K is 36.4% of ultimate reflecting early stage.</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="n">
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 35 months, 63.6% developed. Incurred CL 1.30M, Paid CL 1.38M (6.0% variance), Incurred BF 1.18M (9.5% lower). Framework Â§2 (very green, 0-12 mo equivalent): BF and Paid BF are typically primary, but CL methods have limited credibility. Â§4 Convergence: Paid CL and Incurred CL within 6%. Framework Â§3 Diagnostic override: CL methods increasingly uncertain; however, Incurred CL (1.30M) vs. Paid CL (1.38M) represent case-based development. Selected Incurred CL as more conservative, IBNR 474K is 36.4% of ultimate reflecting early stage.</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="n">
         <v>1301300.2</v>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Very green at 35 months (63.6% developed, CDF 1.5727). Incurred CL 1.301M, Paid CL 1.385M (6.0% higher), Incurred BF 1.177M (9.5% lower). Incurred CL is middle estimate. At this immature stage with high tail extrapolation, Incurred CL reflects observable case development best. IBNR 474K is 36.4% of ultimate.</t>
         </is>
       </c>
-      <c r="O23" s="6" t="n"/>
-      <c r="P23" s="6" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="A24" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8" t="n">
         <v>1651756.674352</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="8" t="n">
         <v>1199242.068356001</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="8" t="n">
         <v>3095494.878246275</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="8" t="n">
         <v>2986282.892939571</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="8" t="n">
         <v>978225.9646000001</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>978225.9646000001</v>
-      </c>
-      <c r="I24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>2108001.072318659</v>
       </c>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="8" t="n">
         <v>1784628.582989602</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="J24" s="9" t="n">
         <v>3095494.88</v>
       </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 23 months, 53.4% developed. Incurred CL 3.10M, Paid CL 2.99M (3.5% variance), Incurred BF 2.11M (31.8% lower). Framework §2 (very green, 0-12 mo): Paid BF and Incurred BF are theoretically primary, but data is sparse. Incurred CL 3.10M shows substantial case reserve activity. Paid CL 2.99M is close alternative. §4 Convergence: Incurred/Paid CL within 4%. Framework §7 Reasonability: Incurred CL is much higher than BF methods, suggesting strong case development early in accident year. Selected Incurred CL (3.10M) reflecting observable case activity, IBNR 1.44M is 46.6% of ultimate.</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="n">
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 23 months, 53.4% developed. Incurred CL 3.10M, Paid CL 2.99M (3.5% variance), Incurred BF 2.11M (31.8% lower). Framework Â§2 (very green, 0-12 mo): Paid BF and Incurred BF are theoretically primary, but data is sparse. Incurred CL 3.10M shows substantial case reserve activity. Paid CL 2.99M is close alternative. Â§4 Convergence: Incurred/Paid CL within 4%. Framework Â§7 Reasonability: Incurred CL is much higher than BF methods, suggesting strong case development early in accident year. Selected Incurred CL (3.10M) reflecting observable case activity, IBNR 1.44M is 46.6% of ultimate.</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="n">
         <v>3095494.88</v>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Very green at 23 months (53.4% developed, CDF 1.8741). Incurred CL 3.095M, Paid CL 2.986M (3.5% variance), Incurred BF 2.108M (31.8% lower). Incurred CL and Paid CL converge within 4%. BF methods significantly lower due to sparse paid development. Incurred CL captures early case activity best at extreme immaturity. IBNR 1.444M is 46.6% of ultimate.</t>
         </is>
       </c>
-      <c r="O24" s="6" t="n"/>
-      <c r="P24" s="6" t="n"/>
+      <c r="N24" s="11" t="n"/>
+      <c r="O24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="A25" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8" t="n">
         <v>890155.221828</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="8" t="n">
         <v>355247.7609319999</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="8" t="n">
         <v>2525664.374673065</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="8" t="n">
         <v>2257985.723530615</v>
       </c>
-      <c r="G25" s="3" t="n">
+      <c r="G25" s="8" t="n">
         <v>997790.4837999999</v>
       </c>
-      <c r="H25" s="3" t="n">
-        <v>997790.4837999999</v>
-      </c>
-      <c r="I25" s="3" t="n">
+      <c r="H25" s="8" t="n">
         <v>1536280.449408108</v>
       </c>
-      <c r="J25" s="3" t="n">
+      <c r="I25" s="8" t="n">
         <v>1196056.368560097</v>
       </c>
-      <c r="K25" s="4" t="n">
+      <c r="J25" s="9" t="n">
         <v>2525664.37</v>
       </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Incurred CL selected. At 11 months, 35.2% developed. Incurred CL 2.53M, Paid CL 2.26M (10.6% variance), Incurred BF 1.54M (38.9% lower). Framework §2 (very green, 0-12 mo): BF methods theoretically primary with sparse data. However, Incurred CL 2.53M reflects early case reserve establishment. CDF 2.837 is very high, indicating substantial tail extrapolation required. Incurred CL selected as least model-dependent, with IBNR 1.64M representing 64.8% of ultimate development expectation. High uncertainty warranted at this extreme green maturity.</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="n">
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Incurred CL selected. At 11 months, 35.2% developed. Incurred CL 2.53M, Paid CL 2.26M (10.6% variance), Incurred BF 1.54M (38.9% lower). Framework Â§2 (very green, 0-12 mo): BF methods theoretically primary with sparse data. However, Incurred CL 2.53M reflects early case reserve establishment. CDF 2.837 is very high, indicating substantial tail extrapolation required. Incurred CL selected as least model-dependent, with IBNR 1.64M representing 64.8% of ultimate development expectation. High uncertainty warranted at this extreme green maturity.</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="n">
         <v>2525664.37</v>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>Incurred CL selected. Extreme immaturity at 11 months (35.2% developed, CDF 2.8373). Incurred CL 2.526M reflects early case reserve establishment. Paid CL 2.258M (10.6% lower) and Incurred BF 1.536M (38.9% lower) show less credibility at this very green stage. CDF 2.837 requires significant tail extrapolation. Incurred CL is least model-dependent. IBNR 1.636M represents 64.8% of ultimate.</t>
         </is>
       </c>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="11" t="n"/>
     </row>
     <row r="26"/>
   </sheetData>
@@ -1875,11 +1710,12 @@
   <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18.7109375" customWidth="1" min="1" max="7"/>
+    <col width="18.7109375" customWidth="1" min="1" max="6"/>
+    <col width="22.7109375" customWidth="1" min="7" max="7"/>
     <col width="30.7109375" customWidth="1" min="8" max="8"/>
-    <col width="18.7109375" customWidth="1" min="9" max="9"/>
+    <col width="22.7109375" customWidth="1" min="9" max="9"/>
     <col width="30.7109375" customWidth="1" min="10" max="10"/>
-    <col width="18.7109375" customWidth="1" min="11" max="11"/>
+    <col width="22.7109375" customWidth="1" min="11" max="11"/>
     <col width="40.7109375" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -1889,32 +1725,32 @@
           <t>Accident Period</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Current Age</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Reported</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Reported CL</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Reported IE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Initial Expected</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Reported BF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Rules-Based AI Selection</t>
         </is>
@@ -1924,7 +1760,7 @@
           <t>Rules-Based AI Reasoning</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Open-Ended AI Selection</t>
         </is>
@@ -1934,7 +1770,7 @@
           <t>Open-Ended AI Reasoning</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>User Selection</t>
         </is>
@@ -1946,1012 +1782,916 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
+      <c r="A2" s="3" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>700.7076000000001</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="8" t="n">
         <v>700.7076000000001</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="8" t="n">
         <v>700.775874480892</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="8" t="n">
         <v>700.7076000000001</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="9" t="n">
         <v>700.71</v>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>Reported CL selected. At 287 months maturity, CDF 1.0 and 100% developed indicate full closure. Reported Count ultimate equals actual (700.71). Closed CL would show similar result. Reported Count is simplest, most direct at complete maturity. IBNR 0 is appropriate. No development expected.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="10" t="n">
         <v>700.71</v>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Tail-mature at 287 months with CDF 1.0 and 100% developed. Reported Count actual equals ultimate (700.71). Direct, fully credible measure at complete maturity. Zero IBNR appropriate; no development expected. Simplest and most reliable selection at extreme tail stage.</t>
         </is>
       </c>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="6" t="n"/>
+      <c r="K2" s="11" t="n"/>
+      <c r="L2" s="11" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="A3" s="3" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C3" s="8" t="n">
         <v>651.8824000000001</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="8" t="n">
         <v>651.8824000000001</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="8" t="n">
         <v>683.1663101357999</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="8" t="n">
         <v>651.8824000000001</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="9" t="n">
         <v>651.88</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 275 months, CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework §2 maturity-based: tail-stage periods use direct actuals when fully developed. Zero IBNR appropriate at this maturity.</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="n">
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 275 months, CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework Â§2 maturity-based: tail-stage periods use direct actuals when fully developed. Zero IBNR appropriate at this maturity.</t>
+        </is>
+      </c>
+      <c r="I3" s="10" t="n">
         <v>651.88</v>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Late maturity at 275 months with CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework preference: at complete development, reported actual is most direct and credible. Zero IBNR reflects full closure and reporting.</t>
         </is>
       </c>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
+      <c r="K3" s="11" t="n"/>
+      <c r="L3" s="11" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" s="3" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>551.5928</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="8" t="n">
         <v>551.5928</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="8" t="n">
         <v>648.4432609290001</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="8" t="n">
         <v>551.5928</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="9" t="n">
         <v>551.59</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 263 months, CDF 1.0 and 100% developed. Reported Count 551.59 is fully developed. Framework §2: at tail maturity with complete development, reported actual is ultimate. No further development indicated.</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="n">
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 263 months, CDF 1.0 and 100% developed. Reported Count 551.59 is fully developed. Framework Â§2: at tail maturity with complete development, reported actual is ultimate. No further development indicated.</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n">
         <v>551.59</v>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Late maturity at 263 months with CDF 1.0 and 100% developed. Reported Count 551.59 fully developed. Actual equals ultimate; no further development expected. Direct measure most appropriate at complete maturity.</t>
         </is>
       </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="A5" s="3" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="C5" s="8" t="n">
         <v>642.6452</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="8" t="n">
         <v>642.6452</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" s="8" t="n">
         <v>627.83790652</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="8" t="n">
         <v>642.6452</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="9" t="n">
         <v>642.65</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 251 months, CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. Framework §2 late maturity: direct reported count is most credible. IBNR 0 reflects complete development.</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 251 months, CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. Framework Â§2 late maturity: direct reported count is most credible. IBNR 0 reflects complete development.</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="n">
         <v>642.65</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Late maturity at 251 months with CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. At late maturity with complete development, reported actual is most credible ultimate. Zero IBNR.</t>
         </is>
       </c>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="A6" s="3" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="C6" s="8" t="n">
         <v>641.3256</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="8" t="n">
         <v>641.3256</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="8" t="n">
         <v>623.61426984</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="8" t="n">
         <v>641.3256</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="9" t="n">
         <v>641.33</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 239 months, CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate. Framework §2: tail/late stage fully developed periods use actual reported count. No uncertainty in development.</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n">
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 239 months, CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate. Framework Â§2: tail/late stage fully developed periods use actual reported count. No uncertainty in development.</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
         <v>641.33</v>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Late maturity at 239 months with CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate at complete development. Fully closed and reported claims; no uncertainty in final count.</t>
         </is>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="A7" s="3" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="C7" s="8" t="n">
         <v>497.4892</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="8" t="n">
         <v>497.4892</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="8" t="n">
         <v>606.7448358759</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="8" t="n">
         <v>497.4892</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="9" t="n">
         <v>497.49</v>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 227 months, CDF 1.0 and 100% developed. Reported Count 497.49 represents fully closed and reported claims. Framework §2 late maturity: actual reported = ultimate. Zero IBNR.</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="n">
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 227 months, CDF 1.0 and 100% developed. Reported Count 497.49 represents fully closed and reported claims. Framework Â§2 late maturity: actual reported = ultimate. Zero IBNR.</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
         <v>497.49</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Late maturity at 227 months with CDF 1.0 and 100% developed. Reported Count 497.49 represents fully developed ultimate. Complete reporting and closure confirmed. Zero IBNR appropriate.</t>
         </is>
       </c>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="A8" s="3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="C8" s="8" t="n">
         <v>476.3756</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="8" t="n">
         <v>476.3756</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="8" t="n">
         <v>550.471610298</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="8" t="n">
         <v>476.3756</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="9" t="n">
         <v>476.38</v>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 215 months, CDF 1.0 and 100% developed. Reported Count 476.38 is complete. Framework §2: late-stage fully developed period uses actual count. All claims reported and closed.</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 215 months, CDF 1.0 and 100% developed. Reported Count 476.38 is complete. Framework Â§2: late-stage fully developed period uses actual count. All claims reported and closed.</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
         <v>476.38</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Late maturity at 215 months with CDF 1.0 and 100% developed. Reported Count 476.38 is complete at full development. All claims reported and closed; actual equals ultimate.</t>
         </is>
       </c>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="A9" s="3" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="C9" s="8" t="n">
         <v>328.5804000000001</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="8" t="n">
         <v>328.5804000000001</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="8" t="n">
         <v>444.0969799109999</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="8" t="n">
         <v>328.5804000000001</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="9" t="n">
         <v>328.58</v>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 203 months, CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Framework §2 mid-to-late stage: full development achieved. No expected reopens or new reports.</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 203 months, CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Framework Â§2 mid-to-late stage: full development achieved. No expected reopens or new reports.</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
         <v>328.58</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Mid-to-late maturity at 203 months with CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Full development achieved; no additional emergence expected. Direct measure most reliable.</t>
         </is>
       </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="A10" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>321.9824</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="8" t="n">
         <v>321.9824</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="8" t="n">
         <v>384.4019144995</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="8" t="n">
         <v>321.9824</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="9" t="n">
         <v>321.98</v>
       </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 191 months, CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Framework §2: complete maturity means actual reported = ultimate. IBNR 0.</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 191 months, CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Framework Â§2: complete maturity means actual reported = ultimate. IBNR 0.</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n">
         <v>321.98</v>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Mid-maturity at 191 months with CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Complete development indicated by CDF = 1.0. Zero IBNR appropriate.</t>
         </is>
       </c>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="A11" s="3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>271.8376</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="8" t="n">
         <v>271.8376</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="8" t="n">
         <v>314.2013025147</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="8" t="n">
         <v>271.8376</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="9" t="n">
         <v>271.84</v>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 179 months, CDF 1.0 and 100% developed. Reported Count 271.84 is fully developed ultimate. Framework §2 mid-stage: at full development, reported actual represents ultimate. No additional development expected.</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 179 months, CDF 1.0 and 100% developed. Reported Count 271.84 is fully developed ultimate. Framework Â§2 mid-stage: at full development, reported actual represents ultimate. No additional development expected.</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="n">
         <v>271.84</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Mid-maturity at 179 months with CDF 1.0 and 100% developed. Reported Count 271.84 fully developed ultimate. Complete reporting and closure by this stage. No additional development expected.</t>
         </is>
       </c>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="A12" s="3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>345.7352</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="8" t="n">
         <v>345.7352</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="8" t="n">
         <v>319.3283418408</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="8" t="n">
         <v>345.7352</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="9" t="n">
         <v>345.74</v>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 167 months, CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. Framework §2: all claims reported by this maturity. Final count established.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 167 months, CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. Framework Â§2: all claims reported by this maturity. Final count established.</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
         <v>345.74</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Mid-maturity at 167 months with CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. All claims reported by this maturity; final count established.</t>
         </is>
       </c>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="A13" s="3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="C13" s="8" t="n">
         <v>261.2808</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="8" t="n">
         <v>261.2808</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="8" t="n">
         <v>298.965375136</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="8" t="n">
         <v>261.2808</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="9" t="n">
         <v>261.28</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 155 months, CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. Framework §2 early-mid stage: even with moderate maturity, CDF 1.0 indicates all claims reported. Ultimate equals reported actual.</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="n">
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 155 months, CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. Framework Â§2 early-mid stage: even with moderate maturity, CDF 1.0 indicates all claims reported. Ultimate equals reported actual.</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="n">
         <v>261.28</v>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Mid-maturity at 155 months with CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. CDF 1.0 indicates all claims reported. Ultimate equals actual reported count.</t>
         </is>
       </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="A14" s="3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C14" s="8" t="n">
         <v>291.6316</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="8" t="n">
         <v>291.6316</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="8" t="n">
         <v>305.7471685908</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="8" t="n">
         <v>291.6316</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="9" t="n">
         <v>291.63</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 143 months, CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. Framework §2 early stage: CDF 1.0 indicates complete reporting. No expected IBNR development.</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n">
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 143 months, CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. Framework Â§2 early stage: CDF 1.0 indicates complete reporting. No expected IBNR development.</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
         <v>291.63</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Early-mid maturity at 143 months with CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. CDF 1.0 confirms complete reporting. Zero IBNR; no expected additional emergence.</t>
         </is>
       </c>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
+      <c r="A15" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <v>455.2620000000001</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="8" t="n">
         <v>455.2620000000001</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="E15" s="8" t="n">
         <v>341.329398159</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="8" t="n">
         <v>455.2620000000001</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="9" t="n">
         <v>455.26</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 131 months, CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Framework §2 early stage: full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n">
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 131 months, CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Framework Â§2 early stage: full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n">
         <v>455.26</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Early-mid maturity at 131 months with CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
         </is>
       </c>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="A16" s="3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="C16" s="8" t="n">
         <v>333.8588</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="8" t="n">
         <v>333.8588</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E16" s="8" t="n">
         <v>367.358834304</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="F16" s="8" t="n">
         <v>333.8588</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="9" t="n">
         <v>333.86</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 119 months, CDF 1.0 and 100% developed. Reported Count 333.86 is fully developed ultimate. Framework §2 early stage: complete reporting maturity. No additional counts expected to emerge.</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 119 months, CDF 1.0 and 100% developed. Reported Count 333.86 is fully developed ultimate. Framework Â§2 early stage: complete reporting maturity. No additional counts expected to emerge.</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
         <v>333.86</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Early maturity at 119 months with CDF 1.0 and 100% developed. Reported Count 333.86 fully developed ultimate. Complete reporting maturity reached. No additional counts expected to emerge.</t>
         </is>
       </c>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="A17" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="C17" s="8" t="n">
         <v>390.6016</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="8" t="n">
         <v>390.6016</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E17" s="8" t="n">
         <v>401.5315549436</v>
       </c>
-      <c r="F17" s="3" t="n">
+      <c r="F17" s="8" t="n">
         <v>390.6016</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="9" t="n">
         <v>390.6</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 107 months, CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. Framework §2 early stage: CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="n">
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 107 months, CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. Framework Â§2 early stage: CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="n">
         <v>390.6</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Early maturity at 107 months with CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
         </is>
       </c>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
+      <c r="A18" s="3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C18" s="8" t="n">
         <v>310.1060000000001</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="8" t="n">
         <v>310.1060000000001</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E18" s="8" t="n">
         <v>351.797848029</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="8" t="n">
         <v>310.1060000000001</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="9" t="n">
         <v>310.11</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 95 months, CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Framework §2 early stage: full development achieved. IBNR 0 appropriate.</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="n">
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 95 months, CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Framework Â§2 early stage: full development achieved. IBNR 0 appropriate.</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
         <v>310.11</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Early maturity at 95 months with CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Full development achieved. Zero IBNR appropriate.</t>
         </is>
       </c>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
+      <c r="A19" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="C19" s="8" t="n">
         <v>325.9412</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="8" t="n">
         <v>325.9412</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E19" s="8" t="n">
         <v>349.5307063275</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F19" s="8" t="n">
         <v>325.9412</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="9" t="n">
         <v>325.94</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 83 months, CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Framework §2 early stage (24-36 mo equivalent): CDF 1.0 indicates complete reporting. Reported actual = ultimate with zero IBNR.</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="n">
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 83 months, CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Framework Â§2 early stage (24-36 mo equivalent): CDF 1.0 indicates complete reporting. Reported actual = ultimate with zero IBNR.</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="n">
         <v>325.94</v>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Early maturity at 83 months with CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Complete reporting confirmed by CDF 1.0. Zero IBNR.</t>
         </is>
       </c>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
+      <c r="A20" s="3" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="C20" s="8" t="n">
         <v>357.6116</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="8" t="n">
         <v>357.68312232</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E20" s="8" t="n">
         <v>337.5429992505</v>
       </c>
-      <c r="F20" s="3" t="n">
+      <c r="F20" s="8" t="n">
         <v>357.67909510083</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="9" t="n">
         <v>357.68</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 71 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 vs. actual 357.61 shows minimal development (0.07 counts, 0.02% IBNR). Framework §2 green stage: Reported CL is primary. §4 Convergence: all methods cluster within 1% (Reported CL/IE/BF all near 357.7). Selected Reported CL reflecting actual report-based development. Minimal development expected from this point.</t>
-        </is>
-      </c>
-      <c r="I20" s="5" t="n">
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 71 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 vs. actual 357.61 shows minimal development (0.07 counts, 0.02% IBNR). Framework Â§2 green stage: Reported CL is primary. Â§4 Convergence: all methods cluster within 1% (Reported CL/IE/BF all near 357.7). Selected Reported CL reflecting actual report-based development. Minimal development expected from this point.</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n">
         <v>357.68</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Green stage at 71 months with CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 shows minimal development (0.07 counts, 0.02% IBNR). All methods converge within 1%. Selected Reported CL reflecting actual report-based development. Minimal emergence expected henceforth.</t>
         </is>
       </c>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="11" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="n">
+      <c r="A21" s="3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="C21" s="8" t="n">
         <v>370.8076</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="8" t="n">
         <v>370.8817615200001</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="E21" s="8" t="n">
         <v>358.1209218321</v>
       </c>
-      <c r="F21" s="3" t="n">
+      <c r="F21" s="8" t="n">
         <v>370.879209862394</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="9" t="n">
         <v>370.88</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 59 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Framework §2 green stage (12-24 mo): Reported CL primary with minimal reported to closed settlement gap. §4 Convergence: methods within 1%. Selected Reported CL as direct indication of claim emergence. Framework §7 Reasonability: very low IBNR consistent with mature reporting patterns.</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="n">
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 59 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Framework Â§2 green stage (12-24 mo): Reported CL primary with minimal reported to closed settlement gap. Â§4 Convergence: methods within 1%. Selected Reported CL as direct indication of claim emergence. Framework Â§7 Reasonability: very low IBNR consistent with mature reporting patterns.</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="n">
         <v>370.88</v>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Green stage at 59 months with CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Methods converge within 1%. Selected Reported CL as direct indication of claim emergence. Very high development completion confirmed.</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
+      <c r="A22" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C22" s="8" t="n">
         <v>329.9</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="8" t="n">
         <v>329.96598</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="E22" s="8" t="n">
         <v>360.1120188906</v>
       </c>
-      <c r="F22" s="3" t="n">
+      <c r="F22" s="8" t="n">
         <v>329.9720080021777</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="9" t="n">
         <v>329.97</v>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 47 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). Framework §2 green stage: Reported CL primary. §4 Convergence: all methods (reported CL, IE, BF) within 1% cluster. Selected Reported CL. Minimal remaining development expected; nearly all claims already reported.</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="n">
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 47 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). Framework Â§2 green stage: Reported CL primary. Â§4 Convergence: all methods (reported CL, IE, BF) within 1% cluster. Selected Reported CL. Minimal remaining development expected; nearly all claims already reported.</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="n">
         <v>329.97</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Green stage at 47 months with CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). All methods cluster tightly within 1%. Nearly all claims already reported; minimal development expected.</t>
         </is>
       </c>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
+      <c r="A23" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C23" s="8" t="n">
         <v>298.2296</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="8" t="n">
         <v>298.43839054296</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E23" s="8" t="n">
         <v>339.9814749044</v>
       </c>
-      <c r="F23" s="3" t="n">
+      <c r="F23" s="8" t="n">
         <v>298.467454508639</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="9" t="n">
         <v>298.44</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 35 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Framework §2 very green (0-12 mo): BF methods theoretically primary, but CDF very close to 1.0. §4 Convergence: Reported CL 298.44 vs. IE 339.98 (13.9% variance) shows some divergence; BF 298.47 clusters with CL (0.01% variance). Selected Reported CL per §2 green stage with CL/BF tight convergence. Minimal IBNR 0.21 reflects high development completion.</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="n">
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 35 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green (0-12 mo): BF methods theoretically primary, but CDF very close to 1.0. Â§4 Convergence: Reported CL 298.44 vs. IE 339.98 (13.9% variance) shows some divergence; BF 298.47 clusters with CL (0.01% variance). Selected Reported CL per Â§2 green stage with CL/BF tight convergence. Minimal IBNR 0.21 reflects high development completion.</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="n">
         <v>298.44</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Very green at 35 months with CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Reported CL and BF cluster tightly (0.01% variance). Selected Reported CL per green-stage preference with strong CL/BF convergence. Minimal IBNR reflects high development completion.</t>
         </is>
       </c>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
+      <c r="A24" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="8" t="n">
         <v>304.8276</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="8" t="n">
         <v>305.04100980276</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="E24" s="8" t="n">
         <v>317.4343255127</v>
       </c>
-      <c r="F24" s="3" t="n">
+      <c r="F24" s="8" t="n">
         <v>305.0496802928784</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="9" t="n">
         <v>305.04</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 23 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Framework §2 very green: BF methods theoretically primary with sparse data. However, CDF 1.0007 is very close to 1.0, indicating nearly complete reporting already. Reported CL 305.04 and BF 305.05 converge within 0.01% (framework §4). Selected Reported CL as most direct measure of reported counts. IBNR 0.21 is minimal (0.07% of ultimate).</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="n">
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 23 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green: BF methods theoretically primary with sparse data. However, CDF 1.0007 is very close to 1.0, indicating nearly complete reporting already. Reported CL 305.04 and BF 305.05 converge within 0.01% (framework Â§4). Selected Reported CL as most direct measure of reported counts. IBNR 0.21 is minimal (0.07% of ultimate).</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
         <v>305.04</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Very green at 23 months with CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Reported CL and BF converge within 0.01%. Selected Reported CL as most direct measure of reported counts. Minimal IBNR (0.07% of ultimate) reflects nearly complete reporting already achieved.</t>
         </is>
       </c>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
+      <c r="A25" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" s="8" t="n">
         <v>256.0024</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="8" t="n">
         <v>290.2537837085119</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="E25" s="8" t="n">
         <v>292.3526117534</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="8" t="n">
         <v>290.5014558104399</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="9" t="n">
         <v>290.25</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Reported CL selected. At 11 months, CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Framework §2 very green (0-12 mo): BF methods typically primary at extreme immaturity. However, CDF 1.134 is more moderate than loss CDFs (2.84), suggesting count development is following expected trajectory. Reported CL 290.25 vs. Closed CL 290.25 and IE 292.35 are very tightly clustered (within 1%). Framework §4 Convergence applies: all methods within 1%. Selected Reported CL reflecting observable reported counts with reasonable IBNR development expectation of 11.8% remaining. Early emergence suggests expected pattern consistent with portfolio development.</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="n">
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Reported CL selected. At 11 months, CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Framework Â§2 very green (0-12 mo): BF methods typically primary at extreme immaturity. However, CDF 1.134 is more moderate than loss CDFs (2.84), suggesting count development is following expected trajectory. Reported CL 290.25 vs. Closed CL 290.25 and IE 292.35 are very tightly clustered (within 1%). Framework Â§4 Convergence applies: all methods within 1%. Selected Reported CL reflecting observable reported counts with reasonable IBNR development expectation of 11.8% remaining. Early emergence suggests expected pattern consistent with portfolio development.</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="n">
         <v>290.25</v>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J25" s="10" t="inlineStr">
         <is>
           <t>Reported CL selected. Extreme immaturity at 11 months with CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Reported CL, Closed CL, and IE methods converge tightly within 1%. Selected Reported CL reflecting observable reported counts. Reasonable IBNR development expectation of 11.8% remaining, consistent with early-stage emergence pattern.</t>
         </is>
       </c>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
     </row>
     <row r="26"/>
   </sheetData>

--- a/sample-data/sample-run/selections/Ultimates.xlsx
+++ b/sample-data/sample-run/selections/Ultimates.xlsx
@@ -581,7 +581,7 @@
         <v>3042294.662276</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>3196360.568794786</v>
+        <v>3201422.606714287</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>3054159.611458877</v>
@@ -590,25 +590,25 @@
         <v>3163773.699688</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>3196028.345938407</v>
+        <v>3200979.853484114</v>
       </c>
       <c r="I2" s="8" t="n">
         <v>3054585.445649627</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>3196360.57</v>
+        <v>3054159.61</v>
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 287 months maturity (tail-exposed), CDF 1.0103 and 98.98% developed indicate full maturity. Incurred CL ultimate of 3.196M reflects final case reserves and estimated IBNR. Paid CL 3.054M is only marginally different (1.4% variance), both reasonable. Incurred preferred at this maturity per framework Â§2. Very high development and low remaining uncertainty support this selection. Loss ratio (3.20M / premium) consistent with historical portfolio.</t>
+          <t>Paid Loss, Paid CL method. Age 287 months (tail maturity). High development completion (99.61%). CL most appropriate at tail; Paid CL preferred to Incurred due to closure completion and minimal remaining reserves. Minimal IBNR (11,865) indicates stability. Slightly favored over Incurred CL (3,201,423) per paid/case adequacy stability.</t>
         </is>
       </c>
       <c r="L2" s="10" t="n">
-        <v>3196360.57</v>
+        <v>3054159.61</v>
       </c>
       <c r="M2" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Tail-mature at 287 months (98.98% developed, CDF 1.0103). Incurred CL 3.196M reflects final case reserves and fully estimated IBNR. Paid CL 3.054M is only 1.4% lower but Incurred CL is preferred at extreme maturity per standard practice. Both measures highly credible; Incurred preferred as more direct reflection of case-based reserve adequacy.</t>
+          <t>Paid CL. Fully mature (age 287), minimal IBNR (11.9k). Paid CDF 1.0039 is highly stable. Both incurred and paid fully developed; paid selected for lower development factor and actuarial conservatism.</t>
         </is>
       </c>
       <c r="N2" s="11" t="n"/>
@@ -628,7 +628,7 @@
         <v>2199646.228088</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>2379694.756036815</v>
+        <v>2383463.450097648</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>2216836.925286216</v>
@@ -637,25 +637,25 @@
         <v>2904344.256599999</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>2391150.55829088</v>
+        <v>2395642.587075747</v>
       </c>
       <c r="I3" s="8" t="n">
         <v>2222168.273848376</v>
       </c>
       <c r="J3" s="9" t="n">
-        <v>2379694.76</v>
+        <v>2216836.93</v>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 275 months, 97.8% developed with CDF 1.0223. Incurred CL 2.38M vs. Paid CL 2.22M (6.7% variance) reflects ongoing case development. Incurred BF 2.39M aligns closely (0.3% variance). Framework Â§4 Convergence: Incurred CL and Paid BF cluster within 2%, midpoint selected. Incurred CL represents expected development trajectory at late maturity.</t>
+          <t>Paid Loss, Paid CL method. Age 275 months (tail maturity). 99.22% developed. CL primary at tail. Paid CL selected over Incurred CL (2,383,463) and Incurred BF (2,395,643) due to paid data reliability and closure maturity. IBNR of 17,191 reasonable.</t>
         </is>
       </c>
       <c r="L3" s="10" t="n">
-        <v>2379694.76</v>
+        <v>2216836.93</v>
       </c>
       <c r="M3" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 275 months (97.8% developed, CDF 1.0223). Incurred CL 2.379M vs. Paid CL 2.217M (6.7% variance). Incurred BF 2.391M converges very closely (0.3% variance). Strong CL/BF convergence combined with late maturity supports Incurred CL selection. Reflects case reserve development credibility.</t>
+          <t>Paid CL. Near-mature (age 275, 99.2% developed). CDF 1.0078 very low. Paid measure shows minimal further development (17k IBNR) versus incurred (55k). Paid CL most credible.</t>
         </is>
       </c>
       <c r="N3" s="11" t="n"/>
@@ -675,34 +675,34 @@
         <v>1778091.575843999</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>1839414.768991383</v>
+        <v>1820661.950897142</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>1805606.841693755</v>
+        <v>1805248.444146774</v>
       </c>
       <c r="G4" s="8" t="n">
         <v>2633272.1256</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1865880.72372408</v>
+        <v>1839662.249053565</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>1818219.46023032</v>
+        <v>1817704.641044055</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>1839414.77</v>
+        <v>1805248.44</v>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 263 months, 96.7% developed. Incurred CL 1.84M vs. Paid CL 1.81M (1.6% variance). Incurred BF 1.87M also close. Framework Â§4 Convergence applies: methods cluster within Â±2%. Selected Incurred CL as primary method at this late maturity, reflecting case adequacy and reserve estimation practices.</t>
+          <t>Paid Loss, Paid CL method. Age 263 months (tail maturity). 98.50% developed. Paid CL primary. Selected over Incurred CL (1,820,662; IE method shows 855k IBNR is inflated) per paid stability. IBNR of 27,157 consistent with tail development.</t>
         </is>
       </c>
       <c r="L4" s="10" t="n">
-        <v>1839414.77</v>
+        <v>1805248.44</v>
       </c>
       <c r="M4" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 263 months (96.7% developed, CDF 1.0345). Incurred CL 1.839M, Paid CL 1.806M (1.6% variance), Incurred BF 1.866M. Methods cluster tightly within 2%. Incurred CL selected as baseline at this maturity; represents expected development trajectory with 61K IBNR (3.3% of ultimate).</t>
+          <t>Paid CL. Mature (age 263, 98.5% developed). Paid CDF 1.0153 vs Incurred CDF 1.0239 shows paid development is more stable. Paid CL 1.8M with 27k IBNR is appropriate selection.</t>
         </is>
       </c>
       <c r="N4" s="11" t="n"/>
@@ -722,34 +722,34 @@
         <v>1122614.7306</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>1161331.701587282</v>
+        <v>1169493.09432337</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1148422.652748158</v>
+        <v>1146826.988085745</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>1678710.98</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1178580.312371218</v>
+        <v>1189904.759321704</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>1160339.554450718</v>
+        <v>1158056.329824789</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1161331.7</v>
+        <v>1146826.99</v>
       </c>
       <c r="K5" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 251 months, 96.7% developed. Incurred CL 1.16M, Paid CL 1.15M (1.1% variance), Incurred BF 1.18M. Tight convergence (Â§4) suggests high credibility across methods. Incurred CL selected per maturity-based hierarchy (Â§2: late stage). IBNR 39K represents 3.3% of ultimate, reasonable for this maturity.</t>
+          <t>Paid Loss, Paid CL method. Age 251 months (tail maturity). 97.89% developed. Paid CL most credible. Incurred CL yields 1,169,493; Paid CL lower at 1,146,827 due to better closure certainty. Paid IBNR (24,212) vs Incurred (46,878) indicates Paid more mature.</t>
         </is>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1161331.7</v>
+        <v>1146827</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 251 months (96.7% developed, CDF 1.0345). Incurred CL 1.161M, Paid CL 1.148M (1.1% variance), Incurred BF 1.179M. Very tight convergence (within 2%) across all methods. Incurred CL selected per maturity-based hierarchy. IBNR 39K represents 3.3% of ultimate, reasonable for this development stage.</t>
+          <t>Paid CL. Mature (age 251, 97.9% developed). Paid CDF 1.0216 vs Incurred 1.0418. Paid CL 1.15M with 24k IBNR reflects stable development pattern. Paid measure preferred.</t>
         </is>
       </c>
       <c r="N5" s="11" t="n"/>
@@ -769,34 +769,34 @@
         <v>2242149.132116</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2351717.567121524</v>
+        <v>2340682.362767447</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2302180.830765267</v>
+        <v>2301730.696700493</v>
       </c>
       <c r="G6" s="8" t="n">
         <v>1712285.2</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2321925.892841888</v>
+        <v>2314229.391802829</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>2286798.70427573</v>
+        <v>2286472.575938997</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>2351717.57</v>
+        <v>2286472.58</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 239 months, 95.3% developed. Incurred CL 2.35M, Paid CL 2.30M (2.2% variance), Incurred BF 2.32M. Framework Â§4 Convergence: methods within 2% range. Note: Incurred IE (alternative method) shows 1.71M with negative IBNR (-0.53M), reflecting data anomaly or shift; rejected due to unreasonableness. Incurred CL represents credible development trajectory.</t>
+          <t>Paid Loss, Paid CL method. Age 239 months (late maturity). 97.41% developed. Incurred IE method fails fitness (negative IBNR -529,864 signals stale a priori loss ratio). Paid CL (2,286,473) selected over Incurred CL (2,340,682) and both BF methods due to IE unreliability and Paid closure maturity.</t>
         </is>
       </c>
       <c r="L6" s="10" t="n">
-        <v>2351717.57</v>
+        <v>2301730.7</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 239 months (95.3% developed, CDF 1.0489). Incurred CL 2.352M, Paid CL 2.302M (2.2% variance), Incurred BF 2.322M. Methods cluster within 2% range. Incurred IE shows 1.712M with negative IBNR (-0.530M), data quality issue; rejected. Incurred CL represents credible development trajectory.</t>
+          <t>Paid CL. Mature (age 239, 97.4% developed). Incurred shows negative IBNR (-530k) on IE, concerning data quality signal. Paid CL 2.30M with CDF 1.0266 and 60k IBNR is credible and stable.</t>
         </is>
       </c>
       <c r="N6" s="11" t="n"/>
@@ -816,34 +816,34 @@
         <v>1462141.027856</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1591800.052318661</v>
+        <v>1591301.741496185</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>1501288.651138375</v>
+        <v>1502796.305705819</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>1746530.9035</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>1599009.088577111</v>
+        <v>1598487.649723837</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>1507683.591445887</v>
+        <v>1509390.078765623</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1591800.05</v>
+        <v>1509390.08</v>
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 227 months, 95.3% developed. Incurred CL 1.59M vs. Paid CL 1.50M (5.4% variance). Incurred BF 1.60M (0.6% offset). Framework Â§2 (late maturity) and Â§4 (Incurred CL/BF convergence) support Incurred CL. Paid CL shows lower IBNR (39K) but Incurred reflects case adequacy changes better at this stage.</t>
+          <t>Paid Loss, Paid CL method. Age 227 months (late maturity). 97.29% developed. Paid CL (1,509,390) selected over Incurred CL (1,591,302) per paid data quality. Incurred BF (1,598,488) and Paid BF (1,598,488) higher; CL preferred at late maturity. IBNR 40,655 reasonable.</t>
         </is>
       </c>
       <c r="L7" s="10" t="n">
-        <v>1591800.05</v>
+        <v>1502796.31</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 227 months (95.3% developed, CDF 1.0489). Incurred CL 1.592M vs. Paid CL 1.501M (5.4% variance), Incurred BF 1.599M (0.6% variance). Incurred CL and BF convergence strong. Incurred CL preferred at late maturity reflecting case adequacy. Paid CL shows lower credibility with greater variance.</t>
+          <t>Paid CL. Mature (age 227, 97.3% developed). Paid CDF 1.0278 very stable. Incurred shows positive variance (IE 1.75M vs CL 1.59M). Paid CL provides conservative, credible selection at 1.50M.</t>
         </is>
       </c>
       <c r="N7" s="11" t="n"/>
@@ -863,34 +863,34 @@
         <v>4790693.153152</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>5045865.598800745</v>
+        <v>5044285.997497818</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>4927814.149603676</v>
+        <v>4939656.318945549</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>2850338.4352</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4943574.201784778</v>
+        <v>4942723.213576031</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>4870006.462175752</v>
+        <v>4876649.626532938</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>5045865.6</v>
+        <v>4939656.32</v>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 215 months, 95.3% developed. Incurred CL 5.05B is primary method selection at late maturity. Paid CL 4.93B (2.4% lower) and Incurred BF 4.94B (2.1% lower). Framework Â§4 Convergence check: Incurred CL and paid estimates within 2.5%, but Incurred CL selected per framework Â§2 (late maturity baseline). IBNR of 235M (4.7% of ultimate) consistent with development trajectory.</t>
+          <t>Paid Loss, Paid CL method. Age 215 months (late maturity). 96.98% developed. Incurred IE fails fitness (negative IBNR -1,960,436; a priori LR stale). Incurred CL (5,044,286) vs Paid CL (4,939,656) show divergence. Paid CL selected due to closure priority. IBNR 148,963.</t>
         </is>
       </c>
       <c r="L8" s="10" t="n">
-        <v>5045865.6</v>
+        <v>4939656.32</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 215 months (95.3% developed, CDF 1.0489). Incurred CL 5.046M is primary method selection. Paid CL 4.928M (2.4% lower), Incurred BF 4.944M (2.1% lower). Methods within 2.5% convergence range. Incurred CL selected per late-maturity framework. IBNR 235M (4.7% of ultimate) consistent with development trajectory.</t>
+          <t>Paid CL. Mature (age 215, 97.0% developed). Incurred CL 5.04M vs Paid CL 4.94M; incurred IE anomaly (-1.96M negative IBNR) signals data quality concern. Paid CL 4.94M with 149k IBNR selected.</t>
         </is>
       </c>
       <c r="N8" s="11" t="n"/>
@@ -910,34 +910,34 @@
         <v>1378427.939547998</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>1448969.131870866</v>
+        <v>1448660.067651608</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>1419583.273515399</v>
+        <v>1424842.39008561</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>2543927.0535</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1502275.745266665</v>
+        <v>1501759.433731642</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>1452179.278711238</v>
+        <v>1461296.737681435</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1448969.13</v>
+        <v>1424842.39</v>
       </c>
       <c r="K9" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 203 months, 95.1% developed. Incurred CL 1.45M, Paid CL 1.42M (1.9% variance), Incurred BF 1.50M. Framework Â§2 (mid-stage, 36-60 months equivalent maturity): Incurred CL and Paid CL are both primary. Incurred CL selected per standard hierarchy, supported by tight method convergence. IBNR 71K is 4.9% of ultimate.</t>
+          <t>Paid Loss, Paid CL method. Age 203 months (late maturity). 96.74% developed. Incurred CL (1,448,660) and Paid CL (1,424,842) converge within 1.6%. Paid CL selected per closure priority. IBNR 46,414 consistent. Incurred IE unreliable (1,165,499 IBNR).</t>
         </is>
       </c>
       <c r="L9" s="10" t="n">
-        <v>1448969.13</v>
+        <v>1424842.39</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Late maturity at 203 months (95.1% developed, CDF 1.0512). Incurred CL 1.449M, Paid CL 1.420M (1.9% variance), Incurred BF 1.502M. Incurred CL and Paid CL converge closely. Incurred CL selected per standard hierarchy at mid-to-late stage. IBNR 71K is 4.9% of ultimate, appropriate for development level.</t>
+          <t>Paid CL. Mature (age 203, 96.7% developed). Paid CDF 1.0337 vs Incurred 1.0510; paid development more credible. Paid CL 1.42M with 46k IBNR is stable and appropriate.</t>
         </is>
       </c>
       <c r="N9" s="11" t="n"/>
@@ -957,34 +957,34 @@
         <v>1169581.089256</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>1243450.075977988</v>
+        <v>1237899.408021547</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1223411.606541121</v>
+        <v>1222503.633211836</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>2594805.5945</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1323729.344750299</v>
+        <v>1312785.581148437</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>1283753.39779014</v>
+        <v>1281910.991107489</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1243450.08</v>
+        <v>1222503.63</v>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 191 months, 94.1% developed. Incurred CL 1.24M, Paid CL 1.22M (1.7% variance), Incurred BF 1.32M (6.4% higher). Framework Â§2 &amp; Â§4: Incurred CL and Paid CL convergence within 2% supports Incurred CL selection. Paid BF shows modest premium reflecting timing expectations. Incurred CL is most direct and credible at this maturity.</t>
+          <t>Paid Loss, Paid CL method. Age 191 months (late maturity). 95.67% developed. Paid CL (1,222,504) and Incurred CL (1,237,899) close (1.2% spread). Paid CL selected per tail convergence and closure priority. IBNR 52,923. Incurred IE shows excessive IBNR (1,425,225).</t>
         </is>
       </c>
       <c r="L10" s="10" t="n">
-        <v>1243450.08</v>
+        <v>1222503.63</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Mid-maturity at 191 months (94.1% developed, CDF 1.0632). Incurred CL 1.243M, Paid CL 1.223M (1.7% variance), Incurred BF 1.324M (6.4% higher). Incurred CL and Paid CL convergence within 2% supports selection. Incurred CL most direct estimate at this maturity. IBNR 74K represents 5.9% of ultimate.</t>
+          <t>Paid CL. Mature (age 191, 95.7% developed). Paid CDF 1.0452 vs Incurred 1.0584. Paid CL 1.22M with 53k IBNR shows more measured development. Incurred IE flag (1.43M negative IBNR) confirms paid credibility.</t>
         </is>
       </c>
       <c r="N10" s="11" t="n"/>
@@ -1004,34 +1004,34 @@
         <v>1277672.072084001</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>1366518.130636961</v>
+        <v>1355414.57030631</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>1344897.335890034</v>
+        <v>1358856.639273344</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>1134300.7311</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1351420.196541743</v>
+        <v>1342732.146324738</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1334370.575269829</v>
+        <v>1345440.599870827</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1366518.13</v>
+        <v>1345440.6</v>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 179 months, 93.5% developed. Incurred CL 1.37M, Paid CL 1.34M (1.6% variance), Incurred BF 1.35M. Framework Â§4 Convergence: all three methods cluster tightly. Incurred CL selected as primary method per Â§2 maturity hierarchy (mid-stage). IBNR 89K represents reasonable 6.5% of ultimate at this development level.</t>
+          <t>Paid Loss, Paid CL method. Age 179 months (late maturity). 94.03% developed. Incurred IE fails fitness (negative IBNR -143,371). Incurred CL (1,355,415) vs Paid CL (1,345,441) within 0.7%. Paid CL selected. IBNR 67,769 reasonable for maturity.</t>
         </is>
       </c>
       <c r="L11" s="10" t="n">
-        <v>1366518.13</v>
+        <v>1358856.64</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Mid-maturity at 179 months (93.5% developed, CDF 1.0695). Incurred CL 1.367M, Paid CL 1.345M (1.6% variance), Incurred BF 1.351M. Tight convergence across all three methods. Incurred CL selected as primary method per mid-stage hierarchy. IBNR 89K represents 6.5% of ultimate, reasonable for development level.</t>
+          <t>Paid CL. Mature (age 179, 94.0% developed). Paid CDF 1.0635 vs Incurred 1.0608. Very close indications; paid CL 1.36M with 81k IBNR selected for consistency with paid development trajectory.</t>
         </is>
       </c>
       <c r="N11" s="11" t="n"/>
@@ -1051,34 +1051,34 @@
         <v>1892658.297732</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>2064690.91616036</v>
+        <v>2056045.072633144</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2001206.411407335</v>
+        <v>2029626.94117379</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>1542648.9944</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>2027116.137961699</v>
+        <v>2021096.078101584</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>1976333.643488819</v>
+        <v>1996763.40975205</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2064690.92</v>
+        <v>1996763.41</v>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 167 months, 92.8% developed. Incurred CL 2.06M, Paid CL 2.00M (2.9% variance). Incurred BF 2.03M (1.5% variance). Framework Â§4 &amp; Â§2: late-mid maturity with method convergence within 3%. Incurred CL selected as primary at this stage, reflecting developed case reserves and estimated IBNR. IBNR 149K is 7.2% of ultimate.</t>
+          <t>Paid Loss, Paid CL method. Age 167 months (mid maturity). 93.25% developed. Incurred IE fails fitness (negative IBNR -373,433). Incurred CL (2,056,045) vs Paid CL (2,029,627) differ by 1.3%. Paid CL selected. IBNR 136,969 consistent with mid maturity.</t>
         </is>
       </c>
       <c r="L12" s="10" t="n">
-        <v>2064690.92</v>
+        <v>2029626.94</v>
       </c>
       <c r="M12" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Mid-maturity at 167 months (92.8% developed, CDF 1.0776). Incurred CL 2.065M, Paid CL 2.001M (2.9% variance), Incurred BF 2.027M (1.5% variance). Methods converge within 3%. Incurred CL selected at late-mid maturity stage, reflecting developed case reserves. IBNR 149K is 7.2% of ultimate.</t>
+          <t>Paid CL. Mature (age 167, 93.3% developed). Paid CDF 1.0724 vs Incurred 1.0730, essentially identical development. Paid CL 2.03M with 137k IBNR preferred for measure consistency across portfolio.</t>
         </is>
       </c>
       <c r="N12" s="11" t="n"/>
@@ -1098,34 +1098,34 @@
         <v>1194236.878339999</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>1475255.850013807</v>
+        <v>1463663.778556022</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1264875.627675566</v>
+        <v>1290266.848705146</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>1573501.9744</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1482681.467398056</v>
+        <v>1471161.386972511</v>
       </c>
       <c r="I13" s="8" t="n">
-        <v>1282111.297861324</v>
+        <v>1311347.031269041</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1475255.85</v>
+        <v>1290266.85</v>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 155 months, 92.4% developed. Incurred CL 1.48M, Paid CL 1.26M (14.8% variance). Incurred BF 1.48M (0.04% variance). Framework Â§4 Convergence: Incurred CL and BF cluster within 1%. Paid CL shows lower credibility (larger deviation). Incurred CL selected per Â§2 (early-mid stage baseline). IBNR 112K is reasonable 7.6% of ultimate.</t>
+          <t>Paid Loss, Paid CL method. Age 155 months (mid maturity). 92.56% developed. Incurred CL (1,463,664) vs Paid CL (1,290,267) show significant divergence (11.8%, suggests recent closure shift). Paid CL selected due to more recent closure certainty. IBNR 96,030.</t>
         </is>
       </c>
       <c r="L13" s="10" t="n">
-        <v>1475255.85</v>
+        <v>1290266.85</v>
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Mid-maturity at 155 months (92.4% developed, CDF 1.0818). Incurred CL 1.475M, Paid CL 1.265M (14.8% variance), Incurred BF 1.483M (0.04% variance). Incurred CL and BF cluster tightly within 1%. Paid CL shows lower credibility. Incurred CL selected per mid-stage baseline. IBNR 112K is 7.6% of ultimate.</t>
+          <t>Paid CL. Mature (age 155, 92.6% developed). Paid CDF 1.0804 vs Incurred 1.0733. Paid measure development slightly higher but credible. Paid CL 1.29M with 96k IBNR selected.</t>
         </is>
       </c>
       <c r="N13" s="11" t="n"/>
@@ -1145,34 +1145,34 @@
         <v>708529.9908599999</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>769526.2801642057</v>
+        <v>761426.4155488787</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>762971.6617653245</v>
+        <v>777445.5657771104</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>1203729.0102</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>803943.2403390912</v>
+        <v>792153.2532444077</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>794421.8029895274</v>
+        <v>815232.8655486186</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>769526.28</v>
+        <v>777445.5699999999</v>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 143 months, 92.1% developed. Incurred CL 769.5K, Paid CL 763.0K (0.9% variance), Incurred BF 803.9K (4.5% variance). Framework Â§2 (early maturity, 24-36 mo equivalent): Incurred CL is primary. Â§4 Convergence: Incurred CL and Paid CL within 1%. Selected Incurred CL. IBNR 61K is 7.9% of ultimate, consistent with remaining development.</t>
+          <t>Paid Loss, Paid CL method. Age 143 months (mid maturity). 91.14% developed. Incurred CL (761,426) vs Paid CL (777,446) within 2.1%, near convergence. Paid CL selected. IBNR 68,916. Paid shows higher maturity indication.</t>
         </is>
       </c>
       <c r="L14" s="10" t="n">
-        <v>769526.28</v>
+        <v>777445.5699999999</v>
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Mid-maturity at 143 months (92.1% developed, CDF 1.0861). Incurred CL 769.5K, Paid CL 763.0K (0.9% variance), Incurred BF 803.9K (4.5% variance). Incurred CL and Paid CL converge tightly within 1%. Selected Incurred CL as primary at early-mid stage. IBNR 61K is 7.9% of ultimate.</t>
+          <t>Paid CL. Mature (age 143, 91.1% developed). Paid CDF 1.0973 vs Incurred 1.0747. Paid shows higher development, but method consistency preferred. Paid CL 777k with 69k IBNR is stable selection.</t>
         </is>
       </c>
       <c r="N14" s="11" t="n"/>
@@ -1192,34 +1192,34 @@
         <v>1389603.684732</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1545756.020435727</v>
+        <v>1545613.876858252</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>1522264.681624703</v>
+        <v>1555869.473487186</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>1227803.5905</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1513636.453103785</v>
+        <v>1513534.943965106</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>1496603.242870816</v>
+        <v>1520811.1773203</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1545756.02</v>
+        <v>1520811.18</v>
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 131 months, 89.9% developed. Incurred CL 1.55M, Paid CL 1.52M (1.8% variance), Incurred BF 1.51M (2.2% variance). Framework Â§2 (early maturity): Incurred CL is primary. Â§4 Convergence: all three methods within 2.5%. Selected Incurred CL as most direct estimate. IBNR 156K is 10.1% of ultimate, reflecting increasing development needs.</t>
+          <t>Paid Loss, Paid CL method. Age 131 months (mid maturity). 89.31% developed. Incurred IE fails fitness (negative IBNR -161,800). Incurred CL (1,545,614) vs Paid CL (1,555,869) within 0.7%. Paid CL selected. IBNR 166,266.</t>
         </is>
       </c>
       <c r="L15" s="10" t="n">
-        <v>1545756.02</v>
+        <v>1555869.47</v>
       </c>
       <c r="M15" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Early-mid maturity at 131 months (89.9% developed, CDF 1.1124). Incurred CL 1.546M, Paid CL 1.522M (1.8% variance), Incurred BF 1.514M (2.2% variance). All methods converge within 2.5%. Incurred CL selected per early-maturity hierarchy. IBNR 156K represents 10.1% of ultimate, reflecting ongoing development needs.</t>
+          <t>Paid CL. Mid-mature (age 131, 89.3% developed). Paid CDF 1.1196 vs Incurred 1.1123; paid slightly higher but credible. Paid CL 1.56M selected for consistency and 166k IBNR appropriate.</t>
         </is>
       </c>
       <c r="N15" s="11" t="n"/>
@@ -1239,34 +1239,34 @@
         <v>3364231.298548001</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>3806012.584434826</v>
+        <v>3777818.117561095</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>3701619.422324063</v>
+        <v>3807441.883544173</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>1669812.8832</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>3568567.798184989</v>
+        <v>3557490.911563986</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>3516428.207912127</v>
+        <v>3558608.19711495</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>3806012.58</v>
+        <v>3558608.2</v>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 119 months, 88.9% developed. Incurred CL 3.81B, Paid CL 3.70B (2.8% variance), Incurred BF 3.57B (6.2% lower). Framework Â§2 (early stage, 24-36 mo): Incurred CL is primary method. Note: Incurred IE (alternative method) shows 1.67B with negative IBNR (-1.71B), indicating data anomaly or reserve adjustment; rejected. Â§4 Convergence: CL methods within 3%. Selected Incurred CL. IBNR 423K is 11.1% of ultimate.</t>
+          <t>Paid Loss, Paid CL method. Age 119 months (mid maturity). 88.36% developed. Incurred IE fails fitness (negative IBNR -1,713,151; a priori loss ratio severely stale). Incurred CL (3,777,818) vs Paid CL (3,807,442) within 0.8%. Paid CL selected. IBNR 443,211.</t>
         </is>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3806012.58</v>
+        <v>3807441.88</v>
       </c>
       <c r="M16" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Early maturity at 119 months (88.9% developed, CDF 1.1251). Incurred CL 3.806M, Paid CL 3.702M (2.8% variance), Incurred BF 3.569M (6.2% lower). Incurred CL and Paid CL converge within 3%. Incurred IE shows 1.669M with negative IBNR (-1.713M), data anomaly; rejected. Incurred CL preferred. IBNR 423K is 11.1% of ultimate.</t>
+          <t>Paid CL. Mid-mature (age 119, 88.4% developed). Paid CDF 1.1317 vs Incurred 1.1167. Paid CL 3.81M with 443k IBNR; incurred IE shows severe anomaly (-1.69M IBNR). Paid CL strongly preferred.</t>
         </is>
       </c>
       <c r="N16" s="11" t="n"/>
@@ -1286,34 +1286,34 @@
         <v>2462208.676391999</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>2884036.877638761</v>
+        <v>2934602.950772311</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2775780.543107491</v>
+        <v>3013413.008539162</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>2554813.7112</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>2840919.555541876</v>
+        <v>2879176.075241898</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>2750818.561824248</v>
+        <v>2929527.421433551</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>2884036.88</v>
+        <v>2929527.42</v>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 107 months, 86.9% developed. Incurred CL 2.88M, Paid CL 2.78M (3.6% variance), Incurred BF 2.84M (1.4% variance). Framework Â§2 (early stage): Incurred CL and BF baseline. Â§4 Convergence: Incurred CL and BF within 2%. Selected Incurred CL per standard hierarchy. IBNR 378K is 13.1% of ultimate, appropriate for 107-month maturity.</t>
+          <t>Paid Loss, Paid CL method. Age 107 months (mid maturity). 81.71% developed. Incurred CL (2,934,603) vs Paid CL (3,013,413) differ by 2.6%. Paid CL selected (lower variability in reserves). IBNR 551,204. Paid BF (2,879,176) and Incurred CL offer alternatives but CL priority at mid maturity.</t>
         </is>
       </c>
       <c r="L17" s="10" t="n">
-        <v>2884036.88</v>
+        <v>3013413.01</v>
       </c>
       <c r="M17" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Early maturity at 107 months (86.9% developed, CDF 1.1507). Incurred CL 2.884M, Paid CL 2.776M (3.6% variance), Incurred BF 2.841M (1.4% variance). Incurred CL and BF convergence strong. Incurred CL selected per early-stage hierarchy. IBNR 378K is 13.1% of ultimate, appropriate for 107-month maturity.</t>
+          <t>Paid CL. Mid-mature (age 107, 81.7% developed). Paid CDF 1.2239 vs Incurred 1.1709; paid development more substantial. Paid CL 3.01M with 551k IBNR captures tail risk appropriately. CL method selected for development visibility.</t>
         </is>
       </c>
       <c r="N17" s="11" t="n"/>
@@ -1333,34 +1333,34 @@
         <v>1205811.828916</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>1408623.103930131</v>
+        <v>1432473.500938687</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1379767.312627784</v>
+        <v>1494051.190141253</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>2605909.9854</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1581006.531627083</v>
+        <v>1618147.494493287</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>1534354.422925048</v>
+        <v>1708556.202441241</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1408623.1</v>
+        <v>1708556.2</v>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 95 months, 85.6% developed. Incurred CL 1.41M, Paid CL 1.38M (2.2% variance), Incurred BF 1.58M (12.2% higher). Framework Â§2 (early stage): Incurred CL primary. Paid CL and BF show higher IBNR (375K and 202K respectively). Â§4 Convergence: CL methods within 2.5%, selected Incurred CL. IBNR 203K is 14.4% of ultimate.</t>
+          <t>Paid Loss, Paid CL method. Age 95 months (early maturity). 80.71% developed. Incurred CL (1,432,474) vs Paid CL (1,494,051) diverge by 4.1% (loss development acceleration). Paid CL primary at early maturity with Incurred option secondary. Selected Paid CL. IBNR 288,239.</t>
         </is>
       </c>
       <c r="L18" s="10" t="n">
-        <v>1408623.1</v>
+        <v>1494051.19</v>
       </c>
       <c r="M18" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Early maturity at 95 months (85.6% developed, CDF 1.1682). Incurred CL 1.409M, Paid CL 1.380M (2.2% variance), Incurred BF 1.581M (12.2% higher). Incurred CL and Paid CL converge within 2.5%. Incurred CL selected as primary at early stage. IBNR 203K is 14.4% of ultimate.</t>
+          <t>Paid CL. Mid-mature (age 95, 80.7% developed). Paid CDF 1.2390 vs Incurred 1.1880. Paid development more credible. Paid CL 1.49M with 288k IBNR; BF shows large tail (503k). CL preferred given data visibility.</t>
         </is>
       </c>
       <c r="N18" s="11" t="n"/>
@@ -1380,34 +1380,34 @@
         <v>2395448.423304001</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>2841165.143915472</v>
+        <v>2867074.222746355</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2796668.708826229</v>
+        <v>3079956.473724868</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>2215023.4875</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>2742937.201645587</v>
+        <v>2759813.675793035</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>2713223.76554902</v>
+        <v>2887728.564922813</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2841165.14</v>
+        <v>2887728.56</v>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 83 months, 84.3% developed. Incurred CL 2.84M, Paid CL 2.80M (1.6% variance), Incurred BF 2.74M (3.7% lower). Framework Â§2 (early stage, 24-36 mo range): Incurred CL primary. Â§4 Convergence: Incurred CL and Paid CL within 2%. Selected Incurred CL. IBNR 446K is 15.7% of ultimate, reasonable for 83-month development.</t>
+          <t>Paid Loss, Paid CL method. Age 83 months (early maturity). 77.78% developed. Incurred CL (2,867,074) vs Paid CL (3,079,956) differ by 7.0% (recent acceleration evident). Paid CL selected per early maturity principle; large IBNR (684,508) reflects emerging tail.</t>
         </is>
       </c>
       <c r="L19" s="10" t="n">
-        <v>2841165.14</v>
+        <v>3079956.47</v>
       </c>
       <c r="M19" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Early maturity at 83 months (84.3% developed, CDF 1.1861). Incurred CL 2.841M, Paid CL 2.797M (1.6% variance), Incurred BF 2.743M (3.7% lower). Incurred CL and Paid CL converge within 2%. Incurred CL selected per early-stage baseline. IBNR 446K is 15.7% of ultimate, reasonable for 83-month development.</t>
+          <t>Paid CL. Mid-mature (age 83, 77.8% developed). Paid CDF 1.2858 vs Incurred 1.1969. Paid shows higher development but more credible than incurred anomalies. Paid CL 3.08M with 684k IBNR selected.</t>
         </is>
       </c>
       <c r="N19" s="11" t="n"/>
@@ -1427,34 +1427,34 @@
         <v>2395189.834488001</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>3198349.686727937</v>
+        <v>3382481.570505805</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>2972537.917173816</v>
+        <v>3444251.472898261</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>2259323.9575</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>3022641.652894619</v>
+        <v>3122618.60739452</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>2834012.278936059</v>
+        <v>3083342.285377441</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3198349.69</v>
+        <v>3083342.29</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 71 months, 81.3% developed. Incurred CL 3.20M, Paid CL 2.97M (7.3% variance), Incurred BF 3.02M (5.6% variance). Framework Â§2 (green stage, 12-24 mo): Incurred CL and BF are co-primary. Â§4 Convergence: Incurred BF and Paid CL cluster near 3.0M (within 2%); Incurred CL slightly higher. Selected Incurred CL as best estimate of developed case reserves, with IBNR 598K (18.7% of ultimate) reflecting substantial remaining development.</t>
+          <t>Paid Loss, Paid BF method. Age 71 months (green maturity). 69.54% developed. Incurred CL (3,382,482) fitness FAIL (unstable link ratios, CDF 1.301 extremely high for green). Paid CL (3,444,251) fitness PARTIAL (high CDF but paid data more stable). Paid BF (3,083,342) selected as most credible for sparse, green data. IBNR 688,152. Dampen movement vs prior (unknown); convergence check: Paid BF vs Paid CL 10.5% spread, not tight.</t>
         </is>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3198349.69</v>
+        <v>3444251.47</v>
       </c>
       <c r="M20" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Green stage at 71 months (81.3% developed, CDF 1.2302). Incurred CL 3.198M, Paid CL 2.973M (7.3% variance), Incurred BF 3.023M (5.6% variance). Paid CL and Incurred BF cluster near 3.0M (within 2%); Incurred CL slightly higher. Incurred CL reflects early case reserve establishment best. IBNR 598K (18.7% of ultimate) reflects substantial remaining development.</t>
+          <t>Paid CL. Immature (age 71, 69.5% developed). Paid CDF 1.4380 vs Incurred 1.3010. Paid development credible based on paid diagonal. Paid CL 3.44M with 1.05M IBNR; incurred IE negative signals paid preference.</t>
         </is>
       </c>
       <c r="N20" s="11" t="n"/>
@@ -1474,34 +1474,34 @@
         <v>976050.8625559999</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>1272753.120311486</v>
+        <v>1404355.764275592</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1341782.33085796</v>
+        <v>1577447.934655859</v>
       </c>
       <c r="G21" s="8" t="n">
         <v>1843608.3492</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1404552.341700722</v>
+        <v>1537429.422995462</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>1478565.743710778</v>
+        <v>1678920.756990659</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1272753.12</v>
+        <v>1678920.76</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 59 months, 76.9% developed. Incurred CL 1.27M, Paid CL 1.34M (5.4% variance), Incurred BF 1.40M (10% variance). Framework Â§2 (green stage, 12-24 mo): Incurred BF and Paid BF primary, but Incurred CL is developing with limited data. Â§4 Convergence: Incurred CL is lowest, Paid/Incurred BF clustered. Framework Â§7 Reasonability: Incurred CL shows strong reserve adequacy with IBNR 294K (23.1% of ultimate). Selected Incurred CL as more conservative estimate given maturity.</t>
+          <t>Paid Loss, Paid BF method. Age 59 months (green maturity). 61.88% developed. Incurred CL (1,404,356) fitness FAIL (CDF 1.4346, extremely high). Paid CL (1,577,448) fitness PARTIAL (high CDF 1.6162). Paid BF (1,678,921) selected per green maturity; BF appropriate for sparse recent development. IBNR 702,870. Spread between Paid BF and Paid CL ~6.2%, supports BF for less volatile estimate.</t>
         </is>
       </c>
       <c r="L21" s="10" t="n">
-        <v>1272753.12</v>
+        <v>1577447.93</v>
       </c>
       <c r="M21" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Green stage at 59 months (76.9% developed, CDF 1.3002). Incurred CL 1.273M is lowest estimate, Paid CL 1.342M (5.4% higher), Incurred BF 1.405M (10.4% higher). Incurred CL more conservative at this immature stage with high tail exposure. IBNR 294K (23.1% of ultimate) reflects reasonable development expectation.</t>
+          <t>Paid CL. Immature (age 59, 61.9% developed). Paid CDF 1.6162 vs Incurred 1.4346. Paid shows higher tail, more appropriate at this maturity. Paid CL 1.58M with 601k IBNR selected; incurred IE positive but immature.</t>
         </is>
       </c>
       <c r="N21" s="11" t="n"/>
@@ -1521,34 +1521,34 @@
         <v>974979.4133360002</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>1382219.838183875</v>
+        <v>1533121.054215918</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1438688.114141852</v>
+        <v>1738015.088099067</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>1410360.3873</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1389771.107480668</v>
+        <v>1491338.658611269</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>1429557.703400638</v>
+        <v>1594165.80426635</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1382219.84</v>
+        <v>1594165.8</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 47 months, 73.2% developed. Incurred CL 1.38M, Paid CL 1.44M (4.3% variance), Incurred BF 1.39M (0.8% variance). Framework Â§2 (green stage): Incurred BF primary with framework Â§4 Convergence: Incurred CL and BF within 1%, extremely tight. Selected Incurred CL reflecting case reserve development credibility. IBNR 371K is 26.8% of ultimate, appropriate for 47-month development stage.</t>
+          <t>Paid Loss, Paid BF method. Age 47 months (green maturity). 56.10% developed. Incurred CL (1,533,121) fitness FAIL (unstable at green). Paid CL (1,738,016) fitness PARTIAL (high CDF 1.783). Paid BF (1,594,166) selected per green maturity and sparse development. IBNR 619,186. Convergence: Paid BF vs Incurred CL 4.0% spread; Paid BF balances conservatism.</t>
         </is>
       </c>
       <c r="L22" s="10" t="n">
-        <v>1382219.84</v>
+        <v>1738015.09</v>
       </c>
       <c r="M22" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Green stage at 47 months (73.2% developed, CDF 1.3668). Incurred CL 1.382M, Paid CL 1.439M (4.3% variance), Incurred BF 1.390M (0.8% variance). Incurred CL and BF converge extremely tightly within 1%. Selected Incurred CL reflecting case reserve credibility. IBNR 371K is 26.8% of ultimate.</t>
+          <t>Paid CL. Immature (age 47, 56.1% developed). Paid CDF 1.7826 vs Incurred 1.5160. Paid development more credible given tail exposure. Paid CL 1.74M with 763k IBNR selected; BF 1.59M alternative too conservative at this stage.</t>
         </is>
       </c>
       <c r="N22" s="11" t="n"/>
@@ -1568,34 +1568,34 @@
         <v>791103.7101360001</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>1301300.197111128</v>
+        <v>1452523.835700334</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>1384955.340447214</v>
+        <v>1644757.189957023</v>
       </c>
       <c r="G23" s="8" t="n">
         <v>959045.0632000001</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1176663.880908888</v>
+        <v>1240150.456872813</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>1202330.309066862</v>
+        <v>1288862.382665193</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1301300.2</v>
+        <v>1288862.38</v>
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 35 months, 63.6% developed. Incurred CL 1.30M, Paid CL 1.38M (6.0% variance), Incurred BF 1.18M (9.5% lower). Framework Â§2 (very green, 0-12 mo equivalent): BF and Paid BF are typically primary, but CL methods have limited credibility. Â§4 Convergence: Paid CL and Incurred CL within 6%. Framework Â§3 Diagnostic override: CL methods increasingly uncertain; however, Incurred CL (1.30M) vs. Paid CL (1.38M) represent case-based development. Selected Incurred CL as more conservative, IBNR 474K is 36.4% of ultimate reflecting early stage.</t>
+          <t>Paid Loss, Paid BF method. Age 35 months (very green maturity). 48.10% developed. Incurred CL (1,452,524) fitness FAIL (CDF 1.755, unstable at very green). Paid CL (1,644,757) fitness PARTIAL (CDF 2.079). Paid BF (1,288,862) selected per very green maturity; lower IBNR (497,759) indicates more conservative a priori loss ratio expectation. Incurred methods not credible here.</t>
         </is>
       </c>
       <c r="L23" s="10" t="n">
-        <v>1301300.2</v>
+        <v>1644757.19</v>
       </c>
       <c r="M23" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Very green at 35 months (63.6% developed, CDF 1.5727). Incurred CL 1.301M, Paid CL 1.385M (6.0% higher), Incurred BF 1.177M (9.5% lower). Incurred CL is middle estimate. At this immature stage with high tail extrapolation, Incurred CL reflects observable case development best. IBNR 474K is 36.4% of ultimate.</t>
+          <t>Paid CL. Immature (age 35, 48.1% developed). Paid CDF 2.0791 vs Incurred 1.7555. Paid tail substantial but justified at low maturity. Paid CL 1.64M with 854k IBNR; IE 959k less credible given method volatility at immature stage.</t>
         </is>
       </c>
       <c r="N23" s="11" t="n"/>
@@ -1615,34 +1615,34 @@
         <v>1199242.068356001</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>3095494.878246275</v>
+        <v>3514374.08126558</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2986282.892939571</v>
+        <v>3546475.554816075</v>
       </c>
       <c r="G24" s="8" t="n">
         <v>978225.9646000001</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2108001.072318659</v>
+        <v>2170216.197278664</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>1784628.582989602</v>
+        <v>1846680.548036402</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>3095494.88</v>
+        <v>1846680.55</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 23 months, 53.4% developed. Incurred CL 3.10M, Paid CL 2.99M (3.5% variance), Incurred BF 2.11M (31.8% lower). Framework Â§2 (very green, 0-12 mo): Paid BF and Incurred BF are theoretically primary, but data is sparse. Incurred CL 3.10M shows substantial case reserve activity. Paid CL 2.99M is close alternative. Â§4 Convergence: Incurred/Paid CL within 4%. Framework Â§7 Reasonability: Incurred CL is much higher than BF methods, suggesting strong case development early in accident year. Selected Incurred CL (3.10M) reflecting observable case activity, IBNR 1.44M is 46.6% of ultimate.</t>
+          <t>Paid Loss, Paid BF method. Age 23 months (very green maturity). 33.82% developed. Incurred CL (3,514,374) fitness FAIL (CDF 2.128, extremely volatile). Paid CL (3,546,476) fitness FAIL (CDF 2.957, severe instability). Paid BF (1,846,681) selected as only credible method; IBNR 647,438 reasonable for immaturity. Incurred measures unreliable; Paid BF best reflects expected ultimate.</t>
         </is>
       </c>
       <c r="L24" s="10" t="n">
-        <v>3095494.88</v>
+        <v>3546475.55</v>
       </c>
       <c r="M24" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Very green at 23 months (53.4% developed, CDF 1.8741). Incurred CL 3.095M, Paid CL 2.986M (3.5% variance), Incurred BF 2.108M (31.8% lower). Incurred CL and Paid CL converge within 4%. BF methods significantly lower due to sparse paid development. Incurred CL captures early case activity best at extreme immaturity. IBNR 1.444M is 46.6% of ultimate.</t>
+          <t>Paid CL. Highly immature (age 23, 33.8% developed). Paid CDF 2.9573 very high, reflecting extreme immaturity. Paid CL 3.55M with 2.35M IBNR; incurred IE 978k shows measure contradiction. Paid CL captures tail risk appropriately.</t>
         </is>
       </c>
       <c r="N24" s="11" t="n"/>
@@ -1662,34 +1662,34 @@
         <v>355247.7609319999</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2525664.374673065</v>
+        <v>3116678.029293693</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>2257985.723530615</v>
+        <v>2755832.825859559</v>
       </c>
       <c r="G25" s="8" t="n">
         <v>997790.4837999999</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1536280.449408108</v>
+        <v>1602966.506269977</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>1196056.368560097</v>
+        <v>1224415.480708334</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2525664.37</v>
+        <v>1224415.48</v>
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>Incurred CL selected. At 11 months, 35.2% developed. Incurred CL 2.53M, Paid CL 2.26M (10.6% variance), Incurred BF 1.54M (38.9% lower). Framework Â§2 (very green, 0-12 mo): BF methods theoretically primary with sparse data. However, Incurred CL 2.53M reflects early case reserve establishment. CDF 2.837 is very high, indicating substantial tail extrapolation required. Incurred CL selected as least model-dependent, with IBNR 1.64M representing 64.8% of ultimate development expectation. High uncertainty warranted at this extreme green maturity.</t>
+          <t>Paid Loss, Paid BF method. Age 11 months (very green maturity). 12.89% developed. Incurred CL (3,116,678) and Paid CL (2,755,833) fitness FAIL (CDF 3.501 and 7.757 respectively; extreme volatility at ultra-immature state). Paid BF (1,224,415) selected as only sensible estimate; IBNR 869,168 large but proportional to immaturity. Credible a priori loss ratio assumption mandatory here.</t>
         </is>
       </c>
       <c r="L25" s="10" t="n">
-        <v>2525664.37</v>
+        <v>2755832.83</v>
       </c>
       <c r="M25" s="10" t="inlineStr">
         <is>
-          <t>Incurred CL selected. Extreme immaturity at 11 months (35.2% developed, CDF 2.8373). Incurred CL 2.526M reflects early case reserve establishment. Paid CL 2.258M (10.6% lower) and Incurred BF 1.536M (38.9% lower) show less credibility at this very green stage. CDF 2.837 requires significant tail extrapolation. Incurred CL is least model-dependent. IBNR 1.636M represents 64.8% of ultimate.</t>
+          <t>Paid CL. Extremely immature (age 11, 12.9% developed). Paid CDF 7.7575 extreme, indicating highly preliminary development. Paid CL 2.76M with 2.40M IBNR largest component; volatility expected at opening stage.</t>
         </is>
       </c>
       <c r="N25" s="11" t="n"/>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 287 months maturity, CDF 1.0 and 100% developed indicate full closure. Reported Count ultimate equals actual (700.71). Closed CL would show similar result. Reported Count is simplest, most direct at complete maturity. IBNR 0 is appropriate. No development expected.</t>
+          <t>Reported Count, Reported CL method. Age 287 months (tail maturity). 100% developed per CL (CDF 1.0, IBNR 0). At tail completion, CL is only appropriate method. IE and BF unnecessary at full development. Closure complete.</t>
         </is>
       </c>
       <c r="I2" s="10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Tail-mature at 287 months with CDF 1.0 and 100% developed. Reported Count actual equals ultimate (700.71). Direct, fully credible measure at complete maturity. Zero IBNR appropriate; no development expected. Simplest and most reliable selection at extreme tail stage.</t>
+          <t>Reported CL. Fully mature (age 287, CDF 1.0). No IBNR needed; actual count 700.71 is ultimate. All three methods converge on fully developed counts.</t>
         </is>
       </c>
       <c r="K2" s="11" t="n"/>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 275 months, CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework Â§2 maturity-based: tail-stage periods use direct actuals when fully developed. Zero IBNR appropriate at this maturity.</t>
+          <t>Reported Count, Reported CL method. Age 275 months (tail maturity). 100% developed. CL primary. IE shows 31.28 IBNR indicating a priori count inflated. BF redundant at full maturity. CL reflects actual closure.</t>
         </is>
       </c>
       <c r="I3" s="10" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="J3" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Late maturity at 275 months with CDF 1.0 and 100% developed. Reported Count actual = ultimate (651.88). Framework preference: at complete development, reported actual is most direct and credible. Zero IBNR reflects full closure and reporting.</t>
+          <t>Reported CL. Fully mature (age 275, CDF 1.0). No IBNR needed; actual count 651.88 is ultimate. CL, IE, and BF all consistent with zero additional development.</t>
         </is>
       </c>
       <c r="K3" s="11" t="n"/>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 263 months, CDF 1.0 and 100% developed. Reported Count 551.59 is fully developed. Framework Â§2: at tail maturity with complete development, reported actual is ultimate. No further development indicated.</t>
+          <t>Reported Count, Reported CL method. Age 263 months (tail maturity). 100% developed. CL primary (IBNR 0). IE and BF show divergence (648 and 552 respectively) but CL reflects actual reported at full maturity. No further development expected.</t>
         </is>
       </c>
       <c r="I4" s="10" t="n">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="J4" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Late maturity at 263 months with CDF 1.0 and 100% developed. Reported Count 551.59 fully developed. Actual equals ultimate; no further development expected. Direct measure most appropriate at complete maturity.</t>
+          <t>Reported CL. Fully mature (age 263, CDF 1.0). No IBNR needed. CL ultimate 551.59 equals actual; IE and BF show modest variance but CL most direct.</t>
         </is>
       </c>
       <c r="K4" s="11" t="n"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 251 months, CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. Framework Â§2 late maturity: direct reported count is most credible. IBNR 0 reflects complete development.</t>
+          <t>Reported Count, Reported CL method. Age 251 months (tail maturity). 100% developed. CL (642.65) primary. IE (627.84) and BF (642.65) show IE lower; CL reflects actual reported counts at closure. IBNR 0.</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Late maturity at 251 months with CDF 1.0 and 100% developed. Reported Count 642.65 represents final count. At late maturity with complete development, reported actual is most credible ultimate. Zero IBNR.</t>
+          <t>Reported CL. Fully mature (age 251, CDF 1.0). No IBNR needed; actual 642.65 is ultimate. All methods show counts are final.</t>
         </is>
       </c>
       <c r="K5" s="11" t="n"/>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 239 months, CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate. Framework Â§2: tail/late stage fully developed periods use actual reported count. No uncertainty in development.</t>
+          <t>Reported Count, Reported CL method. Age 239 months (tail maturity). 100% developed. CL (641.33) selected. IE (623.61) lower, BF (641.33) identical. CL reflects actual reported and closed counts. No additional development expected.</t>
         </is>
       </c>
       <c r="I6" s="10" t="n">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Late maturity at 239 months with CDF 1.0 and 100% developed. Reported Count 641.33 is ultimate at complete development. Fully closed and reported claims; no uncertainty in final count.</t>
+          <t>Reported CL. Fully mature (age 239, CDF 1.0). No IBNR needed. CL 641.33 equals actual; IE shows negative IBNR (-17.7) signals data anomaly, CL preferred.</t>
         </is>
       </c>
       <c r="K6" s="11" t="n"/>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 227 months, CDF 1.0 and 100% developed. Reported Count 497.49 represents fully closed and reported claims. Framework Â§2 late maturity: actual reported = ultimate. Zero IBNR.</t>
+          <t>Reported Count, Reported CL method. Age 227 months (tail maturity). 100% developed. CL (497.49) primary. IE (606.74) inflated by 109, suggesting a priori count excessive. CL most credible for mature reporting.</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="J7" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Late maturity at 227 months with CDF 1.0 and 100% developed. Reported Count 497.49 represents fully developed ultimate. Complete reporting and closure confirmed. Zero IBNR appropriate.</t>
+          <t>Reported CL. Fully mature (age 227, CDF 1.0). No IBNR needed. CL 497.49 equals actual; IE shows inflated ultimate (606.7), likely includes other data adjustments. CL selected.</t>
         </is>
       </c>
       <c r="K7" s="11" t="n"/>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 215 months, CDF 1.0 and 100% developed. Reported Count 476.38 is complete. Framework Â§2: late-stage fully developed period uses actual count. All claims reported and closed.</t>
+          <t>Reported Count, Reported CL method. Age 215 months (tail maturity). 100% developed. CL (476.38) reflects actual reported. IE (550.47) inflated by 74, unreliable a priori count. BF identical to CL. CL selected.</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J8" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Late maturity at 215 months with CDF 1.0 and 100% developed. Reported Count 476.38 is complete at full development. All claims reported and closed; actual equals ultimate.</t>
+          <t>Reported CL. Fully mature (age 215, CDF 1.0). No IBNR needed. CL 476.38 equals actual; IE 550.5 significantly higher, reflects method divergence. CL most direct for mature count.</t>
         </is>
       </c>
       <c r="K8" s="11" t="n"/>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 203 months, CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Framework Â§2 mid-to-late stage: full development achieved. No expected reopens or new reports.</t>
+          <t>Reported Count, Reported CL method. Age 203 months (late maturity). 100% developed. CL (328.58) primary. IE (444.10) inflated by 115, poor a priori. BF identical to CL. Actual reported at closure is CL.</t>
         </is>
       </c>
       <c r="I9" s="10" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J9" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Mid-to-late maturity at 203 months with CDF 1.0 and 100% developed. Reported Count 328.58 actual = ultimate. Full development achieved; no additional emergence expected. Direct measure most reliable.</t>
+          <t>Reported CL. Fully mature (age 203, CDF 1.0). No IBNR needed. CL 328.58 equals actual; IE 444.1 and BF 328.6 show CL and BF agreement, CL selected for consistency.</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 191 months, CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Framework Â§2: complete maturity means actual reported = ultimate. IBNR 0.</t>
+          <t>Reported Count, Reported CL method. Age 191 months (late maturity). 100% developed. CL (321.98) primary. IE (384.40) inflated by 62, unreliable. BF identical. CL reflects actual maturity.</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="J10" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Mid-maturity at 191 months with CDF 1.0 and 100% developed. Reported Count 321.98 represents final count. Complete development indicated by CDF = 1.0. Zero IBNR appropriate.</t>
+          <t>Reported CL. Fully mature (age 191, CDF 1.0). No IBNR needed. CL 321.98 equals actual; IE 384.4 shows method divergence. CL most credible for mature count.</t>
         </is>
       </c>
       <c r="K10" s="11" t="n"/>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 179 months, CDF 1.0 and 100% developed. Reported Count 271.84 is fully developed ultimate. Framework Â§2 mid-stage: at full development, reported actual represents ultimate. No additional development expected.</t>
+          <t>Reported Count, Reported CL method. Age 179 months (late maturity). 100% developed. CL (271.84) primary. IE (314.20) inflated by 42, a priori count overestimate. BF identical. CL most credible.</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="J11" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Mid-maturity at 179 months with CDF 1.0 and 100% developed. Reported Count 271.84 fully developed ultimate. Complete reporting and closure by this stage. No additional development expected.</t>
+          <t>Reported CL. Fully mature (age 179, CDF 1.0). No IBNR needed. CL 271.84 equals actual; IE 314.2 higher. CL is final count at full maturity.</t>
         </is>
       </c>
       <c r="K11" s="11" t="n"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 167 months, CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. Framework Â§2: all claims reported by this maturity. Final count established.</t>
+          <t>Reported Count, Reported CL method. Age 167 months (late maturity). 100% developed. CL (345.74) primary. IE (319.33) lower by 26, a priori understated. BF identical. CL reflects actual reported count.</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="J12" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Mid-maturity at 167 months with CDF 1.0 and 100% developed. Reported Count 345.74 actual = ultimate. All claims reported by this maturity; final count established.</t>
+          <t>Reported CL. Fully mature (age 167, CDF 1.0). No IBNR needed. CL 345.74 equals actual; IE 319.3 lower, CL actual is most credible.</t>
         </is>
       </c>
       <c r="K12" s="11" t="n"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 155 months, CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. Framework Â§2 early-mid stage: even with moderate maturity, CDF 1.0 indicates all claims reported. Ultimate equals reported actual.</t>
+          <t>Reported Count, Reported CL method. Age 155 months (late maturity). 100% developed. CL (261.28) primary. IE (298.97) inflated by 37, a priori overstated. BF identical. CL actual reported.</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J13" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Mid-maturity at 155 months with CDF 1.0 and 100% developed. Reported Count 261.28 represents complete development. CDF 1.0 indicates all claims reported. Ultimate equals actual reported count.</t>
+          <t>Reported CL. Fully mature (age 155, CDF 1.0). No IBNR needed. CL 261.28 equals actual; IE 298.97 and BF 261.28 show CL and BF close, CL selected.</t>
         </is>
       </c>
       <c r="K13" s="11" t="n"/>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 143 months, CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. Framework Â§2 early stage: CDF 1.0 indicates complete reporting. No expected IBNR development.</t>
+          <t>Reported Count, Reported CL method. Age 143 months (mid maturity). 100% developed. CL (291.63) primary. IE (305.75) inflated by 14, minor a priori overstate. BF identical. CL actual reported at closure.</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="J14" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Early-mid maturity at 143 months with CDF 1.0 and 100% developed. Reported Count 291.63 is ultimate. CDF 1.0 confirms complete reporting. Zero IBNR; no expected additional emergence.</t>
+          <t>Reported CL. Fully mature (age 143, CDF 1.0). No IBNR needed. CL 291.63 equals actual; IE 305.7 shows modest method divergence. CL most credible.</t>
         </is>
       </c>
       <c r="K14" s="11" t="n"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 131 months, CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Framework Â§2 early stage: full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
+          <t>Reported Count, Reported CL method. Age 131 months (mid maturity). 100% developed. CL (455.26) primary. IE (341.33) significantly lower by 114, a priori count inadequate. BF identical. CL reflects actual reported.</t>
         </is>
       </c>
       <c r="I15" s="10" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="J15" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Early-mid maturity at 131 months with CDF 1.0 and 100% developed. Reported Count 455.26 is ultimate. Full development achieved (100%). Reported actual = ultimate with zero IBNR.</t>
+          <t>Reported CL. Fully mature (age 131, CDF 1.0). No IBNR needed. CL 455.26 equals actual; IE 341.3 significantly lower, anomalous. CL selected as actual reported count is final.</t>
         </is>
       </c>
       <c r="K15" s="11" t="n"/>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 119 months, CDF 1.0 and 100% developed. Reported Count 333.86 is fully developed ultimate. Framework Â§2 early stage: complete reporting maturity. No additional counts expected to emerge.</t>
+          <t>Reported Count, Reported CL method. Age 119 months (mid maturity). 100% developed. CL (333.86) primary. IE (367.36) inflated by 33, a priori overstated. BF identical. CL actual reported at full maturity.</t>
         </is>
       </c>
       <c r="I16" s="10" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="J16" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Early maturity at 119 months with CDF 1.0 and 100% developed. Reported Count 333.86 fully developed ultimate. Complete reporting maturity reached. No additional counts expected to emerge.</t>
+          <t>Reported CL. Fully mature (age 119, CDF 1.0). No IBNR needed. CL 333.86 equals actual; IE 367.4 and BF 333.86 show CL and BF agreement. CL selected.</t>
         </is>
       </c>
       <c r="K16" s="11" t="n"/>
@@ -2362,28 +2362,28 @@
         <v>390.6016</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>390.6016</v>
+        <v>389.70321632</v>
       </c>
       <c r="E17" s="8" t="n">
         <v>401.5315549436</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>390.6016</v>
+        <v>389.6759484250073</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>390.6</v>
+        <v>389.7</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 107 months, CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. Framework Â§2 early stage: CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
+          <t>Reported Count, Reported CL method. Age 107 months (mid maturity). 100.23% developed (CDF 0.9977, minor negative IBNR -0.898 indicates full closure). CL (389.70) primary. IE (401.53) inflated by 10. At practical maturity, CL reflects actual reported/closed.</t>
         </is>
       </c>
       <c r="I17" s="10" t="n">
-        <v>390.6</v>
+        <v>389.7</v>
       </c>
       <c r="J17" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Early maturity at 107 months with CDF 1.0 and 100% developed. Reported Count 390.60 represents ultimate. CDF 1.0 indicates all counts reported. Actual equals ultimate.</t>
+          <t>Reported CL. Near-mature (age 107, CDF 0.9977, 100.2% pct developed). CL 389.70 with -0.90 IBNR (negligible negative development). Data stable, minimal tail expected. CL most credible.</t>
         </is>
       </c>
       <c r="K17" s="11" t="n"/>
@@ -2400,28 +2400,28 @@
         <v>310.1060000000001</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>310.1060000000001</v>
+        <v>309.3927562000001</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>351.797848029</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>310.1060000000001</v>
+        <v>309.2949996487254</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>310.11</v>
+        <v>309.39</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 95 months, CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Framework Â§2 early stage: full development achieved. IBNR 0 appropriate.</t>
+          <t>Reported Count, Reported CL method. Age 95 months (early maturity). 100.23% developed (CDF 0.9977, negative IBNR -0.713 indicates closure complete). CL (309.39) primary. IE (351.80) inflated by 41, a priori overstated. CL reflects actual reported/closed.</t>
         </is>
       </c>
       <c r="I18" s="10" t="n">
-        <v>310.11</v>
+        <v>309.39</v>
       </c>
       <c r="J18" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Early maturity at 95 months with CDF 1.0 and 100% developed. Reported Count 310.11 is ultimate. Full development achieved. Zero IBNR appropriate.</t>
+          <t>Reported CL. Near-mature (age 95, CDF 0.9977, 100.2% pct developed). CL 309.39 with -0.71 IBNR shows minimal tail. IE 351.8 shows method divergence. CL preferred given near-mature status.</t>
         </is>
       </c>
       <c r="K18" s="11" t="n"/>
@@ -2438,28 +2438,28 @@
         <v>325.9412</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>325.9412</v>
+        <v>324.963901165332</v>
       </c>
       <c r="E19" s="8" t="n">
         <v>349.5307063275</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>325.9412</v>
+        <v>324.890018774179</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>325.94</v>
+        <v>324.96</v>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 83 months, CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Framework Â§2 early stage (24-36 mo equivalent): CDF 1.0 indicates complete reporting. Reported actual = ultimate with zero IBNR.</t>
+          <t>Reported Count, Reported CL method. Age 83 months (early maturity). 100.30% developed (CDF 0.997, negative IBNR -0.977). CL (324.96) primary. IE (349.53) inflated by 23. CL reflects actual reported/closed counts.</t>
         </is>
       </c>
       <c r="I19" s="10" t="n">
-        <v>325.94</v>
+        <v>324.96</v>
       </c>
       <c r="J19" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Early maturity at 83 months with CDF 1.0 and 100% developed. Reported Count 325.94 equals ultimate. Complete reporting confirmed by CDF 1.0. Zero IBNR.</t>
+          <t>Reported CL. Near-mature (age 83, CDF 0.9970, 100.3% pct developed). CL 324.96 with -0.98 IBNR (slight negative development). Data essentially mature. CL selected.</t>
         </is>
       </c>
       <c r="K19" s="11" t="n"/>
@@ -2476,28 +2476,28 @@
         <v>357.6116</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>357.68312232</v>
+        <v>356.539340954676</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>337.5429992505</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>357.67909510083</v>
+        <v>356.5964706929142</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>357.68</v>
+        <v>356.54</v>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 71 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 vs. actual 357.61 shows minimal development (0.07 counts, 0.02% IBNR). Framework Â§2 green stage: Reported CL is primary. Â§4 Convergence: all methods cluster within 1% (Reported CL/IE/BF all near 357.7). Selected Reported CL reflecting actual report-based development. Minimal development expected from this point.</t>
+          <t>Reported Count, Reported CL method. Age 71 months (green maturity). 100.30% developed (CDF 0.997, negative IBNR -1.072 indicates reporting complete). CL (356.54) primary. IE (337.54) lower by 20, a priori understated. CL reflects actual reported at near-closure.</t>
         </is>
       </c>
       <c r="I20" s="10" t="n">
-        <v>357.68</v>
+        <v>356.54</v>
       </c>
       <c r="J20" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Green stage at 71 months with CDF 1.0002 and 99.98% developed. Reported CL ultimate 357.68 shows minimal development (0.07 counts, 0.02% IBNR). All methods converge within 1%. Selected Reported CL reflecting actual report-based development. Minimal emergence expected henceforth.</t>
+          <t>Reported CL. Near-mature (age 71, CDF 0.9970, 100.3% pct developed). CL 356.54 with -1.07 IBNR shows slight negative development, typical near-closure. CL credible and stable.</t>
         </is>
       </c>
       <c r="K20" s="11" t="n"/>
@@ -2514,28 +2514,28 @@
         <v>370.8076</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>370.8817615200001</v>
+        <v>369.4000175808758</v>
       </c>
       <c r="E21" s="8" t="n">
         <v>358.1209218321</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>370.879209862394</v>
+        <v>369.442996076068</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>370.88</v>
+        <v>369.4</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 59 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Framework Â§2 green stage (12-24 mo): Reported CL primary with minimal reported to closed settlement gap. Â§4 Convergence: methods within 1%. Selected Reported CL as direct indication of claim emergence. Framework Â§7 Reasonability: very low IBNR consistent with mature reporting patterns.</t>
+          <t>Reported Count, Reported CL method. Age 59 months (green maturity). 100.38% developed (CDF 0.9962, negative IBNR -1.407 indicates reporting complete). CL (369.40) primary. IE (358.12) lower by 12. CL actual reported count at practical maturity.</t>
         </is>
       </c>
       <c r="I21" s="10" t="n">
-        <v>370.88</v>
+        <v>369.4</v>
       </c>
       <c r="J21" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Green stage at 59 months with CDF 1.0002 and 99.98% developed. Reported CL ultimate 370.88 shows 0.07 counts development (0.02% IBNR). Methods converge within 1%. Selected Reported CL as direct indication of claim emergence. Very high development completion confirmed.</t>
+          <t>Reported CL. Mid-mature (age 59, CDF 0.9962, 100.4% pct developed). CL 369.40 with -1.41 IBNR shows counts nearing closure. IE 358.1 lower, CL captures reported count development pattern.</t>
         </is>
       </c>
       <c r="K21" s="11" t="n"/>
@@ -2552,28 +2552,28 @@
         <v>329.9</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>329.96598</v>
+        <v>328.6477024740888</v>
       </c>
       <c r="E22" s="8" t="n">
         <v>360.1120188906</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>329.9720080021777</v>
+        <v>328.527809088843</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>329.97</v>
+        <v>328.65</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 47 months, CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). Framework Â§2 green stage: Reported CL primary. Â§4 Convergence: all methods (reported CL, IE, BF) within 1% cluster. Selected Reported CL. Minimal remaining development expected; nearly all claims already reported.</t>
+          <t>Reported Count, Reported CL method. Age 47 months (green maturity). 100.38% developed (CDF 0.9962, negative IBNR -1.252). CL (328.65) primary. IE (360.11) inflated by 30. CL reflects actual reported at maturity.</t>
         </is>
       </c>
       <c r="I22" s="10" t="n">
-        <v>329.97</v>
+        <v>328.65</v>
       </c>
       <c r="J22" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Green stage at 47 months with CDF 1.0002 and 99.98% developed. Reported CL ultimate 329.97 shows 0.066 counts development (0.02% IBNR). All methods cluster tightly within 1%. Nearly all claims already reported; minimal development expected.</t>
+          <t>Reported CL. Mid-mature (age 47, CDF 0.9962, 100.4% pct developed). CL 328.65 with -1.25 IBNR reflects slight negative development as claims close. CL most credible method.</t>
         </is>
       </c>
       <c r="K22" s="11" t="n"/>
@@ -2590,28 +2590,28 @@
         <v>298.2296</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>298.43839054296</v>
+        <v>297.3352010550055</v>
       </c>
       <c r="E23" s="8" t="n">
         <v>339.9814749044</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>298.467454508639</v>
+        <v>297.2069189605764</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>298.44</v>
+        <v>297.34</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 35 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green (0-12 mo): BF methods theoretically primary, but CDF very close to 1.0. Â§4 Convergence: Reported CL 298.44 vs. IE 339.98 (13.9% variance) shows some divergence; BF 298.47 clusters with CL (0.01% variance). Selected Reported CL per Â§2 green stage with CL/BF tight convergence. Minimal IBNR 0.21 reflects high development completion.</t>
+          <t>Reported Count, Reported CL method. Age 35 months (very green maturity). 100.30% developed (CDF 0.997, negative IBNR -0.894). CL (297.34) primary. IE (339.98) inflated by 41. CL reflects actual reported; near-complete development.</t>
         </is>
       </c>
       <c r="I23" s="10" t="n">
-        <v>298.44</v>
+        <v>297.34</v>
       </c>
       <c r="J23" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Very green at 35 months with CDF 1.0007 and 99.93% developed. Reported CL ultimate 298.44 shows 0.21 counts development (0.07% IBNR). Reported CL and BF cluster tightly (0.01% variance). Selected Reported CL per green-stage preference with strong CL/BF convergence. Minimal IBNR reflects high development completion.</t>
+          <t>Reported CL. Immature (age 35, CDF 0.9970, 100.3% pct developed). CL 297.34 with -0.89 IBNR; data shows near-closure pattern despite lower age. CL selected; IE 340.0 shows method divergence.</t>
         </is>
       </c>
       <c r="K23" s="11" t="n"/>
@@ -2628,28 +2628,28 @@
         <v>304.8276</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>305.04100980276</v>
+        <v>303.9134134677269</v>
       </c>
       <c r="E24" s="8" t="n">
         <v>317.4343255127</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>305.0496802928784</v>
+        <v>303.8727418976421</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>305.04</v>
+        <v>303.91</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 23 months, CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Framework Â§2 very green: BF methods theoretically primary with sparse data. However, CDF 1.0007 is very close to 1.0, indicating nearly complete reporting already. Reported CL 305.04 and BF 305.05 converge within 0.01% (framework Â§4). Selected Reported CL as most direct measure of reported counts. IBNR 0.21 is minimal (0.07% of ultimate).</t>
+          <t>Reported Count, Reported CL method. Age 23 months (very green maturity). 100.30% developed (CDF 0.997, negative IBNR -0.914). CL (303.91) primary. IE (317.43) inflated by 12. CL reflects actual reported count; reporting essentially complete.</t>
         </is>
       </c>
       <c r="I24" s="10" t="n">
-        <v>305.04</v>
+        <v>303.91</v>
       </c>
       <c r="J24" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Very green at 23 months with CDF 1.0007 and 99.93% developed. Reported CL ultimate 305.04 shows 0.21 counts development (0.07% IBNR). Reported CL and BF converge within 0.01%. Selected Reported CL as most direct measure of reported counts. Minimal IBNR (0.07% of ultimate) reflects nearly complete reporting already achieved.</t>
+          <t>Reported CL. Immature (age 23, CDF 0.9970, 100.3% pct developed). CL 303.91 with -0.91 IBNR; counts approaching final despite young age. CL credible; IE 317.4 shows divergence. CL selected.</t>
         </is>
       </c>
       <c r="K24" s="11" t="n"/>
@@ -2666,28 +2666,28 @@
         <v>256.0024</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>290.2537837085119</v>
+        <v>285.3523293239924</v>
       </c>
       <c r="E25" s="8" t="n">
         <v>292.3526117534</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>290.5014558104399</v>
+        <v>286.0723437533045</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>290.25</v>
+        <v>286.07</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Reported CL selected. At 11 months, CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Framework Â§2 very green (0-12 mo): BF methods typically primary at extreme immaturity. However, CDF 1.134 is more moderate than loss CDFs (2.84), suggesting count development is following expected trajectory. Reported CL 290.25 vs. Closed CL 290.25 and IE 292.35 are very tightly clustered (within 1%). Framework Â§4 Convergence applies: all methods within 1%. Selected Reported CL reflecting observable reported counts with reasonable IBNR development expectation of 11.8% remaining. Early emergence suggests expected pattern consistent with portfolio development.</t>
+          <t>Reported Count, Reported BF method. Age 11 months (ultra-immature). 89.71% developed (CDF 1.1146). CL (285.35) fitness PARTIAL (CDF 1.1146 unstable at 11 months). Reported BF (286.07) selected for very green maturity with immature development pattern. IBNR 30.07 reasonable. IE shows 36.35 IBNR, inflated. BF appropriate given maturity.</t>
         </is>
       </c>
       <c r="I25" s="10" t="n">
-        <v>290.25</v>
+        <v>285.35</v>
       </c>
       <c r="J25" s="10" t="inlineStr">
         <is>
-          <t>Reported CL selected. Extreme immaturity at 11 months with CDF 1.134 and 88.2% developed. Reported CL ultimate 290.25 shows 34.25 counts development (11.8% IBNR). Reported CL, Closed CL, and IE methods converge tightly within 1%. Selected Reported CL reflecting observable reported counts. Reasonable IBNR development expectation of 11.8% remaining, consistent with early-stage emergence pattern.</t>
+          <t>Reported CL. Highly immature (age 11, CDF 1.1146, 89.7% pct developed). CL 285.35 with 29.3 IBNR; youngest cohort showing modest tail. CDF &gt; 1.0 indicates possible reopenings/adjustments. IE 292.4 and BF 286.1 show convergence; CL selected for consistency.</t>
         </is>
       </c>
       <c r="K25" s="11" t="n"/>
